--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2358,7 +2358,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-210</t>
+          <t>RM-STAB-018</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>RLS-контекст на device-маршрутах онбординга</t>
+          <t>Refresh-токены пользователя: обнаружение повтора и атомарная ротация</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2391,54 +2391,50 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+          <t>in_progress</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; bootstrap-RLS миграции 037: без RLS-контекста роль приложения видит 0 onboarding codes (fail-closed); со своим app.rmp_device_code — только свою строку; с чужим кодом — 0 [behavioral: `tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap`]</t>
+          <t>повтор ротированного refresh позже окна отзывает всю семью (audit auth.refresh.replay_detected); повтор в окне - 401 без отзыва (audit auth.refresh.reuse_within_grace); параллельные refresh одним токеном дают ровно одну новую сессию; операции над семьёй сериализованы (повтор против refresh - без выживших, два повтора - без deadlock); отзыв закоммичен при ответе 401 [behavioral: `tests/behavioral/test_rm_stab_018_refresh_replay.py`]</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py; verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap; verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33408891221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика. 2026-08-31 (стадия S, OD-043: зависимость RM-STAB-002 done): реализовано локально - set_rls_context на /identity/device-codes, bootstrap-контекст кода/fingerprint на /device/onboard, миграция 037 (rehearsal down/up), allowlist элевации снят; targeted 97 passed под ролью приложения; design-gate docs/architecture/rm-tech-210-device-onboarding-rls-bootstrap-design-gate.md (на тот момент - до CI-evidence и owner gate). verification 2026-08-31: CI 33408891221 success (условием done тогда оставался owner gate device_contract). 2026-08-31: приёмка №2 уточнена владельцем — три утверждения bootstrap-RLS (без контекста 0; свой app.rmp_device_code — только свой; чужой — 0); ref → TestRMTech210BootstrapRLS. done 2026-08-31: owner gate device_contract granted - OD-045 (fail-closed контракт принят владельцем).</t>
+          <t>OD-046 (2026-09-28), этап RF-01; находка P0-7 ревью main@8ad0228. REQ: REQ-SEC-001; SC: -; DEC: -. Скрытые дефекты: поиск с фильтром rotated_at IS NULL делал ветку повтора недостижимой; отзыв семьи писал несуществующую колонку last_error (CompileError); ротация без блокировки. Риск регрессии: средний - отзыв семьи начинает срабатывать; гонка вкладок портала (P1-13.b) семью не отзывает (окно 10 с), но проигравшая вкладка по-прежнему получает 401 - до single-flight на фронтенде (RF-08).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-005</t>
+          <t>RM-TECH-210</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>retention-policy.yaml + legal decision register (AG): сроки, 152-ФЗ, deletion/archive, review date</t>
+          <t>RLS-контекст на device-маршрутах онбординга</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-253</t>
+          <t>RM-STAB-002</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -2451,34 +2447,34 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>scope_decision</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>юридическое утверждение retention/152-ФЗ (OD-009) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; bootstrap-RLS миграции 037: без RLS-контекста роль приложения видит 0 onboarding codes (fail-closed); со своим app.rmp_device_code — только свою строку; с чужим кодом — 0 [behavioral: `tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap`]</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py; verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap; verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33408891221</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено POPS → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). 2026-08-31: кандидат docs/product/retention-policy.yaml подготовлен (working defaults REQ-DATA-001, legal register) - не действует до OD-009; задача остаётся blocked.</t>
+          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика. 2026-08-31 (стадия S, OD-043: зависимость RM-STAB-002 done): реализовано локально - set_rls_context на /identity/device-codes, bootstrap-контекст кода/fingerprint на /device/onboard, миграция 037 (rehearsal down/up), allowlist элевации снят; targeted 97 passed под ролью приложения; design-gate docs/architecture/rm-tech-210-device-onboarding-rls-bootstrap-design-gate.md (на тот момент - до CI-evidence и owner gate). verification 2026-08-31: CI 33408891221 success (условием done тогда оставался owner gate device_contract). 2026-08-31: приёмка №2 уточнена владельцем — три утверждения bootstrap-RLS (без контекста 0; свой app.rmp_device_code — только свой; чужой — 0); ref → TestRMTech210BootstrapRLS. done 2026-08-31: owner gate device_contract granted - OD-045 (fail-closed контракт принят владельцем).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-OPS-005</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2493,16 +2489,16 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>SLO objectives и измерение</t>
+          <t>retention-policy.yaml + legal decision register (AG): сроки, 152-ФЗ, deletion/archive, review date</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-253</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
@@ -2511,13 +2507,17 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>каждое число ТЗ имеет formula/window/owner/metric либо `not measurable` [artifact: `docs/product/slo-objectives.yaml`]</t>
+          <t>юридическое утверждение retention/152-ФЗ (OD-009) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288 RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/slo-objectives.yaml - 11 объектов, каждое число §8 с formula/window/owner/status; пороги OD-011/OD-025 open. Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено POPS → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). 2026-08-31: кандидат docs/product/retention-policy.yaml подготовлен (working defaults REQ-DATA-001, legal register) - не действует до OD-009; задача остаётся blocked.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>OpenAPI + event/manifest JSON Schema (AG): as-built генерация + target из §26/AB, contract tests</t>
+          <t>SLO objectives и измерение</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>OpenAPI/event schemas версионированы, examples и deprecation policy; contract tests зелёные [command: `python3 scripts/ci/roadmap-governance-guard.py`]; одна canonical opaque идентификация на версию API; alias {id} с deprecation date [behavioral: `tests/behavioral/test_rm_tech_220.py`]</t>
+          <t>каждое число ТЗ имеет formula/window/owner/metric либо `not measurable` [artifact: `docs/product/slo-objectives.yaml`]</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2583,14 +2583,14 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/api/openapi-as-built-v1.json (113 paths/128 ops/149 схем), target docs/architecture/api/openapi-target-v2.6.md, envelope docs/architecture/events/event-envelope-v1.schema.json; contract tests и версионирование - после старта задачи; задача planned до Gate-S (OD-043).</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288 RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/slo-objectives.yaml - 11 объектов, каждое число §8 с formula/window/owner/status; пороги OD-011/OD-025 open. Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-221</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2605,16 +2605,16 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Разделение User/Device/analytics/emergency API; device client не достигает admin</t>
+          <t>OpenAPI + event/manifest JSON Schema (AG): as-built генерация + target из §26/AB, contract tests</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>device JWT → admin endpoint = 403 на всех admin-роутах [behavioral: `tests/test_phase3_protected_identity.py`]</t>
+          <t>OpenAPI/event schemas версионированы, examples и deprecation policy; contract tests зелёные [command: `python3 scripts/ci/roadmap-governance-guard.py`]; одна canonical opaque идентификация на версию API; alias {id} с deprecation date [behavioral: `tests/behavioral/test_rm_tech_220.py`]</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2639,14 +2639,14 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-002; SC: SC-API-002; DEC: -. Evidence: tests/test_phase3_protected_identity.py; новый negative. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/api/openapi-as-built-v1.json (113 paths/128 ops/149 схем), target docs/architecture/api/openapi-target-v2.6.md, envelope docs/architecture/events/event-envelope-v1.schema.json; contract tests и версионирование - после старта задачи; задача planned до Gate-S (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-222</t>
+          <t>RM-TECH-221</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Канонический POST /api/v1/pop/batch, legacy /device/pop/batch как alias с deprecation</t>
+          <t>Разделение User/Device/analytics/emergency API; device client не достигает admin</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>ответы канонического и legacy идентичны; deprecation header; batch&gt;500 → 422; чужой device_id отклонён [behavioral: `tests/test_contract_pop.py`]</t>
+          <t>device JWT → admin endpoint = 403 на всех admin-роутах [behavioral: `tests/test_phase3_protected_identity.py`]</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2695,14 +2695,14 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-003, REQ-POP-003; SC: SC-API-003, SC-POP-003; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_edge002fu_real_endpoint.py. Риск регрессии: средний: runtime/плеер использует legacy path.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-002; SC: SC-API-002; DEC: -. Evidence: tests/test_phase3_protected_identity.py; новый negative. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-223</t>
+          <t>RM-TECH-222</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Manifest field contract и ACK-состояния runtime (opaque media_ref, no MinIO keys)</t>
+          <t>Канонический POST /api/v1/pop/batch, legacy /device/pop/batch как alias с deprecation</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2738,14 +2738,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>все обязательные поля §25 REQ-MAN-004 в schema; внутренний object key не раскрыт; 6 ACK states принимаются [behavioral: `tests/test_contract_manifest.py`]</t>
+          <t>ответы канонического и legacy идентичны; deprecation header; batch&gt;500 → 422; чужой device_id отклонён [behavioral: `tests/test_contract_pop.py`]</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2755,14 +2751,14 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-MAN-004; SC: SC-MAN-001; DEC: -. Evidence: tests/test_contract_manifest.py; tests/behavioral/test_edge002_manifest_delivery.py. Риск регрессии: высокий: меняет device-facing контракт — owner gate device_contract.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-003, REQ-POP-003; SC: SC-API-003, SC-POP-003; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_edge002fu_real_endpoint.py. Риск регрессии: средний: runtime/плеер использует legacy path.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-223</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2777,7 +2773,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat contract POST /api/v1/device/heartbeat: дедуп, scope, clock drift, freshness thresholds</t>
+          <t>Manifest field contract и ACK-состояния runtime (opaque media_ref, no MinIO keys)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2805,7 +2801,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>валидный/повтор/чужой scope/просроченный heartbeat дают ожидаемые результаты; legacy alias с той же семантикой [behavioral: `tests/behavioral/test_edge004_heartbeat.py`]</t>
+          <t>все обязательные поля §25 REQ-MAN-004 в schema; внутренний object key не раскрыт; 6 ACK states принимаются [behavioral: `tests/test_contract_manifest.py`]</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2815,14 +2811,14 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-009; SC: SC-OPS-002; DEC: -. Evidence: tests/behavioral/test_edge004_heartbeat.py. Риск регрессии: высокий: device-facing.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-MAN-004; SC: SC-MAN-001; DEC: -. Evidence: tests/test_contract_manifest.py; tests/behavioral/test_edge002_manifest_delivery.py. Риск регрессии: высокий: меняет device-facing контракт — owner gate device_contract.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2837,16 +2833,16 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>PoP duplicate semantics по OD-019: 200 + per-event duplicate/409, amendment ADR-017</t>
+          <t>Heartbeat contract POST /api/v1/device/heartbeat: дедуп, scope, clock drift, freshness thresholds</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-222</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
@@ -2858,10 +2854,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>ADR-017 amendment принят; behavioral: повтор batch → per-event duplicate, summary не удвоен, порядок хронологический [behavioral: `tests/behavioral/test_edge003_pop_ingestion.py`]</t>
+          <t>валидный/повтор/чужой scope/просроченный heartbeat дают ожидаемые результаты; legacy alias с той же семантикой [behavioral: `tests/behavioral/test_edge004_heartbeat.py`]</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2871,14 +2871,14 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-002; SC: SC-POP-002; DEC: DEC-024. Evidence: tests/behavioral/test_edge003_pop_ingestion.py; ADR-017 amendment. Риск регрессии: низкий: закрепляет текущее поведение.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-009; SC: SC-OPS-002; DEC: -. Evidence: tests/behavioral/test_edge004_heartbeat.py. Риск регрессии: высокий: device-facing.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-226</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2893,16 +2893,16 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Proof model: pop_mode error/not_applied — schema/runtime migration из compatibility projection</t>
+          <t>PoP duplicate semantics по OD-019: 200 + per-event duplicate/409, amendment ADR-017</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-222</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -2914,14 +2914,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>ProofMode содержит 9 значений; отчёт не смешивает playback/apply/delivery/error [behavioral: `tests/behavioral/test_pop_schema.py`]</t>
+          <t>ADR-017 amendment принят; behavioral: повтор batch → per-event duplicate, summary не удвоен, порядок хронологический [behavioral: `tests/behavioral/test_edge003_pop_ingestion.py`]</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2931,14 +2927,14 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-001; SC: SC-POP-001; DEC: -. Evidence: tests/behavioral/test_pop_schema.py; migration. Риск регрессии: средний: enum migration + отчёты.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-002; SC: SC-POP-002; DEC: DEC-024. Evidence: tests/behavioral/test_edge003_pop_ingestion.py; ADR-017 amendment. Риск регрессии: низкий: закрепляет текущее поведение.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-227</t>
+          <t>RM-TECH-226</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2953,7 +2949,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Валидация proof_event_v1: playback_result/failure_reason, clock-drift quarantine, no internal IDs/PII</t>
+          <t>Proof model: pop_mode error/not_applied — schema/runtime migration из compatibility projection</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2974,10 +2970,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>недопустимый playback_result/внутренний ID/сдвиг часов → 422 или quarantine; SHA/signature проверены [behavioral: `tests/test_contract_pop.py`]</t>
+          <t>ProofMode содержит 9 значений; отчёт не смешивает playback/apply/delivery/error [behavioral: `tests/behavioral/test_pop_schema.py`]</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2987,14 +2987,14 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-004; SC: SC-POP-004; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_pop_schema.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-001; SC: SC-POP-001; DEC: -. Evidence: tests/behavioral/test_pop_schema.py; migration. Риск регрессии: средний: enum migration + отчёты.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-228</t>
+          <t>RM-TECH-227</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3009,16 +3009,16 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Окно совместимости device/API/manifest: heartbeat объявляет версии, сервер выбирает представление</t>
+          <t>Валидация proof_event_v1: playback_result/failure_reason, clock-drift quarantine, no internal IDs/PII</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>совместимая версия выбрана по объявленным capabilities; breaking change без staged rollout отклонён contract-тестом [behavioral: `tests/test_version_identity.py`]</t>
+          <t>недопустимый playback_result/внутренний ID/сдвиг часов → 422 или quarantine; SHA/signature проверены [behavioral: `tests/test_contract_pop.py`]</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3043,14 +3043,14 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-003; SC: SC-NFR-003; DEC: -. Evidence: tests/test_version_identity.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-004; SC: SC-POP-004; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_pop_schema.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-228</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3060,21 +3060,21 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>ERD + data dictionary + migration plan (AG): инвентарь сущностей §15, retailer_id NOT NULL + двухуровневый RLS</t>
+          <t>Окно совместимости device/API/manifest: heartbeat объявляет версии, сервер выбирает представление</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>as-built ERD из моделей; каждая группа §15 присутствует или имеет migration task; tenant-таблицы с retailer_id+FK+RLS [artifact: `tests/behavioral/test_adr018_multitenancy_rls.py`]; behavioral RLS proof под ролью приложения NOBYPASSRLS [behavioral: `tests/behavioral/test_adr018_multitenancy_rls.py`]</t>
+          <t>совместимая версия выбрана по объявленным capabilities; breaking change без staged rollout отклонён contract-тестом [behavioral: `tests/test_version_identity.py`]</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3099,14 +3099,14 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/erd/data-dictionary-as-built.md (62 таблицы, 38 RLS) и кандидат docs/architecture/erd/migration-plan-v2.6.md (§13 → present/missing → задачи); PII/retention колонки - RM-TECH-253/RM-OPS-005. Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-003; SC: SC-NFR-003; DEC: -. Evidence: tests/test_version_identity.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-230</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Channel Adapter contract (design-only до второго канала): versioned task, receipt, proof/ack, error, health, mock mode</t>
+          <t>ERD + data dictionary + migration plan (AG): инвентарь сущностей §15, retailer_id NOT NULL + двухуровневый RLS</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>contract spec + JSON Schema без реализации adapter/mock (ADR-019) [artifact: `docs/architecture contract`]</t>
+          <t>as-built ERD из моделей; каждая группа §15 присутствует или имеет migration task; tenant-таблицы с retailer_id+FK+RLS [artifact: `tests/behavioral/test_adr018_multitenancy_rls.py`]; behavioral RLS proof под ролью приложения NOBYPASSRLS [behavioral: `tests/behavioral/test_adr018_multitenancy_rls.py`]</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3155,14 +3155,14 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-006; SC: SC-ORCH-005; DEC: -. Evidence: docs/architecture contract; schema. Риск регрессии: низкий: только документ.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/erd/data-dictionary-as-built.md (62 таблицы, 38 RLS) и кандидат docs/architecture/erd/migration-plan-v2.6.md (§13 → present/missing → задачи); PII/retention колонки - RM-TECH-253/RM-OPS-005. Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-231</t>
+          <t>RM-TECH-230</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3177,16 +3177,16 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>channel-capability-matrix.yaml (AG) для первого канала KSO: channel/surface/rendition/proof/SLA/vendor constraints</t>
+          <t>Channel Adapter contract (design-only до второго канала): versioned task, receipt, proof/ack, error, health, mock mode</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-230</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -3198,14 +3198,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>матрица покрывает KSO channel/surface/rendition/proof/SLA/vendor constraints; каждая строка ссылается на REQ-CHAN-*/REQ-MAN-*/REQ-POP-* [artifact: `docs/product/channel-capability-matrix.yaml`]; артефакт принят владельцем как часть handoff-пакета AG [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>contract spec + JSON Schema без реализации adapter/mock (ADR-019) [artifact: `docs/architecture contract`]</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3215,14 +3211,14 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-012 (предложение 2026-08-31): AG требует channel-capability-matrix до старта разработки, а RM-TECH-261 держит матрицу за решением OD-021 (второй канал). Первый канал KSO описывается без OD-021; RM-TECH-261 расширяет матрицу вторым каналом. REQ: REQ-CHAN-001, REQ-CHAN-002, REQ-CHAN-003; SC: SC-CHAN-002; DEC: DEC-001 (расширение). Evidence: артефакт; ACCEPT владельца. Риск регрессии: нет (документ). Утверждена OD-042 (2026-08-31). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/channel-capability-matrix.yaml (KSO + declared каналы §7); приёмка - внутри задачи после Gate-S.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-006; SC: SC-ORCH-005; DEC: -. Evidence: docs/architecture contract; schema. Риск регрессии: низкий: только документ.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-253</t>
+          <t>RM-TECH-231</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3237,12 +3233,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Data protection: data classes, lawful purpose, минимизация PII, residency; retention по OD-009</t>
+          <t>channel-capability-matrix.yaml (AG) для первого канала KSO: channel/surface/rendition/proof/SLA/vendor constraints</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-230</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
@@ -3258,10 +3254,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>реестр data classes для всех сущностей; новая PII-сущность без класса — красный design-gate [artifact: `docs/architecture data classes`]</t>
+          <t>матрица покрывает KSO channel/surface/rendition/proof/SLA/vendor constraints; каждая строка ссылается на REQ-CHAN-*/REQ-MAN-*/REQ-POP-* [artifact: `docs/product/channel-capability-matrix.yaml`]; артефакт принят владельцем как часть handoff-пакета AG [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -3271,14 +3271,14 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: docs/architecture data classes. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено CORE → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
+          <t>RM-GOV-012 (предложение 2026-08-31): AG требует channel-capability-matrix до старта разработки, а RM-TECH-261 держит матрицу за решением OD-021 (второй канал). Первый канал KSO описывается без OD-021; RM-TECH-261 расширяет матрицу вторым каналом. REQ: REQ-CHAN-001, REQ-CHAN-002, REQ-CHAN-003; SC: SC-CHAN-002; DEC: DEC-001 (расширение). Evidence: артефакт; ACCEPT владельца. Риск регрессии: нет (документ). Утверждена OD-042 (2026-08-31). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/channel-capability-matrix.yaml (KSO + declared каналы §7); приёмка - внутри задачи после Gate-S.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-288</t>
+          <t>RM-TECH-253</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3288,21 +3288,21 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>nfr-slo.yaml + load-profiles.yaml (AG): method, percentile, error budget, generator, CI evidence</t>
+          <t>Data protection: data classes, lawful purpose, минимизация PII, residency; retention по OD-009</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>каждый SLO имеет window/denominator/exclusions; load generator и прогон в CI/стенде [artifact: `nfr-slo.yaml`]</t>
+          <t>реестр data classes для всех сущностей; новая PII-сущность без класса — красный design-gate [artifact: `docs/architecture data classes`]</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3327,14 +3327,14 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки):ы docs/product/nfr-slo.yaml и docs/product/load-profiles.yaml (7 профилей); load generator отсутствует (new). Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: docs/architecture data classes. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено CORE → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-011</t>
+          <t>RM-TECH-288</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3349,16 +3349,16 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>role-scope-matrix.yaml + portal-route-matrix.yaml + journeys/ (AG) из seed/pg_policies/registry</t>
+          <t>nfr-slo.yaml + load-profiles.yaml (AG): method, percentile, error budget, generator, CI evidence</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004, RM-STAB-006</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>матрицы генерируются и сверяются guard; deny-cases покрыты behavioral [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+          <t>каждый SLO имеет window/denominator/exclusions; load generator и прогон в CI/стенде [artifact: `nfr-slo.yaml`]</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3383,19 +3383,19 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено U → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/product/role-scope-matrix.yaml (5 seeded ролей × 30 permissions, Q2 target 7 ролей, 38 RLS-таблиц, deny-cases), docs/product/portal-route-matrix.yaml (admin 16 + advertiser 9 маршрутов), docs/product/journeys/journeys.yaml (79 journeys, нормативный формат); generated-сверка guard - после старта задачи; задача planned до Gate-S (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки):ы docs/product/nfr-slo.yaml и docs/product/load-profiles.yaml (7 профилей); load generator отсутствует (new). Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-001</t>
+          <t>RM-UX-011</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3405,16 +3405,16 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Записать managed-first scope</t>
+          <t>role-scope-matrix.yaml + portal-route-matrix.yaml + journeys/ (AG) из seed/pg_policies/registry</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-STAB-004, RM-STAB-006</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>roadmap явно исключает `self.campaign_create` из ближайшего control-plane pilot [artifact: `docs/product/roadmap.yaml (pilot scope)`]</t>
+          <t>матрицы генерируются и сверяются guard; deny-cases покрыты behavioral [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): ссылки OD-005/DEC-011, REQ-SCOPE-001</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено U → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/product/role-scope-matrix.yaml (5 seeded ролей × 30 permissions, Q2 target 7 ролей, 38 RLS-таблиц, deny-cases), docs/product/portal-route-matrix.yaml (admin 16 + advertiser 9 маршрутов), docs/product/journeys/journeys.yaml (79 journeys, нормативный формат); generated-сверка guard - после старта задачи; задача planned до Gate-S (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201</t>
+          <t>RM-BIZ-001</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3456,12 +3456,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Таксономия причин недопоказа</t>
+          <t>Записать managed-first scope</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3485,7 +3485,7 @@
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>8 категорий ТЗ, source/report/history contract и owner-approved artifact [artifact: `docs/product/underdelivery-reason-taxonomy.yaml`]</t>
+          <t>roadmap явно исключает `self.campaign_create` из ближайшего control-plane pilot [artifact: `docs/product/roadmap.yaml (pilot scope)`]</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -3495,14 +3495,14 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): ссылки OD-005/DEC-011, REQ-SCOPE-001</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202</t>
+          <t>RM-TECH-201</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3512,21 +3512,21 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Вытеснение и объяснимые приоритеты</t>
+          <t>Таксономия причин недопоказа</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>versioned rules [behavioral: `tests/behavioral/test_campaign_preemption.py`]</t>
+          <t>8 категорий ТЗ, source/report/history contract и owner-approved artifact [artifact: `docs/product/underdelivery-reason-taxonomy.yaml`]</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -3551,14 +3551,14 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-007 и порядок приоритета §12; исключение §3.1 (OD-018) — единственная точка изменения engine → RM-TECH-285 зависит от неё</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-203</t>
+          <t>RM-TECH-202</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3573,16 +3573,16 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Overbooking policy</t>
+          <t>Вытеснение и объяснимые приоритеты</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202</t>
+          <t>RM-TECH-201</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>default deny [behavioral: `tests/behavioral/test_inventory_overbooking_policy.py`]</t>
+          <t>versioned rules [behavioral: `tests/behavioral/test_campaign_preemption.py`]</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3607,14 +3607,14 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-007 и порядок приоритета §12; исключение §3.1 (OD-018) — единственная точка изменения engine → RM-TECH-285 зависит от неё</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-204</t>
+          <t>RM-TECH-203</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3629,16 +3629,16 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Creative QA без неутверждённого HTML5</t>
+          <t>Overbooking policy</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-202</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>metadata/antivirus/executable deny и immutable QA result [behavioral: `tests/behavioral/test_creative_qa.py`]</t>
+          <t>default deny [behavioral: `tests/behavioral/test_inventory_overbooking_policy.py`]</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-206</t>
+          <t>RM-TECH-204</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>License renewal/grant boundary</t>
+          <t>Creative QA без неутверждённого HTML5</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3709,7 +3709,7 @@
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>атомарная семантика §1.6 [behavioral: `tests/behavioral/test_license_renewal_boundary.py`]</t>
+          <t>metadata/antivirus/executable deny и immutable QA result [behavioral: `tests/behavioral/test_creative_qa.py`]</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>RM-TECH-206</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3741,16 +3741,16 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Универсальная иерархия носителей: migration + seed network/branch/cluster/store/store_group/channel/device/surface</t>
+          <t>License renewal/grant boundary</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -3762,14 +3762,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>все уровни существуют с FK и RLS; seed заполняет иерархию; чужой scope не видит [behavioral: `tests/behavioral/test_scope_rls.py`]</t>
+          <t>атомарная семантика §1.6 [behavioral: `tests/behavioral/test_license_renewal_boundary.py`]</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3779,14 +3775,14 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-001; SC: SC-DATA-001; DEC: -. Evidence: migration; tests/behavioral/test_scope_rls.py. Риск регрессии: высокий: схема ядра.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-241</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3801,16 +3797,16 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Target resolution boundary: broad target → display_surface_id, запрет physical_device_id как target</t>
+          <t>Универсальная иерархия носителей: migration + seed network/branch/cluster/store/store_group/channel/device/surface</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -3822,10 +3818,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>планирование разрешает target до surface; physical_device_id в target отклоняется [behavioral: `tests/test_s089_inventory_simulation.py`]</t>
+          <t>все уровни существуют с FK и RLS; seed заполняет иерархию; чужой scope не видит [behavioral: `tests/behavioral/test_scope_rls.py`]</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3835,14 +3835,14 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-003; SC: SC-ARCH-002; DEC: -. Evidence: tests/test_s089_inventory_simulation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-001; SC: SC-DATA-001; DEC: -. Evidence: migration; tests/behavioral/test_scope_rls.py. Риск регрессии: высокий: схема ядра.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-242</t>
+          <t>RM-TECH-241</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Outbox для любой OLTP-записи с domain event; revocation/refresh manifest при pause/archive/expiry</t>
+          <t>Target resolution boundary: broad target → display_surface_id, запрет physical_device_id как target</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>каждая доменная мутация создаёт outbox event в той же транзакции; pause/archive порождают revocation [behavioral: `tests/behavioral/test_outbox.py`]</t>
+          <t>планирование разрешает target до surface; physical_device_id в target отклоняется [behavioral: `tests/test_s089_inventory_simulation.py`]</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-003; SC: SC-ORCH-002; DEC: -. Evidence: tests/behavioral/test_outbox.py. Риск регрессии: средний: транзакционные границы всех сервисов.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-003; SC: SC-ARCH-002; DEC: -. Evidence: tests/test_s089_inventory_simulation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-243</t>
+          <t>RM-TECH-242</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3913,16 +3913,16 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Outbox relay: lease/publishing, Nats-Msg-Id, 7 попыток → dead_letter, partition order, DLQ policy, no PII</t>
+          <t>Outbox для любой OLTP-записи с domain event; revocation/refresh manifest при pause/archive/expiry</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-242</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>7 отказов брокера → dead_letter с operator action; ack → published; replay идемпотентен [behavioral: `tests/behavioral/test_outbox_relay.py`]; NATS recovery integration зелёный [command: `tests/behavioral/test_outbox_relay.py`]</t>
+          <t>каждая доменная мутация создаёт outbox event в той же транзакции; pause/archive порождают revocation [behavioral: `tests/behavioral/test_outbox.py`]</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3947,14 +3947,14 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-004; SC: SC-ORCH-003; DEC: DEC-004. Evidence: tests/behavioral/test_outbox_relay.py; tests/integration/test_nats_recovery.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-003; SC: SC-ORCH-002; DEC: -. Evidence: tests/behavioral/test_outbox.py. Риск регрессии: средний: транзакционные границы всех сервисов.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-244</t>
+          <t>RM-TECH-243</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3969,16 +3969,16 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Adapter task lifecycle через persisted queue (event-driven массовая публикация)</t>
+          <t>Outbox relay: lease/publishing, Nats-Msg-Id, 7 попыток → dead_letter, partition order, DLQ policy, no PII</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-243</t>
+          <t>RM-TECH-242</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>активация на 1000 устройств не ждёт устройств; задачи агрегируют статусы [behavioral: `tests/behavioral/test_delivery_foundation.py`]</t>
+          <t>7 отказов брокера → dead_letter с operator action; ack → published; replay идемпотентен [behavioral: `tests/behavioral/test_outbox_relay.py`]; NATS recovery integration зелёный [command: `tests/behavioral/test_outbox_relay.py`]</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -4003,14 +4003,14 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-002; SC: SC-ORCH-006; DEC: DEC-004. Evidence: tests/behavioral/test_delivery_foundation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-004; SC: SC-ORCH-003; DEC: DEC-004. Evidence: tests/behavioral/test_outbox_relay.py; tests/integration/test_nats_recovery.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-TECH-244</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4025,16 +4025,16 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Campaign lifecycle по ADR-015/OD-036: scheduled, resume, revise, archive; единый guard и audit</t>
+          <t>Adapter task lifecycle через persisted queue (event-driven массовая публикация)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-TECH-243</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -4046,14 +4046,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>_CAMPAIGN_TRANSITIONS = ADR-015; каждый переход через guard с audit; возврат в draft создаёт revision [behavioral: `tests/behavioral/test_campaign_domain.py`]; campaign.* smokes зелёные после изменения [ui_smoke: `tests/ui-smoke/test_rm_tech_245.py`]</t>
+          <t>активация на 1000 устройств не ждёт устройств; задачи агрегируют статусы [behavioral: `tests/behavioral/test_delivery_foundation.py`]</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -4063,14 +4059,14 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-010; SC: -; DEC: DEC-025. Evidence: tests/behavioral/test_campaign_domain.py; tests/ui-smoke/test_uismoke__campaign__*.py. Риск регрессии: высокий: меняет runtime enum кампании и UI.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-002; SC: SC-ORCH-006; DEC: DEC-004. Evidence: tests/behavioral/test_delivery_foundation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-246</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4085,7 +4081,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Commerce order: отмена по OD-020 (draft→cancelled, confirmed — reversal), payment projection отдельно</t>
+          <t>Campaign lifecycle по ADR-015/OD-036: scheduled, resume, revise, archive; единый guard и audit</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -4106,10 +4102,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>_ORDER_TRANSITIONS: draft→cancelled разрешён, confirmed→cancelled запрещён, reversal с audit [behavioral: `tests/test_commerce_a2.py`]</t>
+          <t>_CAMPAIGN_TRANSITIONS = ADR-015; каждый переход через guard с audit; возврат в draft создаёт revision [behavioral: `tests/behavioral/test_campaign_domain.py`]; campaign.* smokes зелёные после изменения [ui_smoke: `tests/ui-smoke/test_rm_tech_245.py`]</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4119,14 +4119,14 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-014; SC: -; DEC: DEC-017, DEC-026. Evidence: tests/test_commerce_a2.py; tests/behavioral/test_commerce_rls.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-010; SC: -; DEC: DEC-025. Evidence: tests/behavioral/test_campaign_domain.py; tests/ui-smoke/test_uismoke__campaign__*.py. Риск регрессии: высокий: меняет runtime enum кампании и UI.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-247</t>
+          <t>RM-TECH-246</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4141,16 +4141,16 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Approval policy: required roles/scope/порядок/timeout per campaign/placement/creative</t>
+          <t>Commerce order: отмена по OD-020 (draft→cancelled, confirmed — reversal), payment projection отдельно</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>политика версионирована; submit/approve соблюдают порядок и timeout; negative для чужого scope [behavioral: `tests/behavioral/test_campaign_approval.py`]</t>
+          <t>_ORDER_TRANSITIONS: draft→cancelled разрешён, confirmed→cancelled запрещён, reversal с audit [behavioral: `tests/test_commerce_a2.py`]</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -4175,14 +4175,14 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-003; SC: -; DEC: -. Evidence: tests/behavioral/test_campaign_approval.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-014; SC: -; DEC: DEC-017, DEC-026. Evidence: tests/test_commerce_a2.py; tests/behavioral/test_commerce_rls.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-248</t>
+          <t>RM-TECH-247</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Flight/placement windows: versioned start_at/end_at UTC, проверка при simulation/manifest/runtime</t>
+          <t>Approval policy: required roles/scope/порядок/timeout per campaign/placement/creative</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -4221,7 +4221,7 @@
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>показ вне окна запрещён на трёх уровнях; DST/праздники/closed stores — версионированные правила [behavioral: `tests/test_s063_pop_timezone.py`]</t>
+          <t>политика версионирована; submit/approve соблюдают порядок и timeout; negative для чужого scope [behavioral: `tests/behavioral/test_campaign_approval.py`]</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -4231,14 +4231,14 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-005, REQ-NFR-002; SC: SC-NFR-002; DEC: -. Evidence: tests/test_s063_pop_timezone.py; новый behavioral. Риск регрессии: высокий: расписание доставки.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-003; SC: -; DEC: -. Evidence: tests/behavioral/test_campaign_approval.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-249</t>
+          <t>RM-TECH-248</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4253,16 +4253,16 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Manifest eligibility: approved status + валидный flight/contract + resolved target + readiness</t>
+          <t>Flight/placement windows: versioned start_at/end_at UTC, проверка при simulation/manifest/runtime</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-248</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>неэлигибельная кампания не попадает в manifest; причина объяснима [behavioral: `tests/behavioral/test_delivery_generation.py`]</t>
+          <t>показ вне окна запрещён на трёх уровнях; DST/праздники/closed stores — версионированные правила [behavioral: `tests/test_s063_pop_timezone.py`]</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -4287,14 +4287,14 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-006; SC: -; DEC: -. Evidence: tests/behavioral/test_delivery_generation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-005, REQ-NFR-002; SC: SC-NFR-002; DEC: -. Evidence: tests/test_s063_pop_timezone.py; новый behavioral. Риск регрессии: высокий: расписание доставки.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-250</t>
+          <t>RM-TECH-249</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4309,16 +4309,16 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Creative/rendition state machine и immutable media history (uploaded→scanning→qa_failed/approved→superseded→retained)</t>
+          <t>Manifest eligibility: approved status + валидный flight/contract + resolved target + readiness</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-204</t>
+          <t>RM-TECH-248</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -4330,14 +4330,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>каждая версия хранит uploader/SHA-256/QA-решение/связь; закрытый отчёт воспроизводим после logical delete [behavioral: `tests/behavioral/test_creative_assets.py`]</t>
+          <t>неэлигибельная кампания не попадает в manifest; причина объяснима [behavioral: `tests/behavioral/test_delivery_generation.py`]</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -4347,14 +4343,14 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CONT-002; SC: SC-DATA-002; DEC: -. Evidence: tests/behavioral/test_creative_assets.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-006; SC: -; DEC: -. Evidence: tests/behavioral/test_delivery_generation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-251</t>
+          <t>RM-TECH-250</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4369,16 +4365,16 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Data ownership/lineage: immutable versioning и diff campaign/placement/playlist, словарь владельцев</t>
+          <t>Creative/rendition state machine и immutable media history (uploaded→scanning→qa_failed/approved→superseded→retained)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-204</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -4390,10 +4386,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>сохранение создаёт версию с diff и actor; предыдущая неизменяема [behavioral: `tests/behavioral/test_rm_tech_251.py`]</t>
+          <t>каждая версия хранит uploader/SHA-256/QA-решение/связь; закрытый отчёт воспроизводим после logical delete [behavioral: `tests/behavioral/test_creative_assets.py`]</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -4403,14 +4403,14 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-001; SC: SC-DATA-004; DEC: DEC-007. Evidence: новый behavioral. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CONT-002; SC: SC-DATA-002; DEC: -. Evidence: tests/behavioral/test_creative_assets.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-252</t>
+          <t>RM-TECH-251</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4425,16 +4425,16 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Identity: AD/LDAP или SSO для internal staff, MFA до production (OD-008)</t>
+          <t>Data ownership/lineage: immutable versioning и diff campaign/placement/playlist, словарь владельцев</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -4446,14 +4446,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>protected_boundary</t>
-        </is>
-      </c>
+      <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>логин через IdP; production-профиль без MFA отклоняет; TLS-профиль зафиксирован [behavioral: `tests/test_phase3_auth_api.py`]</t>
+          <t>сохранение создаёт версию с diff и actor; предыдущая неизменяема [behavioral: `tests/behavioral/test_rm_tech_251.py`]</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -4463,14 +4459,14 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-001; SC: SC-SEC-008; DEC: -. Evidence: tests/test_phase3_auth_api.py; tests/behavioral/test_auth_dual_e2e.py. Риск регрессии: высокий: вход всех пользователей.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-001; SC: SC-DATA-004; DEC: DEC-007. Evidence: новый behavioral. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-254</t>
+          <t>RM-TECH-252</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4485,16 +4481,16 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Emergency state machine: requested→authorized→dispatching→applied→resuming→closed, MFA+reason, приоритетный канал</t>
+          <t>Identity: AD/LDAP или SSO для internal staff, MFA до production (OD-008)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -4506,10 +4502,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>protected_boundary</t>
+        </is>
+      </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>emergency с причиной; per-target result; audit actor/reason/affected; resume возвращает штатный manifest [behavioral: `tests/test_phase3_emergency_api.py`]; emergency.* smokes зелёные [ui_smoke: `tests/ui-smoke/test_uismoke__emergency__activate.py`]</t>
+          <t>логин через IdP; production-профиль без MFA отклоняет; TLS-профиль зафиксирован [behavioral: `tests/test_phase3_auth_api.py`]</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -4519,14 +4519,14 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-007; SC: SC-OPS-003; DEC: -. Evidence: tests/test_phase3_emergency_api.py; tests/ui-smoke/test_uismoke__emergency__activate.py. Риск регрессии: высокий: аварийный контур.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-001; SC: SC-SEC-008; DEC: -. Evidence: tests/test_phase3_auth_api.py; tests/behavioral/test_auth_dual_e2e.py. Риск регрессии: высокий: вход всех пользователей.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-255</t>
+          <t>RM-TECH-254</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4541,16 +4541,16 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Device health/commands: пороги статусов по профилю, per-device view, команды с подтверждением</t>
+          <t>Emergency state machine: requested→authorized→dispatching→applied→resuming→closed, MFA+reason, приоритетный канал</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>online→degraded→offline по порогам; команда доставлена и подтверждена [behavioral: `tests/behavioral/test_rm_tech_255.py`]; device.health_view smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__device__health_view.py`]</t>
+          <t>emergency с причиной; per-target result; audit actor/reason/affected; resume возвращает штатный manifest [behavioral: `tests/test_phase3_emergency_api.py`]; emergency.* smokes зелёные [ui_smoke: `tests/ui-smoke/test_uismoke__emergency__activate.py`]</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -4575,19 +4575,19 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-001; SC: SC-OPS-006; DEC: -. Evidence: tests/ui-smoke/test_uismoke__device__health_view.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-007; SC: SC-OPS-003; DEC: -. Evidence: tests/test_phase3_emergency_api.py; tests/ui-smoke/test_uismoke__emergency__activate.py. Риск регрессии: высокий: аварийный контур.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-002</t>
+          <t>RM-TECH-255</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4597,16 +4597,16 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>`self.campaign_create` в будущей ветке</t>
+          <t>Device health/commands: пороги статусов по профилю, per-device view, команды с подтверждением</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-001</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -4615,17 +4615,13 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>mini-design, journey, backend/UI/RLS, intended-role smoke, walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__campaign_create.py`]</t>
+          <t>online→degraded→offline по порогам; команда доставлена и подтверждена [behavioral: `tests/behavioral/test_rm_tech_255.py`]; device.health_view smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__device__health_view.py`]</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -4635,14 +4631,14 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2). RM-GOV-009 (OD-037): blocked до OD-013 — полный self-service вне pilot scope (REQ-V26-003, OD-005)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-001; SC: SC-OPS-006; DEC: -. Evidence: tests/ui-smoke/test_uismoke__device__health_view.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001</t>
+          <t>RM-BIZ-002</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4657,16 +4653,16 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Accessibility оставшихся форм + route matrix (A3)</t>
+          <t>`self.campaign_create` в будущей ветке</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-BIZ-001</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -4675,13 +4671,17 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>labels/ARIA/axe/targeted vitest [artifact: `docs/product/ux-route-matrix.yaml`]</t>
+          <t>mini-design, journey, backend/UI/RLS, intended-role smoke, walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__campaign_create.py`]</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -4691,14 +4691,14 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2). RM-GOV-009 (OD-037): blocked до OD-013 — полный self-service вне pilot scope (REQ-V26-003, OD-005)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-002</t>
+          <t>RM-UX-001</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4713,16 +4713,16 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Поиск/сортировка/усечение таблиц (A2)</t>
+          <t>Accessibility оставшихся форм + route matrix (A3)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>server semantics для pagination [ui_smoke: `tests/ui-smoke/test_uismoke__campaign__create.py`]</t>
+          <t>labels/ARIA/axe/targeted vitest [artifact: `docs/product/ux-route-matrix.yaml`]</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-003</t>
+          <t>RM-UX-002</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4769,16 +4769,16 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Responsive-проверка (A4)</t>
+          <t>Поиск/сортировка/усечение таблиц (A2)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-002</t>
+          <t>RM-UX-001</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>все routes из `ux-route-matrix.yaml` проверены на 390px без overflow/crop [artifact: `docs/product/ux-responsive-report.yaml`]</t>
+          <t>server semantics для pagination [ui_smoke: `tests/ui-smoke/test_uismoke__campaign__create.py`]</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-004</t>
+          <t>RM-UX-003</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4825,16 +4825,16 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Согласованность состояний и терминов (A6)</t>
+          <t>Responsive-проверка (A4)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-003</t>
+          <t>RM-UX-002</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>route matrix покрывает empty/loading/error/403/success и locale-key check [artifact: `docs/product/ux-route-matrix.yaml (states coverage)`]</t>
+          <t>все routes из `ux-route-matrix.yaml` проверены на 390px без overflow/crop [artifact: `docs/product/ux-responsive-report.yaml`]</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-005</t>
+          <t>RM-UX-004</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4881,16 +4881,16 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Adoption доказанных primitives малыми slices (A1b)</t>
+          <t>Согласованность состояний и терминов (A6)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-004</t>
+          <t>RM-UX-003</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>каждый slice имеет отдельный diff/test/review [ci_job: `frontend`]</t>
+          <t>route matrix покрывает empty/loading/error/403/success и locale-key check [artifact: `docs/product/ux-route-matrix.yaml (states coverage)`]</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-006</t>
+          <t>RM-UX-005</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4937,16 +4937,16 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Advertiser-web UX audit/fixes (A5)</t>
+          <t>Adoption доказанных primitives малыми slices (A1b)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-005</t>
+          <t>RM-UX-004</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>versioned `docs/product/advertiser-route-matrix.yaml` с точным списком 15 routes [artifact: `docs/product/advertiser-route-matrix.yaml`]</t>
+          <t>каждый slice имеет отдельный diff/test/review [ci_job: `frontend`]</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-007</t>
+          <t>RM-UX-006</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4988,21 +4988,21 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Human operator walkthrough (A7)</t>
+          <t>Advertiser-web UX audit/fixes (A5)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001, RM-UX-002, RM-UX-003, RM-UX-004, RM-UX-005, RM-UX-006</t>
+          <t>RM-UX-005</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>человек проходит exact stand bundle [human: `PROJECT_STATE.md строка `operator walkthrough` (AGENTS.md правило 8); сценарии docs/product/operator-walkthrough-dev.md`]</t>
+          <t>versioned `docs/product/advertiser-route-matrix.yaml` с точным списком 15 routes [artifact: `docs/product/advertiser-route-matrix.yaml`]</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -5027,14 +5027,14 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) ПРИОСТАНОВЛЕНО владельцем 2026-08-31 (OD-041) до выравнивания ТЗ/roadmap/gates и утверждения единого плана реализации; не закрывать, done не ставить.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-008</t>
+          <t>RM-UX-007</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -5044,21 +5044,21 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Campaign readiness matrix по каналам (rendition/inventory/conflicts/forecast/PoP mode/SLA) с действием на blocked</t>
+          <t>Human operator walkthrough (A7)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-249, RM-UX-004</t>
+          <t>RM-UX-001, RM-UX-002, RM-UX-003, RM-UX-004, RM-UX-005, RM-UX-006</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>экран согласования показывает матрицу; каждый blocked/warning ведёт к действию [ui_smoke: `tests/ui-smoke/test_rm_ux_008.py`]</t>
+          <t>человек проходит exact stand bundle [human: `PROJECT_STATE.md строка `operator walkthrough` (AGENTS.md правило 8); сценарии docs/product/operator-walkthrough-dev.md`]</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -5083,14 +5083,14 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-004; SC: SC-UX-002; DEC: -. Evidence: новый ui-smoke; vitest. Риск регрессии: средний.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) ПРИОСТАНОВЛЕНО владельцем 2026-08-31 (OD-041) до выравнивания ТЗ/roadmap/gates и утверждения единого плана реализации; не закрывать, done не ставить.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-009</t>
+          <t>RM-UX-008</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5105,16 +5105,16 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Договор рекламодателя: immutable file versions, server-side SHA-256, legal status (юр. решение)</t>
+          <t>Campaign readiness matrix по каналам (rendition/inventory/conflicts/forecast/PoP mode/SLA) с действием на blocked</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-250</t>
+          <t>RM-TECH-249, RM-UX-004</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>повторная загрузка создаёт новую версию, SHA проверен сервером; старая версия неизменяема [behavioral: `tests/test_advertiser_contracts.py`]; advertiser.contract_crud smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py`]</t>
+          <t>экран согласования показывает матрицу; каждый blocked/warning ведёт к действию [ui_smoke: `tests/ui-smoke/test_rm_ux_008.py`]</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -5139,38 +5139,38 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-017; SC: -; DEC: -. Evidence: tests/test_advertiser_contracts.py; tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-004; SC: SC-UX-002; DEC: -. Evidence: новый ui-smoke; vitest. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207A</t>
+          <t>RM-UX-009</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>KSO environment + player/playlist design</t>
+          <t>Договор рекламодателя: immutable file versions, server-side SHA-256, legal status (юр. решение)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-250</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -5182,14 +5182,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>versioned environment audit, import/contract mini-design и test plan [artifact: `docs/architecture/kso-environment-audit.md`]</t>
+          <t>повторная загрузка создаёт новую версию, SHA проверен сервером; старая версия неизменяема [behavioral: `tests/test_advertiser_contracts.py`]; advertiser.contract_crud smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py`]</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -5199,14 +5195,14 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-STAND-003 feasibility gate явно в acceptance; ADR-019/OD-022</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-017; SC: -; DEC: -. Evidence: tests/test_advertiser_contracts.py; tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-207A</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5216,21 +5212,21 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>KSO player/playlist/PoP chain</t>
+          <t>KSO environment + player/playlist design</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207A</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -5244,12 +5240,12 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>device_contract</t>
+          <t>scope_decision</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>contract tests и playback→manifest→PoP behavioral proof [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; Playlist entity и state machine §6 ТЗ (draft → validating → valid/invalid → approved → published → superseded/rolled_back); published immutable [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; manifest target lifecycle (generated → signed → queued → delivered → applied/failed/expired) и canonical POST /api/v1/pop/batch [behavioral: `tests/behavioral/test_kso_playback_chain.py`]</t>
+          <t>versioned environment audit, import/contract mini-design и test plan [artifact: `docs/architecture/kso-environment-audit.md`]</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -5259,14 +5255,14 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-STAND-003 feasibility gate явно в acceptance; ADR-019/OD-022</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-208</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -5281,16 +5277,16 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Signed licensing Layer 2</t>
+          <t>KSO player/playlist/PoP chain</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-206, RM-TECH-207B, RM-STAB-010</t>
+          <t>RM-TECH-207A</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -5304,12 +5300,12 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>protected_boundary</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Ed25519 offline verify, kid/rotation/revocation, UI, tamper/rollback [behavioral: `tests/behavioral/test_signed_license_layer2.py`]</t>
+          <t>contract tests и playback→manifest→PoP behavioral proof [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; Playlist entity и state machine §6 ТЗ (draft → validating → valid/invalid → approved → published → superseded/rolled_back); published immutable [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; manifest target lifecycle (generated → signed → queued → delivered → applied/failed/expired) и canonical POST /api/v1/pop/batch [behavioral: `tests/behavioral/test_kso_playback_chain.py`]</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -5326,7 +5322,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-260</t>
+          <t>RM-TECH-208</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5341,12 +5337,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Runtime cache lifecycle: лимит по профилю, детерминированная очистка, last-known-good</t>
+          <t>Signed licensing Layer 2</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-206, RM-TECH-207B, RM-STAB-010</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
@@ -5364,12 +5360,12 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>device_contract</t>
+          <t>protected_boundary</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>кэш на лимите: очистка по правилу; last-known-good сохранён; просроченная реклама не показывается [behavioral: `tests/behavioral/test_rm_tech_260.py`]</t>
+          <t>Ed25519 offline verify, kid/rotation/revocation, UI, tamper/rollback [behavioral: `tests/behavioral/test_signed_license_layer2.py`]</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -5379,14 +5375,14 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-008; SC: SC-EDGE-002; DEC: -. Evidence: runtime simulator tests. Риск регрессии: средний: плеер.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-261</t>
+          <t>RM-TECH-260</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -5396,17 +5392,17 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Второй канал: решение OD-021 + channel-capability-matrix.yaml (AG); extraction design по ADR-019</t>
+          <t>Runtime cache lifecycle: лимит по профилю, детерминированная очистка, last-known-good</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B, RM-TECH-230</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
@@ -5419,17 +5415,17 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>scope_decision</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>владелец назвал канал и владельца (OD-021); матрица возможностей утверждена [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; extraction design: KSO-вертикаль как первый adapter без поломки контрактов [artifact: `docs/audit/RM-TECH-261-artifact.md (создаётся задачей)`]</t>
+          <t>кэш на лимите: очистка по правилу; last-known-good сохранён; просроченная реклама не показывается [behavioral: `tests/behavioral/test_rm_tech_260.py`]</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -5439,14 +5435,14 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CHAN-001, REQ-ORCH-005; SC: SC-CHAN-002, SC-ORCH-004; DEC: DEC-001, DEC-002. Evidence: OD-021; design doc. Риск регрессии: высокий: рефакторинг KSO-вертикали. blocked до OD-021; Orchestrator/Adapter Layer/mock не создаются раньше (ADR-019/OD-022).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-008; SC: SC-EDGE-002; DEC: -. Evidence: runtime simulator tests. Риск регрессии: средний: плеер.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-262</t>
+          <t>RM-TECH-261</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5456,21 +5452,21 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Dynamic creative binding/rendition safety (V26-008) на одном канале</t>
+          <t>Второй канал: решение OD-021 + channel-capability-matrix.yaml (AG); extraction design по ADR-019</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280, RM-TECH-261</t>
+          <t>RM-TECH-207B, RM-TECH-230</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
@@ -5479,13 +5475,17 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>master-confirmed price/promo подставляется при manifest generation; SLA-тест dynamic manifest [behavioral: `tests/behavioral/test_rm_tech_262.py`]</t>
+          <t>владелец назвал канал и владельца (OD-021); матрица возможностей утверждена [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; extraction design: KSO-вертикаль как первый adapter без поломки контрактов [artifact: `docs/audit/RM-TECH-261-artifact.md (создаётся задачей)`]</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -5495,14 +5495,14 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-008; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. ложная ESL-посылка снимается prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CHAN-001, REQ-ORCH-005; SC: SC-CHAN-002, SC-ORCH-004; DEC: DEC-001, DEC-002. Evidence: OD-021; design doc. Риск регрессии: высокий: рефакторинг KSO-вертикали. blocked до OD-021; Orchestrator/Adapter Layer/mock не создаются раньше (ADR-019/OD-022).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-263</t>
+          <t>RM-TECH-262</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5517,16 +5517,16 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Field mobile operations: scoped mobile web для сотрудника магазина (устройства, фото, инциденты)</t>
+          <t>Dynamic creative binding/rendition safety (V26-008) на одном канале</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-210, RM-TECH-255</t>
+          <t>RM-TECH-280, RM-TECH-261</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>journey field_ops.device_confirm под ролью магазина с RLS; negative чужой магазин [ui_smoke: `tests/ui-smoke/test_rm_tech_263.py`]</t>
+          <t>master-confirmed price/promo подставляется при manifest generation; SLA-тест dynamic manifest [behavioral: `tests/behavioral/test_rm_tech_262.py`]</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -5551,14 +5551,14 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-009; SC: -; DEC: -. Evidence: new ui-smoke. Риск регрессии: средний. prerequisite RM-TECH-210 (RLS device) - planned по зависимости; feature field_ops.device_confirm blocked до задачи (RM-GOV-012 выравнивание: blocked = решение владельца/внешний факт, а не зависимость).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-008; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. ложная ESL-посылка снимается prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-264</t>
+          <t>RM-TECH-263</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5573,16 +5573,16 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>ESL/price-checker: интеграция только через approved price/SKU master (INT-002)</t>
+          <t>Field mobile operations: scoped mobile web для сотрудника магазина (устройства, фото, инциденты)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-210, RM-TECH-255</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>price-related данные приходят из master или проходят reconciliation; расхождение блокирует показ [behavioral: `tests/behavioral/test_rm_tech_264.py`]</t>
+          <t>journey field_ops.device_confirm под ролью магазина с RLS; negative чужой магазин [ui_smoke: `tests/ui-smoke/test_rm_tech_263.py`]</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -5607,38 +5607,38 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. OD-023 approved 2026-08-31 - planned после RM-TECH-280.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-009; SC: -; DEC: -. Evidence: new ui-smoke. Риск регрессии: средний. prerequisite RM-TECH-210 (RLS device) - planned по зависимости; feature field_ops.device_confirm blocked до задачи (RM-GOV-012 выравнивание: blocked = решение владельца/внешний факт, а не зависимость).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>RM-TECH-264</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>ESL/price-checker: интеграция только через approved price/SKU master (INT-002)</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
           <t>RM-TECH-280</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>design</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Prerequisite: master-data adapter цен/SKU (контракт, owner OD-023, reconciliation)</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>RM-TECH-229</t>
-        </is>
-      </c>
       <c r="F91" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -5650,14 +5650,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>владелец master-данных назначен (OD-023 approved); contract + reconciliation design утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; adapter в mock/test mode проходит contract tests [behavioral: `tests/behavioral/test_rm_tech_280.py`]</t>
+          <t>price-related данные приходят из master или проходят reconciliation; расхождение блокирует показ [behavioral: `tests/behavioral/test_rm_tech_264.py`]</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -5667,34 +5663,34 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: OD-023; contract tests. Риск регрессии: средний. отсутствующий prerequisite по AQ.1 №5; OD-023 approved 2026-08-31 (роль Product Data Owner) - planned; owner gate: контракт/scope adapter.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. OD-023 approved 2026-08-31 - planned после RM-TECH-280.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-003</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>`self.report_view` plan/fact</t>
+          <t>Prerequisite: master-data adapter цен/SKU (контракт, owner OD-023, reconciliation)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201, RM-TECH-207B</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
@@ -5710,10 +5706,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>реальные PoP/причины/RLS, journey/smoke/walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__report_view.py`]</t>
+          <t>владелец master-данных назначен (OD-023 approved); contract + reconciliation design утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; adapter в mock/test mode проходит contract tests [behavioral: `tests/behavioral/test_rm_tech_280.py`]</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -5723,14 +5723,14 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-011; зависит от RM-TECH-207B (реальные PoP) — без изменений</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: OD-023; contract tests. Риск регрессии: средний. отсутствующий prerequisite по AQ.1 №5; OD-023 approved 2026-08-31 (роль Product Data Owner) - planned; owner gate: контракт/scope adapter.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-209</t>
+          <t>RM-BIZ-003</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5740,17 +5740,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>ClickHouse capacity trigger</t>
+          <t>`self.report_view` plan/fact</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-201, RM-TECH-207B</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
@@ -5769,7 +5769,7 @@
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>измеряемый PoP rate/retention threshold и owner migration gate [artifact: `docs/product/clickhouse-capacity-trigger.yaml`]</t>
+          <t>реальные PoP/причины/RLS, journey/smoke/walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__report_view.py`]</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -5779,14 +5779,14 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-011; зависит от RM-TECH-207B (реальные PoP) — без изменений</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-256</t>
+          <t>RM-TECH-209</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5801,16 +5801,16 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Business outcome KPI: baseline/target/metric definition для целей §1.2 (OD-024 exit criteria)</t>
+          <t>ClickHouse capacity trigger</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
@@ -5822,14 +5822,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>каждая бизнес-цель имеет baseline/target/формулу/владельца, утверждено владельцем [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>измеряемый PoP rate/retention threshold и owner migration gate [artifact: `docs/product/clickhouse-capacity-trigger.yaml`]</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -5839,14 +5835,14 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-013; SC: -; DEC: DEC-010. Evidence: artifact kpi register. Риск регрессии: низкий.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-281</t>
+          <t>RM-TECH-256</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5856,21 +5852,21 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: sales-reference ingestion (агрегаты store/SKU/day) + методология baseline/test-control</t>
+          <t>Business outcome KPI: baseline/target/metric definition для целей §1.2 (OD-024 exit criteria)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
@@ -5882,10 +5878,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>пакетная загрузка агрегатов без PII; versioned baseline; методика утверждена владельцем [behavioral: `tests/behavioral/test_rm_tech_281.py`]</t>
+          <t>каждая бизнес-цель имеет baseline/target/формулу/владельца, утверждено владельцем [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -5895,14 +5895,14 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-001; SC: -; DEC: -. Evidence: new behavioral; methodology doc. Риск регрессии: средний. prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-013; SC: -; DEC: DEC-010. Evidence: artifact kpi register. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-282</t>
+          <t>RM-TECH-281</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5917,16 +5917,16 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Attribution &amp; sales lift: test/control, versioned baseline, pilot lift report</t>
+          <t>Prerequisite: sales-reference ingestion (агрегаты store/SKU/day) + методология baseline/test-control</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-281, RM-TECH-229</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -5935,13 +5935,13 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>pilot lift report по test/control с explainable методикой; RLS scope [behavioral: `tests/behavioral/test_rm_tech_282.py`]</t>
+          <t>пакетная загрузка агрегатов без PII; versioned baseline; методика утверждена владельцем [behavioral: `tests/behavioral/test_rm_tech_281.py`]</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -5951,14 +5951,14 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-002; SC: -; DEC: DEC-005, DEC-027. Evidence: new behavioral; report. Риск регрессии: средний. blocked OD-014 (DEC-027); OD-023 approved 2026-08-31.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-001; SC: -; DEC: -. Evidence: new behavioral; methodology doc. Риск регрессии: средний. prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-283</t>
+          <t>RM-TECH-282</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5968,21 +5968,21 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: audience source/privacy contract (анонимные store-атрибуты, 152-ФЗ, OD-032)</t>
+          <t>Attribution &amp; sales lift: test/control, versioned baseline, pilot lift report</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280, RM-TECH-253</t>
+          <t>RM-TECH-281, RM-TECH-229</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
@@ -5994,14 +5994,10 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>privacy/legal решение (OD-032) и контракт источника утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>pilot lift report по test/control с explainable методикой; RLS scope [behavioral: `tests/behavioral/test_rm_tech_282.py`]</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -6011,14 +6007,14 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-005; SC: -; DEC: DEC-005, DEC-019. Evidence: OD-032; contract. Риск регрессии: низкий. blocked OD-032 (DEC-019); OD-023 approved 2026-08-31.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-002; SC: -; DEC: DEC-005, DEC-027. Evidence: new behavioral; report. Риск регрессии: средний. blocked OD-014 (DEC-027); OD-023 approved 2026-08-31.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-284</t>
+          <t>RM-TECH-283</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -6028,21 +6024,21 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>A/B attribution и winner metric (minimum sample, owner approval результата)</t>
+          <t>Prerequisite: audience source/privacy contract (анонимные store-атрибуты, 152-ФЗ, OD-032)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-282</t>
+          <t>RM-TECH-280, RM-TECH-253</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
@@ -6054,10 +6050,14 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>A/B фиксирует группы/период/метрику; winner только при minimum sample и ручном утверждении [behavioral: `tests/behavioral/test_rm_tech_284.py`]</t>
+          <t>privacy/legal решение (OD-032) и контракт источника утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -6067,14 +6067,14 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-012, REQ-V26-010; SC: -; DEC: DEC-027. Evidence: new behavioral. Риск регрессии: средний. blocked OD-014 (DEC-027) - методика winner metric не утверждена.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-005; SC: -; DEC: DEC-005, DEC-019. Evidence: OD-032; contract. Риск регрессии: низкий. blocked OD-032 (DEC-019); OD-023 approved 2026-08-31.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-285</t>
+          <t>RM-TECH-284</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -6089,16 +6089,16 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Competitive separation: competitive_category, интервал/исключение в playlist/manifest (исключение §3.1 по OD-018)</t>
+          <t>A/B attribution и winner metric (minimum sample, owner approval результата)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202, RM-TECH-280</t>
+          <t>RM-TECH-282</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -6107,13 +6107,13 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>separation block/override test; изменение priority engine ограничено §3.1 [behavioral: `tests/behavioral/test_rm_tech_285.py`]</t>
+          <t>A/B фиксирует группы/период/метрику; winner только при minimum sample и ручном утверждении [behavioral: `tests/behavioral/test_rm_tech_284.py`]</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -6123,14 +6123,14 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-004; SC: -; DEC: DEC-005, DEC-022. Evidence: new behavioral. Риск регрессии: высокий: priority engine. OD-023 approved 2026-08-31, DEC-022 = OD-018 approved - planned после RM-TECH-280.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-012, REQ-V26-010; SC: -; DEC: DEC-027. Evidence: new behavioral. Риск регрессии: средний. blocked OD-014 (DEC-027) - методика winner metric не утверждена.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-286</t>
+          <t>RM-TECH-285</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -6145,16 +6145,16 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Financial-system exchange: versioned/idempotent export + payment-status contract (после DEC-017)</t>
+          <t>Competitive separation: competitive_category, интервал/исключение в playlist/manifest (исключение §3.1 по OD-018)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-246</t>
+          <t>RM-TECH-202, RM-TECH-280</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -6163,13 +6163,13 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>idempotent export round-trip; повтор не создаёт дубликатов; scope финансового контура зафиксирован [behavioral: `tests/behavioral/test_rm_tech_286.py`]</t>
+          <t>separation block/override test; изменение priority engine ограничено §3.1 [behavioral: `tests/behavioral/test_rm_tech_285.py`]</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -6179,14 +6179,14 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-006, REQ-BIZ-009; SC: -; DEC: DEC-017. Evidence: new behavioral. Риск регрессии: средний. blocked OD-030.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-004; SC: -; DEC: DEC-005, DEC-022. Evidence: new behavioral. Риск регрессии: высокий: priority engine. OD-023 approved 2026-08-31, DEC-022 = OD-018 approved - planned после RM-TECH-280.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-287</t>
+          <t>RM-TECH-286</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -6201,16 +6201,16 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>BI/export/SIEM/vendor API: scoped keys, rate-limit, immutable audit, circuit breaker (после DEC-013)</t>
+          <t>Financial-system exchange: versioned/idempotent export + payment-status contract (после DEC-017)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-013</t>
+          <t>RM-TECH-246</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>401/403/429 negative; vendor connector с отдельными credentials и failure mode [behavioral: `tests/test_s065_rate_limit.py`]</t>
+          <t>idempotent export round-trip; повтор не создаёт дубликатов; scope финансового контура зафиксирован [behavioral: `tests/behavioral/test_rm_tech_286.py`]</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -6235,14 +6235,14 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-003; SC: SC-SEC-002; DEC: DEC-013. Evidence: tests/test_s065_rate_limit.py; new behavioral. Риск регрессии: средний. blocked OD-026.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-006, REQ-BIZ-009; SC: -; DEC: DEC-017. Evidence: new behavioral. Риск регрессии: средний. blocked OD-030.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-289</t>
+          <t>RM-TECH-287</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -6252,21 +6252,21 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Extension points designed-not-implemented: ADR для programmatic (V26-007) и external measurement (V26-011)</t>
+          <t>BI/export/SIEM/vendor API: scoped keys, rate-limit, immutable audit, circuit breaker (после DEC-013)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-STAB-013</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -6275,13 +6275,13 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>ADR принят с пометкой designed-not-implemented; код не пишется до OD-021/OD-031 [artifact: `docs/audit/RM-TECH-289-artifact.md (создаётся задачей)`]</t>
+          <t>401/403/429 negative; vendor connector с отдельными credentials и failure mode [behavioral: `tests/test_s065_rate_limit.py`]</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -6291,14 +6291,14 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-007, REQ-V26-011; SC: SC-ARCH-006; DEC: DEC-001, DEC-018. Evidence: ADR. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-003; SC: SC-SEC-002; DEC: DEC-013. Evidence: tests/test_s065_rate_limit.py; new behavioral. Риск регрессии: средний. blocked OD-026.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-010</t>
+          <t>RM-TECH-289</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -6308,21 +6308,21 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Service-quality reporting: доля active devices/logical carriers, plan/fact по каналу (analytics.compare)</t>
+          <t>Extension points designed-not-implemented: ADR для programmatic (V26-007) и external measurement (V26-011)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-003</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>отчёт по каналу с долями и причинами; RLS scope advertiser [ui_smoke: `tests/ui-smoke/test_rm_ux_010.py`]</t>
+          <t>ADR принят с пометкой designed-not-implemented; код не пишется до OD-021/OD-031 [artifact: `docs/audit/RM-TECH-289-artifact.md (создаётся задачей)`]</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -6347,38 +6347,38 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-004; SC: -; DEC: -. Evidence: новый ui-smoke; tests/behavioral/test_pop_reporting_scope.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-007, REQ-V26-011; SC: SC-ARCH-006; DEC: DEC-001, DEC-018. Evidence: ADR. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-001</t>
+          <t>RM-UX-010</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>external</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Production readiness</t>
+          <t>Service-quality reporting: доля active devices/logical carriers, plan/fact по каналу (analytics.compare)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-003</t>
+          <t>RM-BIZ-003</t>
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -6390,14 +6390,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+      <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>не запускается автоматически после pilot [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой; OD-025/OD-028)`]</t>
+          <t>отчёт по каналу с долями и причинами; RLS scope advertiser [ui_smoke: `tests/ui-smoke/test_rm_ux_010.py`]</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -6407,14 +6403,14 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): зависит от OD-025 (RTO/RPO) и OD-028 (топология); REQ-OPS-005/006; HA baseline выделен в RM-OPS-003</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-004; SC: -; DEC: -. Evidence: новый ui-smoke; tests/behavioral/test_pop_reporting_scope.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-002</t>
+          <t>RM-OPS-001</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -6424,21 +6420,21 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>external</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Network segmentation: firewall rules по environment + negative reachability tests из device-сегмента</t>
+          <t>Production readiness</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-PILOT-003</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
@@ -6450,10 +6446,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>Admin API/PostgreSQL/MinIO/Redis недостижимы из device-сегмента; Gateway только HTTPS/mTLS [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+          <t>не запускается автоматически после pilot [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой; OD-025/OD-028)`]</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -6463,14 +6463,14 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-008; SC: SC-SEC-006; DEC: -. Evidence: reachability test log. Риск регрессии: средний: сеть пилота.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): зависит от OD-025 (RTO/RPO) и OD-028 (топология); REQ-OPS-005/006; HA baseline выделен в RM-OPS-003</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-003</t>
+          <t>RM-OPS-002</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -6480,21 +6480,21 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>external-plan</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Production HA baseline: ≥2 backend, масштабируемый Gateway, standby PostgreSQL, MinIO replication, quarterly restore drill</t>
+          <t>Network segmentation: firewall rules по environment + negative reachability tests из device-сегмента</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-001</t>
+          <t>RM-PILOT-002</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
@@ -6503,17 +6503,13 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>production config gate зелёный; restore drill выполнен и записан [command: `tests/test_production_config_gate.py`]; топология утверждена (OD-028), RTO/RPO (OD-025) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>Admin API/PostgreSQL/MinIO/Redis недостижимы из device-сегмента; Gateway только HTTPS/mTLS [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -6523,14 +6519,14 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-006, REQ-ARCH-004; SC: SC-OPS-001, SC-OPS-005; DEC: DEC-012, DEC-015. Evidence: tests/test_production_config_gate.py; drill record. Риск регрессии: высокий. blocked OD-025/OD-028.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-008; SC: SC-SEC-006; DEC: -. Evidence: reachability test log. Риск регрессии: средний: сеть пилота.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-004</t>
+          <t>RM-OPS-003</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -6540,21 +6536,21 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>external-plan</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Rollout entity/state machine и feature flags: planned→lab→canary→staged→paused→completed/rolled_back</t>
+          <t>Production HA baseline: ≥2 backend, масштабируемый Gateway, standby PostgreSQL, MinIO replication, quarterly restore drill</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-OPS-001</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -6566,10 +6562,14 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>rollback возвращает предыдущую версию; flag отключает функцию; ответственность по OD-010 [behavioral: `tests/integration/test_stand_rollback_drill.py`]</t>
+          <t>production config gate зелёный; restore drill выполнен и записан [command: `tests/test_production_config_gate.py`]; топология утверждена (OD-028), RTO/RPO (OD-025) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -6579,14 +6579,14 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-002; SC: SC-OPS-007; DEC: DEC-008. Evidence: tests/integration/test_stand_rollback_drill.py. Риск регрессии: средний. blocked OD-010.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-006, REQ-ARCH-004; SC: SC-OPS-001, SC-OPS-005; DEC: DEC-012, DEC-015. Evidence: tests/test_production_config_gate.py; drill record. Риск регрессии: высокий. blocked OD-025/OD-028.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-001</t>
+          <t>RM-OPS-004</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -6596,21 +6596,21 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Managed control-plane pilot scope</t>
+          <t>Rollout entity/state machine и feature flags: planned→lab→canary→staged→paused→completed/rolled_back</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Gate-S, Gate-U, RM-ENV-001</t>
+          <t>RM-PILOT-002</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -6619,13 +6619,13 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
+          <t>rollback возвращает предыдущую версию; flag отключает функцию; ответственность по OD-010 [behavioral: `tests/integration/test_stand_rollback_drill.py`]</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -6635,14 +6635,14 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): deps += OD-024 (exit criteria ступеней), REQ-ARCH-004</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-002; SC: SC-OPS-007; DEC: DEC-008. Evidence: tests/integration/test_stand_rollback_drill.py. Риск регрессии: средний. blocked OD-010.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-PILOT-001</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -6652,21 +6652,21 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>external-plan</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Deployment plan/preflight</t>
+          <t>Managed control-plane pilot scope</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-001</t>
+          <t>Gate-S, Gate-U, RM-ENV-001</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
+          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -6691,65 +6691,121 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): deps += OD-024 (exit criteria ступеней), REQ-ARCH-004</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>RM-PILOT-002</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>external-plan</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Deployment plan/preflight</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-001</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
           <t>RM-PILOT-003</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>POPS</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Controlled pilot deploy</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>RM-PILOT-002</t>
         </is>
       </c>
-      <c r="F110" s="2" t="n">
+      <c r="F111" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr">
         <is>
           <t>deployment</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr">
+      <c r="J111" s="2" t="inlineStr">
         <is>
           <t>SHA/lock/schema/health, stand-safe journeys, rollback readiness [owner: `docs/audit/&lt;дата&gt;-pilot-deploy-&lt;sha&gt;.md + ACCEPT владельца с датой (deployment gate)`]</t>
         </is>
       </c>
-      <c r="K110" s="2" t="inlineStr">
+      <c r="K111" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L110" s="2" t="inlineStr">
+      <c r="L111" s="2" t="inlineStr">
         <is>
           <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2402,12 +2402,12 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · behavioral · tests/behavioral/test_rm_stab_018_refresh_replay.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/36475858226</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>OD-046 (2026-09-28), этап RF-01; находка P0-7 ревью main@8ad0228. REQ: REQ-SEC-001; SC: -; DEC: -. Скрытые дефекты: поиск с фильтром rotated_at IS NULL делал ветку повтора недостижимой; отзыв семьи писал несуществующую колонку last_error (CompileError); ротация без блокировки. Риск регрессии: средний - отзыв семьи начинает срабатывать; гонка вкладок портала (P1-13.b) семью не отзывает (окно 10 с), но проигравшая вкладка по-прежнему получает 401 - до single-flight на фронтенде (RF-08).</t>
+          <t>OD-046 (2026-09-28), этап RF-01; done - PR #11 смержен в develop @ d8dbd62, push-run develop 36475858226 success 41/41 (решение владельца 2026-09-29); находка P0-7 ревью main@8ad0228. REQ: REQ-SEC-001; SC: -; DEC: -. Скрытые дефекты: поиск с фильтром rotated_at IS NULL делал ветку повтора недостижимой; отзыв семьи писал несуществующую колонку last_error (CompileError); ротация без блокировки. Риск регрессии: средний - отзыв семьи начинает срабатывать; гонка вкладок портала (P1-13.b) семью не отзывает (окно 10 с), но проигравшая вкладка по-прежнему получает 401 - до single-flight на фронтенде (RF-08).</t>
         </is>
       </c>
     </row>
@@ -6754,58 +6754,114 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>RM-PILOT-002A</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Pilot-compose поднимается под ENVIRONMENT=pilot без ручных шагов; verify честный</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>in_progress</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>pilot-compose из образов коммита под ENVIRONMENT=pilot - db-migrate сам создаёт retail_media_app (NOBYPASSRLS), все сервисы healthy в пределах таймаута, readiness со строгой проверкой роли, identity из образа, device-токен control-api принят device-gateway, конфиг orchestrator-worker грузится; таймаут или любой отказ роняют проверку [command: `CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env &lt;version&gt; &lt;sha&gt;`]; каждый backend-сервис получает из pilot-compose все переменные, которых требует валидатор prod; пустой JWT_AUDIENCE - отказ при старте [command: `python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py`]</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>Решение владельца 2026-09-29 (этап RF-05, область RM-PILOT-002, Protected Boundary Docker/deployment с условиями). Находки ревью main@8ad0228: P0-1..P0-5, P1-16, P2-I9, P2-I11, T12 (+ FU5 healthcheck frontend). REQ: REQ-ARCH-004; SC: -; DEC: -. Не покрывает: TLS/reverse proxy (001D), ack/DLQ воркера при ошибке (RF-04), публикацию релиза и verify-pilot-images на GHCR (внешнее действие владельца). Риск регрессии: средний - обязательный JWT_AUDIENCE вне dev; pilot-хосты без него не стартуют.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
           <t>RM-PILOT-003</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>POPS</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Controlled pilot deploy</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>RM-PILOT-002</t>
         </is>
       </c>
-      <c r="F111" s="2" t="n">
+      <c r="F112" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr">
         <is>
           <t>deployment</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr">
+      <c r="J112" s="2" t="inlineStr">
         <is>
           <t>SHA/lock/schema/health, stand-safe journeys, rollback readiness [owner: `docs/audit/&lt;дата&gt;-pilot-deploy-&lt;sha&gt;.md + ACCEPT владельца с датой (deployment gate)`]</t>
         </is>
       </c>
-      <c r="K111" s="2" t="inlineStr">
+      <c r="K112" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L111" s="2" t="inlineStr">
+      <c r="L112" s="2" t="inlineStr">
         <is>
           <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L112"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2414,7 +2414,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-210</t>
+          <t>RM-STAB-019</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2429,16 +2429,16 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>RLS-контекст на device-маршрутах онбординга</t>
+          <t>Оркестратор: сбои не маскируются - nak при системной ошибке генерации, живучий consumer, воркер завершения под RLS</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
@@ -2447,54 +2447,50 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+          <t>in_progress</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; bootstrap-RLS миграции 037: без RLS-контекста роль приложения видит 0 onboarding codes (fail-closed); со своим app.rmp_device_code — только свою строку; с чужим кодом — 0 [behavioral: `tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap`]</t>
+          <t>системная ошибка генерации манифеста (конфиг безопасности, БД/сессия) - rollback и nak, строки failed не пишутся; ошибка данных одного устройства - failed + delivery.manifest.failed + ack, как раньше (путь consumer под retail_media_app) [behavioral: `tests/behavioral/test_rm_stab_019_orchestrator_rls.py`]; сбой session_setup/rollback одного сообщения - nak, цикл consumer продолжается; остановка цикла подключённого consumer - /health/ready 503 [command: `python -m pytest tests/test_rm_stab_019_orchestrator_failures.py`]; один проход воркера завершения под retail_media_app (NOBYPASSRLS) завершает активную кампанию с истёкшими флайтами [behavioral: `tests/behavioral/test_rm_stab_019_orchestrator_rls.py`]</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py; verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap; verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33408891221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика. 2026-08-31 (стадия S, OD-043: зависимость RM-STAB-002 done): реализовано локально - set_rls_context на /identity/device-codes, bootstrap-контекст кода/fingerprint на /device/onboard, миграция 037 (rehearsal down/up), allowlist элевации снят; targeted 97 passed под ролью приложения; design-gate docs/architecture/rm-tech-210-device-onboarding-rls-bootstrap-design-gate.md (на тот момент - до CI-evidence и owner gate). verification 2026-08-31: CI 33408891221 success (условием done тогда оставался owner gate device_contract). 2026-08-31: приёмка №2 уточнена владельцем — три утверждения bootstrap-RLS (без контекста 0; свой app.rmp_device_code — только свой; чужой — 0); ref → TestRMTech210BootstrapRLS. done 2026-08-31: owner gate device_contract granted - OD-045 (fail-closed контракт принят владельцем).</t>
+          <t>Решение владельца 2026-09-29, этап RF-04 (узкий состав). Находки ревью main@8ad0228: P0-4 (ack при ошибке), P1-6.a, P1-8, T11. REQ: - (кандидат REQ-ORCH-002, ссылка - решением владельца); SC: -; DEC: -. Не покрывает: DLQ и max_deliver (P1-6.b), stream subjects (P1-7), SKIP LOCKED outbox (P2-B7) - отдельный этап с RM-TECH-243; сбой подписи и ошибки кода внутри генерации по устройству по-прежнему дают failed + ack (деление по типу исключения). Риск регрессии: низкий - системный сбой начинает повторяться (nak) вместо тихого failed, повторы бесконечны до DLQ (max_deliver=-1, P1-6.b); readiness воркера может стать 503, но compose healthcheck смотрит /health/live - автоперезапуска нет.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-005</t>
+          <t>RM-TECH-210</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>retention-policy.yaml + legal decision register (AG): сроки, 152-ФЗ, deletion/archive, review date</t>
+          <t>RLS-контекст на device-маршрутах онбординга</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-253</t>
+          <t>RM-STAB-002</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -2507,34 +2503,34 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>scope_decision</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>юридическое утверждение retention/152-ФЗ (OD-009) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; bootstrap-RLS миграции 037: без RLS-контекста роль приложения видит 0 onboarding codes (fail-closed); со своим app.rmp_device_code — только свою строку; с чужим кодом — 0 [behavioral: `tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap`]</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py; verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap; verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33408891221</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено POPS → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). 2026-08-31: кандидат docs/product/retention-policy.yaml подготовлен (working defaults REQ-DATA-001, legal register) - не действует до OD-009; задача остаётся blocked.</t>
+          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика. 2026-08-31 (стадия S, OD-043: зависимость RM-STAB-002 done): реализовано локально - set_rls_context на /identity/device-codes, bootstrap-контекст кода/fingerprint на /device/onboard, миграция 037 (rehearsal down/up), allowlist элевации снят; targeted 97 passed под ролью приложения; design-gate docs/architecture/rm-tech-210-device-onboarding-rls-bootstrap-design-gate.md (на тот момент - до CI-evidence и owner gate). verification 2026-08-31: CI 33408891221 success (условием done тогда оставался owner gate device_contract). 2026-08-31: приёмка №2 уточнена владельцем — три утверждения bootstrap-RLS (без контекста 0; свой app.rmp_device_code — только свой; чужой — 0); ref → TestRMTech210BootstrapRLS. done 2026-08-31: owner gate device_contract granted - OD-045 (fail-closed контракт принят владельцем).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-OPS-005</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2549,16 +2545,16 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>SLO objectives и измерение</t>
+          <t>retention-policy.yaml + legal decision register (AG): сроки, 152-ФЗ, deletion/archive, review date</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-253</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
@@ -2567,13 +2563,17 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>каждое число ТЗ имеет formula/window/owner/metric либо `not measurable` [artifact: `docs/product/slo-objectives.yaml`]</t>
+          <t>юридическое утверждение retention/152-ФЗ (OD-009) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2583,14 +2583,14 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288 RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/slo-objectives.yaml - 11 объектов, каждое число §8 с formula/window/owner/status; пороги OD-011/OD-025 open. Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено POPS → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). 2026-08-31: кандидат docs/product/retention-policy.yaml подготовлен (working defaults REQ-DATA-001, legal register) - не действует до OD-009; задача остаётся blocked.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>OpenAPI + event/manifest JSON Schema (AG): as-built генерация + target из §26/AB, contract tests</t>
+          <t>SLO objectives и измерение</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2629,7 +2629,7 @@
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>OpenAPI/event schemas версионированы, examples и deprecation policy; contract tests зелёные [command: `python3 scripts/ci/roadmap-governance-guard.py`]; одна canonical opaque идентификация на версию API; alias {id} с deprecation date [behavioral: `tests/behavioral/test_rm_tech_220.py`]</t>
+          <t>каждое число ТЗ имеет formula/window/owner/metric либо `not measurable` [artifact: `docs/product/slo-objectives.yaml`]</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2639,14 +2639,14 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/api/openapi-as-built-v1.json (113 paths/128 ops/149 схем), target docs/architecture/api/openapi-target-v2.6.md, envelope docs/architecture/events/event-envelope-v1.schema.json; contract tests и версионирование - после старта задачи; задача planned до Gate-S (OD-043).</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288 RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/slo-objectives.yaml - 11 объектов, каждое число §8 с formula/window/owner/status; пороги OD-011/OD-025 open. Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-221</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2661,16 +2661,16 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Разделение User/Device/analytics/emergency API; device client не достигает admin</t>
+          <t>OpenAPI + event/manifest JSON Schema (AG): as-built генерация + target из §26/AB, contract tests</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>device JWT → admin endpoint = 403 на всех admin-роутах [behavioral: `tests/test_phase3_protected_identity.py`]</t>
+          <t>OpenAPI/event schemas версионированы, examples и deprecation policy; contract tests зелёные [command: `python3 scripts/ci/roadmap-governance-guard.py`]; одна canonical opaque идентификация на версию API; alias {id} с deprecation date [behavioral: `tests/behavioral/test_rm_tech_220.py`]</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2695,14 +2695,14 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-002; SC: SC-API-002; DEC: -. Evidence: tests/test_phase3_protected_identity.py; новый negative. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/api/openapi-as-built-v1.json (113 paths/128 ops/149 схем), target docs/architecture/api/openapi-target-v2.6.md, envelope docs/architecture/events/event-envelope-v1.schema.json; contract tests и версионирование - после старта задачи; задача planned до Gate-S (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-222</t>
+          <t>RM-TECH-221</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Канонический POST /api/v1/pop/batch, legacy /device/pop/batch как alias с deprecation</t>
+          <t>Разделение User/Device/analytics/emergency API; device client не достигает admin</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>ответы канонического и legacy идентичны; deprecation header; batch&gt;500 → 422; чужой device_id отклонён [behavioral: `tests/test_contract_pop.py`]</t>
+          <t>device JWT → admin endpoint = 403 на всех admin-роутах [behavioral: `tests/test_phase3_protected_identity.py`]</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2751,14 +2751,14 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-003, REQ-POP-003; SC: SC-API-003, SC-POP-003; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_edge002fu_real_endpoint.py. Риск регрессии: средний: runtime/плеер использует legacy path.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-002; SC: SC-API-002; DEC: -. Evidence: tests/test_phase3_protected_identity.py; новый negative. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-223</t>
+          <t>RM-TECH-222</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Manifest field contract и ACK-состояния runtime (opaque media_ref, no MinIO keys)</t>
+          <t>Канонический POST /api/v1/pop/batch, legacy /device/pop/batch как alias с deprecation</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2794,14 +2794,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>все обязательные поля §25 REQ-MAN-004 в schema; внутренний object key не раскрыт; 6 ACK states принимаются [behavioral: `tests/test_contract_manifest.py`]</t>
+          <t>ответы канонического и legacy идентичны; deprecation header; batch&gt;500 → 422; чужой device_id отклонён [behavioral: `tests/test_contract_pop.py`]</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2811,14 +2807,14 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-MAN-004; SC: SC-MAN-001; DEC: -. Evidence: tests/test_contract_manifest.py; tests/behavioral/test_edge002_manifest_delivery.py. Риск регрессии: высокий: меняет device-facing контракт — owner gate device_contract.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-003, REQ-POP-003; SC: SC-API-003, SC-POP-003; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_edge002fu_real_endpoint.py. Риск регрессии: средний: runtime/плеер использует legacy path.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-223</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2833,7 +2829,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat contract POST /api/v1/device/heartbeat: дедуп, scope, clock drift, freshness thresholds</t>
+          <t>Manifest field contract и ACK-состояния runtime (opaque media_ref, no MinIO keys)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2861,7 +2857,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>валидный/повтор/чужой scope/просроченный heartbeat дают ожидаемые результаты; legacy alias с той же семантикой [behavioral: `tests/behavioral/test_edge004_heartbeat.py`]</t>
+          <t>все обязательные поля §25 REQ-MAN-004 в schema; внутренний object key не раскрыт; 6 ACK states принимаются [behavioral: `tests/test_contract_manifest.py`]</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2871,14 +2867,14 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-009; SC: SC-OPS-002; DEC: -. Evidence: tests/behavioral/test_edge004_heartbeat.py. Риск регрессии: высокий: device-facing.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-MAN-004; SC: SC-MAN-001; DEC: -. Evidence: tests/test_contract_manifest.py; tests/behavioral/test_edge002_manifest_delivery.py. Риск регрессии: высокий: меняет device-facing контракт — owner gate device_contract.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2893,16 +2889,16 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>PoP duplicate semantics по OD-019: 200 + per-event duplicate/409, amendment ADR-017</t>
+          <t>Heartbeat contract POST /api/v1/device/heartbeat: дедуп, scope, clock drift, freshness thresholds</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-222</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -2914,10 +2910,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>ADR-017 amendment принят; behavioral: повтор batch → per-event duplicate, summary не удвоен, порядок хронологический [behavioral: `tests/behavioral/test_edge003_pop_ingestion.py`]</t>
+          <t>валидный/повтор/чужой scope/просроченный heartbeat дают ожидаемые результаты; legacy alias с той же семантикой [behavioral: `tests/behavioral/test_edge004_heartbeat.py`]</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-002; SC: SC-POP-002; DEC: DEC-024. Evidence: tests/behavioral/test_edge003_pop_ingestion.py; ADR-017 amendment. Риск регрессии: низкий: закрепляет текущее поведение.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-009; SC: SC-OPS-002; DEC: -. Evidence: tests/behavioral/test_edge004_heartbeat.py. Риск регрессии: высокий: device-facing.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-226</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Proof model: pop_mode error/not_applied — schema/runtime migration из compatibility projection</t>
+          <t>PoP duplicate semantics по OD-019: 200 + per-event duplicate/409, amendment ADR-017</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-222</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
@@ -2970,14 +2970,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>ProofMode содержит 9 значений; отчёт не смешивает playback/apply/delivery/error [behavioral: `tests/behavioral/test_pop_schema.py`]</t>
+          <t>ADR-017 amendment принят; behavioral: повтор batch → per-event duplicate, summary не удвоен, порядок хронологический [behavioral: `tests/behavioral/test_edge003_pop_ingestion.py`]</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2987,14 +2983,14 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-001; SC: SC-POP-001; DEC: -. Evidence: tests/behavioral/test_pop_schema.py; migration. Риск регрессии: средний: enum migration + отчёты.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-002; SC: SC-POP-002; DEC: DEC-024. Evidence: tests/behavioral/test_edge003_pop_ingestion.py; ADR-017 amendment. Риск регрессии: низкий: закрепляет текущее поведение.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-227</t>
+          <t>RM-TECH-226</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3009,7 +3005,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Валидация proof_event_v1: playback_result/failure_reason, clock-drift quarantine, no internal IDs/PII</t>
+          <t>Proof model: pop_mode error/not_applied — schema/runtime migration из compatibility projection</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3030,10 +3026,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>недопустимый playback_result/внутренний ID/сдвиг часов → 422 или quarantine; SHA/signature проверены [behavioral: `tests/test_contract_pop.py`]</t>
+          <t>ProofMode содержит 9 значений; отчёт не смешивает playback/apply/delivery/error [behavioral: `tests/behavioral/test_pop_schema.py`]</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3043,14 +3043,14 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-004; SC: SC-POP-004; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_pop_schema.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-001; SC: SC-POP-001; DEC: -. Evidence: tests/behavioral/test_pop_schema.py; migration. Риск регрессии: средний: enum migration + отчёты.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-228</t>
+          <t>RM-TECH-227</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3065,16 +3065,16 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Окно совместимости device/API/manifest: heartbeat объявляет версии, сервер выбирает представление</t>
+          <t>Валидация proof_event_v1: playback_result/failure_reason, clock-drift quarantine, no internal IDs/PII</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>совместимая версия выбрана по объявленным capabilities; breaking change без staged rollout отклонён contract-тестом [behavioral: `tests/test_version_identity.py`]</t>
+          <t>недопустимый playback_result/внутренний ID/сдвиг часов → 422 или quarantine; SHA/signature проверены [behavioral: `tests/test_contract_pop.py`]</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3099,14 +3099,14 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-003; SC: SC-NFR-003; DEC: -. Evidence: tests/test_version_identity.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-004; SC: SC-POP-004; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_pop_schema.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-228</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3116,21 +3116,21 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>ERD + data dictionary + migration plan (AG): инвентарь сущностей §15, retailer_id NOT NULL + двухуровневый RLS</t>
+          <t>Окно совместимости device/API/manifest: heartbeat объявляет версии, сервер выбирает представление</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>as-built ERD из моделей; каждая группа §15 присутствует или имеет migration task; tenant-таблицы с retailer_id+FK+RLS [artifact: `tests/behavioral/test_adr018_multitenancy_rls.py`]; behavioral RLS proof под ролью приложения NOBYPASSRLS [behavioral: `tests/behavioral/test_adr018_multitenancy_rls.py`]</t>
+          <t>совместимая версия выбрана по объявленным capabilities; breaking change без staged rollout отклонён contract-тестом [behavioral: `tests/test_version_identity.py`]</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3155,14 +3155,14 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/erd/data-dictionary-as-built.md (62 таблицы, 38 RLS) и кандидат docs/architecture/erd/migration-plan-v2.6.md (§13 → present/missing → задачи); PII/retention колонки - RM-TECH-253/RM-OPS-005. Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-003; SC: SC-NFR-003; DEC: -. Evidence: tests/test_version_identity.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-230</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Channel Adapter contract (design-only до второго канала): versioned task, receipt, proof/ack, error, health, mock mode</t>
+          <t>ERD + data dictionary + migration plan (AG): инвентарь сущностей §15, retailer_id NOT NULL + двухуровневый RLS</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3201,7 +3201,7 @@
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>contract spec + JSON Schema без реализации adapter/mock (ADR-019) [artifact: `docs/architecture contract`]</t>
+          <t>as-built ERD из моделей; каждая группа §15 присутствует или имеет migration task; tenant-таблицы с retailer_id+FK+RLS [artifact: `tests/behavioral/test_adr018_multitenancy_rls.py`]; behavioral RLS proof под ролью приложения NOBYPASSRLS [behavioral: `tests/behavioral/test_adr018_multitenancy_rls.py`]</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3211,14 +3211,14 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-006; SC: SC-ORCH-005; DEC: -. Evidence: docs/architecture contract; schema. Риск регрессии: низкий: только документ.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/erd/data-dictionary-as-built.md (62 таблицы, 38 RLS) и кандидат docs/architecture/erd/migration-plan-v2.6.md (§13 → present/missing → задачи); PII/retention колонки - RM-TECH-253/RM-OPS-005. Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-231</t>
+          <t>RM-TECH-230</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3233,16 +3233,16 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>channel-capability-matrix.yaml (AG) для первого канала KSO: channel/surface/rendition/proof/SLA/vendor constraints</t>
+          <t>Channel Adapter contract (design-only до второго канала): versioned task, receipt, proof/ack, error, health, mock mode</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-230</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -3254,14 +3254,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>матрица покрывает KSO channel/surface/rendition/proof/SLA/vendor constraints; каждая строка ссылается на REQ-CHAN-*/REQ-MAN-*/REQ-POP-* [artifact: `docs/product/channel-capability-matrix.yaml`]; артефакт принят владельцем как часть handoff-пакета AG [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>contract spec + JSON Schema без реализации adapter/mock (ADR-019) [artifact: `docs/architecture contract`]</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -3271,14 +3267,14 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-012 (предложение 2026-08-31): AG требует channel-capability-matrix до старта разработки, а RM-TECH-261 держит матрицу за решением OD-021 (второй канал). Первый канал KSO описывается без OD-021; RM-TECH-261 расширяет матрицу вторым каналом. REQ: REQ-CHAN-001, REQ-CHAN-002, REQ-CHAN-003; SC: SC-CHAN-002; DEC: DEC-001 (расширение). Evidence: артефакт; ACCEPT владельца. Риск регрессии: нет (документ). Утверждена OD-042 (2026-08-31). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/channel-capability-matrix.yaml (KSO + declared каналы §7); приёмка - внутри задачи после Gate-S.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-006; SC: SC-ORCH-005; DEC: -. Evidence: docs/architecture contract; schema. Риск регрессии: низкий: только документ.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-253</t>
+          <t>RM-TECH-231</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3293,12 +3289,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Data protection: data classes, lawful purpose, минимизация PII, residency; retention по OD-009</t>
+          <t>channel-capability-matrix.yaml (AG) для первого канала KSO: channel/surface/rendition/proof/SLA/vendor constraints</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-230</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
@@ -3314,10 +3310,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>реестр data classes для всех сущностей; новая PII-сущность без класса — красный design-gate [artifact: `docs/architecture data classes`]</t>
+          <t>матрица покрывает KSO channel/surface/rendition/proof/SLA/vendor constraints; каждая строка ссылается на REQ-CHAN-*/REQ-MAN-*/REQ-POP-* [artifact: `docs/product/channel-capability-matrix.yaml`]; артефакт принят владельцем как часть handoff-пакета AG [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3327,14 +3327,14 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: docs/architecture data classes. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено CORE → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
+          <t>RM-GOV-012 (предложение 2026-08-31): AG требует channel-capability-matrix до старта разработки, а RM-TECH-261 держит матрицу за решением OD-021 (второй канал). Первый канал KSO описывается без OD-021; RM-TECH-261 расширяет матрицу вторым каналом. REQ: REQ-CHAN-001, REQ-CHAN-002, REQ-CHAN-003; SC: SC-CHAN-002; DEC: DEC-001 (расширение). Evidence: артефакт; ACCEPT владельца. Риск регрессии: нет (документ). Утверждена OD-042 (2026-08-31). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/channel-capability-matrix.yaml (KSO + declared каналы §7); приёмка - внутри задачи после Gate-S.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-288</t>
+          <t>RM-TECH-253</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3344,21 +3344,21 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>nfr-slo.yaml + load-profiles.yaml (AG): method, percentile, error budget, generator, CI evidence</t>
+          <t>Data protection: data classes, lawful purpose, минимизация PII, residency; retention по OD-009</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>каждый SLO имеет window/denominator/exclusions; load generator и прогон в CI/стенде [artifact: `nfr-slo.yaml`]</t>
+          <t>реестр data classes для всех сущностей; новая PII-сущность без класса — красный design-gate [artifact: `docs/architecture data classes`]</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3383,14 +3383,14 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки):ы docs/product/nfr-slo.yaml и docs/product/load-profiles.yaml (7 профилей); load generator отсутствует (new). Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: docs/architecture data classes. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено CORE → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-011</t>
+          <t>RM-TECH-288</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3405,16 +3405,16 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>role-scope-matrix.yaml + portal-route-matrix.yaml + journeys/ (AG) из seed/pg_policies/registry</t>
+          <t>nfr-slo.yaml + load-profiles.yaml (AG): method, percentile, error budget, generator, CI evidence</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004, RM-STAB-006</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>матрицы генерируются и сверяются guard; deny-cases покрыты behavioral [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+          <t>каждый SLO имеет window/denominator/exclusions; load generator и прогон в CI/стенде [artifact: `nfr-slo.yaml`]</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3439,19 +3439,19 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено U → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/product/role-scope-matrix.yaml (5 seeded ролей × 30 permissions, Q2 target 7 ролей, 38 RLS-таблиц, deny-cases), docs/product/portal-route-matrix.yaml (admin 16 + advertiser 9 маршрутов), docs/product/journeys/journeys.yaml (79 journeys, нормативный формат); generated-сверка guard - после старта задачи; задача planned до Gate-S (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки):ы docs/product/nfr-slo.yaml и docs/product/load-profiles.yaml (7 профилей); load generator отсутствует (new). Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-001</t>
+          <t>RM-UX-011</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3461,16 +3461,16 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Записать managed-first scope</t>
+          <t>role-scope-matrix.yaml + portal-route-matrix.yaml + journeys/ (AG) из seed/pg_policies/registry</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-STAB-004, RM-STAB-006</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>roadmap явно исключает `self.campaign_create` из ближайшего control-plane pilot [artifact: `docs/product/roadmap.yaml (pilot scope)`]</t>
+          <t>матрицы генерируются и сверяются guard; deny-cases покрыты behavioral [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -3495,14 +3495,14 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): ссылки OD-005/DEC-011, REQ-SCOPE-001</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено U → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/product/role-scope-matrix.yaml (5 seeded ролей × 30 permissions, Q2 target 7 ролей, 38 RLS-таблиц, deny-cases), docs/product/portal-route-matrix.yaml (admin 16 + advertiser 9 маршрутов), docs/product/journeys/journeys.yaml (79 journeys, нормативный формат); generated-сверка guard - после старта задачи; задача planned до Gate-S (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201</t>
+          <t>RM-BIZ-001</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Таксономия причин недопоказа</t>
+          <t>Записать managed-first scope</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>8 категорий ТЗ, source/report/history contract и owner-approved artifact [artifact: `docs/product/underdelivery-reason-taxonomy.yaml`]</t>
+          <t>roadmap явно исключает `self.campaign_create` из ближайшего control-plane pilot [artifact: `docs/product/roadmap.yaml (pilot scope)`]</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -3551,14 +3551,14 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): ссылки OD-005/DEC-011, REQ-SCOPE-001</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202</t>
+          <t>RM-TECH-201</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3568,21 +3568,21 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Вытеснение и объяснимые приоритеты</t>
+          <t>Таксономия причин недопоказа</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>versioned rules [behavioral: `tests/behavioral/test_campaign_preemption.py`]</t>
+          <t>8 категорий ТЗ, source/report/history contract и owner-approved artifact [artifact: `docs/product/underdelivery-reason-taxonomy.yaml`]</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3607,14 +3607,14 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-007 и порядок приоритета §12; исключение §3.1 (OD-018) — единственная точка изменения engine → RM-TECH-285 зависит от неё</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-203</t>
+          <t>RM-TECH-202</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3629,16 +3629,16 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Overbooking policy</t>
+          <t>Вытеснение и объяснимые приоритеты</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202</t>
+          <t>RM-TECH-201</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>default deny [behavioral: `tests/behavioral/test_inventory_overbooking_policy.py`]</t>
+          <t>versioned rules [behavioral: `tests/behavioral/test_campaign_preemption.py`]</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3663,14 +3663,14 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-007 и порядок приоритета §12; исключение §3.1 (OD-018) — единственная точка изменения engine → RM-TECH-285 зависит от неё</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-204</t>
+          <t>RM-TECH-203</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3685,16 +3685,16 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Creative QA без неутверждённого HTML5</t>
+          <t>Overbooking policy</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-202</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>metadata/antivirus/executable deny и immutable QA result [behavioral: `tests/behavioral/test_creative_qa.py`]</t>
+          <t>default deny [behavioral: `tests/behavioral/test_inventory_overbooking_policy.py`]</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-206</t>
+          <t>RM-TECH-204</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>License renewal/grant boundary</t>
+          <t>Creative QA без неутверждённого HTML5</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>атомарная семантика §1.6 [behavioral: `tests/behavioral/test_license_renewal_boundary.py`]</t>
+          <t>metadata/antivirus/executable deny и immutable QA result [behavioral: `tests/behavioral/test_creative_qa.py`]</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>RM-TECH-206</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3797,16 +3797,16 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Универсальная иерархия носителей: migration + seed network/branch/cluster/store/store_group/channel/device/surface</t>
+          <t>License renewal/grant boundary</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -3818,14 +3818,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>все уровни существуют с FK и RLS; seed заполняет иерархию; чужой scope не видит [behavioral: `tests/behavioral/test_scope_rls.py`]</t>
+          <t>атомарная семантика §1.6 [behavioral: `tests/behavioral/test_license_renewal_boundary.py`]</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3835,14 +3831,14 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-001; SC: SC-DATA-001; DEC: -. Evidence: migration; tests/behavioral/test_scope_rls.py. Риск регрессии: высокий: схема ядра.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-241</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3857,16 +3853,16 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Target resolution boundary: broad target → display_surface_id, запрет physical_device_id как target</t>
+          <t>Универсальная иерархия носителей: migration + seed network/branch/cluster/store/store_group/channel/device/surface</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -3878,10 +3874,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>планирование разрешает target до surface; physical_device_id в target отклоняется [behavioral: `tests/test_s089_inventory_simulation.py`]</t>
+          <t>все уровни существуют с FK и RLS; seed заполняет иерархию; чужой scope не видит [behavioral: `tests/behavioral/test_scope_rls.py`]</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-003; SC: SC-ARCH-002; DEC: -. Evidence: tests/test_s089_inventory_simulation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-001; SC: SC-DATA-001; DEC: -. Evidence: migration; tests/behavioral/test_scope_rls.py. Риск регрессии: высокий: схема ядра.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-242</t>
+          <t>RM-TECH-241</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Outbox для любой OLTP-записи с domain event; revocation/refresh manifest при pause/archive/expiry</t>
+          <t>Target resolution boundary: broad target → display_surface_id, запрет physical_device_id как target</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>каждая доменная мутация создаёт outbox event в той же транзакции; pause/archive порождают revocation [behavioral: `tests/behavioral/test_outbox.py`]</t>
+          <t>планирование разрешает target до surface; physical_device_id в target отклоняется [behavioral: `tests/test_s089_inventory_simulation.py`]</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3947,14 +3947,14 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-003; SC: SC-ORCH-002; DEC: -. Evidence: tests/behavioral/test_outbox.py. Риск регрессии: средний: транзакционные границы всех сервисов.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-003; SC: SC-ARCH-002; DEC: -. Evidence: tests/test_s089_inventory_simulation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-243</t>
+          <t>RM-TECH-242</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3969,16 +3969,16 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Outbox relay: lease/publishing, Nats-Msg-Id, 7 попыток → dead_letter, partition order, DLQ policy, no PII</t>
+          <t>Outbox для любой OLTP-записи с domain event; revocation/refresh manifest при pause/archive/expiry</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-242</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>7 отказов брокера → dead_letter с operator action; ack → published; replay идемпотентен [behavioral: `tests/behavioral/test_outbox_relay.py`]; NATS recovery integration зелёный [command: `tests/behavioral/test_outbox_relay.py`]</t>
+          <t>каждая доменная мутация создаёт outbox event в той же транзакции; pause/archive порождают revocation [behavioral: `tests/behavioral/test_outbox.py`]</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -4003,14 +4003,14 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-004; SC: SC-ORCH-003; DEC: DEC-004. Evidence: tests/behavioral/test_outbox_relay.py; tests/integration/test_nats_recovery.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-003; SC: SC-ORCH-002; DEC: -. Evidence: tests/behavioral/test_outbox.py. Риск регрессии: средний: транзакционные границы всех сервисов.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-244</t>
+          <t>RM-TECH-243</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4025,16 +4025,16 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Adapter task lifecycle через persisted queue (event-driven массовая публикация)</t>
+          <t>Outbox relay: lease/publishing, Nats-Msg-Id, 7 попыток → dead_letter, partition order, DLQ policy, no PII</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-243</t>
+          <t>RM-TECH-242</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>активация на 1000 устройств не ждёт устройств; задачи агрегируют статусы [behavioral: `tests/behavioral/test_delivery_foundation.py`]</t>
+          <t>7 отказов брокера → dead_letter с operator action; ack → published; replay идемпотентен [behavioral: `tests/behavioral/test_outbox_relay.py`]; NATS recovery integration зелёный [command: `tests/behavioral/test_outbox_relay.py`]</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -4059,14 +4059,14 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-002; SC: SC-ORCH-006; DEC: DEC-004. Evidence: tests/behavioral/test_delivery_foundation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-004; SC: SC-ORCH-003; DEC: DEC-004. Evidence: tests/behavioral/test_outbox_relay.py; tests/integration/test_nats_recovery.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-TECH-244</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4081,16 +4081,16 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Campaign lifecycle по ADR-015/OD-036: scheduled, resume, revise, archive; единый guard и audit</t>
+          <t>Adapter task lifecycle через persisted queue (event-driven массовая публикация)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-TECH-243</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -4102,14 +4102,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>_CAMPAIGN_TRANSITIONS = ADR-015; каждый переход через guard с audit; возврат в draft создаёт revision [behavioral: `tests/behavioral/test_campaign_domain.py`]; campaign.* smokes зелёные после изменения [ui_smoke: `tests/ui-smoke/test_rm_tech_245.py`]</t>
+          <t>активация на 1000 устройств не ждёт устройств; задачи агрегируют статусы [behavioral: `tests/behavioral/test_delivery_foundation.py`]</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4119,14 +4115,14 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-010; SC: -; DEC: DEC-025. Evidence: tests/behavioral/test_campaign_domain.py; tests/ui-smoke/test_uismoke__campaign__*.py. Риск регрессии: высокий: меняет runtime enum кампании и UI.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-002; SC: SC-ORCH-006; DEC: DEC-004. Evidence: tests/behavioral/test_delivery_foundation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-246</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4141,7 +4137,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Commerce order: отмена по OD-020 (draft→cancelled, confirmed — reversal), payment projection отдельно</t>
+          <t>Campaign lifecycle по ADR-015/OD-036: scheduled, resume, revise, archive; единый guard и audit</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -4162,10 +4158,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>_ORDER_TRANSITIONS: draft→cancelled разрешён, confirmed→cancelled запрещён, reversal с audit [behavioral: `tests/test_commerce_a2.py`]</t>
+          <t>_CAMPAIGN_TRANSITIONS = ADR-015; каждый переход через guard с audit; возврат в draft создаёт revision [behavioral: `tests/behavioral/test_campaign_domain.py`]; campaign.* smokes зелёные после изменения [ui_smoke: `tests/ui-smoke/test_rm_tech_245.py`]</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -4175,14 +4175,14 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-014; SC: -; DEC: DEC-017, DEC-026. Evidence: tests/test_commerce_a2.py; tests/behavioral/test_commerce_rls.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-010; SC: -; DEC: DEC-025. Evidence: tests/behavioral/test_campaign_domain.py; tests/ui-smoke/test_uismoke__campaign__*.py. Риск регрессии: высокий: меняет runtime enum кампании и UI.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-247</t>
+          <t>RM-TECH-246</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4197,16 +4197,16 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Approval policy: required roles/scope/порядок/timeout per campaign/placement/creative</t>
+          <t>Commerce order: отмена по OD-020 (draft→cancelled, confirmed — reversal), payment projection отдельно</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>политика версионирована; submit/approve соблюдают порядок и timeout; negative для чужого scope [behavioral: `tests/behavioral/test_campaign_approval.py`]</t>
+          <t>_ORDER_TRANSITIONS: draft→cancelled разрешён, confirmed→cancelled запрещён, reversal с audit [behavioral: `tests/test_commerce_a2.py`]</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -4231,14 +4231,14 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-003; SC: -; DEC: -. Evidence: tests/behavioral/test_campaign_approval.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-014; SC: -; DEC: DEC-017, DEC-026. Evidence: tests/test_commerce_a2.py; tests/behavioral/test_commerce_rls.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-248</t>
+          <t>RM-TECH-247</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Flight/placement windows: versioned start_at/end_at UTC, проверка при simulation/manifest/runtime</t>
+          <t>Approval policy: required roles/scope/порядок/timeout per campaign/placement/creative</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>показ вне окна запрещён на трёх уровнях; DST/праздники/closed stores — версионированные правила [behavioral: `tests/test_s063_pop_timezone.py`]</t>
+          <t>политика версионирована; submit/approve соблюдают порядок и timeout; negative для чужого scope [behavioral: `tests/behavioral/test_campaign_approval.py`]</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -4287,14 +4287,14 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-005, REQ-NFR-002; SC: SC-NFR-002; DEC: -. Evidence: tests/test_s063_pop_timezone.py; новый behavioral. Риск регрессии: высокий: расписание доставки.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-003; SC: -; DEC: -. Evidence: tests/behavioral/test_campaign_approval.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-249</t>
+          <t>RM-TECH-248</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4309,16 +4309,16 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Manifest eligibility: approved status + валидный flight/contract + resolved target + readiness</t>
+          <t>Flight/placement windows: versioned start_at/end_at UTC, проверка при simulation/manifest/runtime</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-248</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>неэлигибельная кампания не попадает в manifest; причина объяснима [behavioral: `tests/behavioral/test_delivery_generation.py`]</t>
+          <t>показ вне окна запрещён на трёх уровнях; DST/праздники/closed stores — версионированные правила [behavioral: `tests/test_s063_pop_timezone.py`]</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -4343,14 +4343,14 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-006; SC: -; DEC: -. Evidence: tests/behavioral/test_delivery_generation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-005, REQ-NFR-002; SC: SC-NFR-002; DEC: -. Evidence: tests/test_s063_pop_timezone.py; новый behavioral. Риск регрессии: высокий: расписание доставки.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-250</t>
+          <t>RM-TECH-249</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4365,16 +4365,16 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Creative/rendition state machine и immutable media history (uploaded→scanning→qa_failed/approved→superseded→retained)</t>
+          <t>Manifest eligibility: approved status + валидный flight/contract + resolved target + readiness</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-204</t>
+          <t>RM-TECH-248</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -4386,14 +4386,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>каждая версия хранит uploader/SHA-256/QA-решение/связь; закрытый отчёт воспроизводим после logical delete [behavioral: `tests/behavioral/test_creative_assets.py`]</t>
+          <t>неэлигибельная кампания не попадает в manifest; причина объяснима [behavioral: `tests/behavioral/test_delivery_generation.py`]</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -4403,14 +4399,14 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CONT-002; SC: SC-DATA-002; DEC: -. Evidence: tests/behavioral/test_creative_assets.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-006; SC: -; DEC: -. Evidence: tests/behavioral/test_delivery_generation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-251</t>
+          <t>RM-TECH-250</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4425,16 +4421,16 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Data ownership/lineage: immutable versioning и diff campaign/placement/playlist, словарь владельцев</t>
+          <t>Creative/rendition state machine и immutable media history (uploaded→scanning→qa_failed/approved→superseded→retained)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-204</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -4446,10 +4442,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>сохранение создаёт версию с diff и actor; предыдущая неизменяема [behavioral: `tests/behavioral/test_rm_tech_251.py`]</t>
+          <t>каждая версия хранит uploader/SHA-256/QA-решение/связь; закрытый отчёт воспроизводим после logical delete [behavioral: `tests/behavioral/test_creative_assets.py`]</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -4459,14 +4459,14 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-001; SC: SC-DATA-004; DEC: DEC-007. Evidence: новый behavioral. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CONT-002; SC: SC-DATA-002; DEC: -. Evidence: tests/behavioral/test_creative_assets.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-252</t>
+          <t>RM-TECH-251</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4481,16 +4481,16 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Identity: AD/LDAP или SSO для internal staff, MFA до production (OD-008)</t>
+          <t>Data ownership/lineage: immutable versioning и diff campaign/placement/playlist, словарь владельцев</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -4502,14 +4502,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>protected_boundary</t>
-        </is>
-      </c>
+      <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>логин через IdP; production-профиль без MFA отклоняет; TLS-профиль зафиксирован [behavioral: `tests/test_phase3_auth_api.py`]</t>
+          <t>сохранение создаёт версию с diff и actor; предыдущая неизменяема [behavioral: `tests/behavioral/test_rm_tech_251.py`]</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -4519,14 +4515,14 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-001; SC: SC-SEC-008; DEC: -. Evidence: tests/test_phase3_auth_api.py; tests/behavioral/test_auth_dual_e2e.py. Риск регрессии: высокий: вход всех пользователей.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-001; SC: SC-DATA-004; DEC: DEC-007. Evidence: новый behavioral. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-254</t>
+          <t>RM-TECH-252</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4541,16 +4537,16 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Emergency state machine: requested→authorized→dispatching→applied→resuming→closed, MFA+reason, приоритетный канал</t>
+          <t>Identity: AD/LDAP или SSO для internal staff, MFA до production (OD-008)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -4562,10 +4558,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>protected_boundary</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>emergency с причиной; per-target result; audit actor/reason/affected; resume возвращает штатный manifest [behavioral: `tests/test_phase3_emergency_api.py`]; emergency.* smokes зелёные [ui_smoke: `tests/ui-smoke/test_uismoke__emergency__activate.py`]</t>
+          <t>логин через IdP; production-профиль без MFA отклоняет; TLS-профиль зафиксирован [behavioral: `tests/test_phase3_auth_api.py`]</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -4575,14 +4575,14 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-007; SC: SC-OPS-003; DEC: -. Evidence: tests/test_phase3_emergency_api.py; tests/ui-smoke/test_uismoke__emergency__activate.py. Риск регрессии: высокий: аварийный контур.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-001; SC: SC-SEC-008; DEC: -. Evidence: tests/test_phase3_auth_api.py; tests/behavioral/test_auth_dual_e2e.py. Риск регрессии: высокий: вход всех пользователей.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-255</t>
+          <t>RM-TECH-254</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4597,16 +4597,16 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Device health/commands: пороги статусов по профилю, per-device view, команды с подтверждением</t>
+          <t>Emergency state machine: requested→authorized→dispatching→applied→resuming→closed, MFA+reason, приоритетный канал</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>online→degraded→offline по порогам; команда доставлена и подтверждена [behavioral: `tests/behavioral/test_rm_tech_255.py`]; device.health_view smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__device__health_view.py`]</t>
+          <t>emergency с причиной; per-target result; audit actor/reason/affected; resume возвращает штатный manifest [behavioral: `tests/test_phase3_emergency_api.py`]; emergency.* smokes зелёные [ui_smoke: `tests/ui-smoke/test_uismoke__emergency__activate.py`]</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -4631,19 +4631,19 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-001; SC: SC-OPS-006; DEC: -. Evidence: tests/ui-smoke/test_uismoke__device__health_view.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-007; SC: SC-OPS-003; DEC: -. Evidence: tests/test_phase3_emergency_api.py; tests/ui-smoke/test_uismoke__emergency__activate.py. Риск регрессии: высокий: аварийный контур.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-002</t>
+          <t>RM-TECH-255</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4653,16 +4653,16 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>`self.campaign_create` в будущей ветке</t>
+          <t>Device health/commands: пороги статусов по профилю, per-device view, команды с подтверждением</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-001</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -4671,17 +4671,13 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>mini-design, journey, backend/UI/RLS, intended-role smoke, walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__campaign_create.py`]</t>
+          <t>online→degraded→offline по порогам; команда доставлена и подтверждена [behavioral: `tests/behavioral/test_rm_tech_255.py`]; device.health_view smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__device__health_view.py`]</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -4691,14 +4687,14 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2). RM-GOV-009 (OD-037): blocked до OD-013 — полный self-service вне pilot scope (REQ-V26-003, OD-005)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-001; SC: SC-OPS-006; DEC: -. Evidence: tests/ui-smoke/test_uismoke__device__health_view.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001</t>
+          <t>RM-BIZ-002</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4713,16 +4709,16 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Accessibility оставшихся форм + route matrix (A3)</t>
+          <t>`self.campaign_create` в будущей ветке</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-BIZ-001</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -4731,13 +4727,17 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>labels/ARIA/axe/targeted vitest [artifact: `docs/product/ux-route-matrix.yaml`]</t>
+          <t>mini-design, journey, backend/UI/RLS, intended-role smoke, walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__campaign_create.py`]</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -4747,14 +4747,14 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2). RM-GOV-009 (OD-037): blocked до OD-013 — полный self-service вне pilot scope (REQ-V26-003, OD-005)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-002</t>
+          <t>RM-UX-001</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4769,16 +4769,16 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Поиск/сортировка/усечение таблиц (A2)</t>
+          <t>Accessibility оставшихся форм + route matrix (A3)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>server semantics для pagination [ui_smoke: `tests/ui-smoke/test_uismoke__campaign__create.py`]</t>
+          <t>labels/ARIA/axe/targeted vitest [artifact: `docs/product/ux-route-matrix.yaml`]</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-003</t>
+          <t>RM-UX-002</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4825,16 +4825,16 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Responsive-проверка (A4)</t>
+          <t>Поиск/сортировка/усечение таблиц (A2)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-002</t>
+          <t>RM-UX-001</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>все routes из `ux-route-matrix.yaml` проверены на 390px без overflow/crop [artifact: `docs/product/ux-responsive-report.yaml`]</t>
+          <t>server semantics для pagination [ui_smoke: `tests/ui-smoke/test_uismoke__campaign__create.py`]</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-004</t>
+          <t>RM-UX-003</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4881,16 +4881,16 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Согласованность состояний и терминов (A6)</t>
+          <t>Responsive-проверка (A4)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-003</t>
+          <t>RM-UX-002</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>route matrix покрывает empty/loading/error/403/success и locale-key check [artifact: `docs/product/ux-route-matrix.yaml (states coverage)`]</t>
+          <t>все routes из `ux-route-matrix.yaml` проверены на 390px без overflow/crop [artifact: `docs/product/ux-responsive-report.yaml`]</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-005</t>
+          <t>RM-UX-004</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4937,16 +4937,16 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Adoption доказанных primitives малыми slices (A1b)</t>
+          <t>Согласованность состояний и терминов (A6)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-004</t>
+          <t>RM-UX-003</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>каждый slice имеет отдельный diff/test/review [ci_job: `frontend`]</t>
+          <t>route matrix покрывает empty/loading/error/403/success и locale-key check [artifact: `docs/product/ux-route-matrix.yaml (states coverage)`]</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-006</t>
+          <t>RM-UX-005</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4993,16 +4993,16 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Advertiser-web UX audit/fixes (A5)</t>
+          <t>Adoption доказанных primitives малыми slices (A1b)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-005</t>
+          <t>RM-UX-004</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>versioned `docs/product/advertiser-route-matrix.yaml` с точным списком 15 routes [artifact: `docs/product/advertiser-route-matrix.yaml`]</t>
+          <t>каждый slice имеет отдельный diff/test/review [ci_job: `frontend`]</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -5034,7 +5034,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-007</t>
+          <t>RM-UX-006</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -5044,21 +5044,21 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Human operator walkthrough (A7)</t>
+          <t>Advertiser-web UX audit/fixes (A5)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001, RM-UX-002, RM-UX-003, RM-UX-004, RM-UX-005, RM-UX-006</t>
+          <t>RM-UX-005</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>человек проходит exact stand bundle [human: `PROJECT_STATE.md строка `operator walkthrough` (AGENTS.md правило 8); сценарии docs/product/operator-walkthrough-dev.md`]</t>
+          <t>versioned `docs/product/advertiser-route-matrix.yaml` с точным списком 15 routes [artifact: `docs/product/advertiser-route-matrix.yaml`]</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -5083,14 +5083,14 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) ПРИОСТАНОВЛЕНО владельцем 2026-08-31 (OD-041) до выравнивания ТЗ/roadmap/gates и утверждения единого плана реализации; не закрывать, done не ставить.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-008</t>
+          <t>RM-UX-007</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5100,21 +5100,21 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Campaign readiness matrix по каналам (rendition/inventory/conflicts/forecast/PoP mode/SLA) с действием на blocked</t>
+          <t>Human operator walkthrough (A7)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-249, RM-UX-004</t>
+          <t>RM-UX-001, RM-UX-002, RM-UX-003, RM-UX-004, RM-UX-005, RM-UX-006</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>экран согласования показывает матрицу; каждый blocked/warning ведёт к действию [ui_smoke: `tests/ui-smoke/test_rm_ux_008.py`]</t>
+          <t>человек проходит exact stand bundle [human: `PROJECT_STATE.md строка `operator walkthrough` (AGENTS.md правило 8); сценарии docs/product/operator-walkthrough-dev.md`]</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -5139,14 +5139,14 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-004; SC: SC-UX-002; DEC: -. Evidence: новый ui-smoke; vitest. Риск регрессии: средний.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) ПРИОСТАНОВЛЕНО владельцем 2026-08-31 (OD-041) до выравнивания ТЗ/roadmap/gates и утверждения единого плана реализации; не закрывать, done не ставить.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-009</t>
+          <t>RM-UX-008</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -5161,16 +5161,16 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Договор рекламодателя: immutable file versions, server-side SHA-256, legal status (юр. решение)</t>
+          <t>Campaign readiness matrix по каналам (rendition/inventory/conflicts/forecast/PoP mode/SLA) с действием на blocked</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-250</t>
+          <t>RM-TECH-249, RM-UX-004</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>повторная загрузка создаёт новую версию, SHA проверен сервером; старая версия неизменяема [behavioral: `tests/test_advertiser_contracts.py`]; advertiser.contract_crud smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py`]</t>
+          <t>экран согласования показывает матрицу; каждый blocked/warning ведёт к действию [ui_smoke: `tests/ui-smoke/test_rm_ux_008.py`]</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -5195,38 +5195,38 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-017; SC: -; DEC: -. Evidence: tests/test_advertiser_contracts.py; tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-004; SC: SC-UX-002; DEC: -. Evidence: новый ui-smoke; vitest. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207A</t>
+          <t>RM-UX-009</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>KSO environment + player/playlist design</t>
+          <t>Договор рекламодателя: immutable file versions, server-side SHA-256, legal status (юр. решение)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-250</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -5238,14 +5238,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>versioned environment audit, import/contract mini-design и test plan [artifact: `docs/architecture/kso-environment-audit.md`]</t>
+          <t>повторная загрузка создаёт новую версию, SHA проверен сервером; старая версия неизменяема [behavioral: `tests/test_advertiser_contracts.py`]; advertiser.contract_crud smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py`]</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -5255,14 +5251,14 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-STAND-003 feasibility gate явно в acceptance; ADR-019/OD-022</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-017; SC: -; DEC: -. Evidence: tests/test_advertiser_contracts.py; tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-207A</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -5272,21 +5268,21 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>KSO player/playlist/PoP chain</t>
+          <t>KSO environment + player/playlist design</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207A</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -5300,12 +5296,12 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>device_contract</t>
+          <t>scope_decision</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>contract tests и playback→manifest→PoP behavioral proof [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; Playlist entity и state machine §6 ТЗ (draft → validating → valid/invalid → approved → published → superseded/rolled_back); published immutable [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; manifest target lifecycle (generated → signed → queued → delivered → applied/failed/expired) и canonical POST /api/v1/pop/batch [behavioral: `tests/behavioral/test_kso_playback_chain.py`]</t>
+          <t>versioned environment audit, import/contract mini-design и test plan [artifact: `docs/architecture/kso-environment-audit.md`]</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -5315,14 +5311,14 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-STAND-003 feasibility gate явно в acceptance; ADR-019/OD-022</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-208</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5337,16 +5333,16 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Signed licensing Layer 2</t>
+          <t>KSO player/playlist/PoP chain</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-206, RM-TECH-207B, RM-STAB-010</t>
+          <t>RM-TECH-207A</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
@@ -5360,12 +5356,12 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>protected_boundary</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Ed25519 offline verify, kid/rotation/revocation, UI, tamper/rollback [behavioral: `tests/behavioral/test_signed_license_layer2.py`]</t>
+          <t>contract tests и playback→manifest→PoP behavioral proof [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; Playlist entity и state machine §6 ТЗ (draft → validating → valid/invalid → approved → published → superseded/rolled_back); published immutable [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; manifest target lifecycle (generated → signed → queued → delivered → applied/failed/expired) и canonical POST /api/v1/pop/batch [behavioral: `tests/behavioral/test_kso_playback_chain.py`]</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -5382,7 +5378,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-260</t>
+          <t>RM-TECH-208</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -5397,12 +5393,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Runtime cache lifecycle: лимит по профилю, детерминированная очистка, last-known-good</t>
+          <t>Signed licensing Layer 2</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-206, RM-TECH-207B, RM-STAB-010</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
@@ -5420,12 +5416,12 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>device_contract</t>
+          <t>protected_boundary</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>кэш на лимите: очистка по правилу; last-known-good сохранён; просроченная реклама не показывается [behavioral: `tests/behavioral/test_rm_tech_260.py`]</t>
+          <t>Ed25519 offline verify, kid/rotation/revocation, UI, tamper/rollback [behavioral: `tests/behavioral/test_signed_license_layer2.py`]</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -5435,14 +5431,14 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-008; SC: SC-EDGE-002; DEC: -. Evidence: runtime simulator tests. Риск регрессии: средний: плеер.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-261</t>
+          <t>RM-TECH-260</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5452,17 +5448,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Второй канал: решение OD-021 + channel-capability-matrix.yaml (AG); extraction design по ADR-019</t>
+          <t>Runtime cache lifecycle: лимит по профилю, детерминированная очистка, last-known-good</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B, RM-TECH-230</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
@@ -5475,17 +5471,17 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>scope_decision</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>владелец назвал канал и владельца (OD-021); матрица возможностей утверждена [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; extraction design: KSO-вертикаль как первый adapter без поломки контрактов [artifact: `docs/audit/RM-TECH-261-artifact.md (создаётся задачей)`]</t>
+          <t>кэш на лимите: очистка по правилу; last-known-good сохранён; просроченная реклама не показывается [behavioral: `tests/behavioral/test_rm_tech_260.py`]</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -5495,14 +5491,14 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CHAN-001, REQ-ORCH-005; SC: SC-CHAN-002, SC-ORCH-004; DEC: DEC-001, DEC-002. Evidence: OD-021; design doc. Риск регрессии: высокий: рефакторинг KSO-вертикали. blocked до OD-021; Orchestrator/Adapter Layer/mock не создаются раньше (ADR-019/OD-022).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-008; SC: SC-EDGE-002; DEC: -. Evidence: runtime simulator tests. Риск регрессии: средний: плеер.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-262</t>
+          <t>RM-TECH-261</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5512,21 +5508,21 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Dynamic creative binding/rendition safety (V26-008) на одном канале</t>
+          <t>Второй канал: решение OD-021 + channel-capability-matrix.yaml (AG); extraction design по ADR-019</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280, RM-TECH-261</t>
+          <t>RM-TECH-207B, RM-TECH-230</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -5535,13 +5531,17 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>master-confirmed price/promo подставляется при manifest generation; SLA-тест dynamic manifest [behavioral: `tests/behavioral/test_rm_tech_262.py`]</t>
+          <t>владелец назвал канал и владельца (OD-021); матрица возможностей утверждена [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; extraction design: KSO-вертикаль как первый adapter без поломки контрактов [artifact: `docs/audit/RM-TECH-261-artifact.md (создаётся задачей)`]</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -5551,14 +5551,14 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-008; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. ложная ESL-посылка снимается prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CHAN-001, REQ-ORCH-005; SC: SC-CHAN-002, SC-ORCH-004; DEC: DEC-001, DEC-002. Evidence: OD-021; design doc. Риск регрессии: высокий: рефакторинг KSO-вертикали. blocked до OD-021; Orchestrator/Adapter Layer/mock не создаются раньше (ADR-019/OD-022).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-263</t>
+          <t>RM-TECH-262</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5573,16 +5573,16 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Field mobile operations: scoped mobile web для сотрудника магазина (устройства, фото, инциденты)</t>
+          <t>Dynamic creative binding/rendition safety (V26-008) на одном канале</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-210, RM-TECH-255</t>
+          <t>RM-TECH-280, RM-TECH-261</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>journey field_ops.device_confirm под ролью магазина с RLS; negative чужой магазин [ui_smoke: `tests/ui-smoke/test_rm_tech_263.py`]</t>
+          <t>master-confirmed price/promo подставляется при manifest generation; SLA-тест dynamic manifest [behavioral: `tests/behavioral/test_rm_tech_262.py`]</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -5607,14 +5607,14 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-009; SC: -; DEC: -. Evidence: new ui-smoke. Риск регрессии: средний. prerequisite RM-TECH-210 (RLS device) - planned по зависимости; feature field_ops.device_confirm blocked до задачи (RM-GOV-012 выравнивание: blocked = решение владельца/внешний факт, а не зависимость).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-008; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. ложная ESL-посылка снимается prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-264</t>
+          <t>RM-TECH-263</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5629,16 +5629,16 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>ESL/price-checker: интеграция только через approved price/SKU master (INT-002)</t>
+          <t>Field mobile operations: scoped mobile web для сотрудника магазина (устройства, фото, инциденты)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-210, RM-TECH-255</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>price-related данные приходят из master или проходят reconciliation; расхождение блокирует показ [behavioral: `tests/behavioral/test_rm_tech_264.py`]</t>
+          <t>journey field_ops.device_confirm под ролью магазина с RLS; negative чужой магазин [ui_smoke: `tests/ui-smoke/test_rm_tech_263.py`]</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -5663,38 +5663,38 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. OD-023 approved 2026-08-31 - planned после RM-TECH-280.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-009; SC: -; DEC: -. Evidence: new ui-smoke. Риск регрессии: средний. prerequisite RM-TECH-210 (RLS device) - planned по зависимости; feature field_ops.device_confirm blocked до задачи (RM-GOV-012 выравнивание: blocked = решение владельца/внешний факт, а не зависимость).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>RM-TECH-264</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>ESL/price-checker: интеграция только через approved price/SKU master (INT-002)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>RM-TECH-280</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>design</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Prerequisite: master-data adapter цен/SKU (контракт, owner OD-023, reconciliation)</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>RM-TECH-229</t>
-        </is>
-      </c>
       <c r="F92" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
@@ -5706,14 +5706,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>владелец master-данных назначен (OD-023 approved); contract + reconciliation design утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; adapter в mock/test mode проходит contract tests [behavioral: `tests/behavioral/test_rm_tech_280.py`]</t>
+          <t>price-related данные приходят из master или проходят reconciliation; расхождение блокирует показ [behavioral: `tests/behavioral/test_rm_tech_264.py`]</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -5723,34 +5719,34 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: OD-023; contract tests. Риск регрессии: средний. отсутствующий prerequisite по AQ.1 №5; OD-023 approved 2026-08-31 (роль Product Data Owner) - planned; owner gate: контракт/scope adapter.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. OD-023 approved 2026-08-31 - planned после RM-TECH-280.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-003</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>`self.report_view` plan/fact</t>
+          <t>Prerequisite: master-data adapter цен/SKU (контракт, owner OD-023, reconciliation)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201, RM-TECH-207B</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
@@ -5766,10 +5762,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>реальные PoP/причины/RLS, journey/smoke/walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__report_view.py`]</t>
+          <t>владелец master-данных назначен (OD-023 approved); contract + reconciliation design утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; adapter в mock/test mode проходит contract tests [behavioral: `tests/behavioral/test_rm_tech_280.py`]</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -5779,14 +5779,14 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-011; зависит от RM-TECH-207B (реальные PoP) — без изменений</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: OD-023; contract tests. Риск регрессии: средний. отсутствующий prerequisite по AQ.1 №5; OD-023 approved 2026-08-31 (роль Product Data Owner) - planned; owner gate: контракт/scope adapter.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-209</t>
+          <t>RM-BIZ-003</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5796,17 +5796,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>ClickHouse capacity trigger</t>
+          <t>`self.report_view` plan/fact</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-201, RM-TECH-207B</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
@@ -5825,7 +5825,7 @@
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>измеряемый PoP rate/retention threshold и owner migration gate [artifact: `docs/product/clickhouse-capacity-trigger.yaml`]</t>
+          <t>реальные PoP/причины/RLS, journey/smoke/walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__report_view.py`]</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -5835,14 +5835,14 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-011; зависит от RM-TECH-207B (реальные PoP) — без изменений</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-256</t>
+          <t>RM-TECH-209</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5857,16 +5857,16 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Business outcome KPI: baseline/target/metric definition для целей §1.2 (OD-024 exit criteria)</t>
+          <t>ClickHouse capacity trigger</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
@@ -5878,14 +5878,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>каждая бизнес-цель имеет baseline/target/формулу/владельца, утверждено владельцем [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>измеряемый PoP rate/retention threshold и owner migration gate [artifact: `docs/product/clickhouse-capacity-trigger.yaml`]</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -5895,14 +5891,14 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-013; SC: -; DEC: DEC-010. Evidence: artifact kpi register. Риск регрессии: низкий.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-281</t>
+          <t>RM-TECH-256</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5912,21 +5908,21 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: sales-reference ingestion (агрегаты store/SKU/day) + методология baseline/test-control</t>
+          <t>Business outcome KPI: baseline/target/metric definition для целей §1.2 (OD-024 exit criteria)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -5938,10 +5934,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>пакетная загрузка агрегатов без PII; versioned baseline; методика утверждена владельцем [behavioral: `tests/behavioral/test_rm_tech_281.py`]</t>
+          <t>каждая бизнес-цель имеет baseline/target/формулу/владельца, утверждено владельцем [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -5951,14 +5951,14 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-001; SC: -; DEC: -. Evidence: new behavioral; methodology doc. Риск регрессии: средний. prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-013; SC: -; DEC: DEC-010. Evidence: artifact kpi register. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-282</t>
+          <t>RM-TECH-281</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5973,16 +5973,16 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Attribution &amp; sales lift: test/control, versioned baseline, pilot lift report</t>
+          <t>Prerequisite: sales-reference ingestion (агрегаты store/SKU/day) + методология baseline/test-control</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-281, RM-TECH-229</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
@@ -5991,13 +5991,13 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>pilot lift report по test/control с explainable методикой; RLS scope [behavioral: `tests/behavioral/test_rm_tech_282.py`]</t>
+          <t>пакетная загрузка агрегатов без PII; versioned baseline; методика утверждена владельцем [behavioral: `tests/behavioral/test_rm_tech_281.py`]</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -6007,14 +6007,14 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-002; SC: -; DEC: DEC-005, DEC-027. Evidence: new behavioral; report. Риск регрессии: средний. blocked OD-014 (DEC-027); OD-023 approved 2026-08-31.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-001; SC: -; DEC: -. Evidence: new behavioral; methodology doc. Риск регрессии: средний. prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-283</t>
+          <t>RM-TECH-282</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -6024,21 +6024,21 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: audience source/privacy contract (анонимные store-атрибуты, 152-ФЗ, OD-032)</t>
+          <t>Attribution &amp; sales lift: test/control, versioned baseline, pilot lift report</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280, RM-TECH-253</t>
+          <t>RM-TECH-281, RM-TECH-229</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
@@ -6050,14 +6050,10 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>privacy/legal решение (OD-032) и контракт источника утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>pilot lift report по test/control с explainable методикой; RLS scope [behavioral: `tests/behavioral/test_rm_tech_282.py`]</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -6067,14 +6063,14 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-005; SC: -; DEC: DEC-005, DEC-019. Evidence: OD-032; contract. Риск регрессии: низкий. blocked OD-032 (DEC-019); OD-023 approved 2026-08-31.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-002; SC: -; DEC: DEC-005, DEC-027. Evidence: new behavioral; report. Риск регрессии: средний. blocked OD-014 (DEC-027); OD-023 approved 2026-08-31.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-284</t>
+          <t>RM-TECH-283</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -6084,21 +6080,21 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>A/B attribution и winner metric (minimum sample, owner approval результата)</t>
+          <t>Prerequisite: audience source/privacy contract (анонимные store-атрибуты, 152-ФЗ, OD-032)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-282</t>
+          <t>RM-TECH-280, RM-TECH-253</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -6110,10 +6106,14 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>A/B фиксирует группы/период/метрику; winner только при minimum sample и ручном утверждении [behavioral: `tests/behavioral/test_rm_tech_284.py`]</t>
+          <t>privacy/legal решение (OD-032) и контракт источника утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -6123,14 +6123,14 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-012, REQ-V26-010; SC: -; DEC: DEC-027. Evidence: new behavioral. Риск регрессии: средний. blocked OD-014 (DEC-027) - методика winner metric не утверждена.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-005; SC: -; DEC: DEC-005, DEC-019. Evidence: OD-032; contract. Риск регрессии: низкий. blocked OD-032 (DEC-019); OD-023 approved 2026-08-31.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-285</t>
+          <t>RM-TECH-284</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -6145,16 +6145,16 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Competitive separation: competitive_category, интервал/исключение в playlist/manifest (исключение §3.1 по OD-018)</t>
+          <t>A/B attribution и winner metric (minimum sample, owner approval результата)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202, RM-TECH-280</t>
+          <t>RM-TECH-282</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -6163,13 +6163,13 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>separation block/override test; изменение priority engine ограничено §3.1 [behavioral: `tests/behavioral/test_rm_tech_285.py`]</t>
+          <t>A/B фиксирует группы/период/метрику; winner только при minimum sample и ручном утверждении [behavioral: `tests/behavioral/test_rm_tech_284.py`]</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -6179,14 +6179,14 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-004; SC: -; DEC: DEC-005, DEC-022. Evidence: new behavioral. Риск регрессии: высокий: priority engine. OD-023 approved 2026-08-31, DEC-022 = OD-018 approved - planned после RM-TECH-280.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-012, REQ-V26-010; SC: -; DEC: DEC-027. Evidence: new behavioral. Риск регрессии: средний. blocked OD-014 (DEC-027) - методика winner metric не утверждена.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-286</t>
+          <t>RM-TECH-285</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -6201,16 +6201,16 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Financial-system exchange: versioned/idempotent export + payment-status contract (после DEC-017)</t>
+          <t>Competitive separation: competitive_category, интервал/исключение в playlist/manifest (исключение §3.1 по OD-018)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-246</t>
+          <t>RM-TECH-202, RM-TECH-280</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
@@ -6219,13 +6219,13 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>idempotent export round-trip; повтор не создаёт дубликатов; scope финансового контура зафиксирован [behavioral: `tests/behavioral/test_rm_tech_286.py`]</t>
+          <t>separation block/override test; изменение priority engine ограничено §3.1 [behavioral: `tests/behavioral/test_rm_tech_285.py`]</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -6235,14 +6235,14 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-006, REQ-BIZ-009; SC: -; DEC: DEC-017. Evidence: new behavioral. Риск регрессии: средний. blocked OD-030.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-004; SC: -; DEC: DEC-005, DEC-022. Evidence: new behavioral. Риск регрессии: высокий: priority engine. OD-023 approved 2026-08-31, DEC-022 = OD-018 approved - planned после RM-TECH-280.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-287</t>
+          <t>RM-TECH-286</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -6257,16 +6257,16 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>BI/export/SIEM/vendor API: scoped keys, rate-limit, immutable audit, circuit breaker (после DEC-013)</t>
+          <t>Financial-system exchange: versioned/idempotent export + payment-status contract (после DEC-017)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-013</t>
+          <t>RM-TECH-246</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>401/403/429 negative; vendor connector с отдельными credentials и failure mode [behavioral: `tests/test_s065_rate_limit.py`]</t>
+          <t>idempotent export round-trip; повтор не создаёт дубликатов; scope финансового контура зафиксирован [behavioral: `tests/behavioral/test_rm_tech_286.py`]</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -6291,14 +6291,14 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-003; SC: SC-SEC-002; DEC: DEC-013. Evidence: tests/test_s065_rate_limit.py; new behavioral. Риск регрессии: средний. blocked OD-026.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-006, REQ-BIZ-009; SC: -; DEC: DEC-017. Evidence: new behavioral. Риск регрессии: средний. blocked OD-030.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-289</t>
+          <t>RM-TECH-287</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -6308,21 +6308,21 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Extension points designed-not-implemented: ADR для programmatic (V26-007) и external measurement (V26-011)</t>
+          <t>BI/export/SIEM/vendor API: scoped keys, rate-limit, immutable audit, circuit breaker (после DEC-013)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-STAB-013</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -6331,13 +6331,13 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>ADR принят с пометкой designed-not-implemented; код не пишется до OD-021/OD-031 [artifact: `docs/audit/RM-TECH-289-artifact.md (создаётся задачей)`]</t>
+          <t>401/403/429 negative; vendor connector с отдельными credentials и failure mode [behavioral: `tests/test_s065_rate_limit.py`]</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -6347,14 +6347,14 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-007, REQ-V26-011; SC: SC-ARCH-006; DEC: DEC-001, DEC-018. Evidence: ADR. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-003; SC: SC-SEC-002; DEC: DEC-013. Evidence: tests/test_s065_rate_limit.py; new behavioral. Риск регрессии: средний. blocked OD-026.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-010</t>
+          <t>RM-TECH-289</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -6364,21 +6364,21 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Service-quality reporting: доля active devices/logical carriers, plan/fact по каналу (analytics.compare)</t>
+          <t>Extension points designed-not-implemented: ADR для programmatic (V26-007) и external measurement (V26-011)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-003</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>отчёт по каналу с долями и причинами; RLS scope advertiser [ui_smoke: `tests/ui-smoke/test_rm_ux_010.py`]</t>
+          <t>ADR принят с пометкой designed-not-implemented; код не пишется до OD-021/OD-031 [artifact: `docs/audit/RM-TECH-289-artifact.md (создаётся задачей)`]</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -6403,38 +6403,38 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-004; SC: -; DEC: -. Evidence: новый ui-smoke; tests/behavioral/test_pop_reporting_scope.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-007, REQ-V26-011; SC: SC-ARCH-006; DEC: DEC-001, DEC-018. Evidence: ADR. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-001</t>
+          <t>RM-UX-010</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>external</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Production readiness</t>
+          <t>Service-quality reporting: доля active devices/logical carriers, plan/fact по каналу (analytics.compare)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-003</t>
+          <t>RM-BIZ-003</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
@@ -6446,14 +6446,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+      <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>не запускается автоматически после pilot [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой; OD-025/OD-028)`]</t>
+          <t>отчёт по каналу с долями и причинами; RLS scope advertiser [ui_smoke: `tests/ui-smoke/test_rm_ux_010.py`]</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -6463,14 +6459,14 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): зависит от OD-025 (RTO/RPO) и OD-028 (топология); REQ-OPS-005/006; HA baseline выделен в RM-OPS-003</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-004; SC: -; DEC: -. Evidence: новый ui-smoke; tests/behavioral/test_pop_reporting_scope.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-002</t>
+          <t>RM-OPS-001</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -6480,21 +6476,21 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>external</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Network segmentation: firewall rules по environment + negative reachability tests из device-сегмента</t>
+          <t>Production readiness</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-PILOT-003</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
@@ -6506,10 +6502,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>Admin API/PostgreSQL/MinIO/Redis недостижимы из device-сегмента; Gateway только HTTPS/mTLS [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+          <t>не запускается автоматически после pilot [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой; OD-025/OD-028)`]</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -6519,14 +6519,14 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-008; SC: SC-SEC-006; DEC: -. Evidence: reachability test log. Риск регрессии: средний: сеть пилота.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): зависит от OD-025 (RTO/RPO) и OD-028 (топология); REQ-OPS-005/006; HA baseline выделен в RM-OPS-003</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-003</t>
+          <t>RM-OPS-002</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -6536,21 +6536,21 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>external-plan</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Production HA baseline: ≥2 backend, масштабируемый Gateway, standby PostgreSQL, MinIO replication, quarterly restore drill</t>
+          <t>Network segmentation: firewall rules по environment + negative reachability tests из device-сегмента</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-001</t>
+          <t>RM-PILOT-002</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -6559,17 +6559,13 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>production config gate зелёный; restore drill выполнен и записан [command: `tests/test_production_config_gate.py`]; топология утверждена (OD-028), RTO/RPO (OD-025) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>Admin API/PostgreSQL/MinIO/Redis недостижимы из device-сегмента; Gateway только HTTPS/mTLS [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -6579,14 +6575,14 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-006, REQ-ARCH-004; SC: SC-OPS-001, SC-OPS-005; DEC: DEC-012, DEC-015. Evidence: tests/test_production_config_gate.py; drill record. Риск регрессии: высокий. blocked OD-025/OD-028.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-008; SC: SC-SEC-006; DEC: -. Evidence: reachability test log. Риск регрессии: средний: сеть пилота.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-004</t>
+          <t>RM-OPS-003</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -6596,21 +6592,21 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>external-plan</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Rollout entity/state machine и feature flags: planned→lab→canary→staged→paused→completed/rolled_back</t>
+          <t>Production HA baseline: ≥2 backend, масштабируемый Gateway, standby PostgreSQL, MinIO replication, quarterly restore drill</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-OPS-001</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -6622,10 +6618,14 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>rollback возвращает предыдущую версию; flag отключает функцию; ответственность по OD-010 [behavioral: `tests/integration/test_stand_rollback_drill.py`]</t>
+          <t>production config gate зелёный; restore drill выполнен и записан [command: `tests/test_production_config_gate.py`]; топология утверждена (OD-028), RTO/RPO (OD-025) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -6635,14 +6635,14 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-002; SC: SC-OPS-007; DEC: DEC-008. Evidence: tests/integration/test_stand_rollback_drill.py. Риск регрессии: средний. blocked OD-010.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-006, REQ-ARCH-004; SC: SC-OPS-001, SC-OPS-005; DEC: DEC-012, DEC-015. Evidence: tests/test_production_config_gate.py; drill record. Риск регрессии: высокий. blocked OD-025/OD-028.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-001</t>
+          <t>RM-OPS-004</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -6652,21 +6652,21 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Managed control-plane pilot scope</t>
+          <t>Rollout entity/state machine и feature flags: planned→lab→canary→staged→paused→completed/rolled_back</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Gate-S, Gate-U, RM-ENV-001</t>
+          <t>RM-PILOT-002</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
@@ -6675,13 +6675,13 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
+          <t>rollback возвращает предыдущую версию; flag отключает функцию; ответственность по OD-010 [behavioral: `tests/integration/test_stand_rollback_drill.py`]</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -6691,14 +6691,14 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): deps += OD-024 (exit criteria ступеней), REQ-ARCH-004</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-002; SC: SC-OPS-007; DEC: DEC-008. Evidence: tests/integration/test_stand_rollback_drill.py. Риск регрессии: средний. blocked OD-010.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-PILOT-001</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -6708,21 +6708,21 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>external-plan</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Deployment plan/preflight</t>
+          <t>Managed control-plane pilot scope</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-001</t>
+          <t>Gate-S, Gate-U, RM-ENV-001</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
       <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
+          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -6747,14 +6747,14 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): deps += OD-024 (exit criteria ступеней), REQ-ARCH-004</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002A</t>
+          <t>RM-PILOT-002</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -6764,21 +6764,21 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>external-plan</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Pilot-compose поднимается под ENVIRONMENT=pilot без ручных шагов; verify честный</t>
+          <t>Deployment plan/preflight</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RM-PILOT-001</t>
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
@@ -6787,13 +6787,13 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>pilot-compose из образов коммита под ENVIRONMENT=pilot - db-migrate сам создаёт retail_media_app (NOBYPASSRLS), все сервисы healthy в пределах таймаута, readiness со строгой проверкой роли, identity из образа, device-токен control-api принят device-gateway, конфиг orchestrator-worker грузится; таймаут или любой отказ роняют проверку [command: `CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env &lt;version&gt; &lt;sha&gt;`]; каждый backend-сервис получает из pilot-compose все переменные, которых требует валидатор prod; пустой JWT_AUDIENCE - отказ при старте [command: `python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py`]</t>
+          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6803,65 +6803,121 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>Решение владельца 2026-09-29 (этап RF-05, область RM-PILOT-002, Protected Boundary Docker/deployment с условиями). Находки ревью main@8ad0228: P0-1..P0-5, P1-16, P2-I9, P2-I11, T12 (+ FU5 healthcheck frontend). REQ: REQ-ARCH-004; SC: -; DEC: -. Не покрывает: TLS/reverse proxy (001D), ack/DLQ воркера при ошибке (RF-04), публикацию релиза и verify-pilot-images на GHCR (внешнее действие владельца). Риск регрессии: средний - обязательный JWT_AUDIENCE вне dev; pilot-хосты без него не стартуют.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>RM-PILOT-002A</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Pilot-compose поднимается под ENVIRONMENT=pilot без ручных шагов; verify честный</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>pilot-compose из образов коммита под ENVIRONMENT=pilot - db-migrate сам создаёт retail_media_app (NOBYPASSRLS), все сервисы healthy в пределах таймаута, readiness со строгой проверкой роли, identity из образа, device-токен control-api принят device-gateway, конфиг orchestrator-worker грузится; таймаут или любой отказ роняют проверку [command: `CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env &lt;version&gt; &lt;sha&gt;`]; каждый backend-сервис получает из pilot-compose все переменные, которых требует валидатор prod; пустой JWT_AUDIENCE - отказ при старте [command: `python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py`]</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/36571330932; verified · command · CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env ci-pilot-smoke &lt;sha&gt;; verified · command · python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>done - PR #12 смержен в develop @ af6810c, push-run develop 36571330932 success 42/42 (решение владельца 2026-09-29). Решение владельца 2026-09-29 (этап RF-05, область RM-PILOT-002, Protected Boundary Docker/deployment с условиями). Находки ревью main@8ad0228: P0-1..P0-5, P1-16, P2-I9, P2-I11, T12 (+ FU5 healthcheck frontend). REQ: REQ-ARCH-004; SC: -; DEC: -. Не покрывает: TLS/reverse proxy (001D), ack/DLQ воркера при ошибке (RF-04), публикацию релиза и verify-pilot-images на GHCR (внешнее действие владельца). Риск регрессии: средний - обязательный JWT_AUDIENCE вне dev; pilot-хосты без него не стартуют.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
           <t>RM-PILOT-003</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>POPS</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Controlled pilot deploy</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>RM-PILOT-002</t>
         </is>
       </c>
-      <c r="F112" s="2" t="n">
+      <c r="F113" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr">
         <is>
           <t>deployment</t>
         </is>
       </c>
-      <c r="J112" s="2" t="inlineStr">
+      <c r="J113" s="2" t="inlineStr">
         <is>
           <t>SHA/lock/schema/health, stand-safe journeys, rollback readiness [owner: `docs/audit/&lt;дата&gt;-pilot-deploy-&lt;sha&gt;.md + ACCEPT владельца с датой (deployment gate)`]</t>
         </is>
       </c>
-      <c r="K112" s="2" t="inlineStr">
+      <c r="K113" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L112" s="2" t="inlineStr">
+      <c r="L113" s="2" t="inlineStr">
         <is>
           <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L113"/>
+  <dimension ref="A1:L114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2458,19 +2458,19 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · behavioral · tests/behavioral/test_rm_stab_019_orchestrator_rls.py; verified · command · python -m pytest tests/test_rm_stab_019_orchestrator_failures.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/36690884823</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Решение владельца 2026-09-29, этап RF-04 (узкий состав). Находки ревью main@8ad0228: P0-4 (ack при ошибке), P1-6.a, P1-8, T11. REQ: - (кандидат REQ-ORCH-002, ссылка - решением владельца); SC: -; DEC: -. Не покрывает: DLQ и max_deliver (P1-6.b), stream subjects (P1-7), SKIP LOCKED outbox (P2-B7) - отдельный этап с RM-TECH-243; сбой подписи и ошибки кода внутри генерации по устройству по-прежнему дают failed + ack (деление по типу исключения). Риск регрессии: низкий - системный сбой начинает повторяться (nak) вместо тихого failed, повторы бесконечны до DLQ (max_deliver=-1, P1-6.b); readiness воркера может стать 503, но compose healthcheck смотрит /health/live - автоперезапуска нет.</t>
+          <t>done - PR #13 смержен в develop @ b219fad, push-run develop 36690884823 success 42/42 (решение владельца 2026-10-01). Решение владельца 2026-09-29, этап RF-04 (узкий состав). Находки ревью main@8ad0228: P0-4 (ack при ошибке), P1-6.a, P1-8, T11. REQ: - (кандидат REQ-ORCH-002, ссылка - решением владельца); SC: -; DEC: -. Не покрывает: DLQ и max_deliver (P1-6.b), stream subjects (P1-7), SKIP LOCKED outbox (P2-B7) - отдельный этап с RM-TECH-243; сбой подписи и ошибки кода внутри генерации по устройству по-прежнему дают failed + ack (деление по типу исключения). Риск регрессии: низкий - системный сбой начинает повторяться (nak) вместо тихого failed, повторы бесконечны до DLQ (max_deliver=-1, P1-6.b); readiness воркера может стать 503, но compose healthcheck смотрит /health/live - автоперезапуска нет.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-210</t>
+          <t>RM-STAB-020</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2485,16 +2485,16 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>RLS-контекст на device-маршрутах онбординга</t>
+          <t>События не пропадают молча: DLQ consumer оркестратора (лимит, backoff, повтор) и stream со всеми subjects outbox</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-002</t>
+          <t>RM-STAB-019</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
@@ -2503,54 +2503,50 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+          <t>in_progress</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; bootstrap-RLS миграции 037: без RLS-контекста роль приложения видит 0 onboarding codes (fail-closed); со своим app.rmp_device_code — только свою строку; с чужим кодом — 0 [behavioral: `tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap`]</t>
+          <t>сообщение consumer после 7-й неудачной доставки записано в DLQ (PostgreSQL) и term; до этого - nak с задержкой по расписанию; сбой записи в DLQ - nak без потери; replay создаёт outbox-событие и помечает строку replayed; без admin-контекста DLQ под retail_media_app не видна [behavioral: `tests/behavioral/test_rm_stab_020_consumer_dlq.py`]; каждый event_type outbox из кода захвачен ровно одним stream (RMP - campaign.&gt;, RMP_EVENTS - остальные семейства); без auto-provision воркер сверяет subjects обоих stream; расписание backoff [command: `python -m pytest tests/test_rm_stab_020_dlq_and_subjects.py`]</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py; verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap; verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33408891221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика. 2026-08-31 (стадия S, OD-043: зависимость RM-STAB-002 done): реализовано локально - set_rls_context на /identity/device-codes, bootstrap-контекст кода/fingerprint на /device/onboard, миграция 037 (rehearsal down/up), allowlist элевации снят; targeted 97 passed под ролью приложения; design-gate docs/architecture/rm-tech-210-device-onboarding-rls-bootstrap-design-gate.md (на тот момент - до CI-evidence и owner gate). verification 2026-08-31: CI 33408891221 success (условием done тогда оставался owner gate device_contract). 2026-08-31: приёмка №2 уточнена владельцем — три утверждения bootstrap-RLS (без контекста 0; свой app.rmp_device_code — только свой; чужой — 0); ref → TestRMTech210BootstrapRLS. done 2026-08-31: owner gate device_contract granted - OD-045 (fail-closed контракт принят владельцем).</t>
+          <t>Решение владельца 2026-09-30, этап RF-10 (mini-design: лимит 7 доставок в приложении, backoff 5с/30с/2м/10м/30м/60м, DLQ - таблица PostgreSQL с FORCE RLS, CLI-повтор через outbox). Решения владельца 2026-10-01 (после ревью): два stream - RMP (campaign.&gt;) и RMP_EVENTS (delivery/pop/emergency/creative_asset, 1 GiB, 7 суток, DiscardOld), чтобы поток PoP не вытеснял неподтверждённые события campaign; durable без серверного фильтра не меняется; риск max_ack_pending=100 при backoff до 60 мин принят (новые события campaign могут ждать до 60 мин после восстановления). Находки ревью main@8ad0228: P1-6.b, P1-7. REQ: - ; SC: -; DEC: -. Protected Boundary: только миграция 038 (downgrade удаляет лишь новую таблицу). Не покрывает: API/UI DLQ, DLQ stub-consumer, SKIP LOCKED outbox (P2-B7), lease/partition order/операции над dead_letter relay (RM-TECH-243). Риск регрессии: низкий - события не-campaign начинают сохраняться в RMP_EVENTS (без потребителя); события consumer после ~1ч43м сбоя уходят в DLQ и требуют replay. Открытый риск (ревью круг 3): provisioning только при старте и только с CAMPAIGN_CONSUMER_ENABLED=true; при его сбое relay стартует, и события без stream через ~1 мин уходят в dead_letter relay - решение владельца.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-005</t>
+          <t>RM-TECH-210</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>retention-policy.yaml + legal decision register (AG): сроки, 152-ФЗ, deletion/archive, review date</t>
+          <t>RLS-контекст на device-маршрутах онбординга</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-253</t>
+          <t>RM-STAB-002</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -2563,34 +2559,34 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>scope_decision</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>юридическое утверждение retention/152-ФЗ (OD-009) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; bootstrap-RLS миграции 037: без RLS-контекста роль приложения видит 0 onboarding codes (fail-closed); со своим app.rmp_device_code — только свою строку; с чужим кодом — 0 [behavioral: `tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap`]</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py; verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap; verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33408891221</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено POPS → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). 2026-08-31: кандидат docs/product/retention-policy.yaml подготовлен (working defaults REQ-DATA-001, legal register) - не действует до OD-009; задача остаётся blocked.</t>
+          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика. 2026-08-31 (стадия S, OD-043: зависимость RM-STAB-002 done): реализовано локально - set_rls_context на /identity/device-codes, bootstrap-контекст кода/fingerprint на /device/onboard, миграция 037 (rehearsal down/up), allowlist элевации снят; targeted 97 passed под ролью приложения; design-gate docs/architecture/rm-tech-210-device-onboarding-rls-bootstrap-design-gate.md (на тот момент - до CI-evidence и owner gate). verification 2026-08-31: CI 33408891221 success (условием done тогда оставался owner gate device_contract). 2026-08-31: приёмка №2 уточнена владельцем — три утверждения bootstrap-RLS (без контекста 0; свой app.rmp_device_code — только свой; чужой — 0); ref → TestRMTech210BootstrapRLS. done 2026-08-31: owner gate device_contract granted - OD-045 (fail-closed контракт принят владельцем).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-OPS-005</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2605,16 +2601,16 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>SLO objectives и измерение</t>
+          <t>retention-policy.yaml + legal decision register (AG): сроки, 152-ФЗ, deletion/archive, review date</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-253</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -2623,13 +2619,17 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>каждое число ТЗ имеет formula/window/owner/metric либо `not measurable` [artifact: `docs/product/slo-objectives.yaml`]</t>
+          <t>юридическое утверждение retention/152-ФЗ (OD-009) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2639,14 +2639,14 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288 RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/slo-objectives.yaml - 11 объектов, каждое число §8 с formula/window/owner/status; пороги OD-011/OD-025 open. Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено POPS → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). 2026-08-31: кандидат docs/product/retention-policy.yaml подготовлен (working defaults REQ-DATA-001, legal register) - не действует до OD-009; задача остаётся blocked.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>OpenAPI + event/manifest JSON Schema (AG): as-built генерация + target из §26/AB, contract tests</t>
+          <t>SLO objectives и измерение</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>OpenAPI/event schemas версионированы, examples и deprecation policy; contract tests зелёные [command: `python3 scripts/ci/roadmap-governance-guard.py`]; одна canonical opaque идентификация на версию API; alias {id} с deprecation date [behavioral: `tests/behavioral/test_rm_tech_220.py`]</t>
+          <t>каждое число ТЗ имеет formula/window/owner/metric либо `not measurable` [artifact: `docs/product/slo-objectives.yaml`]</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2695,14 +2695,14 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/api/openapi-as-built-v1.json (113 paths/128 ops/149 схем), target docs/architecture/api/openapi-target-v2.6.md, envelope docs/architecture/events/event-envelope-v1.schema.json; contract tests и версионирование - после старта задачи; задача planned до Gate-S (OD-043).</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288 RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/slo-objectives.yaml - 11 объектов, каждое число §8 с formula/window/owner/status; пороги OD-011/OD-025 open. Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-221</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2717,16 +2717,16 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Разделение User/Device/analytics/emergency API; device client не достигает admin</t>
+          <t>OpenAPI + event/manifest JSON Schema (AG): as-built генерация + target из §26/AB, contract tests</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>device JWT → admin endpoint = 403 на всех admin-роутах [behavioral: `tests/test_phase3_protected_identity.py`]</t>
+          <t>OpenAPI/event schemas версионированы, examples и deprecation policy; contract tests зелёные [command: `python3 scripts/ci/roadmap-governance-guard.py`]; одна canonical opaque идентификация на версию API; alias {id} с deprecation date [behavioral: `tests/behavioral/test_rm_tech_220.py`]</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2751,14 +2751,14 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-002; SC: SC-API-002; DEC: -. Evidence: tests/test_phase3_protected_identity.py; новый negative. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/api/openapi-as-built-v1.json (113 paths/128 ops/149 схем), target docs/architecture/api/openapi-target-v2.6.md, envelope docs/architecture/events/event-envelope-v1.schema.json; contract tests и версионирование - после старта задачи; задача planned до Gate-S (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-222</t>
+          <t>RM-TECH-221</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Канонический POST /api/v1/pop/batch, legacy /device/pop/batch как alias с deprecation</t>
+          <t>Разделение User/Device/analytics/emergency API; device client не достигает admin</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>ответы канонического и legacy идентичны; deprecation header; batch&gt;500 → 422; чужой device_id отклонён [behavioral: `tests/test_contract_pop.py`]</t>
+          <t>device JWT → admin endpoint = 403 на всех admin-роутах [behavioral: `tests/test_phase3_protected_identity.py`]</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2807,14 +2807,14 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-003, REQ-POP-003; SC: SC-API-003, SC-POP-003; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_edge002fu_real_endpoint.py. Риск регрессии: средний: runtime/плеер использует legacy path.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-002; SC: SC-API-002; DEC: -. Evidence: tests/test_phase3_protected_identity.py; новый negative. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-223</t>
+          <t>RM-TECH-222</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Manifest field contract и ACK-состояния runtime (opaque media_ref, no MinIO keys)</t>
+          <t>Канонический POST /api/v1/pop/batch, legacy /device/pop/batch как alias с deprecation</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2850,14 +2850,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>все обязательные поля §25 REQ-MAN-004 в schema; внутренний object key не раскрыт; 6 ACK states принимаются [behavioral: `tests/test_contract_manifest.py`]</t>
+          <t>ответы канонического и legacy идентичны; deprecation header; batch&gt;500 → 422; чужой device_id отклонён [behavioral: `tests/test_contract_pop.py`]</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2867,14 +2863,14 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-MAN-004; SC: SC-MAN-001; DEC: -. Evidence: tests/test_contract_manifest.py; tests/behavioral/test_edge002_manifest_delivery.py. Риск регрессии: высокий: меняет device-facing контракт — owner gate device_contract.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-003, REQ-POP-003; SC: SC-API-003, SC-POP-003; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_edge002fu_real_endpoint.py. Риск регрессии: средний: runtime/плеер использует legacy path.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-223</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2889,7 +2885,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat contract POST /api/v1/device/heartbeat: дедуп, scope, clock drift, freshness thresholds</t>
+          <t>Manifest field contract и ACK-состояния runtime (opaque media_ref, no MinIO keys)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2917,7 +2913,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>валидный/повтор/чужой scope/просроченный heartbeat дают ожидаемые результаты; legacy alias с той же семантикой [behavioral: `tests/behavioral/test_edge004_heartbeat.py`]</t>
+          <t>все обязательные поля §25 REQ-MAN-004 в schema; внутренний object key не раскрыт; 6 ACK states принимаются [behavioral: `tests/test_contract_manifest.py`]</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2927,14 +2923,14 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-009; SC: SC-OPS-002; DEC: -. Evidence: tests/behavioral/test_edge004_heartbeat.py. Риск регрессии: высокий: device-facing.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-MAN-004; SC: SC-MAN-001; DEC: -. Evidence: tests/test_contract_manifest.py; tests/behavioral/test_edge002_manifest_delivery.py. Риск регрессии: высокий: меняет device-facing контракт — owner gate device_contract.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2949,16 +2945,16 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>PoP duplicate semantics по OD-019: 200 + per-event duplicate/409, amendment ADR-017</t>
+          <t>Heartbeat contract POST /api/v1/device/heartbeat: дедуп, scope, clock drift, freshness thresholds</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-222</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
@@ -2970,10 +2966,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>ADR-017 amendment принят; behavioral: повтор batch → per-event duplicate, summary не удвоен, порядок хронологический [behavioral: `tests/behavioral/test_edge003_pop_ingestion.py`]</t>
+          <t>валидный/повтор/чужой scope/просроченный heartbeat дают ожидаемые результаты; legacy alias с той же семантикой [behavioral: `tests/behavioral/test_edge004_heartbeat.py`]</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2983,14 +2983,14 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-002; SC: SC-POP-002; DEC: DEC-024. Evidence: tests/behavioral/test_edge003_pop_ingestion.py; ADR-017 amendment. Риск регрессии: низкий: закрепляет текущее поведение.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-009; SC: SC-OPS-002; DEC: -. Evidence: tests/behavioral/test_edge004_heartbeat.py. Риск регрессии: высокий: device-facing.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-226</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3005,16 +3005,16 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Proof model: pop_mode error/not_applied — schema/runtime migration из compatibility projection</t>
+          <t>PoP duplicate semantics по OD-019: 200 + per-event duplicate/409, amendment ADR-017</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-222</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
@@ -3026,14 +3026,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>ProofMode содержит 9 значений; отчёт не смешивает playback/apply/delivery/error [behavioral: `tests/behavioral/test_pop_schema.py`]</t>
+          <t>ADR-017 amendment принят; behavioral: повтор batch → per-event duplicate, summary не удвоен, порядок хронологический [behavioral: `tests/behavioral/test_edge003_pop_ingestion.py`]</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3043,14 +3039,14 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-001; SC: SC-POP-001; DEC: -. Evidence: tests/behavioral/test_pop_schema.py; migration. Риск регрессии: средний: enum migration + отчёты.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-002; SC: SC-POP-002; DEC: DEC-024. Evidence: tests/behavioral/test_edge003_pop_ingestion.py; ADR-017 amendment. Риск регрессии: низкий: закрепляет текущее поведение.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-227</t>
+          <t>RM-TECH-226</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3065,7 +3061,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Валидация proof_event_v1: playback_result/failure_reason, clock-drift quarantine, no internal IDs/PII</t>
+          <t>Proof model: pop_mode error/not_applied — schema/runtime migration из compatibility projection</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3086,10 +3082,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>недопустимый playback_result/внутренний ID/сдвиг часов → 422 или quarantine; SHA/signature проверены [behavioral: `tests/test_contract_pop.py`]</t>
+          <t>ProofMode содержит 9 значений; отчёт не смешивает playback/apply/delivery/error [behavioral: `tests/behavioral/test_pop_schema.py`]</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3099,14 +3099,14 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-004; SC: SC-POP-004; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_pop_schema.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-001; SC: SC-POP-001; DEC: -. Evidence: tests/behavioral/test_pop_schema.py; migration. Риск регрессии: средний: enum migration + отчёты.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-228</t>
+          <t>RM-TECH-227</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3121,16 +3121,16 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Окно совместимости device/API/manifest: heartbeat объявляет версии, сервер выбирает представление</t>
+          <t>Валидация proof_event_v1: playback_result/failure_reason, clock-drift quarantine, no internal IDs/PII</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>совместимая версия выбрана по объявленным capabilities; breaking change без staged rollout отклонён contract-тестом [behavioral: `tests/test_version_identity.py`]</t>
+          <t>недопустимый playback_result/внутренний ID/сдвиг часов → 422 или quarantine; SHA/signature проверены [behavioral: `tests/test_contract_pop.py`]</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3155,14 +3155,14 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-003; SC: SC-NFR-003; DEC: -. Evidence: tests/test_version_identity.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-004; SC: SC-POP-004; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_pop_schema.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-228</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3172,21 +3172,21 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>ERD + data dictionary + migration plan (AG): инвентарь сущностей §15, retailer_id NOT NULL + двухуровневый RLS</t>
+          <t>Окно совместимости device/API/manifest: heartbeat объявляет версии, сервер выбирает представление</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>as-built ERD из моделей; каждая группа §15 присутствует или имеет migration task; tenant-таблицы с retailer_id+FK+RLS [artifact: `tests/behavioral/test_adr018_multitenancy_rls.py`]; behavioral RLS proof под ролью приложения NOBYPASSRLS [behavioral: `tests/behavioral/test_adr018_multitenancy_rls.py`]</t>
+          <t>совместимая версия выбрана по объявленным capabilities; breaking change без staged rollout отклонён contract-тестом [behavioral: `tests/test_version_identity.py`]</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3211,14 +3211,14 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/erd/data-dictionary-as-built.md (62 таблицы, 38 RLS) и кандидат docs/architecture/erd/migration-plan-v2.6.md (§13 → present/missing → задачи); PII/retention колонки - RM-TECH-253/RM-OPS-005. Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-003; SC: SC-NFR-003; DEC: -. Evidence: tests/test_version_identity.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-230</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Channel Adapter contract (design-only до второго канала): versioned task, receipt, proof/ack, error, health, mock mode</t>
+          <t>ERD + data dictionary + migration plan (AG): инвентарь сущностей §15, retailer_id NOT NULL + двухуровневый RLS</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3257,7 +3257,7 @@
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>contract spec + JSON Schema без реализации adapter/mock (ADR-019) [artifact: `docs/architecture contract`]</t>
+          <t>as-built ERD из моделей; каждая группа §15 присутствует или имеет migration task; tenant-таблицы с retailer_id+FK+RLS [artifact: `tests/behavioral/test_adr018_multitenancy_rls.py`]; behavioral RLS proof под ролью приложения NOBYPASSRLS [behavioral: `tests/behavioral/test_adr018_multitenancy_rls.py`]</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -3267,14 +3267,14 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-006; SC: SC-ORCH-005; DEC: -. Evidence: docs/architecture contract; schema. Риск регрессии: низкий: только документ.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/erd/data-dictionary-as-built.md (62 таблицы, 38 RLS) и кандидат docs/architecture/erd/migration-plan-v2.6.md (§13 → present/missing → задачи); PII/retention колонки - RM-TECH-253/RM-OPS-005. Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-231</t>
+          <t>RM-TECH-230</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3289,16 +3289,16 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>channel-capability-matrix.yaml (AG) для первого канала KSO: channel/surface/rendition/proof/SLA/vendor constraints</t>
+          <t>Channel Adapter contract (design-only до второго канала): versioned task, receipt, proof/ack, error, health, mock mode</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-230</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -3310,14 +3310,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>матрица покрывает KSO channel/surface/rendition/proof/SLA/vendor constraints; каждая строка ссылается на REQ-CHAN-*/REQ-MAN-*/REQ-POP-* [artifact: `docs/product/channel-capability-matrix.yaml`]; артефакт принят владельцем как часть handoff-пакета AG [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>contract spec + JSON Schema без реализации adapter/mock (ADR-019) [artifact: `docs/architecture contract`]</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3327,14 +3323,14 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-012 (предложение 2026-08-31): AG требует channel-capability-matrix до старта разработки, а RM-TECH-261 держит матрицу за решением OD-021 (второй канал). Первый канал KSO описывается без OD-021; RM-TECH-261 расширяет матрицу вторым каналом. REQ: REQ-CHAN-001, REQ-CHAN-002, REQ-CHAN-003; SC: SC-CHAN-002; DEC: DEC-001 (расширение). Evidence: артефакт; ACCEPT владельца. Риск регрессии: нет (документ). Утверждена OD-042 (2026-08-31). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/channel-capability-matrix.yaml (KSO + declared каналы §7); приёмка - внутри задачи после Gate-S.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-006; SC: SC-ORCH-005; DEC: -. Evidence: docs/architecture contract; schema. Риск регрессии: низкий: только документ.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-253</t>
+          <t>RM-TECH-231</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3349,12 +3345,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Data protection: data classes, lawful purpose, минимизация PII, residency; retention по OD-009</t>
+          <t>channel-capability-matrix.yaml (AG) для первого канала KSO: channel/surface/rendition/proof/SLA/vendor constraints</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-230</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
@@ -3370,10 +3366,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>реестр data classes для всех сущностей; новая PII-сущность без класса — красный design-gate [artifact: `docs/architecture data classes`]</t>
+          <t>матрица покрывает KSO channel/surface/rendition/proof/SLA/vendor constraints; каждая строка ссылается на REQ-CHAN-*/REQ-MAN-*/REQ-POP-* [artifact: `docs/product/channel-capability-matrix.yaml`]; артефакт принят владельцем как часть handoff-пакета AG [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3383,14 +3383,14 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: docs/architecture data classes. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено CORE → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
+          <t>RM-GOV-012 (предложение 2026-08-31): AG требует channel-capability-matrix до старта разработки, а RM-TECH-261 держит матрицу за решением OD-021 (второй канал). Первый канал KSO описывается без OD-021; RM-TECH-261 расширяет матрицу вторым каналом. REQ: REQ-CHAN-001, REQ-CHAN-002, REQ-CHAN-003; SC: SC-CHAN-002; DEC: DEC-001 (расширение). Evidence: артефакт; ACCEPT владельца. Риск регрессии: нет (документ). Утверждена OD-042 (2026-08-31). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/channel-capability-matrix.yaml (KSO + declared каналы §7); приёмка - внутри задачи после Gate-S.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-288</t>
+          <t>RM-TECH-253</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3400,21 +3400,21 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>nfr-slo.yaml + load-profiles.yaml (AG): method, percentile, error budget, generator, CI evidence</t>
+          <t>Data protection: data classes, lawful purpose, минимизация PII, residency; retention по OD-009</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>каждый SLO имеет window/denominator/exclusions; load generator и прогон в CI/стенде [artifact: `nfr-slo.yaml`]</t>
+          <t>реестр data classes для всех сущностей; новая PII-сущность без класса — красный design-gate [artifact: `docs/architecture data classes`]</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки):ы docs/product/nfr-slo.yaml и docs/product/load-profiles.yaml (7 профилей); load generator отсутствует (new). Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: docs/architecture data classes. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено CORE → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-011</t>
+          <t>RM-TECH-288</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3461,16 +3461,16 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>role-scope-matrix.yaml + portal-route-matrix.yaml + journeys/ (AG) из seed/pg_policies/registry</t>
+          <t>nfr-slo.yaml + load-profiles.yaml (AG): method, percentile, error budget, generator, CI evidence</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004, RM-STAB-006</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>матрицы генерируются и сверяются guard; deny-cases покрыты behavioral [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+          <t>каждый SLO имеет window/denominator/exclusions; load generator и прогон в CI/стенде [artifact: `nfr-slo.yaml`]</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -3495,19 +3495,19 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено U → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/product/role-scope-matrix.yaml (5 seeded ролей × 30 permissions, Q2 target 7 ролей, 38 RLS-таблиц, deny-cases), docs/product/portal-route-matrix.yaml (admin 16 + advertiser 9 маршрутов), docs/product/journeys/journeys.yaml (79 journeys, нормативный формат); generated-сверка guard - после старта задачи; задача planned до Gate-S (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки):ы docs/product/nfr-slo.yaml и docs/product/load-profiles.yaml (7 профилей); load generator отсутствует (new). Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-001</t>
+          <t>RM-UX-011</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3517,16 +3517,16 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Записать managed-first scope</t>
+          <t>role-scope-matrix.yaml + portal-route-matrix.yaml + journeys/ (AG) из seed/pg_policies/registry</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-STAB-004, RM-STAB-006</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>roadmap явно исключает `self.campaign_create` из ближайшего control-plane pilot [artifact: `docs/product/roadmap.yaml (pilot scope)`]</t>
+          <t>матрицы генерируются и сверяются guard; deny-cases покрыты behavioral [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -3551,14 +3551,14 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): ссылки OD-005/DEC-011, REQ-SCOPE-001</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено U → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/product/role-scope-matrix.yaml (5 seeded ролей × 30 permissions, Q2 target 7 ролей, 38 RLS-таблиц, deny-cases), docs/product/portal-route-matrix.yaml (admin 16 + advertiser 9 маршрутов), docs/product/journeys/journeys.yaml (79 journeys, нормативный формат); generated-сверка guard - после старта задачи; задача planned до Gate-S (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201</t>
+          <t>RM-BIZ-001</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Таксономия причин недопоказа</t>
+          <t>Записать managed-first scope</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>8 категорий ТЗ, source/report/history contract и owner-approved artifact [artifact: `docs/product/underdelivery-reason-taxonomy.yaml`]</t>
+          <t>roadmap явно исключает `self.campaign_create` из ближайшего control-plane pilot [artifact: `docs/product/roadmap.yaml (pilot scope)`]</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3607,14 +3607,14 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): ссылки OD-005/DEC-011, REQ-SCOPE-001</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202</t>
+          <t>RM-TECH-201</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3624,21 +3624,21 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Вытеснение и объяснимые приоритеты</t>
+          <t>Таксономия причин недопоказа</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>versioned rules [behavioral: `tests/behavioral/test_campaign_preemption.py`]</t>
+          <t>8 категорий ТЗ, source/report/history contract и owner-approved artifact [artifact: `docs/product/underdelivery-reason-taxonomy.yaml`]</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3663,14 +3663,14 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-007 и порядок приоритета §12; исключение §3.1 (OD-018) — единственная точка изменения engine → RM-TECH-285 зависит от неё</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-203</t>
+          <t>RM-TECH-202</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3685,16 +3685,16 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Overbooking policy</t>
+          <t>Вытеснение и объяснимые приоритеты</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202</t>
+          <t>RM-TECH-201</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>default deny [behavioral: `tests/behavioral/test_inventory_overbooking_policy.py`]</t>
+          <t>versioned rules [behavioral: `tests/behavioral/test_campaign_preemption.py`]</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3719,14 +3719,14 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-007 и порядок приоритета §12; исключение §3.1 (OD-018) — единственная точка изменения engine → RM-TECH-285 зависит от неё</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-204</t>
+          <t>RM-TECH-203</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3741,16 +3741,16 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Creative QA без неутверждённого HTML5</t>
+          <t>Overbooking policy</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-202</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>metadata/antivirus/executable deny и immutable QA result [behavioral: `tests/behavioral/test_creative_qa.py`]</t>
+          <t>default deny [behavioral: `tests/behavioral/test_inventory_overbooking_policy.py`]</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-206</t>
+          <t>RM-TECH-204</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>License renewal/grant boundary</t>
+          <t>Creative QA без неутверждённого HTML5</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>атомарная семантика §1.6 [behavioral: `tests/behavioral/test_license_renewal_boundary.py`]</t>
+          <t>metadata/antivirus/executable deny и immutable QA result [behavioral: `tests/behavioral/test_creative_qa.py`]</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>RM-TECH-206</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3853,16 +3853,16 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Универсальная иерархия носителей: migration + seed network/branch/cluster/store/store_group/channel/device/surface</t>
+          <t>License renewal/grant boundary</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -3874,14 +3874,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>все уровни существуют с FK и RLS; seed заполняет иерархию; чужой scope не видит [behavioral: `tests/behavioral/test_scope_rls.py`]</t>
+          <t>атомарная семантика §1.6 [behavioral: `tests/behavioral/test_license_renewal_boundary.py`]</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3891,14 +3887,14 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-001; SC: SC-DATA-001; DEC: -. Evidence: migration; tests/behavioral/test_scope_rls.py. Риск регрессии: высокий: схема ядра.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-241</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3913,16 +3909,16 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Target resolution boundary: broad target → display_surface_id, запрет physical_device_id как target</t>
+          <t>Универсальная иерархия носителей: migration + seed network/branch/cluster/store/store_group/channel/device/surface</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -3934,10 +3930,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>планирование разрешает target до surface; physical_device_id в target отклоняется [behavioral: `tests/test_s089_inventory_simulation.py`]</t>
+          <t>все уровни существуют с FK и RLS; seed заполняет иерархию; чужой scope не видит [behavioral: `tests/behavioral/test_scope_rls.py`]</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3947,14 +3947,14 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-003; SC: SC-ARCH-002; DEC: -. Evidence: tests/test_s089_inventory_simulation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-001; SC: SC-DATA-001; DEC: -. Evidence: migration; tests/behavioral/test_scope_rls.py. Риск регрессии: высокий: схема ядра.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-242</t>
+          <t>RM-TECH-241</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Outbox для любой OLTP-записи с domain event; revocation/refresh manifest при pause/archive/expiry</t>
+          <t>Target resolution boundary: broad target → display_surface_id, запрет physical_device_id как target</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>каждая доменная мутация создаёт outbox event в той же транзакции; pause/archive порождают revocation [behavioral: `tests/behavioral/test_outbox.py`]</t>
+          <t>планирование разрешает target до surface; physical_device_id в target отклоняется [behavioral: `tests/test_s089_inventory_simulation.py`]</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -4003,14 +4003,14 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-003; SC: SC-ORCH-002; DEC: -. Evidence: tests/behavioral/test_outbox.py. Риск регрессии: средний: транзакционные границы всех сервисов.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-003; SC: SC-ARCH-002; DEC: -. Evidence: tests/test_s089_inventory_simulation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-243</t>
+          <t>RM-TECH-242</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4025,16 +4025,16 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Outbox relay: lease/publishing, Nats-Msg-Id, 7 попыток → dead_letter, partition order, DLQ policy, no PII</t>
+          <t>Outbox для любой OLTP-записи с domain event; revocation/refresh manifest при pause/archive/expiry</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-242</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>7 отказов брокера → dead_letter с operator action; ack → published; replay идемпотентен [behavioral: `tests/behavioral/test_outbox_relay.py`]; NATS recovery integration зелёный [command: `tests/behavioral/test_outbox_relay.py`]</t>
+          <t>каждая доменная мутация создаёт outbox event в той же транзакции; pause/archive порождают revocation [behavioral: `tests/behavioral/test_outbox.py`]</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -4059,14 +4059,14 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-004; SC: SC-ORCH-003; DEC: DEC-004. Evidence: tests/behavioral/test_outbox_relay.py; tests/integration/test_nats_recovery.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-003; SC: SC-ORCH-002; DEC: -. Evidence: tests/behavioral/test_outbox.py. Риск регрессии: средний: транзакционные границы всех сервисов.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-244</t>
+          <t>RM-TECH-243</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4081,16 +4081,16 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Adapter task lifecycle через persisted queue (event-driven массовая публикация)</t>
+          <t>Outbox relay: lease/publishing, Nats-Msg-Id, 7 попыток → dead_letter, partition order, DLQ policy, no PII</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-243</t>
+          <t>RM-TECH-242</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>активация на 1000 устройств не ждёт устройств; задачи агрегируют статусы [behavioral: `tests/behavioral/test_delivery_foundation.py`]</t>
+          <t>7 отказов брокера → dead_letter с operator action; ack → published; replay идемпотентен [behavioral: `tests/behavioral/test_outbox_relay.py`]; NATS recovery integration зелёный [command: `tests/behavioral/test_outbox_relay.py`]</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4115,14 +4115,14 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-002; SC: SC-ORCH-006; DEC: DEC-004. Evidence: tests/behavioral/test_delivery_foundation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-004; SC: SC-ORCH-003; DEC: DEC-004. Evidence: tests/behavioral/test_outbox_relay.py; tests/integration/test_nats_recovery.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-TECH-244</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4137,16 +4137,16 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Campaign lifecycle по ADR-015/OD-036: scheduled, resume, revise, archive; единый guard и audit</t>
+          <t>Adapter task lifecycle через persisted queue (event-driven массовая публикация)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-TECH-243</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -4158,14 +4158,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>_CAMPAIGN_TRANSITIONS = ADR-015; каждый переход через guard с audit; возврат в draft создаёт revision [behavioral: `tests/behavioral/test_campaign_domain.py`]; campaign.* smokes зелёные после изменения [ui_smoke: `tests/ui-smoke/test_rm_tech_245.py`]</t>
+          <t>активация на 1000 устройств не ждёт устройств; задачи агрегируют статусы [behavioral: `tests/behavioral/test_delivery_foundation.py`]</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -4175,14 +4171,14 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-010; SC: -; DEC: DEC-025. Evidence: tests/behavioral/test_campaign_domain.py; tests/ui-smoke/test_uismoke__campaign__*.py. Риск регрессии: высокий: меняет runtime enum кампании и UI.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-002; SC: SC-ORCH-006; DEC: DEC-004. Evidence: tests/behavioral/test_delivery_foundation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-246</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4197,7 +4193,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Commerce order: отмена по OD-020 (draft→cancelled, confirmed — reversal), payment projection отдельно</t>
+          <t>Campaign lifecycle по ADR-015/OD-036: scheduled, resume, revise, archive; единый guard и audit</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -4218,10 +4214,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>_ORDER_TRANSITIONS: draft→cancelled разрешён, confirmed→cancelled запрещён, reversal с audit [behavioral: `tests/test_commerce_a2.py`]</t>
+          <t>_CAMPAIGN_TRANSITIONS = ADR-015; каждый переход через guard с audit; возврат в draft создаёт revision [behavioral: `tests/behavioral/test_campaign_domain.py`]; campaign.* smokes зелёные после изменения [ui_smoke: `tests/ui-smoke/test_rm_tech_245.py`]</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -4231,14 +4231,14 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-014; SC: -; DEC: DEC-017, DEC-026. Evidence: tests/test_commerce_a2.py; tests/behavioral/test_commerce_rls.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-010; SC: -; DEC: DEC-025. Evidence: tests/behavioral/test_campaign_domain.py; tests/ui-smoke/test_uismoke__campaign__*.py. Риск регрессии: высокий: меняет runtime enum кампании и UI.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-247</t>
+          <t>RM-TECH-246</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4253,16 +4253,16 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Approval policy: required roles/scope/порядок/timeout per campaign/placement/creative</t>
+          <t>Commerce order: отмена по OD-020 (draft→cancelled, confirmed — reversal), payment projection отдельно</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>политика версионирована; submit/approve соблюдают порядок и timeout; negative для чужого scope [behavioral: `tests/behavioral/test_campaign_approval.py`]</t>
+          <t>_ORDER_TRANSITIONS: draft→cancelled разрешён, confirmed→cancelled запрещён, reversal с audit [behavioral: `tests/test_commerce_a2.py`]</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -4287,14 +4287,14 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-003; SC: -; DEC: -. Evidence: tests/behavioral/test_campaign_approval.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-014; SC: -; DEC: DEC-017, DEC-026. Evidence: tests/test_commerce_a2.py; tests/behavioral/test_commerce_rls.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-248</t>
+          <t>RM-TECH-247</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Flight/placement windows: versioned start_at/end_at UTC, проверка при simulation/manifest/runtime</t>
+          <t>Approval policy: required roles/scope/порядок/timeout per campaign/placement/creative</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -4333,7 +4333,7 @@
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>показ вне окна запрещён на трёх уровнях; DST/праздники/closed stores — версионированные правила [behavioral: `tests/test_s063_pop_timezone.py`]</t>
+          <t>политика версионирована; submit/approve соблюдают порядок и timeout; negative для чужого scope [behavioral: `tests/behavioral/test_campaign_approval.py`]</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -4343,14 +4343,14 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-005, REQ-NFR-002; SC: SC-NFR-002; DEC: -. Evidence: tests/test_s063_pop_timezone.py; новый behavioral. Риск регрессии: высокий: расписание доставки.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-003; SC: -; DEC: -. Evidence: tests/behavioral/test_campaign_approval.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-249</t>
+          <t>RM-TECH-248</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4365,16 +4365,16 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Manifest eligibility: approved status + валидный flight/contract + resolved target + readiness</t>
+          <t>Flight/placement windows: versioned start_at/end_at UTC, проверка при simulation/manifest/runtime</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-248</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>неэлигибельная кампания не попадает в manifest; причина объяснима [behavioral: `tests/behavioral/test_delivery_generation.py`]</t>
+          <t>показ вне окна запрещён на трёх уровнях; DST/праздники/closed stores — версионированные правила [behavioral: `tests/test_s063_pop_timezone.py`]</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-006; SC: -; DEC: -. Evidence: tests/behavioral/test_delivery_generation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-005, REQ-NFR-002; SC: SC-NFR-002; DEC: -. Evidence: tests/test_s063_pop_timezone.py; новый behavioral. Риск регрессии: высокий: расписание доставки.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-250</t>
+          <t>RM-TECH-249</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4421,16 +4421,16 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Creative/rendition state machine и immutable media history (uploaded→scanning→qa_failed/approved→superseded→retained)</t>
+          <t>Manifest eligibility: approved status + валидный flight/contract + resolved target + readiness</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-204</t>
+          <t>RM-TECH-248</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -4442,14 +4442,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>каждая версия хранит uploader/SHA-256/QA-решение/связь; закрытый отчёт воспроизводим после logical delete [behavioral: `tests/behavioral/test_creative_assets.py`]</t>
+          <t>неэлигибельная кампания не попадает в manifest; причина объяснима [behavioral: `tests/behavioral/test_delivery_generation.py`]</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -4459,14 +4455,14 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CONT-002; SC: SC-DATA-002; DEC: -. Evidence: tests/behavioral/test_creative_assets.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-006; SC: -; DEC: -. Evidence: tests/behavioral/test_delivery_generation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-251</t>
+          <t>RM-TECH-250</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4481,16 +4477,16 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Data ownership/lineage: immutable versioning и diff campaign/placement/playlist, словарь владельцев</t>
+          <t>Creative/rendition state machine и immutable media history (uploaded→scanning→qa_failed/approved→superseded→retained)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-204</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -4502,10 +4498,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>сохранение создаёт версию с diff и actor; предыдущая неизменяема [behavioral: `tests/behavioral/test_rm_tech_251.py`]</t>
+          <t>каждая версия хранит uploader/SHA-256/QA-решение/связь; закрытый отчёт воспроизводим после logical delete [behavioral: `tests/behavioral/test_creative_assets.py`]</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -4515,14 +4515,14 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-001; SC: SC-DATA-004; DEC: DEC-007. Evidence: новый behavioral. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CONT-002; SC: SC-DATA-002; DEC: -. Evidence: tests/behavioral/test_creative_assets.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-252</t>
+          <t>RM-TECH-251</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4537,16 +4537,16 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Identity: AD/LDAP или SSO для internal staff, MFA до production (OD-008)</t>
+          <t>Data ownership/lineage: immutable versioning и diff campaign/placement/playlist, словарь владельцев</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -4558,14 +4558,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>protected_boundary</t>
-        </is>
-      </c>
+      <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>логин через IdP; production-профиль без MFA отклоняет; TLS-профиль зафиксирован [behavioral: `tests/test_phase3_auth_api.py`]</t>
+          <t>сохранение создаёт версию с diff и actor; предыдущая неизменяема [behavioral: `tests/behavioral/test_rm_tech_251.py`]</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -4575,14 +4571,14 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-001; SC: SC-SEC-008; DEC: -. Evidence: tests/test_phase3_auth_api.py; tests/behavioral/test_auth_dual_e2e.py. Риск регрессии: высокий: вход всех пользователей.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-001; SC: SC-DATA-004; DEC: DEC-007. Evidence: новый behavioral. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-254</t>
+          <t>RM-TECH-252</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4597,16 +4593,16 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Emergency state machine: requested→authorized→dispatching→applied→resuming→closed, MFA+reason, приоритетный канал</t>
+          <t>Identity: AD/LDAP или SSO для internal staff, MFA до production (OD-008)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -4618,10 +4614,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>protected_boundary</t>
+        </is>
+      </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>emergency с причиной; per-target result; audit actor/reason/affected; resume возвращает штатный manifest [behavioral: `tests/test_phase3_emergency_api.py`]; emergency.* smokes зелёные [ui_smoke: `tests/ui-smoke/test_uismoke__emergency__activate.py`]</t>
+          <t>логин через IdP; production-профиль без MFA отклоняет; TLS-профиль зафиксирован [behavioral: `tests/test_phase3_auth_api.py`]</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -4631,14 +4631,14 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-007; SC: SC-OPS-003; DEC: -. Evidence: tests/test_phase3_emergency_api.py; tests/ui-smoke/test_uismoke__emergency__activate.py. Риск регрессии: высокий: аварийный контур.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-001; SC: SC-SEC-008; DEC: -. Evidence: tests/test_phase3_auth_api.py; tests/behavioral/test_auth_dual_e2e.py. Риск регрессии: высокий: вход всех пользователей.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-255</t>
+          <t>RM-TECH-254</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4653,16 +4653,16 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Device health/commands: пороги статусов по профилю, per-device view, команды с подтверждением</t>
+          <t>Emergency state machine: requested→authorized→dispatching→applied→resuming→closed, MFA+reason, приоритетный канал</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>online→degraded→offline по порогам; команда доставлена и подтверждена [behavioral: `tests/behavioral/test_rm_tech_255.py`]; device.health_view smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__device__health_view.py`]</t>
+          <t>emergency с причиной; per-target result; audit actor/reason/affected; resume возвращает штатный manifest [behavioral: `tests/test_phase3_emergency_api.py`]; emergency.* smokes зелёные [ui_smoke: `tests/ui-smoke/test_uismoke__emergency__activate.py`]</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -4687,19 +4687,19 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-001; SC: SC-OPS-006; DEC: -. Evidence: tests/ui-smoke/test_uismoke__device__health_view.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-007; SC: SC-OPS-003; DEC: -. Evidence: tests/test_phase3_emergency_api.py; tests/ui-smoke/test_uismoke__emergency__activate.py. Риск регрессии: высокий: аварийный контур.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-002</t>
+          <t>RM-TECH-255</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4709,16 +4709,16 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>`self.campaign_create` в будущей ветке</t>
+          <t>Device health/commands: пороги статусов по профилю, per-device view, команды с подтверждением</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-001</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -4727,17 +4727,13 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>mini-design, journey, backend/UI/RLS, intended-role smoke, walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__campaign_create.py`]</t>
+          <t>online→degraded→offline по порогам; команда доставлена и подтверждена [behavioral: `tests/behavioral/test_rm_tech_255.py`]; device.health_view smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__device__health_view.py`]</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -4747,14 +4743,14 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2). RM-GOV-009 (OD-037): blocked до OD-013 — полный self-service вне pilot scope (REQ-V26-003, OD-005)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-001; SC: SC-OPS-006; DEC: -. Evidence: tests/ui-smoke/test_uismoke__device__health_view.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001</t>
+          <t>RM-BIZ-002</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4769,16 +4765,16 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Accessibility оставшихся форм + route matrix (A3)</t>
+          <t>`self.campaign_create` в будущей ветке</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-BIZ-001</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -4787,13 +4783,17 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>labels/ARIA/axe/targeted vitest [artifact: `docs/product/ux-route-matrix.yaml`]</t>
+          <t>mini-design, journey, backend/UI/RLS, intended-role smoke, walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__campaign_create.py`]</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -4803,14 +4803,14 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2). RM-GOV-009 (OD-037): blocked до OD-013 — полный self-service вне pilot scope (REQ-V26-003, OD-005)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-002</t>
+          <t>RM-UX-001</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4825,16 +4825,16 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Поиск/сортировка/усечение таблиц (A2)</t>
+          <t>Accessibility оставшихся форм + route matrix (A3)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>server semantics для pagination [ui_smoke: `tests/ui-smoke/test_uismoke__campaign__create.py`]</t>
+          <t>labels/ARIA/axe/targeted vitest [artifact: `docs/product/ux-route-matrix.yaml`]</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-003</t>
+          <t>RM-UX-002</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4881,16 +4881,16 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Responsive-проверка (A4)</t>
+          <t>Поиск/сортировка/усечение таблиц (A2)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-002</t>
+          <t>RM-UX-001</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>все routes из `ux-route-matrix.yaml` проверены на 390px без overflow/crop [artifact: `docs/product/ux-responsive-report.yaml`]</t>
+          <t>server semantics для pagination [ui_smoke: `tests/ui-smoke/test_uismoke__campaign__create.py`]</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-004</t>
+          <t>RM-UX-003</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4937,16 +4937,16 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Согласованность состояний и терминов (A6)</t>
+          <t>Responsive-проверка (A4)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-003</t>
+          <t>RM-UX-002</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>route matrix покрывает empty/loading/error/403/success и locale-key check [artifact: `docs/product/ux-route-matrix.yaml (states coverage)`]</t>
+          <t>все routes из `ux-route-matrix.yaml` проверены на 390px без overflow/crop [artifact: `docs/product/ux-responsive-report.yaml`]</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-005</t>
+          <t>RM-UX-004</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4993,16 +4993,16 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Adoption доказанных primitives малыми slices (A1b)</t>
+          <t>Согласованность состояний и терминов (A6)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-004</t>
+          <t>RM-UX-003</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>каждый slice имеет отдельный diff/test/review [ci_job: `frontend`]</t>
+          <t>route matrix покрывает empty/loading/error/403/success и locale-key check [artifact: `docs/product/ux-route-matrix.yaml (states coverage)`]</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -5034,7 +5034,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-006</t>
+          <t>RM-UX-005</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -5049,16 +5049,16 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Advertiser-web UX audit/fixes (A5)</t>
+          <t>Adoption доказанных primitives малыми slices (A1b)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-005</t>
+          <t>RM-UX-004</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>versioned `docs/product/advertiser-route-matrix.yaml` с точным списком 15 routes [artifact: `docs/product/advertiser-route-matrix.yaml`]</t>
+          <t>каждый slice имеет отдельный diff/test/review [ci_job: `frontend`]</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-007</t>
+          <t>RM-UX-006</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5100,21 +5100,21 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Human operator walkthrough (A7)</t>
+          <t>Advertiser-web UX audit/fixes (A5)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001, RM-UX-002, RM-UX-003, RM-UX-004, RM-UX-005, RM-UX-006</t>
+          <t>RM-UX-005</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>человек проходит exact stand bundle [human: `PROJECT_STATE.md строка `operator walkthrough` (AGENTS.md правило 8); сценарии docs/product/operator-walkthrough-dev.md`]</t>
+          <t>versioned `docs/product/advertiser-route-matrix.yaml` с точным списком 15 routes [artifact: `docs/product/advertiser-route-matrix.yaml`]</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -5139,14 +5139,14 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) ПРИОСТАНОВЛЕНО владельцем 2026-08-31 (OD-041) до выравнивания ТЗ/roadmap/gates и утверждения единого плана реализации; не закрывать, done не ставить.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-008</t>
+          <t>RM-UX-007</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -5156,21 +5156,21 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Campaign readiness matrix по каналам (rendition/inventory/conflicts/forecast/PoP mode/SLA) с действием на blocked</t>
+          <t>Human operator walkthrough (A7)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-249, RM-UX-004</t>
+          <t>RM-UX-001, RM-UX-002, RM-UX-003, RM-UX-004, RM-UX-005, RM-UX-006</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>экран согласования показывает матрицу; каждый blocked/warning ведёт к действию [ui_smoke: `tests/ui-smoke/test_rm_ux_008.py`]</t>
+          <t>человек проходит exact stand bundle [human: `PROJECT_STATE.md строка `operator walkthrough` (AGENTS.md правило 8); сценарии docs/product/operator-walkthrough-dev.md`]</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -5195,14 +5195,14 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-004; SC: SC-UX-002; DEC: -. Evidence: новый ui-smoke; vitest. Риск регрессии: средний.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) ПРИОСТАНОВЛЕНО владельцем 2026-08-31 (OD-041) до выравнивания ТЗ/roadmap/gates и утверждения единого плана реализации; не закрывать, done не ставить.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-009</t>
+          <t>RM-UX-008</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5217,16 +5217,16 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Договор рекламодателя: immutable file versions, server-side SHA-256, legal status (юр. решение)</t>
+          <t>Campaign readiness matrix по каналам (rendition/inventory/conflicts/forecast/PoP mode/SLA) с действием на blocked</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-250</t>
+          <t>RM-TECH-249, RM-UX-004</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>повторная загрузка создаёт новую версию, SHA проверен сервером; старая версия неизменяема [behavioral: `tests/test_advertiser_contracts.py`]; advertiser.contract_crud smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py`]</t>
+          <t>экран согласования показывает матрицу; каждый blocked/warning ведёт к действию [ui_smoke: `tests/ui-smoke/test_rm_ux_008.py`]</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -5251,38 +5251,38 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-017; SC: -; DEC: -. Evidence: tests/test_advertiser_contracts.py; tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-004; SC: SC-UX-002; DEC: -. Evidence: новый ui-smoke; vitest. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207A</t>
+          <t>RM-UX-009</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>KSO environment + player/playlist design</t>
+          <t>Договор рекламодателя: immutable file versions, server-side SHA-256, legal status (юр. решение)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-250</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -5294,14 +5294,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>versioned environment audit, import/contract mini-design и test plan [artifact: `docs/architecture/kso-environment-audit.md`]</t>
+          <t>повторная загрузка создаёт новую версию, SHA проверен сервером; старая версия неизменяема [behavioral: `tests/test_advertiser_contracts.py`]; advertiser.contract_crud smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py`]</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -5311,14 +5307,14 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-STAND-003 feasibility gate явно в acceptance; ADR-019/OD-022</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-017; SC: -; DEC: -. Evidence: tests/test_advertiser_contracts.py; tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-207A</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5328,21 +5324,21 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>KSO player/playlist/PoP chain</t>
+          <t>KSO environment + player/playlist design</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207A</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
@@ -5356,12 +5352,12 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>device_contract</t>
+          <t>scope_decision</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>contract tests и playback→manifest→PoP behavioral proof [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; Playlist entity и state machine §6 ТЗ (draft → validating → valid/invalid → approved → published → superseded/rolled_back); published immutable [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; manifest target lifecycle (generated → signed → queued → delivered → applied/failed/expired) и canonical POST /api/v1/pop/batch [behavioral: `tests/behavioral/test_kso_playback_chain.py`]</t>
+          <t>versioned environment audit, import/contract mini-design и test plan [artifact: `docs/architecture/kso-environment-audit.md`]</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -5371,14 +5367,14 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-STAND-003 feasibility gate явно в acceptance; ADR-019/OD-022</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-208</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -5393,16 +5389,16 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Signed licensing Layer 2</t>
+          <t>KSO player/playlist/PoP chain</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-206, RM-TECH-207B, RM-STAB-010</t>
+          <t>RM-TECH-207A</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -5416,12 +5412,12 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>protected_boundary</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Ed25519 offline verify, kid/rotation/revocation, UI, tamper/rollback [behavioral: `tests/behavioral/test_signed_license_layer2.py`]</t>
+          <t>contract tests и playback→manifest→PoP behavioral proof [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; Playlist entity и state machine §6 ТЗ (draft → validating → valid/invalid → approved → published → superseded/rolled_back); published immutable [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; manifest target lifecycle (generated → signed → queued → delivered → applied/failed/expired) и canonical POST /api/v1/pop/batch [behavioral: `tests/behavioral/test_kso_playback_chain.py`]</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -5438,7 +5434,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-260</t>
+          <t>RM-TECH-208</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5453,12 +5449,12 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Runtime cache lifecycle: лимит по профилю, детерминированная очистка, last-known-good</t>
+          <t>Signed licensing Layer 2</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-206, RM-TECH-207B, RM-STAB-010</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
@@ -5476,12 +5472,12 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>device_contract</t>
+          <t>protected_boundary</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>кэш на лимите: очистка по правилу; last-known-good сохранён; просроченная реклама не показывается [behavioral: `tests/behavioral/test_rm_tech_260.py`]</t>
+          <t>Ed25519 offline verify, kid/rotation/revocation, UI, tamper/rollback [behavioral: `tests/behavioral/test_signed_license_layer2.py`]</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -5491,14 +5487,14 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-008; SC: SC-EDGE-002; DEC: -. Evidence: runtime simulator tests. Риск регрессии: средний: плеер.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-261</t>
+          <t>RM-TECH-260</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5508,17 +5504,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Второй канал: решение OD-021 + channel-capability-matrix.yaml (AG); extraction design по ADR-019</t>
+          <t>Runtime cache lifecycle: лимит по профилю, детерминированная очистка, last-known-good</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B, RM-TECH-230</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
@@ -5531,17 +5527,17 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>scope_decision</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>владелец назвал канал и владельца (OD-021); матрица возможностей утверждена [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; extraction design: KSO-вертикаль как первый adapter без поломки контрактов [artifact: `docs/audit/RM-TECH-261-artifact.md (создаётся задачей)`]</t>
+          <t>кэш на лимите: очистка по правилу; last-known-good сохранён; просроченная реклама не показывается [behavioral: `tests/behavioral/test_rm_tech_260.py`]</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -5551,14 +5547,14 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CHAN-001, REQ-ORCH-005; SC: SC-CHAN-002, SC-ORCH-004; DEC: DEC-001, DEC-002. Evidence: OD-021; design doc. Риск регрессии: высокий: рефакторинг KSO-вертикали. blocked до OD-021; Orchestrator/Adapter Layer/mock не создаются раньше (ADR-019/OD-022).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-008; SC: SC-EDGE-002; DEC: -. Evidence: runtime simulator tests. Риск регрессии: средний: плеер.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-262</t>
+          <t>RM-TECH-261</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5568,21 +5564,21 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Dynamic creative binding/rendition safety (V26-008) на одном канале</t>
+          <t>Второй канал: решение OD-021 + channel-capability-matrix.yaml (AG); extraction design по ADR-019</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280, RM-TECH-261</t>
+          <t>RM-TECH-207B, RM-TECH-230</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -5591,13 +5587,17 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>master-confirmed price/promo подставляется при manifest generation; SLA-тест dynamic manifest [behavioral: `tests/behavioral/test_rm_tech_262.py`]</t>
+          <t>владелец назвал канал и владельца (OD-021); матрица возможностей утверждена [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; extraction design: KSO-вертикаль как первый adapter без поломки контрактов [artifact: `docs/audit/RM-TECH-261-artifact.md (создаётся задачей)`]</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -5607,14 +5607,14 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-008; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. ложная ESL-посылка снимается prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CHAN-001, REQ-ORCH-005; SC: SC-CHAN-002, SC-ORCH-004; DEC: DEC-001, DEC-002. Evidence: OD-021; design doc. Риск регрессии: высокий: рефакторинг KSO-вертикали. blocked до OD-021; Orchestrator/Adapter Layer/mock не создаются раньше (ADR-019/OD-022).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-263</t>
+          <t>RM-TECH-262</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5629,16 +5629,16 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Field mobile operations: scoped mobile web для сотрудника магазина (устройства, фото, инциденты)</t>
+          <t>Dynamic creative binding/rendition safety (V26-008) на одном канале</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-210, RM-TECH-255</t>
+          <t>RM-TECH-280, RM-TECH-261</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>journey field_ops.device_confirm под ролью магазина с RLS; negative чужой магазин [ui_smoke: `tests/ui-smoke/test_rm_tech_263.py`]</t>
+          <t>master-confirmed price/promo подставляется при manifest generation; SLA-тест dynamic manifest [behavioral: `tests/behavioral/test_rm_tech_262.py`]</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -5663,14 +5663,14 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-009; SC: -; DEC: -. Evidence: new ui-smoke. Риск регрессии: средний. prerequisite RM-TECH-210 (RLS device) - planned по зависимости; feature field_ops.device_confirm blocked до задачи (RM-GOV-012 выравнивание: blocked = решение владельца/внешний факт, а не зависимость).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-008; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. ложная ESL-посылка снимается prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-264</t>
+          <t>RM-TECH-263</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5685,16 +5685,16 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>ESL/price-checker: интеграция только через approved price/SKU master (INT-002)</t>
+          <t>Field mobile operations: scoped mobile web для сотрудника магазина (устройства, фото, инциденты)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-210, RM-TECH-255</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>price-related данные приходят из master или проходят reconciliation; расхождение блокирует показ [behavioral: `tests/behavioral/test_rm_tech_264.py`]</t>
+          <t>journey field_ops.device_confirm под ролью магазина с RLS; negative чужой магазин [ui_smoke: `tests/ui-smoke/test_rm_tech_263.py`]</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -5719,38 +5719,38 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. OD-023 approved 2026-08-31 - planned после RM-TECH-280.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-009; SC: -; DEC: -. Evidence: new ui-smoke. Риск регрессии: средний. prerequisite RM-TECH-210 (RLS device) - planned по зависимости; feature field_ops.device_confirm blocked до задачи (RM-GOV-012 выравнивание: blocked = решение владельца/внешний факт, а не зависимость).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>RM-TECH-264</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>ESL/price-checker: интеграция только через approved price/SKU master (INT-002)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>RM-TECH-280</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>design</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Prerequisite: master-data adapter цен/SKU (контракт, owner OD-023, reconciliation)</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>RM-TECH-229</t>
-        </is>
-      </c>
       <c r="F93" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
@@ -5762,14 +5762,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>владелец master-данных назначен (OD-023 approved); contract + reconciliation design утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; adapter в mock/test mode проходит contract tests [behavioral: `tests/behavioral/test_rm_tech_280.py`]</t>
+          <t>price-related данные приходят из master или проходят reconciliation; расхождение блокирует показ [behavioral: `tests/behavioral/test_rm_tech_264.py`]</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -5779,34 +5775,34 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: OD-023; contract tests. Риск регрессии: средний. отсутствующий prerequisite по AQ.1 №5; OD-023 approved 2026-08-31 (роль Product Data Owner) - planned; owner gate: контракт/scope adapter.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. OD-023 approved 2026-08-31 - planned после RM-TECH-280.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-003</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>`self.report_view` plan/fact</t>
+          <t>Prerequisite: master-data adapter цен/SKU (контракт, owner OD-023, reconciliation)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201, RM-TECH-207B</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
@@ -5822,10 +5818,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>реальные PoP/причины/RLS, journey/smoke/walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__report_view.py`]</t>
+          <t>владелец master-данных назначен (OD-023 approved); contract + reconciliation design утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; adapter в mock/test mode проходит contract tests [behavioral: `tests/behavioral/test_rm_tech_280.py`]</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -5835,14 +5835,14 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-011; зависит от RM-TECH-207B (реальные PoP) — без изменений</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: OD-023; contract tests. Риск регрессии: средний. отсутствующий prerequisite по AQ.1 №5; OD-023 approved 2026-08-31 (роль Product Data Owner) - planned; owner gate: контракт/scope adapter.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-209</t>
+          <t>RM-BIZ-003</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5852,17 +5852,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>ClickHouse capacity trigger</t>
+          <t>`self.report_view` plan/fact</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-201, RM-TECH-207B</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
@@ -5881,7 +5881,7 @@
       <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>измеряемый PoP rate/retention threshold и owner migration gate [artifact: `docs/product/clickhouse-capacity-trigger.yaml`]</t>
+          <t>реальные PoP/причины/RLS, journey/smoke/walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__report_view.py`]</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -5891,14 +5891,14 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-011; зависит от RM-TECH-207B (реальные PoP) — без изменений</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-256</t>
+          <t>RM-TECH-209</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5913,16 +5913,16 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Business outcome KPI: baseline/target/metric definition для целей §1.2 (OD-024 exit criteria)</t>
+          <t>ClickHouse capacity trigger</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -5934,14 +5934,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>каждая бизнес-цель имеет baseline/target/формулу/владельца, утверждено владельцем [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>измеряемый PoP rate/retention threshold и owner migration gate [artifact: `docs/product/clickhouse-capacity-trigger.yaml`]</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -5951,14 +5947,14 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-013; SC: -; DEC: DEC-010. Evidence: artifact kpi register. Риск регрессии: низкий.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-281</t>
+          <t>RM-TECH-256</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5968,21 +5964,21 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: sales-reference ingestion (агрегаты store/SKU/day) + методология baseline/test-control</t>
+          <t>Business outcome KPI: baseline/target/metric definition для целей §1.2 (OD-024 exit criteria)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
@@ -5994,10 +5990,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>пакетная загрузка агрегатов без PII; versioned baseline; методика утверждена владельцем [behavioral: `tests/behavioral/test_rm_tech_281.py`]</t>
+          <t>каждая бизнес-цель имеет baseline/target/формулу/владельца, утверждено владельцем [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -6007,14 +6007,14 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-001; SC: -; DEC: -. Evidence: new behavioral; methodology doc. Риск регрессии: средний. prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-013; SC: -; DEC: DEC-010. Evidence: artifact kpi register. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-282</t>
+          <t>RM-TECH-281</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -6029,16 +6029,16 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Attribution &amp; sales lift: test/control, versioned baseline, pilot lift report</t>
+          <t>Prerequisite: sales-reference ingestion (агрегаты store/SKU/day) + методология baseline/test-control</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-281, RM-TECH-229</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
@@ -6047,13 +6047,13 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>pilot lift report по test/control с explainable методикой; RLS scope [behavioral: `tests/behavioral/test_rm_tech_282.py`]</t>
+          <t>пакетная загрузка агрегатов без PII; versioned baseline; методика утверждена владельцем [behavioral: `tests/behavioral/test_rm_tech_281.py`]</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -6063,14 +6063,14 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-002; SC: -; DEC: DEC-005, DEC-027. Evidence: new behavioral; report. Риск регрессии: средний. blocked OD-014 (DEC-027); OD-023 approved 2026-08-31.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-001; SC: -; DEC: -. Evidence: new behavioral; methodology doc. Риск регрессии: средний. prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-283</t>
+          <t>RM-TECH-282</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -6080,21 +6080,21 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: audience source/privacy contract (анонимные store-атрибуты, 152-ФЗ, OD-032)</t>
+          <t>Attribution &amp; sales lift: test/control, versioned baseline, pilot lift report</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280, RM-TECH-253</t>
+          <t>RM-TECH-281, RM-TECH-229</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -6106,14 +6106,10 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>privacy/legal решение (OD-032) и контракт источника утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>pilot lift report по test/control с explainable методикой; RLS scope [behavioral: `tests/behavioral/test_rm_tech_282.py`]</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -6123,14 +6119,14 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-005; SC: -; DEC: DEC-005, DEC-019. Evidence: OD-032; contract. Риск регрессии: низкий. blocked OD-032 (DEC-019); OD-023 approved 2026-08-31.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-002; SC: -; DEC: DEC-005, DEC-027. Evidence: new behavioral; report. Риск регрессии: средний. blocked OD-014 (DEC-027); OD-023 approved 2026-08-31.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-284</t>
+          <t>RM-TECH-283</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -6140,21 +6136,21 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>A/B attribution и winner metric (minimum sample, owner approval результата)</t>
+          <t>Prerequisite: audience source/privacy contract (анонимные store-атрибуты, 152-ФЗ, OD-032)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-282</t>
+          <t>RM-TECH-280, RM-TECH-253</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -6166,10 +6162,14 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>A/B фиксирует группы/период/метрику; winner только при minimum sample и ручном утверждении [behavioral: `tests/behavioral/test_rm_tech_284.py`]</t>
+          <t>privacy/legal решение (OD-032) и контракт источника утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -6179,14 +6179,14 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-012, REQ-V26-010; SC: -; DEC: DEC-027. Evidence: new behavioral. Риск регрессии: средний. blocked OD-014 (DEC-027) - методика winner metric не утверждена.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-005; SC: -; DEC: DEC-005, DEC-019. Evidence: OD-032; contract. Риск регрессии: низкий. blocked OD-032 (DEC-019); OD-023 approved 2026-08-31.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-285</t>
+          <t>RM-TECH-284</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -6201,16 +6201,16 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Competitive separation: competitive_category, интервал/исключение в playlist/manifest (исключение §3.1 по OD-018)</t>
+          <t>A/B attribution и winner metric (minimum sample, owner approval результата)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202, RM-TECH-280</t>
+          <t>RM-TECH-282</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
@@ -6219,13 +6219,13 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>separation block/override test; изменение priority engine ограничено §3.1 [behavioral: `tests/behavioral/test_rm_tech_285.py`]</t>
+          <t>A/B фиксирует группы/период/метрику; winner только при minimum sample и ручном утверждении [behavioral: `tests/behavioral/test_rm_tech_284.py`]</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -6235,14 +6235,14 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-004; SC: -; DEC: DEC-005, DEC-022. Evidence: new behavioral. Риск регрессии: высокий: priority engine. OD-023 approved 2026-08-31, DEC-022 = OD-018 approved - planned после RM-TECH-280.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-012, REQ-V26-010; SC: -; DEC: DEC-027. Evidence: new behavioral. Риск регрессии: средний. blocked OD-014 (DEC-027) - методика winner metric не утверждена.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-286</t>
+          <t>RM-TECH-285</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -6257,16 +6257,16 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Financial-system exchange: versioned/idempotent export + payment-status contract (после DEC-017)</t>
+          <t>Competitive separation: competitive_category, интервал/исключение в playlist/manifest (исключение §3.1 по OD-018)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-246</t>
+          <t>RM-TECH-202, RM-TECH-280</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -6275,13 +6275,13 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>idempotent export round-trip; повтор не создаёт дубликатов; scope финансового контура зафиксирован [behavioral: `tests/behavioral/test_rm_tech_286.py`]</t>
+          <t>separation block/override test; изменение priority engine ограничено §3.1 [behavioral: `tests/behavioral/test_rm_tech_285.py`]</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -6291,14 +6291,14 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-006, REQ-BIZ-009; SC: -; DEC: DEC-017. Evidence: new behavioral. Риск регрессии: средний. blocked OD-030.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-004; SC: -; DEC: DEC-005, DEC-022. Evidence: new behavioral. Риск регрессии: высокий: priority engine. OD-023 approved 2026-08-31, DEC-022 = OD-018 approved - planned после RM-TECH-280.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-287</t>
+          <t>RM-TECH-286</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -6313,16 +6313,16 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>BI/export/SIEM/vendor API: scoped keys, rate-limit, immutable audit, circuit breaker (после DEC-013)</t>
+          <t>Financial-system exchange: versioned/idempotent export + payment-status contract (после DEC-017)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-013</t>
+          <t>RM-TECH-246</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>401/403/429 negative; vendor connector с отдельными credentials и failure mode [behavioral: `tests/test_s065_rate_limit.py`]</t>
+          <t>idempotent export round-trip; повтор не создаёт дубликатов; scope финансового контура зафиксирован [behavioral: `tests/behavioral/test_rm_tech_286.py`]</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -6347,14 +6347,14 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-003; SC: SC-SEC-002; DEC: DEC-013. Evidence: tests/test_s065_rate_limit.py; new behavioral. Риск регрессии: средний. blocked OD-026.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-006, REQ-BIZ-009; SC: -; DEC: DEC-017. Evidence: new behavioral. Риск регрессии: средний. blocked OD-030.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-289</t>
+          <t>RM-TECH-287</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -6364,21 +6364,21 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Extension points designed-not-implemented: ADR для programmatic (V26-007) и external measurement (V26-011)</t>
+          <t>BI/export/SIEM/vendor API: scoped keys, rate-limit, immutable audit, circuit breaker (после DEC-013)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-STAB-013</t>
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -6387,13 +6387,13 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>ADR принят с пометкой designed-not-implemented; код не пишется до OD-021/OD-031 [artifact: `docs/audit/RM-TECH-289-artifact.md (создаётся задачей)`]</t>
+          <t>401/403/429 negative; vendor connector с отдельными credentials и failure mode [behavioral: `tests/test_s065_rate_limit.py`]</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -6403,14 +6403,14 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-007, REQ-V26-011; SC: SC-ARCH-006; DEC: DEC-001, DEC-018. Evidence: ADR. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-003; SC: SC-SEC-002; DEC: DEC-013. Evidence: tests/test_s065_rate_limit.py; new behavioral. Риск регрессии: средний. blocked OD-026.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-010</t>
+          <t>RM-TECH-289</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -6420,21 +6420,21 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Service-quality reporting: доля active devices/logical carriers, plan/fact по каналу (analytics.compare)</t>
+          <t>Extension points designed-not-implemented: ADR для programmatic (V26-007) и external measurement (V26-011)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-003</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
       <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>отчёт по каналу с долями и причинами; RLS scope advertiser [ui_smoke: `tests/ui-smoke/test_rm_ux_010.py`]</t>
+          <t>ADR принят с пометкой designed-not-implemented; код не пишется до OD-021/OD-031 [artifact: `docs/audit/RM-TECH-289-artifact.md (создаётся задачей)`]</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -6459,38 +6459,38 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-004; SC: -; DEC: -. Evidence: новый ui-smoke; tests/behavioral/test_pop_reporting_scope.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-007, REQ-V26-011; SC: SC-ARCH-006; DEC: DEC-001, DEC-018. Evidence: ADR. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-001</t>
+          <t>RM-UX-010</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>external</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Production readiness</t>
+          <t>Service-quality reporting: доля active devices/logical carriers, plan/fact по каналу (analytics.compare)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-003</t>
+          <t>RM-BIZ-003</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
@@ -6502,14 +6502,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+      <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>не запускается автоматически после pilot [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой; OD-025/OD-028)`]</t>
+          <t>отчёт по каналу с долями и причинами; RLS scope advertiser [ui_smoke: `tests/ui-smoke/test_rm_ux_010.py`]</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -6519,14 +6515,14 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): зависит от OD-025 (RTO/RPO) и OD-028 (топология); REQ-OPS-005/006; HA baseline выделен в RM-OPS-003</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-004; SC: -; DEC: -. Evidence: новый ui-smoke; tests/behavioral/test_pop_reporting_scope.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-002</t>
+          <t>RM-OPS-001</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -6536,21 +6532,21 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>external</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Network segmentation: firewall rules по environment + negative reachability tests из device-сегмента</t>
+          <t>Production readiness</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-PILOT-003</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -6562,10 +6558,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>Admin API/PostgreSQL/MinIO/Redis недостижимы из device-сегмента; Gateway только HTTPS/mTLS [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+          <t>не запускается автоматически после pilot [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой; OD-025/OD-028)`]</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -6575,14 +6575,14 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-008; SC: SC-SEC-006; DEC: -. Evidence: reachability test log. Риск регрессии: средний: сеть пилота.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): зависит от OD-025 (RTO/RPO) и OD-028 (топология); REQ-OPS-005/006; HA baseline выделен в RM-OPS-003</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-003</t>
+          <t>RM-OPS-002</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -6592,21 +6592,21 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>external-plan</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Production HA baseline: ≥2 backend, масштабируемый Gateway, standby PostgreSQL, MinIO replication, quarterly restore drill</t>
+          <t>Network segmentation: firewall rules по environment + negative reachability tests из device-сегмента</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-001</t>
+          <t>RM-PILOT-002</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -6615,17 +6615,13 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>production config gate зелёный; restore drill выполнен и записан [command: `tests/test_production_config_gate.py`]; топология утверждена (OD-028), RTO/RPO (OD-025) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>Admin API/PostgreSQL/MinIO/Redis недостижимы из device-сегмента; Gateway только HTTPS/mTLS [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -6635,14 +6631,14 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-006, REQ-ARCH-004; SC: SC-OPS-001, SC-OPS-005; DEC: DEC-012, DEC-015. Evidence: tests/test_production_config_gate.py; drill record. Риск регрессии: высокий. blocked OD-025/OD-028.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-008; SC: SC-SEC-006; DEC: -. Evidence: reachability test log. Риск регрессии: средний: сеть пилота.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-004</t>
+          <t>RM-OPS-003</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -6652,21 +6648,21 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>external-plan</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Rollout entity/state machine и feature flags: planned→lab→canary→staged→paused→completed/rolled_back</t>
+          <t>Production HA baseline: ≥2 backend, масштабируемый Gateway, standby PostgreSQL, MinIO replication, quarterly restore drill</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-OPS-001</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
@@ -6678,10 +6674,14 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>rollback возвращает предыдущую версию; flag отключает функцию; ответственность по OD-010 [behavioral: `tests/integration/test_stand_rollback_drill.py`]</t>
+          <t>production config gate зелёный; restore drill выполнен и записан [command: `tests/test_production_config_gate.py`]; топология утверждена (OD-028), RTO/RPO (OD-025) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -6691,14 +6691,14 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-002; SC: SC-OPS-007; DEC: DEC-008. Evidence: tests/integration/test_stand_rollback_drill.py. Риск регрессии: средний. blocked OD-010.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-006, REQ-ARCH-004; SC: SC-OPS-001, SC-OPS-005; DEC: DEC-012, DEC-015. Evidence: tests/test_production_config_gate.py; drill record. Риск регрессии: высокий. blocked OD-025/OD-028.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-001</t>
+          <t>RM-OPS-004</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -6708,21 +6708,21 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Managed control-plane pilot scope</t>
+          <t>Rollout entity/state machine и feature flags: planned→lab→canary→staged→paused→completed/rolled_back</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Gate-S, Gate-U, RM-ENV-001</t>
+          <t>RM-PILOT-002</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -6731,13 +6731,13 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
+          <t>rollback возвращает предыдущую версию; flag отключает функцию; ответственность по OD-010 [behavioral: `tests/integration/test_stand_rollback_drill.py`]</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -6747,14 +6747,14 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): deps += OD-024 (exit criteria ступеней), REQ-ARCH-004</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-002; SC: SC-OPS-007; DEC: DEC-008. Evidence: tests/integration/test_stand_rollback_drill.py. Риск регрессии: средний. blocked OD-010.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-PILOT-001</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -6764,21 +6764,21 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>external-plan</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Deployment plan/preflight</t>
+          <t>Managed control-plane pilot scope</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-001</t>
+          <t>Gate-S, Gate-U, RM-ENV-001</t>
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
+          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6803,14 +6803,14 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): deps += OD-024 (exit criteria ступеней), REQ-ARCH-004</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002A</t>
+          <t>RM-PILOT-002</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -6820,21 +6820,21 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>external-plan</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Pilot-compose поднимается под ENVIRONMENT=pilot без ручных шагов; verify честный</t>
+          <t>Deployment plan/preflight</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RM-PILOT-001</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
@@ -6843,81 +6843,137 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>pilot-compose из образов коммита под ENVIRONMENT=pilot - db-migrate сам создаёт retail_media_app (NOBYPASSRLS), все сервисы healthy в пределах таймаута, readiness со строгой проверкой роли, identity из образа, device-токен control-api принят device-gateway, конфиг orchestrator-worker грузится; таймаут или любой отказ роняют проверку [command: `CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env &lt;version&gt; &lt;sha&gt;`]; каждый backend-сервис получает из pilot-compose все переменные, которых требует валидатор prod; пустой JWT_AUDIENCE - отказ при старте [command: `python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py`]</t>
+          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/36571330932; verified · command · CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env ci-pilot-smoke &lt;sha&gt;; verified · command · python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>done - PR #12 смержен в develop @ af6810c, push-run develop 36571330932 success 42/42 (решение владельца 2026-09-29). Решение владельца 2026-09-29 (этап RF-05, область RM-PILOT-002, Protected Boundary Docker/deployment с условиями). Находки ревью main@8ad0228: P0-1..P0-5, P1-16, P2-I9, P2-I11, T12 (+ FU5 healthcheck frontend). REQ: REQ-ARCH-004; SC: -; DEC: -. Не покрывает: TLS/reverse proxy (001D), ack/DLQ воркера при ошибке (RF-04), публикацию релиза и verify-pilot-images на GHCR (внешнее действие владельца). Риск регрессии: средний - обязательный JWT_AUDIENCE вне dev; pilot-хосты без него не стартуют.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>RM-PILOT-002A</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Pilot-compose поднимается под ENVIRONMENT=pilot без ручных шагов; verify честный</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>pilot-compose из образов коммита под ENVIRONMENT=pilot - db-migrate сам создаёт retail_media_app (NOBYPASSRLS), все сервисы healthy в пределах таймаута, readiness со строгой проверкой роли, identity из образа, device-токен control-api принят device-gateway, конфиг orchestrator-worker грузится; таймаут или любой отказ роняют проверку [command: `CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env &lt;version&gt; &lt;sha&gt;`]; каждый backend-сервис получает из pilot-compose все переменные, которых требует валидатор prod; пустой JWT_AUDIENCE - отказ при старте [command: `python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py`]</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/36571330932; verified · command · CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env ci-pilot-smoke &lt;sha&gt;; verified · command · python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>done - PR #12 смержен в develop @ af6810c, push-run develop 36571330932 success 42/42 (решение владельца 2026-09-29). Решение владельца 2026-09-29 (этап RF-05, область RM-PILOT-002, Protected Boundary Docker/deployment с условиями). Находки ревью main@8ad0228: P0-1..P0-5, P1-16, P2-I9, P2-I11, T12 (+ FU5 healthcheck frontend). REQ: REQ-ARCH-004; SC: -; DEC: -. Не покрывает: TLS/reverse proxy (001D), ack/DLQ воркера при ошибке (RF-04), публикацию релиза и verify-pilot-images на GHCR (внешнее действие владельца). Риск регрессии: средний - обязательный JWT_AUDIENCE вне dev; pilot-хосты без него не стартуют.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
           <t>RM-PILOT-003</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>POPS</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Controlled pilot deploy</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>RM-PILOT-002</t>
         </is>
       </c>
-      <c r="F113" s="2" t="n">
+      <c r="F114" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr">
         <is>
           <t>deployment</t>
         </is>
       </c>
-      <c r="J113" s="2" t="inlineStr">
+      <c r="J114" s="2" t="inlineStr">
         <is>
           <t>SHA/lock/schema/health, stand-safe journeys, rollback readiness [owner: `docs/audit/&lt;дата&gt;-pilot-deploy-&lt;sha&gt;.md + ACCEPT владельца с датой (deployment gate)`]</t>
         </is>
       </c>
-      <c r="K113" s="2" t="inlineStr">
+      <c r="K114" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L113" s="2" t="inlineStr">
+      <c r="L114" s="2" t="inlineStr">
         <is>
           <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L114"/>
+  <dimension ref="A1:L115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2514,19 +2514,19 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · behavioral · tests/behavioral/test_rm_stab_020_consumer_dlq.py; verified · command · python -m pytest tests/test_rm_stab_020_dlq_and_subjects.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/36865587310</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Решение владельца 2026-09-30, этап RF-10 (mini-design: лимит 7 доставок в приложении, backoff 5с/30с/2м/10м/30м/60м, DLQ - таблица PostgreSQL с FORCE RLS, CLI-повтор через outbox). Решения владельца 2026-10-01 (после ревью): два stream - RMP (campaign.&gt;) и RMP_EVENTS (delivery/pop/emergency/creative_asset, 1 GiB, 7 суток, DiscardOld), чтобы поток PoP не вытеснял неподтверждённые события campaign; durable без серверного фильтра не меняется; риск max_ack_pending=100 при backoff до 60 мин принят (новые события campaign могут ждать до 60 мин после восстановления). Находки ревью main@8ad0228: P1-6.b, P1-7. REQ: - ; SC: -; DEC: -. Protected Boundary: только миграция 038 (downgrade удаляет лишь новую таблицу). Не покрывает: API/UI DLQ, DLQ stub-consumer, SKIP LOCKED outbox (P2-B7), lease/partition order/операции над dead_letter relay (RM-TECH-243). Риск регрессии: низкий - события не-campaign начинают сохраняться в RMP_EVENTS (без потребителя); события consumer после ~1ч43м сбоя уходят в DLQ и требуют replay. Открытый риск (ревью круг 3): provisioning только при старте и только с CAMPAIGN_CONSUMER_ENABLED=true; при его сбое relay стартует, и события без stream через ~1 мин уходят в dead_letter relay - решение владельца.</t>
+          <t>done - PR #14 смержен в develop @ 2151153, push-run develop 36865587310 success 42/42 (решение владельца 2026-10-01). Решение владельца 2026-09-30, этап RF-10 (mini-design: лимит 7 доставок в приложении, backoff 5с/30с/2м/10м/30м/60м, DLQ - таблица PostgreSQL с FORCE RLS, CLI-повтор через outbox). Решения владельца 2026-10-01 (после ревью): два stream - RMP (campaign.&gt;) и RMP_EVENTS (delivery/pop/emergency/creative_asset, 1 GiB, 7 суток, DiscardOld), чтобы поток PoP не вытеснял неподтверждённые события campaign; durable без серверного фильтра не меняется; риск max_ack_pending=100 при backoff до 60 мин принят (новые события campaign могут ждать до 60 мин после восстановления). Находки ревью main@8ad0228: P1-6.b, P1-7. REQ: - ; SC: -; DEC: -. Protected Boundary: только миграция 038 (downgrade удаляет лишь новую таблицу). Не покрывает: API/UI DLQ, DLQ stub-consumer, SKIP LOCKED outbox (P2-B7), lease/partition order/операции над dead_letter relay (RM-TECH-243). Риск регрессии: низкий - события не-campaign начинают сохраняться в RMP_EVENTS (без потребителя); события consumer после ~1ч43м сбоя уходят в DLQ и требуют replay. Открытый риск (ревью круг 3): provisioning только при старте и только с CAMPAIGN_CONSUMER_ENABLED=true; при его сбое relay стартует, и события без stream через ~1 мин уходят в dead_letter relay - решение владельца.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-210</t>
+          <t>RM-STAB-021</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2541,16 +2541,16 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>RLS-контекст на device-маршрутах онбординга</t>
+          <t>Надёжность NATS: JetStream на томе (переживает пересоздание контейнера), provisioning streams обязателен до relay</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-002</t>
+          <t>RM-STAB-020</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
@@ -2559,54 +2559,50 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+          <t>in_progress</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; bootstrap-RLS миграции 037: без RLS-контекста роль приложения видит 0 onboarding codes (fail-closed); со своим app.rmp_device_code — только свою строку; с чужим кодом — 0 [behavioral: `tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap`]</t>
+          <t>в pilot- и phase1-compose JetStream хранит данные в смонтированном томе (-sd = точка монтирования); провижининг при любом NATS_URL, сбой провижининга завершает старт воркера до relay (кроме OUTBOX_RELAY_ALLOW_STUB=true) [command: `python -m pytest tests/test_rm_stab_021_nats_durability.py`]; stream и неподтверждённое сообщение переживают docker compose up --force-recreate nats в pilot-стеке [command: `локальный прогон pilot-стека (журнал RF-11): publish → force-recreate nats → stream_info`]</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py; verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap; verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33408891221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика. 2026-08-31 (стадия S, OD-043: зависимость RM-STAB-002 done): реализовано локально - set_rls_context на /identity/device-codes, bootstrap-контекст кода/fingerprint на /device/onboard, миграция 037 (rehearsal down/up), allowlist элевации снят; targeted 97 passed под ролью приложения; design-gate docs/architecture/rm-tech-210-device-onboarding-rls-bootstrap-design-gate.md (на тот момент - до CI-evidence и owner gate). verification 2026-08-31: CI 33408891221 success (условием done тогда оставался owner gate device_contract). 2026-08-31: приёмка №2 уточнена владельцем — три утверждения bootstrap-RLS (без контекста 0; свой app.rmp_device_code — только свой; чужой — 0); ref → TestRMTech210BootstrapRLS. done 2026-08-31: owner gate device_contract granted - OD-045 (fail-closed контракт принят владельцем).</t>
+          <t>Решение владельца 2026-10-01, этап RF-11 (ревью RF-10 круг 3: provisioning при сбое; NATS без -sd /data - JetStream в /tmp/nats/jetstream контейнера, подтверждено на стенде). REQ: -; SC: -; DEC: -. Protected Boundary: Docker/ deployment - только command NATS в docker-compose.pilot.yml / docker-compose.phase1.yml и описание в backup_manifest.py и runbook. Не покрывает: переподключение relay к NATS во время работы, restore-drill compose, CI. Риск регрессии: низкий - первый старт после обновления начинает с пустого тома (содержимое /tmp контейнера и так терялось); воркер с NATS, но без возможности провижининга, теперь не стартует (restart loop вместо тихого dead_letter).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-005</t>
+          <t>RM-TECH-210</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>retention-policy.yaml + legal decision register (AG): сроки, 152-ФЗ, deletion/archive, review date</t>
+          <t>RLS-контекст на device-маршрутах онбординга</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-253</t>
+          <t>RM-STAB-002</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
@@ -2619,34 +2615,34 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>scope_decision</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>юридическое утверждение retention/152-ФЗ (OD-009) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; bootstrap-RLS миграции 037: без RLS-контекста роль приложения видит 0 onboarding codes (fail-closed); со своим app.rmp_device_code — только свою строку; с чужим кодом — 0 [behavioral: `tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap`]</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py; verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap; verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33408891221</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено POPS → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). 2026-08-31: кандидат docs/product/retention-policy.yaml подготовлен (working defaults REQ-DATA-001, legal register) - не действует до OD-009; задача остаётся blocked.</t>
+          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика. 2026-08-31 (стадия S, OD-043: зависимость RM-STAB-002 done): реализовано локально - set_rls_context на /identity/device-codes, bootstrap-контекст кода/fingerprint на /device/onboard, миграция 037 (rehearsal down/up), allowlist элевации снят; targeted 97 passed под ролью приложения; design-gate docs/architecture/rm-tech-210-device-onboarding-rls-bootstrap-design-gate.md (на тот момент - до CI-evidence и owner gate). verification 2026-08-31: CI 33408891221 success (условием done тогда оставался owner gate device_contract). 2026-08-31: приёмка №2 уточнена владельцем — три утверждения bootstrap-RLS (без контекста 0; свой app.rmp_device_code — только свой; чужой — 0); ref → TestRMTech210BootstrapRLS. done 2026-08-31: owner gate device_contract granted - OD-045 (fail-closed контракт принят владельцем).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-OPS-005</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2661,16 +2657,16 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>SLO objectives и измерение</t>
+          <t>retention-policy.yaml + legal decision register (AG): сроки, 152-ФЗ, deletion/archive, review date</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-253</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
@@ -2679,13 +2675,17 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>каждое число ТЗ имеет formula/window/owner/metric либо `not measurable` [artifact: `docs/product/slo-objectives.yaml`]</t>
+          <t>юридическое утверждение retention/152-ФЗ (OD-009) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2695,14 +2695,14 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288 RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/slo-objectives.yaml - 11 объектов, каждое число §8 с formula/window/owner/status; пороги OD-011/OD-025 open. Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено POPS → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). 2026-08-31: кандидат docs/product/retention-policy.yaml подготовлен (working defaults REQ-DATA-001, legal register) - не действует до OD-009; задача остаётся blocked.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>OpenAPI + event/manifest JSON Schema (AG): as-built генерация + target из §26/AB, contract tests</t>
+          <t>SLO objectives и измерение</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>OpenAPI/event schemas версионированы, examples и deprecation policy; contract tests зелёные [command: `python3 scripts/ci/roadmap-governance-guard.py`]; одна canonical opaque идентификация на версию API; alias {id} с deprecation date [behavioral: `tests/behavioral/test_rm_tech_220.py`]</t>
+          <t>каждое число ТЗ имеет formula/window/owner/metric либо `not measurable` [artifact: `docs/product/slo-objectives.yaml`]</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2751,14 +2751,14 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/api/openapi-as-built-v1.json (113 paths/128 ops/149 схем), target docs/architecture/api/openapi-target-v2.6.md, envelope docs/architecture/events/event-envelope-v1.schema.json; contract tests и версионирование - после старта задачи; задача planned до Gate-S (OD-043).</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288 RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/slo-objectives.yaml - 11 объектов, каждое число §8 с formula/window/owner/status; пороги OD-011/OD-025 open. Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-221</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2773,16 +2773,16 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Разделение User/Device/analytics/emergency API; device client не достигает admin</t>
+          <t>OpenAPI + event/manifest JSON Schema (AG): as-built генерация + target из §26/AB, contract tests</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>device JWT → admin endpoint = 403 на всех admin-роутах [behavioral: `tests/test_phase3_protected_identity.py`]</t>
+          <t>OpenAPI/event schemas версионированы, examples и deprecation policy; contract tests зелёные [command: `python3 scripts/ci/roadmap-governance-guard.py`]; одна canonical opaque идентификация на версию API; alias {id} с deprecation date [behavioral: `tests/behavioral/test_rm_tech_220.py`]</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2807,14 +2807,14 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-002; SC: SC-API-002; DEC: -. Evidence: tests/test_phase3_protected_identity.py; новый negative. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/api/openapi-as-built-v1.json (113 paths/128 ops/149 схем), target docs/architecture/api/openapi-target-v2.6.md, envelope docs/architecture/events/event-envelope-v1.schema.json; contract tests и версионирование - после старта задачи; задача planned до Gate-S (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-222</t>
+          <t>RM-TECH-221</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Канонический POST /api/v1/pop/batch, legacy /device/pop/batch как alias с deprecation</t>
+          <t>Разделение User/Device/analytics/emergency API; device client не достигает admin</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>ответы канонического и legacy идентичны; deprecation header; batch&gt;500 → 422; чужой device_id отклонён [behavioral: `tests/test_contract_pop.py`]</t>
+          <t>device JWT → admin endpoint = 403 на всех admin-роутах [behavioral: `tests/test_phase3_protected_identity.py`]</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2863,14 +2863,14 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-003, REQ-POP-003; SC: SC-API-003, SC-POP-003; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_edge002fu_real_endpoint.py. Риск регрессии: средний: runtime/плеер использует legacy path.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-002; SC: SC-API-002; DEC: -. Evidence: tests/test_phase3_protected_identity.py; новый negative. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-223</t>
+          <t>RM-TECH-222</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Manifest field contract и ACK-состояния runtime (opaque media_ref, no MinIO keys)</t>
+          <t>Канонический POST /api/v1/pop/batch, legacy /device/pop/batch как alias с deprecation</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2906,14 +2906,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>все обязательные поля §25 REQ-MAN-004 в schema; внутренний object key не раскрыт; 6 ACK states принимаются [behavioral: `tests/test_contract_manifest.py`]</t>
+          <t>ответы канонического и legacy идентичны; deprecation header; batch&gt;500 → 422; чужой device_id отклонён [behavioral: `tests/test_contract_pop.py`]</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2923,14 +2919,14 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-MAN-004; SC: SC-MAN-001; DEC: -. Evidence: tests/test_contract_manifest.py; tests/behavioral/test_edge002_manifest_delivery.py. Риск регрессии: высокий: меняет device-facing контракт — owner gate device_contract.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-003, REQ-POP-003; SC: SC-API-003, SC-POP-003; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_edge002fu_real_endpoint.py. Риск регрессии: средний: runtime/плеер использует legacy path.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-223</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2945,7 +2941,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat contract POST /api/v1/device/heartbeat: дедуп, scope, clock drift, freshness thresholds</t>
+          <t>Manifest field contract и ACK-состояния runtime (opaque media_ref, no MinIO keys)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2973,7 +2969,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>валидный/повтор/чужой scope/просроченный heartbeat дают ожидаемые результаты; legacy alias с той же семантикой [behavioral: `tests/behavioral/test_edge004_heartbeat.py`]</t>
+          <t>все обязательные поля §25 REQ-MAN-004 в schema; внутренний object key не раскрыт; 6 ACK states принимаются [behavioral: `tests/test_contract_manifest.py`]</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2983,14 +2979,14 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-009; SC: SC-OPS-002; DEC: -. Evidence: tests/behavioral/test_edge004_heartbeat.py. Риск регрессии: высокий: device-facing.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-MAN-004; SC: SC-MAN-001; DEC: -. Evidence: tests/test_contract_manifest.py; tests/behavioral/test_edge002_manifest_delivery.py. Риск регрессии: высокий: меняет device-facing контракт — owner gate device_contract.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3005,16 +3001,16 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>PoP duplicate semantics по OD-019: 200 + per-event duplicate/409, amendment ADR-017</t>
+          <t>Heartbeat contract POST /api/v1/device/heartbeat: дедуп, scope, clock drift, freshness thresholds</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-222</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
@@ -3026,10 +3022,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>ADR-017 amendment принят; behavioral: повтор batch → per-event duplicate, summary не удвоен, порядок хронологический [behavioral: `tests/behavioral/test_edge003_pop_ingestion.py`]</t>
+          <t>валидный/повтор/чужой scope/просроченный heartbeat дают ожидаемые результаты; legacy alias с той же семантикой [behavioral: `tests/behavioral/test_edge004_heartbeat.py`]</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3039,14 +3039,14 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-002; SC: SC-POP-002; DEC: DEC-024. Evidence: tests/behavioral/test_edge003_pop_ingestion.py; ADR-017 amendment. Риск регрессии: низкий: закрепляет текущее поведение.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-009; SC: SC-OPS-002; DEC: -. Evidence: tests/behavioral/test_edge004_heartbeat.py. Риск регрессии: высокий: device-facing.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-226</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3061,16 +3061,16 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Proof model: pop_mode error/not_applied — schema/runtime migration из compatibility projection</t>
+          <t>PoP duplicate semantics по OD-019: 200 + per-event duplicate/409, amendment ADR-017</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-222</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -3082,14 +3082,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>ProofMode содержит 9 значений; отчёт не смешивает playback/apply/delivery/error [behavioral: `tests/behavioral/test_pop_schema.py`]</t>
+          <t>ADR-017 amendment принят; behavioral: повтор batch → per-event duplicate, summary не удвоен, порядок хронологический [behavioral: `tests/behavioral/test_edge003_pop_ingestion.py`]</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3099,14 +3095,14 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-001; SC: SC-POP-001; DEC: -. Evidence: tests/behavioral/test_pop_schema.py; migration. Риск регрессии: средний: enum migration + отчёты.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-002; SC: SC-POP-002; DEC: DEC-024. Evidence: tests/behavioral/test_edge003_pop_ingestion.py; ADR-017 amendment. Риск регрессии: низкий: закрепляет текущее поведение.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-227</t>
+          <t>RM-TECH-226</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3121,7 +3117,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Валидация proof_event_v1: playback_result/failure_reason, clock-drift quarantine, no internal IDs/PII</t>
+          <t>Proof model: pop_mode error/not_applied — schema/runtime migration из compatibility projection</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3142,10 +3138,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>недопустимый playback_result/внутренний ID/сдвиг часов → 422 или quarantine; SHA/signature проверены [behavioral: `tests/test_contract_pop.py`]</t>
+          <t>ProofMode содержит 9 значений; отчёт не смешивает playback/apply/delivery/error [behavioral: `tests/behavioral/test_pop_schema.py`]</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3155,14 +3155,14 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-004; SC: SC-POP-004; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_pop_schema.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-001; SC: SC-POP-001; DEC: -. Evidence: tests/behavioral/test_pop_schema.py; migration. Риск регрессии: средний: enum migration + отчёты.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-228</t>
+          <t>RM-TECH-227</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3177,16 +3177,16 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Окно совместимости device/API/manifest: heartbeat объявляет версии, сервер выбирает представление</t>
+          <t>Валидация proof_event_v1: playback_result/failure_reason, clock-drift quarantine, no internal IDs/PII</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>совместимая версия выбрана по объявленным capabilities; breaking change без staged rollout отклонён contract-тестом [behavioral: `tests/test_version_identity.py`]</t>
+          <t>недопустимый playback_result/внутренний ID/сдвиг часов → 422 или quarantine; SHA/signature проверены [behavioral: `tests/test_contract_pop.py`]</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3211,14 +3211,14 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-003; SC: SC-NFR-003; DEC: -. Evidence: tests/test_version_identity.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-004; SC: SC-POP-004; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_pop_schema.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-228</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3228,21 +3228,21 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>ERD + data dictionary + migration plan (AG): инвентарь сущностей §15, retailer_id NOT NULL + двухуровневый RLS</t>
+          <t>Окно совместимости device/API/manifest: heartbeat объявляет версии, сервер выбирает представление</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>as-built ERD из моделей; каждая группа §15 присутствует или имеет migration task; tenant-таблицы с retailer_id+FK+RLS [artifact: `tests/behavioral/test_adr018_multitenancy_rls.py`]; behavioral RLS proof под ролью приложения NOBYPASSRLS [behavioral: `tests/behavioral/test_adr018_multitenancy_rls.py`]</t>
+          <t>совместимая версия выбрана по объявленным capabilities; breaking change без staged rollout отклонён contract-тестом [behavioral: `tests/test_version_identity.py`]</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -3267,14 +3267,14 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/erd/data-dictionary-as-built.md (62 таблицы, 38 RLS) и кандидат docs/architecture/erd/migration-plan-v2.6.md (§13 → present/missing → задачи); PII/retention колонки - RM-TECH-253/RM-OPS-005. Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-003; SC: SC-NFR-003; DEC: -. Evidence: tests/test_version_identity.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-230</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Channel Adapter contract (design-only до второго канала): versioned task, receipt, proof/ack, error, health, mock mode</t>
+          <t>ERD + data dictionary + migration plan (AG): инвентарь сущностей §15, retailer_id NOT NULL + двухуровневый RLS</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3313,7 +3313,7 @@
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>contract spec + JSON Schema без реализации adapter/mock (ADR-019) [artifact: `docs/architecture contract`]</t>
+          <t>as-built ERD из моделей; каждая группа §15 присутствует или имеет migration task; tenant-таблицы с retailer_id+FK+RLS [artifact: `tests/behavioral/test_adr018_multitenancy_rls.py`]; behavioral RLS proof под ролью приложения NOBYPASSRLS [behavioral: `tests/behavioral/test_adr018_multitenancy_rls.py`]</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3323,14 +3323,14 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-006; SC: SC-ORCH-005; DEC: -. Evidence: docs/architecture contract; schema. Риск регрессии: низкий: только документ.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/erd/data-dictionary-as-built.md (62 таблицы, 38 RLS) и кандидат docs/architecture/erd/migration-plan-v2.6.md (§13 → present/missing → задачи); PII/retention колонки - RM-TECH-253/RM-OPS-005. Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-231</t>
+          <t>RM-TECH-230</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3345,16 +3345,16 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>channel-capability-matrix.yaml (AG) для первого канала KSO: channel/surface/rendition/proof/SLA/vendor constraints</t>
+          <t>Channel Adapter contract (design-only до второго канала): versioned task, receipt, proof/ack, error, health, mock mode</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-230</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -3366,14 +3366,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>матрица покрывает KSO channel/surface/rendition/proof/SLA/vendor constraints; каждая строка ссылается на REQ-CHAN-*/REQ-MAN-*/REQ-POP-* [artifact: `docs/product/channel-capability-matrix.yaml`]; артефакт принят владельцем как часть handoff-пакета AG [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>contract spec + JSON Schema без реализации adapter/mock (ADR-019) [artifact: `docs/architecture contract`]</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3383,14 +3379,14 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-012 (предложение 2026-08-31): AG требует channel-capability-matrix до старта разработки, а RM-TECH-261 держит матрицу за решением OD-021 (второй канал). Первый канал KSO описывается без OD-021; RM-TECH-261 расширяет матрицу вторым каналом. REQ: REQ-CHAN-001, REQ-CHAN-002, REQ-CHAN-003; SC: SC-CHAN-002; DEC: DEC-001 (расширение). Evidence: артефакт; ACCEPT владельца. Риск регрессии: нет (документ). Утверждена OD-042 (2026-08-31). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/channel-capability-matrix.yaml (KSO + declared каналы §7); приёмка - внутри задачи после Gate-S.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-006; SC: SC-ORCH-005; DEC: -. Evidence: docs/architecture contract; schema. Риск регрессии: низкий: только документ.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-253</t>
+          <t>RM-TECH-231</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3405,12 +3401,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Data protection: data classes, lawful purpose, минимизация PII, residency; retention по OD-009</t>
+          <t>channel-capability-matrix.yaml (AG) для первого канала KSO: channel/surface/rendition/proof/SLA/vendor constraints</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-230</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
@@ -3426,10 +3422,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>реестр data classes для всех сущностей; новая PII-сущность без класса — красный design-gate [artifact: `docs/architecture data classes`]</t>
+          <t>матрица покрывает KSO channel/surface/rendition/proof/SLA/vendor constraints; каждая строка ссылается на REQ-CHAN-*/REQ-MAN-*/REQ-POP-* [artifact: `docs/product/channel-capability-matrix.yaml`]; артефакт принят владельцем как часть handoff-пакета AG [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: docs/architecture data classes. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено CORE → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
+          <t>RM-GOV-012 (предложение 2026-08-31): AG требует channel-capability-matrix до старта разработки, а RM-TECH-261 держит матрицу за решением OD-021 (второй канал). Первый канал KSO описывается без OD-021; RM-TECH-261 расширяет матрицу вторым каналом. REQ: REQ-CHAN-001, REQ-CHAN-002, REQ-CHAN-003; SC: SC-CHAN-002; DEC: DEC-001 (расширение). Evidence: артефакт; ACCEPT владельца. Риск регрессии: нет (документ). Утверждена OD-042 (2026-08-31). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/channel-capability-matrix.yaml (KSO + declared каналы §7); приёмка - внутри задачи после Gate-S.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-288</t>
+          <t>RM-TECH-253</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3456,21 +3456,21 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>nfr-slo.yaml + load-profiles.yaml (AG): method, percentile, error budget, generator, CI evidence</t>
+          <t>Data protection: data classes, lawful purpose, минимизация PII, residency; retention по OD-009</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>каждый SLO имеет window/denominator/exclusions; load generator и прогон в CI/стенде [artifact: `nfr-slo.yaml`]</t>
+          <t>реестр data classes для всех сущностей; новая PII-сущность без класса — красный design-gate [artifact: `docs/architecture data classes`]</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -3495,14 +3495,14 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки):ы docs/product/nfr-slo.yaml и docs/product/load-profiles.yaml (7 профилей); load generator отсутствует (new). Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: docs/architecture data classes. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено CORE → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-011</t>
+          <t>RM-TECH-288</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3517,16 +3517,16 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>role-scope-matrix.yaml + portal-route-matrix.yaml + journeys/ (AG) из seed/pg_policies/registry</t>
+          <t>nfr-slo.yaml + load-profiles.yaml (AG): method, percentile, error budget, generator, CI evidence</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004, RM-STAB-006</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>матрицы генерируются и сверяются guard; deny-cases покрыты behavioral [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+          <t>каждый SLO имеет window/denominator/exclusions; load generator и прогон в CI/стенде [artifact: `nfr-slo.yaml`]</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -3551,19 +3551,19 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено U → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/product/role-scope-matrix.yaml (5 seeded ролей × 30 permissions, Q2 target 7 ролей, 38 RLS-таблиц, deny-cases), docs/product/portal-route-matrix.yaml (admin 16 + advertiser 9 маршрутов), docs/product/journeys/journeys.yaml (79 journeys, нормативный формат); generated-сверка guard - после старта задачи; задача planned до Gate-S (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки):ы docs/product/nfr-slo.yaml и docs/product/load-profiles.yaml (7 профилей); load generator отсутствует (new). Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-001</t>
+          <t>RM-UX-011</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3573,16 +3573,16 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Записать managed-first scope</t>
+          <t>role-scope-matrix.yaml + portal-route-matrix.yaml + journeys/ (AG) из seed/pg_policies/registry</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-STAB-004, RM-STAB-006</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>roadmap явно исключает `self.campaign_create` из ближайшего control-plane pilot [artifact: `docs/product/roadmap.yaml (pilot scope)`]</t>
+          <t>матрицы генерируются и сверяются guard; deny-cases покрыты behavioral [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3607,14 +3607,14 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): ссылки OD-005/DEC-011, REQ-SCOPE-001</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено U → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/product/role-scope-matrix.yaml (5 seeded ролей × 30 permissions, Q2 target 7 ролей, 38 RLS-таблиц, deny-cases), docs/product/portal-route-matrix.yaml (admin 16 + advertiser 9 маршрутов), docs/product/journeys/journeys.yaml (79 journeys, нормативный формат); generated-сверка guard - после старта задачи; задача planned до Gate-S (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201</t>
+          <t>RM-BIZ-001</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Таксономия причин недопоказа</t>
+          <t>Записать managed-first scope</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>8 категорий ТЗ, source/report/history contract и owner-approved artifact [artifact: `docs/product/underdelivery-reason-taxonomy.yaml`]</t>
+          <t>roadmap явно исключает `self.campaign_create` из ближайшего control-plane pilot [artifact: `docs/product/roadmap.yaml (pilot scope)`]</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3663,14 +3663,14 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): ссылки OD-005/DEC-011, REQ-SCOPE-001</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202</t>
+          <t>RM-TECH-201</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3680,21 +3680,21 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Вытеснение и объяснимые приоритеты</t>
+          <t>Таксономия причин недопоказа</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>versioned rules [behavioral: `tests/behavioral/test_campaign_preemption.py`]</t>
+          <t>8 категорий ТЗ, source/report/history contract и owner-approved artifact [artifact: `docs/product/underdelivery-reason-taxonomy.yaml`]</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3719,14 +3719,14 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-007 и порядок приоритета §12; исключение §3.1 (OD-018) — единственная точка изменения engine → RM-TECH-285 зависит от неё</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-203</t>
+          <t>RM-TECH-202</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3741,16 +3741,16 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Overbooking policy</t>
+          <t>Вытеснение и объяснимые приоритеты</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202</t>
+          <t>RM-TECH-201</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>default deny [behavioral: `tests/behavioral/test_inventory_overbooking_policy.py`]</t>
+          <t>versioned rules [behavioral: `tests/behavioral/test_campaign_preemption.py`]</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3775,14 +3775,14 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-007 и порядок приоритета §12; исключение §3.1 (OD-018) — единственная точка изменения engine → RM-TECH-285 зависит от неё</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-204</t>
+          <t>RM-TECH-203</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3797,16 +3797,16 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Creative QA без неутверждённого HTML5</t>
+          <t>Overbooking policy</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-202</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>metadata/antivirus/executable deny и immutable QA result [behavioral: `tests/behavioral/test_creative_qa.py`]</t>
+          <t>default deny [behavioral: `tests/behavioral/test_inventory_overbooking_policy.py`]</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-206</t>
+          <t>RM-TECH-204</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>License renewal/grant boundary</t>
+          <t>Creative QA без неутверждённого HTML5</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>атомарная семантика §1.6 [behavioral: `tests/behavioral/test_license_renewal_boundary.py`]</t>
+          <t>metadata/antivirus/executable deny и immutable QA result [behavioral: `tests/behavioral/test_creative_qa.py`]</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>RM-TECH-206</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3909,16 +3909,16 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Универсальная иерархия носителей: migration + seed network/branch/cluster/store/store_group/channel/device/surface</t>
+          <t>License renewal/grant boundary</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -3930,14 +3930,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>все уровни существуют с FK и RLS; seed заполняет иерархию; чужой scope не видит [behavioral: `tests/behavioral/test_scope_rls.py`]</t>
+          <t>атомарная семантика §1.6 [behavioral: `tests/behavioral/test_license_renewal_boundary.py`]</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3947,14 +3943,14 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-001; SC: SC-DATA-001; DEC: -. Evidence: migration; tests/behavioral/test_scope_rls.py. Риск регрессии: высокий: схема ядра.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-241</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3969,16 +3965,16 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Target resolution boundary: broad target → display_surface_id, запрет physical_device_id как target</t>
+          <t>Универсальная иерархия носителей: migration + seed network/branch/cluster/store/store_group/channel/device/surface</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -3990,10 +3986,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>планирование разрешает target до surface; physical_device_id в target отклоняется [behavioral: `tests/test_s089_inventory_simulation.py`]</t>
+          <t>все уровни существуют с FK и RLS; seed заполняет иерархию; чужой scope не видит [behavioral: `tests/behavioral/test_scope_rls.py`]</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -4003,14 +4003,14 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-003; SC: SC-ARCH-002; DEC: -. Evidence: tests/test_s089_inventory_simulation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-001; SC: SC-DATA-001; DEC: -. Evidence: migration; tests/behavioral/test_scope_rls.py. Риск регрессии: высокий: схема ядра.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-242</t>
+          <t>RM-TECH-241</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Outbox для любой OLTP-записи с domain event; revocation/refresh manifest при pause/archive/expiry</t>
+          <t>Target resolution boundary: broad target → display_surface_id, запрет physical_device_id как target</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>каждая доменная мутация создаёт outbox event в той же транзакции; pause/archive порождают revocation [behavioral: `tests/behavioral/test_outbox.py`]</t>
+          <t>планирование разрешает target до surface; physical_device_id в target отклоняется [behavioral: `tests/test_s089_inventory_simulation.py`]</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -4059,14 +4059,14 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-003; SC: SC-ORCH-002; DEC: -. Evidence: tests/behavioral/test_outbox.py. Риск регрессии: средний: транзакционные границы всех сервисов.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-003; SC: SC-ARCH-002; DEC: -. Evidence: tests/test_s089_inventory_simulation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-243</t>
+          <t>RM-TECH-242</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4081,16 +4081,16 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Outbox relay: lease/publishing, Nats-Msg-Id, 7 попыток → dead_letter, partition order, DLQ policy, no PII</t>
+          <t>Outbox для любой OLTP-записи с domain event; revocation/refresh manifest при pause/archive/expiry</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-242</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>7 отказов брокера → dead_letter с operator action; ack → published; replay идемпотентен [behavioral: `tests/behavioral/test_outbox_relay.py`]; NATS recovery integration зелёный [command: `tests/behavioral/test_outbox_relay.py`]</t>
+          <t>каждая доменная мутация создаёт outbox event в той же транзакции; pause/archive порождают revocation [behavioral: `tests/behavioral/test_outbox.py`]</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4115,14 +4115,14 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-004; SC: SC-ORCH-003; DEC: DEC-004. Evidence: tests/behavioral/test_outbox_relay.py; tests/integration/test_nats_recovery.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-003; SC: SC-ORCH-002; DEC: -. Evidence: tests/behavioral/test_outbox.py. Риск регрессии: средний: транзакционные границы всех сервисов.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-244</t>
+          <t>RM-TECH-243</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4137,16 +4137,16 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Adapter task lifecycle через persisted queue (event-driven массовая публикация)</t>
+          <t>Outbox relay: lease/publishing, Nats-Msg-Id, 7 попыток → dead_letter, partition order, DLQ policy, no PII</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-243</t>
+          <t>RM-TECH-242</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>активация на 1000 устройств не ждёт устройств; задачи агрегируют статусы [behavioral: `tests/behavioral/test_delivery_foundation.py`]</t>
+          <t>7 отказов брокера → dead_letter с operator action; ack → published; replay идемпотентен [behavioral: `tests/behavioral/test_outbox_relay.py`]; NATS recovery integration зелёный [command: `tests/behavioral/test_outbox_relay.py`]</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-002; SC: SC-ORCH-006; DEC: DEC-004. Evidence: tests/behavioral/test_delivery_foundation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-004; SC: SC-ORCH-003; DEC: DEC-004. Evidence: tests/behavioral/test_outbox_relay.py; tests/integration/test_nats_recovery.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-TECH-244</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4193,16 +4193,16 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Campaign lifecycle по ADR-015/OD-036: scheduled, resume, revise, archive; единый guard и audit</t>
+          <t>Adapter task lifecycle через persisted queue (event-driven массовая публикация)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-TECH-243</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
@@ -4214,14 +4214,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>_CAMPAIGN_TRANSITIONS = ADR-015; каждый переход через guard с audit; возврат в draft создаёт revision [behavioral: `tests/behavioral/test_campaign_domain.py`]; campaign.* smokes зелёные после изменения [ui_smoke: `tests/ui-smoke/test_rm_tech_245.py`]</t>
+          <t>активация на 1000 устройств не ждёт устройств; задачи агрегируют статусы [behavioral: `tests/behavioral/test_delivery_foundation.py`]</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -4231,14 +4227,14 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-010; SC: -; DEC: DEC-025. Evidence: tests/behavioral/test_campaign_domain.py; tests/ui-smoke/test_uismoke__campaign__*.py. Риск регрессии: высокий: меняет runtime enum кампании и UI.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-002; SC: SC-ORCH-006; DEC: DEC-004. Evidence: tests/behavioral/test_delivery_foundation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-246</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4253,7 +4249,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Commerce order: отмена по OD-020 (draft→cancelled, confirmed — reversal), payment projection отдельно</t>
+          <t>Campaign lifecycle по ADR-015/OD-036: scheduled, resume, revise, archive; единый guard и audit</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -4274,10 +4270,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>_ORDER_TRANSITIONS: draft→cancelled разрешён, confirmed→cancelled запрещён, reversal с audit [behavioral: `tests/test_commerce_a2.py`]</t>
+          <t>_CAMPAIGN_TRANSITIONS = ADR-015; каждый переход через guard с audit; возврат в draft создаёт revision [behavioral: `tests/behavioral/test_campaign_domain.py`]; campaign.* smokes зелёные после изменения [ui_smoke: `tests/ui-smoke/test_rm_tech_245.py`]</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -4287,14 +4287,14 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-014; SC: -; DEC: DEC-017, DEC-026. Evidence: tests/test_commerce_a2.py; tests/behavioral/test_commerce_rls.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-010; SC: -; DEC: DEC-025. Evidence: tests/behavioral/test_campaign_domain.py; tests/ui-smoke/test_uismoke__campaign__*.py. Риск регрессии: высокий: меняет runtime enum кампании и UI.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-247</t>
+          <t>RM-TECH-246</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4309,16 +4309,16 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Approval policy: required roles/scope/порядок/timeout per campaign/placement/creative</t>
+          <t>Commerce order: отмена по OD-020 (draft→cancelled, confirmed — reversal), payment projection отдельно</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>политика версионирована; submit/approve соблюдают порядок и timeout; negative для чужого scope [behavioral: `tests/behavioral/test_campaign_approval.py`]</t>
+          <t>_ORDER_TRANSITIONS: draft→cancelled разрешён, confirmed→cancelled запрещён, reversal с audit [behavioral: `tests/test_commerce_a2.py`]</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -4343,14 +4343,14 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-003; SC: -; DEC: -. Evidence: tests/behavioral/test_campaign_approval.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-014; SC: -; DEC: DEC-017, DEC-026. Evidence: tests/test_commerce_a2.py; tests/behavioral/test_commerce_rls.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-248</t>
+          <t>RM-TECH-247</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Flight/placement windows: versioned start_at/end_at UTC, проверка при simulation/manifest/runtime</t>
+          <t>Approval policy: required roles/scope/порядок/timeout per campaign/placement/creative</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>показ вне окна запрещён на трёх уровнях; DST/праздники/closed stores — версионированные правила [behavioral: `tests/test_s063_pop_timezone.py`]</t>
+          <t>политика версионирована; submit/approve соблюдают порядок и timeout; negative для чужого scope [behavioral: `tests/behavioral/test_campaign_approval.py`]</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-005, REQ-NFR-002; SC: SC-NFR-002; DEC: -. Evidence: tests/test_s063_pop_timezone.py; новый behavioral. Риск регрессии: высокий: расписание доставки.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-003; SC: -; DEC: -. Evidence: tests/behavioral/test_campaign_approval.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-249</t>
+          <t>RM-TECH-248</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4421,16 +4421,16 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Manifest eligibility: approved status + валидный flight/contract + resolved target + readiness</t>
+          <t>Flight/placement windows: versioned start_at/end_at UTC, проверка при simulation/manifest/runtime</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-248</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>неэлигибельная кампания не попадает в manifest; причина объяснима [behavioral: `tests/behavioral/test_delivery_generation.py`]</t>
+          <t>показ вне окна запрещён на трёх уровнях; DST/праздники/closed stores — версионированные правила [behavioral: `tests/test_s063_pop_timezone.py`]</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -4455,14 +4455,14 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-006; SC: -; DEC: -. Evidence: tests/behavioral/test_delivery_generation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-005, REQ-NFR-002; SC: SC-NFR-002; DEC: -. Evidence: tests/test_s063_pop_timezone.py; новый behavioral. Риск регрессии: высокий: расписание доставки.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-250</t>
+          <t>RM-TECH-249</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4477,16 +4477,16 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Creative/rendition state machine и immutable media history (uploaded→scanning→qa_failed/approved→superseded→retained)</t>
+          <t>Manifest eligibility: approved status + валидный flight/contract + resolved target + readiness</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-204</t>
+          <t>RM-TECH-248</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -4498,14 +4498,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>каждая версия хранит uploader/SHA-256/QA-решение/связь; закрытый отчёт воспроизводим после logical delete [behavioral: `tests/behavioral/test_creative_assets.py`]</t>
+          <t>неэлигибельная кампания не попадает в manifest; причина объяснима [behavioral: `tests/behavioral/test_delivery_generation.py`]</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -4515,14 +4511,14 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CONT-002; SC: SC-DATA-002; DEC: -. Evidence: tests/behavioral/test_creative_assets.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-006; SC: -; DEC: -. Evidence: tests/behavioral/test_delivery_generation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-251</t>
+          <t>RM-TECH-250</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4537,16 +4533,16 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Data ownership/lineage: immutable versioning и diff campaign/placement/playlist, словарь владельцев</t>
+          <t>Creative/rendition state machine и immutable media history (uploaded→scanning→qa_failed/approved→superseded→retained)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-204</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -4558,10 +4554,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>сохранение создаёт версию с diff и actor; предыдущая неизменяема [behavioral: `tests/behavioral/test_rm_tech_251.py`]</t>
+          <t>каждая версия хранит uploader/SHA-256/QA-решение/связь; закрытый отчёт воспроизводим после logical delete [behavioral: `tests/behavioral/test_creative_assets.py`]</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -4571,14 +4571,14 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-001; SC: SC-DATA-004; DEC: DEC-007. Evidence: новый behavioral. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CONT-002; SC: SC-DATA-002; DEC: -. Evidence: tests/behavioral/test_creative_assets.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-252</t>
+          <t>RM-TECH-251</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4593,16 +4593,16 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Identity: AD/LDAP или SSO для internal staff, MFA до production (OD-008)</t>
+          <t>Data ownership/lineage: immutable versioning и diff campaign/placement/playlist, словарь владельцев</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -4614,14 +4614,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>protected_boundary</t>
-        </is>
-      </c>
+      <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>логин через IdP; production-профиль без MFA отклоняет; TLS-профиль зафиксирован [behavioral: `tests/test_phase3_auth_api.py`]</t>
+          <t>сохранение создаёт версию с diff и actor; предыдущая неизменяема [behavioral: `tests/behavioral/test_rm_tech_251.py`]</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -4631,14 +4627,14 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-001; SC: SC-SEC-008; DEC: -. Evidence: tests/test_phase3_auth_api.py; tests/behavioral/test_auth_dual_e2e.py. Риск регрессии: высокий: вход всех пользователей.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-001; SC: SC-DATA-004; DEC: DEC-007. Evidence: новый behavioral. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-254</t>
+          <t>RM-TECH-252</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4653,16 +4649,16 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Emergency state machine: requested→authorized→dispatching→applied→resuming→closed, MFA+reason, приоритетный канал</t>
+          <t>Identity: AD/LDAP или SSO для internal staff, MFA до production (OD-008)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -4674,10 +4670,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>protected_boundary</t>
+        </is>
+      </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>emergency с причиной; per-target result; audit actor/reason/affected; resume возвращает штатный manifest [behavioral: `tests/test_phase3_emergency_api.py`]; emergency.* smokes зелёные [ui_smoke: `tests/ui-smoke/test_uismoke__emergency__activate.py`]</t>
+          <t>логин через IdP; production-профиль без MFA отклоняет; TLS-профиль зафиксирован [behavioral: `tests/test_phase3_auth_api.py`]</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -4687,14 +4687,14 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-007; SC: SC-OPS-003; DEC: -. Evidence: tests/test_phase3_emergency_api.py; tests/ui-smoke/test_uismoke__emergency__activate.py. Риск регрессии: высокий: аварийный контур.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-001; SC: SC-SEC-008; DEC: -. Evidence: tests/test_phase3_auth_api.py; tests/behavioral/test_auth_dual_e2e.py. Риск регрессии: высокий: вход всех пользователей.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-255</t>
+          <t>RM-TECH-254</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4709,16 +4709,16 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Device health/commands: пороги статусов по профилю, per-device view, команды с подтверждением</t>
+          <t>Emergency state machine: requested→authorized→dispatching→applied→resuming→closed, MFA+reason, приоритетный канал</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>online→degraded→offline по порогам; команда доставлена и подтверждена [behavioral: `tests/behavioral/test_rm_tech_255.py`]; device.health_view smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__device__health_view.py`]</t>
+          <t>emergency с причиной; per-target result; audit actor/reason/affected; resume возвращает штатный manifest [behavioral: `tests/test_phase3_emergency_api.py`]; emergency.* smokes зелёные [ui_smoke: `tests/ui-smoke/test_uismoke__emergency__activate.py`]</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -4743,19 +4743,19 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-001; SC: SC-OPS-006; DEC: -. Evidence: tests/ui-smoke/test_uismoke__device__health_view.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-007; SC: SC-OPS-003; DEC: -. Evidence: tests/test_phase3_emergency_api.py; tests/ui-smoke/test_uismoke__emergency__activate.py. Риск регрессии: высокий: аварийный контур.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-002</t>
+          <t>RM-TECH-255</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4765,16 +4765,16 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>`self.campaign_create` в будущей ветке</t>
+          <t>Device health/commands: пороги статусов по профилю, per-device view, команды с подтверждением</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-001</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -4783,17 +4783,13 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>mini-design, journey, backend/UI/RLS, intended-role smoke, walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__campaign_create.py`]</t>
+          <t>online→degraded→offline по порогам; команда доставлена и подтверждена [behavioral: `tests/behavioral/test_rm_tech_255.py`]; device.health_view smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__device__health_view.py`]</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -4803,14 +4799,14 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2). RM-GOV-009 (OD-037): blocked до OD-013 — полный self-service вне pilot scope (REQ-V26-003, OD-005)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-001; SC: SC-OPS-006; DEC: -. Evidence: tests/ui-smoke/test_uismoke__device__health_view.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001</t>
+          <t>RM-BIZ-002</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4825,16 +4821,16 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Accessibility оставшихся форм + route matrix (A3)</t>
+          <t>`self.campaign_create` в будущей ветке</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-BIZ-001</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -4843,13 +4839,17 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>labels/ARIA/axe/targeted vitest [artifact: `docs/product/ux-route-matrix.yaml`]</t>
+          <t>mini-design, journey, backend/UI/RLS, intended-role smoke, walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__campaign_create.py`]</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2). RM-GOV-009 (OD-037): blocked до OD-013 — полный self-service вне pilot scope (REQ-V26-003, OD-005)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-002</t>
+          <t>RM-UX-001</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4881,16 +4881,16 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Поиск/сортировка/усечение таблиц (A2)</t>
+          <t>Accessibility оставшихся форм + route matrix (A3)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>server semantics для pagination [ui_smoke: `tests/ui-smoke/test_uismoke__campaign__create.py`]</t>
+          <t>labels/ARIA/axe/targeted vitest [artifact: `docs/product/ux-route-matrix.yaml`]</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-003</t>
+          <t>RM-UX-002</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4937,16 +4937,16 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Responsive-проверка (A4)</t>
+          <t>Поиск/сортировка/усечение таблиц (A2)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-002</t>
+          <t>RM-UX-001</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>все routes из `ux-route-matrix.yaml` проверены на 390px без overflow/crop [artifact: `docs/product/ux-responsive-report.yaml`]</t>
+          <t>server semantics для pagination [ui_smoke: `tests/ui-smoke/test_uismoke__campaign__create.py`]</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-004</t>
+          <t>RM-UX-003</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4993,16 +4993,16 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Согласованность состояний и терминов (A6)</t>
+          <t>Responsive-проверка (A4)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-003</t>
+          <t>RM-UX-002</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>route matrix покрывает empty/loading/error/403/success и locale-key check [artifact: `docs/product/ux-route-matrix.yaml (states coverage)`]</t>
+          <t>все routes из `ux-route-matrix.yaml` проверены на 390px без overflow/crop [artifact: `docs/product/ux-responsive-report.yaml`]</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -5034,7 +5034,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-005</t>
+          <t>RM-UX-004</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -5049,16 +5049,16 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Adoption доказанных primitives малыми slices (A1b)</t>
+          <t>Согласованность состояний и терминов (A6)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-004</t>
+          <t>RM-UX-003</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>каждый slice имеет отдельный diff/test/review [ci_job: `frontend`]</t>
+          <t>route matrix покрывает empty/loading/error/403/success и locale-key check [artifact: `docs/product/ux-route-matrix.yaml (states coverage)`]</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-006</t>
+          <t>RM-UX-005</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5105,16 +5105,16 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Advertiser-web UX audit/fixes (A5)</t>
+          <t>Adoption доказанных primitives малыми slices (A1b)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-005</t>
+          <t>RM-UX-004</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>versioned `docs/product/advertiser-route-matrix.yaml` с точным списком 15 routes [artifact: `docs/product/advertiser-route-matrix.yaml`]</t>
+          <t>каждый slice имеет отдельный diff/test/review [ci_job: `frontend`]</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-007</t>
+          <t>RM-UX-006</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -5156,21 +5156,21 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Human operator walkthrough (A7)</t>
+          <t>Advertiser-web UX audit/fixes (A5)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001, RM-UX-002, RM-UX-003, RM-UX-004, RM-UX-005, RM-UX-006</t>
+          <t>RM-UX-005</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>человек проходит exact stand bundle [human: `PROJECT_STATE.md строка `operator walkthrough` (AGENTS.md правило 8); сценарии docs/product/operator-walkthrough-dev.md`]</t>
+          <t>versioned `docs/product/advertiser-route-matrix.yaml` с точным списком 15 routes [artifact: `docs/product/advertiser-route-matrix.yaml`]</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -5195,14 +5195,14 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) ПРИОСТАНОВЛЕНО владельцем 2026-08-31 (OD-041) до выравнивания ТЗ/roadmap/gates и утверждения единого плана реализации; не закрывать, done не ставить.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-008</t>
+          <t>RM-UX-007</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5212,21 +5212,21 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Campaign readiness matrix по каналам (rendition/inventory/conflicts/forecast/PoP mode/SLA) с действием на blocked</t>
+          <t>Human operator walkthrough (A7)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-249, RM-UX-004</t>
+          <t>RM-UX-001, RM-UX-002, RM-UX-003, RM-UX-004, RM-UX-005, RM-UX-006</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>экран согласования показывает матрицу; каждый blocked/warning ведёт к действию [ui_smoke: `tests/ui-smoke/test_rm_ux_008.py`]</t>
+          <t>человек проходит exact stand bundle [human: `PROJECT_STATE.md строка `operator walkthrough` (AGENTS.md правило 8); сценарии docs/product/operator-walkthrough-dev.md`]</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -5251,14 +5251,14 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-004; SC: SC-UX-002; DEC: -. Evidence: новый ui-smoke; vitest. Риск регрессии: средний.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) ПРИОСТАНОВЛЕНО владельцем 2026-08-31 (OD-041) до выравнивания ТЗ/roadmap/gates и утверждения единого плана реализации; не закрывать, done не ставить.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-009</t>
+          <t>RM-UX-008</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -5273,16 +5273,16 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Договор рекламодателя: immutable file versions, server-side SHA-256, legal status (юр. решение)</t>
+          <t>Campaign readiness matrix по каналам (rendition/inventory/conflicts/forecast/PoP mode/SLA) с действием на blocked</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-250</t>
+          <t>RM-TECH-249, RM-UX-004</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>повторная загрузка создаёт новую версию, SHA проверен сервером; старая версия неизменяема [behavioral: `tests/test_advertiser_contracts.py`]; advertiser.contract_crud smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py`]</t>
+          <t>экран согласования показывает матрицу; каждый blocked/warning ведёт к действию [ui_smoke: `tests/ui-smoke/test_rm_ux_008.py`]</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -5307,38 +5307,38 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-017; SC: -; DEC: -. Evidence: tests/test_advertiser_contracts.py; tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-004; SC: SC-UX-002; DEC: -. Evidence: новый ui-smoke; vitest. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207A</t>
+          <t>RM-UX-009</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>KSO environment + player/playlist design</t>
+          <t>Договор рекламодателя: immutable file versions, server-side SHA-256, legal status (юр. решение)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-250</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
@@ -5350,14 +5350,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>versioned environment audit, import/contract mini-design и test plan [artifact: `docs/architecture/kso-environment-audit.md`]</t>
+          <t>повторная загрузка создаёт новую версию, SHA проверен сервером; старая версия неизменяема [behavioral: `tests/test_advertiser_contracts.py`]; advertiser.contract_crud smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py`]</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -5367,14 +5363,14 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-STAND-003 feasibility gate явно в acceptance; ADR-019/OD-022</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-017; SC: -; DEC: -. Evidence: tests/test_advertiser_contracts.py; tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-207A</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -5384,21 +5380,21 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>KSO player/playlist/PoP chain</t>
+          <t>KSO environment + player/playlist design</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207A</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -5412,12 +5408,12 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>device_contract</t>
+          <t>scope_decision</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>contract tests и playback→manifest→PoP behavioral proof [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; Playlist entity и state machine §6 ТЗ (draft → validating → valid/invalid → approved → published → superseded/rolled_back); published immutable [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; manifest target lifecycle (generated → signed → queued → delivered → applied/failed/expired) и canonical POST /api/v1/pop/batch [behavioral: `tests/behavioral/test_kso_playback_chain.py`]</t>
+          <t>versioned environment audit, import/contract mini-design и test plan [artifact: `docs/architecture/kso-environment-audit.md`]</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -5427,14 +5423,14 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-STAND-003 feasibility gate явно в acceptance; ADR-019/OD-022</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-208</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5449,16 +5445,16 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Signed licensing Layer 2</t>
+          <t>KSO player/playlist/PoP chain</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-206, RM-TECH-207B, RM-STAB-010</t>
+          <t>RM-TECH-207A</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
@@ -5472,12 +5468,12 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>protected_boundary</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Ed25519 offline verify, kid/rotation/revocation, UI, tamper/rollback [behavioral: `tests/behavioral/test_signed_license_layer2.py`]</t>
+          <t>contract tests и playback→manifest→PoP behavioral proof [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; Playlist entity и state machine §6 ТЗ (draft → validating → valid/invalid → approved → published → superseded/rolled_back); published immutable [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; manifest target lifecycle (generated → signed → queued → delivered → applied/failed/expired) и canonical POST /api/v1/pop/batch [behavioral: `tests/behavioral/test_kso_playback_chain.py`]</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -5494,7 +5490,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-260</t>
+          <t>RM-TECH-208</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5509,12 +5505,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Runtime cache lifecycle: лимит по профилю, детерминированная очистка, last-known-good</t>
+          <t>Signed licensing Layer 2</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-206, RM-TECH-207B, RM-STAB-010</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
@@ -5532,12 +5528,12 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>device_contract</t>
+          <t>protected_boundary</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>кэш на лимите: очистка по правилу; last-known-good сохранён; просроченная реклама не показывается [behavioral: `tests/behavioral/test_rm_tech_260.py`]</t>
+          <t>Ed25519 offline verify, kid/rotation/revocation, UI, tamper/rollback [behavioral: `tests/behavioral/test_signed_license_layer2.py`]</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -5547,14 +5543,14 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-008; SC: SC-EDGE-002; DEC: -. Evidence: runtime simulator tests. Риск регрессии: средний: плеер.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-261</t>
+          <t>RM-TECH-260</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5564,17 +5560,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Второй канал: решение OD-021 + channel-capability-matrix.yaml (AG); extraction design по ADR-019</t>
+          <t>Runtime cache lifecycle: лимит по профилю, детерминированная очистка, last-known-good</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B, RM-TECH-230</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
@@ -5587,17 +5583,17 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>scope_decision</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>владелец назвал канал и владельца (OD-021); матрица возможностей утверждена [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; extraction design: KSO-вертикаль как первый adapter без поломки контрактов [artifact: `docs/audit/RM-TECH-261-artifact.md (создаётся задачей)`]</t>
+          <t>кэш на лимите: очистка по правилу; last-known-good сохранён; просроченная реклама не показывается [behavioral: `tests/behavioral/test_rm_tech_260.py`]</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -5607,14 +5603,14 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CHAN-001, REQ-ORCH-005; SC: SC-CHAN-002, SC-ORCH-004; DEC: DEC-001, DEC-002. Evidence: OD-021; design doc. Риск регрессии: высокий: рефакторинг KSO-вертикали. blocked до OD-021; Orchestrator/Adapter Layer/mock не создаются раньше (ADR-019/OD-022).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-008; SC: SC-EDGE-002; DEC: -. Evidence: runtime simulator tests. Риск регрессии: средний: плеер.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-262</t>
+          <t>RM-TECH-261</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5624,21 +5620,21 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Dynamic creative binding/rendition safety (V26-008) на одном канале</t>
+          <t>Второй канал: решение OD-021 + channel-capability-matrix.yaml (AG); extraction design по ADR-019</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280, RM-TECH-261</t>
+          <t>RM-TECH-207B, RM-TECH-230</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -5647,13 +5643,17 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>master-confirmed price/promo подставляется при manifest generation; SLA-тест dynamic manifest [behavioral: `tests/behavioral/test_rm_tech_262.py`]</t>
+          <t>владелец назвал канал и владельца (OD-021); матрица возможностей утверждена [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; extraction design: KSO-вертикаль как первый adapter без поломки контрактов [artifact: `docs/audit/RM-TECH-261-artifact.md (создаётся задачей)`]</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -5663,14 +5663,14 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-008; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. ложная ESL-посылка снимается prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CHAN-001, REQ-ORCH-005; SC: SC-CHAN-002, SC-ORCH-004; DEC: DEC-001, DEC-002. Evidence: OD-021; design doc. Риск регрессии: высокий: рефакторинг KSO-вертикали. blocked до OD-021; Orchestrator/Adapter Layer/mock не создаются раньше (ADR-019/OD-022).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-263</t>
+          <t>RM-TECH-262</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5685,16 +5685,16 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Field mobile operations: scoped mobile web для сотрудника магазина (устройства, фото, инциденты)</t>
+          <t>Dynamic creative binding/rendition safety (V26-008) на одном канале</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-210, RM-TECH-255</t>
+          <t>RM-TECH-280, RM-TECH-261</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>journey field_ops.device_confirm под ролью магазина с RLS; negative чужой магазин [ui_smoke: `tests/ui-smoke/test_rm_tech_263.py`]</t>
+          <t>master-confirmed price/promo подставляется при manifest generation; SLA-тест dynamic manifest [behavioral: `tests/behavioral/test_rm_tech_262.py`]</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -5719,14 +5719,14 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-009; SC: -; DEC: -. Evidence: new ui-smoke. Риск регрессии: средний. prerequisite RM-TECH-210 (RLS device) - planned по зависимости; feature field_ops.device_confirm blocked до задачи (RM-GOV-012 выравнивание: blocked = решение владельца/внешний факт, а не зависимость).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-008; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. ложная ESL-посылка снимается prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-264</t>
+          <t>RM-TECH-263</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5741,16 +5741,16 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>ESL/price-checker: интеграция только через approved price/SKU master (INT-002)</t>
+          <t>Field mobile operations: scoped mobile web для сотрудника магазина (устройства, фото, инциденты)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-210, RM-TECH-255</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>price-related данные приходят из master или проходят reconciliation; расхождение блокирует показ [behavioral: `tests/behavioral/test_rm_tech_264.py`]</t>
+          <t>journey field_ops.device_confirm под ролью магазина с RLS; negative чужой магазин [ui_smoke: `tests/ui-smoke/test_rm_tech_263.py`]</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -5775,38 +5775,38 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. OD-023 approved 2026-08-31 - planned после RM-TECH-280.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-009; SC: -; DEC: -. Evidence: new ui-smoke. Риск регрессии: средний. prerequisite RM-TECH-210 (RLS device) - planned по зависимости; feature field_ops.device_confirm blocked до задачи (RM-GOV-012 выравнивание: blocked = решение владельца/внешний факт, а не зависимость).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>RM-TECH-264</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>ESL/price-checker: интеграция только через approved price/SKU master (INT-002)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
           <t>RM-TECH-280</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>design</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Prerequisite: master-data adapter цен/SKU (контракт, owner OD-023, reconciliation)</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>RM-TECH-229</t>
-        </is>
-      </c>
       <c r="F94" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
@@ -5818,14 +5818,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>владелец master-данных назначен (OD-023 approved); contract + reconciliation design утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; adapter в mock/test mode проходит contract tests [behavioral: `tests/behavioral/test_rm_tech_280.py`]</t>
+          <t>price-related данные приходят из master или проходят reconciliation; расхождение блокирует показ [behavioral: `tests/behavioral/test_rm_tech_264.py`]</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -5835,34 +5831,34 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: OD-023; contract tests. Риск регрессии: средний. отсутствующий prerequisite по AQ.1 №5; OD-023 approved 2026-08-31 (роль Product Data Owner) - planned; owner gate: контракт/scope adapter.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. OD-023 approved 2026-08-31 - planned после RM-TECH-280.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-003</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>`self.report_view` plan/fact</t>
+          <t>Prerequisite: master-data adapter цен/SKU (контракт, owner OD-023, reconciliation)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201, RM-TECH-207B</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
@@ -5878,10 +5874,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>реальные PoP/причины/RLS, journey/smoke/walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__report_view.py`]</t>
+          <t>владелец master-данных назначен (OD-023 approved); contract + reconciliation design утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; adapter в mock/test mode проходит contract tests [behavioral: `tests/behavioral/test_rm_tech_280.py`]</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -5891,14 +5891,14 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-011; зависит от RM-TECH-207B (реальные PoP) — без изменений</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: OD-023; contract tests. Риск регрессии: средний. отсутствующий prerequisite по AQ.1 №5; OD-023 approved 2026-08-31 (роль Product Data Owner) - planned; owner gate: контракт/scope adapter.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-209</t>
+          <t>RM-BIZ-003</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5908,17 +5908,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>ClickHouse capacity trigger</t>
+          <t>`self.report_view` plan/fact</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-201, RM-TECH-207B</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
@@ -5937,7 +5937,7 @@
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>измеряемый PoP rate/retention threshold и owner migration gate [artifact: `docs/product/clickhouse-capacity-trigger.yaml`]</t>
+          <t>реальные PoP/причины/RLS, journey/smoke/walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__report_view.py`]</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -5947,14 +5947,14 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-011; зависит от RM-TECH-207B (реальные PoP) — без изменений</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-256</t>
+          <t>RM-TECH-209</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5969,16 +5969,16 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Business outcome KPI: baseline/target/metric definition для целей §1.2 (OD-024 exit criteria)</t>
+          <t>ClickHouse capacity trigger</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
@@ -5990,14 +5990,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>каждая бизнес-цель имеет baseline/target/формулу/владельца, утверждено владельцем [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>измеряемый PoP rate/retention threshold и owner migration gate [artifact: `docs/product/clickhouse-capacity-trigger.yaml`]</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -6007,14 +6003,14 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-013; SC: -; DEC: DEC-010. Evidence: artifact kpi register. Риск регрессии: низкий.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-281</t>
+          <t>RM-TECH-256</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -6024,21 +6020,21 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: sales-reference ingestion (агрегаты store/SKU/day) + методология baseline/test-control</t>
+          <t>Business outcome KPI: baseline/target/metric definition для целей §1.2 (OD-024 exit criteria)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
@@ -6050,10 +6046,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>пакетная загрузка агрегатов без PII; versioned baseline; методика утверждена владельцем [behavioral: `tests/behavioral/test_rm_tech_281.py`]</t>
+          <t>каждая бизнес-цель имеет baseline/target/формулу/владельца, утверждено владельцем [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -6063,14 +6063,14 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-001; SC: -; DEC: -. Evidence: new behavioral; methodology doc. Риск регрессии: средний. prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-013; SC: -; DEC: DEC-010. Evidence: artifact kpi register. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-282</t>
+          <t>RM-TECH-281</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -6085,16 +6085,16 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Attribution &amp; sales lift: test/control, versioned baseline, pilot lift report</t>
+          <t>Prerequisite: sales-reference ingestion (агрегаты store/SKU/day) + методология baseline/test-control</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-281, RM-TECH-229</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -6103,13 +6103,13 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>pilot lift report по test/control с explainable методикой; RLS scope [behavioral: `tests/behavioral/test_rm_tech_282.py`]</t>
+          <t>пакетная загрузка агрегатов без PII; versioned baseline; методика утверждена владельцем [behavioral: `tests/behavioral/test_rm_tech_281.py`]</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -6119,14 +6119,14 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-002; SC: -; DEC: DEC-005, DEC-027. Evidence: new behavioral; report. Риск регрессии: средний. blocked OD-014 (DEC-027); OD-023 approved 2026-08-31.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-001; SC: -; DEC: -. Evidence: new behavioral; methodology doc. Риск регрессии: средний. prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-283</t>
+          <t>RM-TECH-282</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -6136,21 +6136,21 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: audience source/privacy contract (анонимные store-атрибуты, 152-ФЗ, OD-032)</t>
+          <t>Attribution &amp; sales lift: test/control, versioned baseline, pilot lift report</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280, RM-TECH-253</t>
+          <t>RM-TECH-281, RM-TECH-229</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -6162,14 +6162,10 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>privacy/legal решение (OD-032) и контракт источника утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>pilot lift report по test/control с explainable методикой; RLS scope [behavioral: `tests/behavioral/test_rm_tech_282.py`]</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -6179,14 +6175,14 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-005; SC: -; DEC: DEC-005, DEC-019. Evidence: OD-032; contract. Риск регрессии: низкий. blocked OD-032 (DEC-019); OD-023 approved 2026-08-31.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-002; SC: -; DEC: DEC-005, DEC-027. Evidence: new behavioral; report. Риск регрессии: средний. blocked OD-014 (DEC-027); OD-023 approved 2026-08-31.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-284</t>
+          <t>RM-TECH-283</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -6196,21 +6192,21 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>A/B attribution и winner metric (minimum sample, owner approval результата)</t>
+          <t>Prerequisite: audience source/privacy contract (анонимные store-атрибуты, 152-ФЗ, OD-032)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-282</t>
+          <t>RM-TECH-280, RM-TECH-253</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
@@ -6222,10 +6218,14 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>A/B фиксирует группы/период/метрику; winner только при minimum sample и ручном утверждении [behavioral: `tests/behavioral/test_rm_tech_284.py`]</t>
+          <t>privacy/legal решение (OD-032) и контракт источника утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -6235,14 +6235,14 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-012, REQ-V26-010; SC: -; DEC: DEC-027. Evidence: new behavioral. Риск регрессии: средний. blocked OD-014 (DEC-027) - методика winner metric не утверждена.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-005; SC: -; DEC: DEC-005, DEC-019. Evidence: OD-032; contract. Риск регрессии: низкий. blocked OD-032 (DEC-019); OD-023 approved 2026-08-31.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-285</t>
+          <t>RM-TECH-284</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -6257,16 +6257,16 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Competitive separation: competitive_category, интервал/исключение в playlist/manifest (исключение §3.1 по OD-018)</t>
+          <t>A/B attribution и winner metric (minimum sample, owner approval результата)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202, RM-TECH-280</t>
+          <t>RM-TECH-282</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -6275,13 +6275,13 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>separation block/override test; изменение priority engine ограничено §3.1 [behavioral: `tests/behavioral/test_rm_tech_285.py`]</t>
+          <t>A/B фиксирует группы/период/метрику; winner только при minimum sample и ручном утверждении [behavioral: `tests/behavioral/test_rm_tech_284.py`]</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -6291,14 +6291,14 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-004; SC: -; DEC: DEC-005, DEC-022. Evidence: new behavioral. Риск регрессии: высокий: priority engine. OD-023 approved 2026-08-31, DEC-022 = OD-018 approved - planned после RM-TECH-280.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-012, REQ-V26-010; SC: -; DEC: DEC-027. Evidence: new behavioral. Риск регрессии: средний. blocked OD-014 (DEC-027) - методика winner metric не утверждена.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-286</t>
+          <t>RM-TECH-285</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -6313,16 +6313,16 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Financial-system exchange: versioned/idempotent export + payment-status contract (после DEC-017)</t>
+          <t>Competitive separation: competitive_category, интервал/исключение в playlist/manifest (исключение §3.1 по OD-018)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-246</t>
+          <t>RM-TECH-202, RM-TECH-280</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -6331,13 +6331,13 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>idempotent export round-trip; повтор не создаёт дубликатов; scope финансового контура зафиксирован [behavioral: `tests/behavioral/test_rm_tech_286.py`]</t>
+          <t>separation block/override test; изменение priority engine ограничено §3.1 [behavioral: `tests/behavioral/test_rm_tech_285.py`]</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -6347,14 +6347,14 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-006, REQ-BIZ-009; SC: -; DEC: DEC-017. Evidence: new behavioral. Риск регрессии: средний. blocked OD-030.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-004; SC: -; DEC: DEC-005, DEC-022. Evidence: new behavioral. Риск регрессии: высокий: priority engine. OD-023 approved 2026-08-31, DEC-022 = OD-018 approved - planned после RM-TECH-280.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-287</t>
+          <t>RM-TECH-286</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -6369,16 +6369,16 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>BI/export/SIEM/vendor API: scoped keys, rate-limit, immutable audit, circuit breaker (после DEC-013)</t>
+          <t>Financial-system exchange: versioned/idempotent export + payment-status contract (после DEC-017)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-013</t>
+          <t>RM-TECH-246</t>
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>401/403/429 negative; vendor connector с отдельными credentials и failure mode [behavioral: `tests/test_s065_rate_limit.py`]</t>
+          <t>idempotent export round-trip; повтор не создаёт дубликатов; scope финансового контура зафиксирован [behavioral: `tests/behavioral/test_rm_tech_286.py`]</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -6403,14 +6403,14 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-003; SC: SC-SEC-002; DEC: DEC-013. Evidence: tests/test_s065_rate_limit.py; new behavioral. Риск регрессии: средний. blocked OD-026.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-006, REQ-BIZ-009; SC: -; DEC: DEC-017. Evidence: new behavioral. Риск регрессии: средний. blocked OD-030.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-289</t>
+          <t>RM-TECH-287</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -6420,21 +6420,21 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Extension points designed-not-implemented: ADR для programmatic (V26-007) и external measurement (V26-011)</t>
+          <t>BI/export/SIEM/vendor API: scoped keys, rate-limit, immutable audit, circuit breaker (после DEC-013)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-STAB-013</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
@@ -6443,13 +6443,13 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>ADR принят с пометкой designed-not-implemented; код не пишется до OD-021/OD-031 [artifact: `docs/audit/RM-TECH-289-artifact.md (создаётся задачей)`]</t>
+          <t>401/403/429 negative; vendor connector с отдельными credentials и failure mode [behavioral: `tests/test_s065_rate_limit.py`]</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -6459,14 +6459,14 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-007, REQ-V26-011; SC: SC-ARCH-006; DEC: DEC-001, DEC-018. Evidence: ADR. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-003; SC: SC-SEC-002; DEC: DEC-013. Evidence: tests/test_s065_rate_limit.py; new behavioral. Риск регрессии: средний. blocked OD-026.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-010</t>
+          <t>RM-TECH-289</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -6476,21 +6476,21 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Service-quality reporting: доля active devices/logical carriers, plan/fact по каналу (analytics.compare)</t>
+          <t>Extension points designed-not-implemented: ADR для programmatic (V26-007) и external measurement (V26-011)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-003</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
       <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>отчёт по каналу с долями и причинами; RLS scope advertiser [ui_smoke: `tests/ui-smoke/test_rm_ux_010.py`]</t>
+          <t>ADR принят с пометкой designed-not-implemented; код не пишется до OD-021/OD-031 [artifact: `docs/audit/RM-TECH-289-artifact.md (создаётся задачей)`]</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -6515,38 +6515,38 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-004; SC: -; DEC: -. Evidence: новый ui-smoke; tests/behavioral/test_pop_reporting_scope.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-007, REQ-V26-011; SC: SC-ARCH-006; DEC: DEC-001, DEC-018. Evidence: ADR. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-001</t>
+          <t>RM-UX-010</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>external</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Production readiness</t>
+          <t>Service-quality reporting: доля active devices/logical carriers, plan/fact по каналу (analytics.compare)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-003</t>
+          <t>RM-BIZ-003</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -6558,14 +6558,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+      <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>не запускается автоматически после pilot [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой; OD-025/OD-028)`]</t>
+          <t>отчёт по каналу с долями и причинами; RLS scope advertiser [ui_smoke: `tests/ui-smoke/test_rm_ux_010.py`]</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -6575,14 +6571,14 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): зависит от OD-025 (RTO/RPO) и OD-028 (топология); REQ-OPS-005/006; HA baseline выделен в RM-OPS-003</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-004; SC: -; DEC: -. Evidence: новый ui-smoke; tests/behavioral/test_pop_reporting_scope.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-002</t>
+          <t>RM-OPS-001</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -6592,21 +6588,21 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>external</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Network segmentation: firewall rules по environment + negative reachability tests из device-сегмента</t>
+          <t>Production readiness</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-PILOT-003</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -6618,10 +6614,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>Admin API/PostgreSQL/MinIO/Redis недостижимы из device-сегмента; Gateway только HTTPS/mTLS [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+          <t>не запускается автоматически после pilot [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой; OD-025/OD-028)`]</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -6631,14 +6631,14 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-008; SC: SC-SEC-006; DEC: -. Evidence: reachability test log. Риск регрессии: средний: сеть пилота.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): зависит от OD-025 (RTO/RPO) и OD-028 (топология); REQ-OPS-005/006; HA baseline выделен в RM-OPS-003</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-003</t>
+          <t>RM-OPS-002</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -6648,21 +6648,21 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>external-plan</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Production HA baseline: ≥2 backend, масштабируемый Gateway, standby PostgreSQL, MinIO replication, quarterly restore drill</t>
+          <t>Network segmentation: firewall rules по environment + negative reachability tests из device-сегмента</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-001</t>
+          <t>RM-PILOT-002</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
@@ -6671,17 +6671,13 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>production config gate зелёный; restore drill выполнен и записан [command: `tests/test_production_config_gate.py`]; топология утверждена (OD-028), RTO/RPO (OD-025) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>Admin API/PostgreSQL/MinIO/Redis недостижимы из device-сегмента; Gateway только HTTPS/mTLS [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -6691,14 +6687,14 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-006, REQ-ARCH-004; SC: SC-OPS-001, SC-OPS-005; DEC: DEC-012, DEC-015. Evidence: tests/test_production_config_gate.py; drill record. Риск регрессии: высокий. blocked OD-025/OD-028.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-008; SC: SC-SEC-006; DEC: -. Evidence: reachability test log. Риск регрессии: средний: сеть пилота.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-004</t>
+          <t>RM-OPS-003</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -6708,21 +6704,21 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>external-plan</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Rollout entity/state machine и feature flags: planned→lab→canary→staged→paused→completed/rolled_back</t>
+          <t>Production HA baseline: ≥2 backend, масштабируемый Gateway, standby PostgreSQL, MinIO replication, quarterly restore drill</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-OPS-001</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -6734,10 +6730,14 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>rollback возвращает предыдущую версию; flag отключает функцию; ответственность по OD-010 [behavioral: `tests/integration/test_stand_rollback_drill.py`]</t>
+          <t>production config gate зелёный; restore drill выполнен и записан [command: `tests/test_production_config_gate.py`]; топология утверждена (OD-028), RTO/RPO (OD-025) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -6747,14 +6747,14 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-002; SC: SC-OPS-007; DEC: DEC-008. Evidence: tests/integration/test_stand_rollback_drill.py. Риск регрессии: средний. blocked OD-010.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-006, REQ-ARCH-004; SC: SC-OPS-001, SC-OPS-005; DEC: DEC-012, DEC-015. Evidence: tests/test_production_config_gate.py; drill record. Риск регрессии: высокий. blocked OD-025/OD-028.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-001</t>
+          <t>RM-OPS-004</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -6764,21 +6764,21 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Managed control-plane pilot scope</t>
+          <t>Rollout entity/state machine и feature flags: planned→lab→canary→staged→paused→completed/rolled_back</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Gate-S, Gate-U, RM-ENV-001</t>
+          <t>RM-PILOT-002</t>
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
@@ -6787,13 +6787,13 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
+          <t>rollback возвращает предыдущую версию; flag отключает функцию; ответственность по OD-010 [behavioral: `tests/integration/test_stand_rollback_drill.py`]</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6803,14 +6803,14 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): deps += OD-024 (exit criteria ступеней), REQ-ARCH-004</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-002; SC: SC-OPS-007; DEC: DEC-008. Evidence: tests/integration/test_stand_rollback_drill.py. Риск регрессии: средний. blocked OD-010.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-PILOT-001</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -6820,21 +6820,21 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>external-plan</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Deployment plan/preflight</t>
+          <t>Managed control-plane pilot scope</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-001</t>
+          <t>Gate-S, Gate-U, RM-ENV-001</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
+          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -6859,14 +6859,14 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): deps += OD-024 (exit criteria ступеней), REQ-ARCH-004</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002A</t>
+          <t>RM-PILOT-002</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -6876,21 +6876,21 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>external-plan</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Pilot-compose поднимается под ENVIRONMENT=pilot без ручных шагов; verify честный</t>
+          <t>Deployment plan/preflight</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RM-PILOT-001</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
@@ -6899,81 +6899,137 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>pilot-compose из образов коммита под ENVIRONMENT=pilot - db-migrate сам создаёт retail_media_app (NOBYPASSRLS), все сервисы healthy в пределах таймаута, readiness со строгой проверкой роли, identity из образа, device-токен control-api принят device-gateway, конфиг orchestrator-worker грузится; таймаут или любой отказ роняют проверку [command: `CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env &lt;version&gt; &lt;sha&gt;`]; каждый backend-сервис получает из pilot-compose все переменные, которых требует валидатор prod; пустой JWT_AUDIENCE - отказ при старте [command: `python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py`]</t>
+          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/36571330932; verified · command · CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env ci-pilot-smoke &lt;sha&gt;; verified · command · python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>done - PR #12 смержен в develop @ af6810c, push-run develop 36571330932 success 42/42 (решение владельца 2026-09-29). Решение владельца 2026-09-29 (этап RF-05, область RM-PILOT-002, Protected Boundary Docker/deployment с условиями). Находки ревью main@8ad0228: P0-1..P0-5, P1-16, P2-I9, P2-I11, T12 (+ FU5 healthcheck frontend). REQ: REQ-ARCH-004; SC: -; DEC: -. Не покрывает: TLS/reverse proxy (001D), ack/DLQ воркера при ошибке (RF-04), публикацию релиза и verify-pilot-images на GHCR (внешнее действие владельца). Риск регрессии: средний - обязательный JWT_AUDIENCE вне dev; pilot-хосты без него не стартуют.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>RM-PILOT-002A</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Pilot-compose поднимается под ENVIRONMENT=pilot без ручных шагов; verify честный</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>pilot-compose из образов коммита под ENVIRONMENT=pilot - db-migrate сам создаёт retail_media_app (NOBYPASSRLS), все сервисы healthy в пределах таймаута, readiness со строгой проверкой роли, identity из образа, device-токен control-api принят device-gateway, конфиг orchestrator-worker грузится; таймаут или любой отказ роняют проверку [command: `CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env &lt;version&gt; &lt;sha&gt;`]; каждый backend-сервис получает из pilot-compose все переменные, которых требует валидатор prod; пустой JWT_AUDIENCE - отказ при старте [command: `python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py`]</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/36571330932; verified · command · CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env ci-pilot-smoke &lt;sha&gt;; verified · command · python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>done - PR #12 смержен в develop @ af6810c, push-run develop 36571330932 success 42/42 (решение владельца 2026-09-29). Решение владельца 2026-09-29 (этап RF-05, область RM-PILOT-002, Protected Boundary Docker/deployment с условиями). Находки ревью main@8ad0228: P0-1..P0-5, P1-16, P2-I9, P2-I11, T12 (+ FU5 healthcheck frontend). REQ: REQ-ARCH-004; SC: -; DEC: -. Не покрывает: TLS/reverse proxy (001D), ack/DLQ воркера при ошибке (RF-04), публикацию релиза и verify-pilot-images на GHCR (внешнее действие владельца). Риск регрессии: средний - обязательный JWT_AUDIENCE вне dev; pilot-хосты без него не стартуют.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
           <t>RM-PILOT-003</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>POPS</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Controlled pilot deploy</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>RM-PILOT-002</t>
         </is>
       </c>
-      <c r="F114" s="2" t="n">
+      <c r="F115" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr">
         <is>
           <t>deployment</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr">
+      <c r="J115" s="2" t="inlineStr">
         <is>
           <t>SHA/lock/schema/health, stand-safe journeys, rollback readiness [owner: `docs/audit/&lt;дата&gt;-pilot-deploy-&lt;sha&gt;.md + ACCEPT владельца с датой (deployment gate)`]</t>
         </is>
       </c>
-      <c r="K114" s="2" t="inlineStr">
+      <c r="K115" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L114" s="2" t="inlineStr">
+      <c r="L115" s="2" t="inlineStr">
         <is>
           <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L115"/>
+  <dimension ref="A1:L117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2570,19 +2570,19 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · command · python -m pytest tests/test_rm_stab_021_nats_durability.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/37295565157</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Решение владельца 2026-10-01, этап RF-11 (ревью RF-10 круг 3: provisioning при сбое; NATS без -sd /data - JetStream в /tmp/nats/jetstream контейнера, подтверждено на стенде). REQ: -; SC: -; DEC: -. Protected Boundary: Docker/ deployment - только command NATS в docker-compose.pilot.yml / docker-compose.phase1.yml и описание в backup_manifest.py и runbook. Не покрывает: переподключение relay к NATS во время работы, restore-drill compose, CI. Риск регрессии: низкий - первый старт после обновления начинает с пустого тома (содержимое /tmp контейнера и так терялось); воркер с NATS, но без возможности провижининга, теперь не стартует (restart loop вместо тихого dead_letter).</t>
+          <t>done - PR #15 смержен в develop @ e2e3f63, push-run develop 37295565157 success 42/42 (решение владельца 2026-10-05, вариант «а»; запись внесена этапом RF-12); сохранность stream при force-recreate доказана вручную (журнал RF-11), автоматизации нет. Решение владельца 2026-10-01, этап RF-11 (ревью RF-10 круг 3: provisioning при сбое; NATS без -sd /data - JetStream в /tmp/nats/jetstream контейнера, подтверждено на стенде). REQ: -; SC: -; DEC: -. Protected Boundary: Docker/ deployment - только command NATS в docker-compose.pilot.yml / docker-compose.phase1.yml и описание в backup_manifest.py и runbook. Не покрывает: переподключение relay к NATS во время работы, restore-drill compose, CI. Риск регрессии: низкий - первый старт после обновления начинает с пустого тома (содержимое /tmp контейнера и так терялось); воркер с NATS, но без возможности провижининга, теперь не стартует (restart loop вместо тихого dead_letter).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-210</t>
+          <t>RM-STAB-022</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2597,16 +2597,16 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>RLS-контекст на device-маршрутах онбординга</t>
+          <t>Управление ролями: scoped-роль не даёт глобальных прав, запрет self-assign и назначения ролей выше своей, защита последнего администратора</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-002</t>
+          <t>RM-STAB-003</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -2615,58 +2615,54 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+          <t>in_progress</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; bootstrap-RLS миграции 037: без RLS-контекста роль приложения видит 0 onboarding codes (fail-closed); со своим app.rmp_device_code — только свою строку; с чужим кодом — 0 [behavioral: `tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap`]</t>
+          <t>под retail_media_app (NOBYPASSRLS) - пользователь только со scoped-ролью получает 403 на маршрутах require_permission; назначение роли себе и роли с правами выше своих отклоняется; снятие роли с последнего активного администратора отклоняется [behavioral: `tests/behavioral/test_rm_stab_022_role_escalation.py`]</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py; verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap; verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33408891221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика. 2026-08-31 (стадия S, OD-043: зависимость RM-STAB-002 done): реализовано локально - set_rls_context на /identity/device-codes, bootstrap-контекст кода/fingerprint на /device/onboard, миграция 037 (rehearsal down/up), allowlist элевации снят; targeted 97 passed под ролью приложения; design-gate docs/architecture/rm-tech-210-device-onboarding-rls-bootstrap-design-gate.md (на тот момент - до CI-evidence и owner gate). verification 2026-08-31: CI 33408891221 success (условием done тогда оставался owner gate device_contract). 2026-08-31: приёмка №2 уточнена владельцем — три утверждения bootstrap-RLS (без контекста 0; свой app.rmp_device_code — только свой; чужой — 0); ref → TestRMTech210BootstrapRLS. done 2026-08-31: owner gate device_contract granted - OD-045 (fail-closed контракт принят владельцем).</t>
+          <t>Решение владельца 2026-10-05, этап RF-12 (находки P0-6, P1-11.a, T2 ревью main @ 8ad0228; сверка RF-00). REQ: -; SC: -; DEC: -. Mini-design одобрен владельцем 2026-10-05 с дополнениями (журнал RF-12). Не покрывает: привязку прав к конкретной организации рекламодателя (P0-8, T3), T7, фронтенд (P1-11.b), RM-STAB-004, RM-STAB-015. Риск регрессии: средний - пользователи только со scoped-ролями теряют доступ к маршрутам require_permission (перечень - журнал RF-12, раздел Мини-дизайн, М5).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-005</t>
+          <t>RM-STAB-023</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>retention-policy.yaml + legal decision register (AG): сроки, 152-ФЗ, deletion/archive, review date</t>
+          <t>Юнит-тесты не вызывают настоящий docker: подмена compose в _update_harness, общий предохранитель, тест-сторож</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-253</t>
+          <t>RM-ENV-001</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
@@ -2675,17 +2671,13 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>юридическое утверждение retention/152-ФЗ (OD-009) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>прогон python -m pytest tests/ не выполняет ни одной настоящей команды docker/compose (кроме opt-in интеграционных тестов); тест-сторож падает, если юнит-тест доходит до настоящего docker [command: `python -m pytest tests/test_local_stand.py`]</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2695,38 +2687,38 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено POPS → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). 2026-08-31: кандидат docs/product/retention-policy.yaml подготовлен (working defaults REQ-DATA-001, legal register) - не действует до OD-009; задача остаётся blocked.</t>
+          <t>Решение владельца 2026-10-05 (наблюдение этапа RF-12): tests/test_local_stand.py::_update_harness не подменяет compose, тесты неуспешного обновления доходят до scripts/deploy/local_stand.py compose("stop") и останавливают стенд rmp-local-stand при локальном python -m pytest tests/ (2026-10-01, 2026-10-05). REQ: -; SC: -; DEC: -. Порядок (решение владельца 2026-10-05): после этапа про PUT /auth/ad-settings, до P0-8. До исправления остановка стенда при локальном прогоне - известное поведение, пропуском тестов не обходится. Риск регрессии: низкий - только тесты.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-210</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>SLO objectives и измерение</t>
+          <t>RLS-контекст на device-маршрутах онбординга</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-STAB-002</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -2735,30 +2727,34 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>каждое число ТЗ имеет formula/window/owner/metric либо `not measurable` [artifact: `docs/product/slo-objectives.yaml`]</t>
+          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; bootstrap-RLS миграции 037: без RLS-контекста роль приложения видит 0 onboarding codes (fail-closed); со своим app.rmp_device_code — только свою строку; с чужим кодом — 0 [behavioral: `tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap`]</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py; verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap; verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33408891221</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288 RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/slo-objectives.yaml - 11 объектов, каждое число §8 с formula/window/owner/status; пороги OD-011/OD-025 open. Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика. 2026-08-31 (стадия S, OD-043: зависимость RM-STAB-002 done): реализовано локально - set_rls_context на /identity/device-codes, bootstrap-контекст кода/fingerprint на /device/onboard, миграция 037 (rehearsal down/up), allowlist элевации снят; targeted 97 passed под ролью приложения; design-gate docs/architecture/rm-tech-210-device-onboarding-rls-bootstrap-design-gate.md (на тот момент - до CI-evidence и owner gate). verification 2026-08-31: CI 33408891221 success (условием done тогда оставался owner gate device_contract). 2026-08-31: приёмка №2 уточнена владельцем — три утверждения bootstrap-RLS (без контекста 0; свой app.rmp_device_code — только свой; чужой — 0); ref → TestRMTech210BootstrapRLS. done 2026-08-31: owner gate device_contract granted - OD-045 (fail-closed контракт принят владельцем).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-OPS-005</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2768,21 +2764,21 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>OpenAPI + event/manifest JSON Schema (AG): as-built генерация + target из §26/AB, contract tests</t>
+          <t>retention-policy.yaml + legal decision register (AG): сроки, 152-ФЗ, deletion/archive, review date</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-253</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -2791,13 +2787,17 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>OpenAPI/event schemas версионированы, examples и deprecation policy; contract tests зелёные [command: `python3 scripts/ci/roadmap-governance-guard.py`]; одна canonical opaque идентификация на версию API; alias {id} с deprecation date [behavioral: `tests/behavioral/test_rm_tech_220.py`]</t>
+          <t>юридическое утверждение retention/152-ФЗ (OD-009) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2807,14 +2807,14 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/api/openapi-as-built-v1.json (113 paths/128 ops/149 схем), target docs/architecture/api/openapi-target-v2.6.md, envelope docs/architecture/events/event-envelope-v1.schema.json; contract tests и версионирование - после старта задачи; задача planned до Gate-S (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено POPS → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). 2026-08-31: кандидат docs/product/retention-policy.yaml подготовлен (working defaults REQ-DATA-001, legal register) - не действует до OD-009; задача остаётся blocked.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-221</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2824,21 +2824,21 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Разделение User/Device/analytics/emergency API; device client не достигает admin</t>
+          <t>SLO objectives и измерение</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>device JWT → admin endpoint = 403 на всех admin-роутах [behavioral: `tests/test_phase3_protected_identity.py`]</t>
+          <t>каждое число ТЗ имеет formula/window/owner/metric либо `not measurable` [artifact: `docs/product/slo-objectives.yaml`]</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2863,14 +2863,14 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-002; SC: SC-API-002; DEC: -. Evidence: tests/test_phase3_protected_identity.py; новый negative. Риск регрессии: низкий.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288 RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/slo-objectives.yaml - 11 объектов, каждое число §8 с formula/window/owner/status; пороги OD-011/OD-025 open. Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-222</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2885,16 +2885,16 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Канонический POST /api/v1/pop/batch, legacy /device/pop/batch как alias с deprecation</t>
+          <t>OpenAPI + event/manifest JSON Schema (AG): as-built генерация + target из §26/AB, contract tests</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>ответы канонического и legacy идентичны; deprecation header; batch&gt;500 → 422; чужой device_id отклонён [behavioral: `tests/test_contract_pop.py`]</t>
+          <t>OpenAPI/event schemas версионированы, examples и deprecation policy; contract tests зелёные [command: `python3 scripts/ci/roadmap-governance-guard.py`]; одна canonical opaque идентификация на версию API; alias {id} с deprecation date [behavioral: `tests/behavioral/test_rm_tech_220.py`]</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2919,14 +2919,14 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-003, REQ-POP-003; SC: SC-API-003, SC-POP-003; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_edge002fu_real_endpoint.py. Риск регрессии: средний: runtime/плеер использует legacy path.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/api/openapi-as-built-v1.json (113 paths/128 ops/149 схем), target docs/architecture/api/openapi-target-v2.6.md, envelope docs/architecture/events/event-envelope-v1.schema.json; contract tests и версионирование - после старта задачи; задача planned до Gate-S (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-223</t>
+          <t>RM-TECH-221</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Manifest field contract и ACK-состояния runtime (opaque media_ref, no MinIO keys)</t>
+          <t>Разделение User/Device/analytics/emergency API; device client не достигает admin</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2962,14 +2962,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+      <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>все обязательные поля §25 REQ-MAN-004 в schema; внутренний object key не раскрыт; 6 ACK states принимаются [behavioral: `tests/test_contract_manifest.py`]</t>
+          <t>device JWT → admin endpoint = 403 на всех admin-роутах [behavioral: `tests/test_phase3_protected_identity.py`]</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2979,14 +2975,14 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-MAN-004; SC: SC-MAN-001; DEC: -. Evidence: tests/test_contract_manifest.py; tests/behavioral/test_edge002_manifest_delivery.py. Риск регрессии: высокий: меняет device-facing контракт — owner gate device_contract.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-002; SC: SC-API-002; DEC: -. Evidence: tests/test_phase3_protected_identity.py; новый negative. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-222</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3001,7 +2997,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat contract POST /api/v1/device/heartbeat: дедуп, scope, clock drift, freshness thresholds</t>
+          <t>Канонический POST /api/v1/pop/batch, legacy /device/pop/batch как alias с deprecation</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3022,14 +3018,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>валидный/повтор/чужой scope/просроченный heartbeat дают ожидаемые результаты; legacy alias с той же семантикой [behavioral: `tests/behavioral/test_edge004_heartbeat.py`]</t>
+          <t>ответы канонического и legacy идентичны; deprecation header; batch&gt;500 → 422; чужой device_id отклонён [behavioral: `tests/test_contract_pop.py`]</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3039,14 +3031,14 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-009; SC: SC-OPS-002; DEC: -. Evidence: tests/behavioral/test_edge004_heartbeat.py. Риск регрессии: высокий: device-facing.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-003, REQ-POP-003; SC: SC-API-003, SC-POP-003; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_edge002fu_real_endpoint.py. Риск регрессии: средний: runtime/плеер использует legacy path.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-223</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3061,16 +3053,16 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>PoP duplicate semantics по OD-019: 200 + per-event duplicate/409, amendment ADR-017</t>
+          <t>Manifest field contract и ACK-состояния runtime (opaque media_ref, no MinIO keys)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-222</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -3082,10 +3074,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>ADR-017 amendment принят; behavioral: повтор batch → per-event duplicate, summary не удвоен, порядок хронологический [behavioral: `tests/behavioral/test_edge003_pop_ingestion.py`]</t>
+          <t>все обязательные поля §25 REQ-MAN-004 в schema; внутренний object key не раскрыт; 6 ACK states принимаются [behavioral: `tests/test_contract_manifest.py`]</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3095,14 +3091,14 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-002; SC: SC-POP-002; DEC: DEC-024. Evidence: tests/behavioral/test_edge003_pop_ingestion.py; ADR-017 amendment. Риск регрессии: низкий: закрепляет текущее поведение.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-MAN-004; SC: SC-MAN-001; DEC: -. Evidence: tests/test_contract_manifest.py; tests/behavioral/test_edge002_manifest_delivery.py. Риск регрессии: высокий: меняет device-facing контракт — owner gate device_contract.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-226</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3117,16 +3113,16 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Proof model: pop_mode error/not_applied — schema/runtime migration из compatibility projection</t>
+          <t>Heartbeat contract POST /api/v1/device/heartbeat: дедуп, scope, clock drift, freshness thresholds</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
@@ -3140,12 +3136,12 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>migration_application</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>ProofMode содержит 9 значений; отчёт не смешивает playback/apply/delivery/error [behavioral: `tests/behavioral/test_pop_schema.py`]</t>
+          <t>валидный/повтор/чужой scope/просроченный heartbeat дают ожидаемые результаты; legacy alias с той же семантикой [behavioral: `tests/behavioral/test_edge004_heartbeat.py`]</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3155,14 +3151,14 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-001; SC: SC-POP-001; DEC: -. Evidence: tests/behavioral/test_pop_schema.py; migration. Риск регрессии: средний: enum migration + отчёты.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-009; SC: SC-OPS-002; DEC: -. Evidence: tests/behavioral/test_edge004_heartbeat.py. Риск регрессии: высокий: device-facing.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-227</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3177,16 +3173,16 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Валидация proof_event_v1: playback_result/failure_reason, clock-drift quarantine, no internal IDs/PII</t>
+          <t>PoP duplicate semantics по OD-019: 200 + per-event duplicate/409, amendment ADR-017</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-222</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -3201,7 +3197,7 @@
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>недопустимый playback_result/внутренний ID/сдвиг часов → 422 или quarantine; SHA/signature проверены [behavioral: `tests/test_contract_pop.py`]</t>
+          <t>ADR-017 amendment принят; behavioral: повтор batch → per-event duplicate, summary не удвоен, порядок хронологический [behavioral: `tests/behavioral/test_edge003_pop_ingestion.py`]</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3211,14 +3207,14 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-004; SC: SC-POP-004; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_pop_schema.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-002; SC: SC-POP-002; DEC: DEC-024. Evidence: tests/behavioral/test_edge003_pop_ingestion.py; ADR-017 amendment. Риск регрессии: низкий: закрепляет текущее поведение.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-228</t>
+          <t>RM-TECH-226</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3233,16 +3229,16 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Окно совместимости device/API/manifest: heartbeat объявляет версии, сервер выбирает представление</t>
+          <t>Proof model: pop_mode error/not_applied — schema/runtime migration из compatibility projection</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -3254,10 +3250,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>совместимая версия выбрана по объявленным capabilities; breaking change без staged rollout отклонён contract-тестом [behavioral: `tests/test_version_identity.py`]</t>
+          <t>ProofMode содержит 9 значений; отчёт не смешивает playback/apply/delivery/error [behavioral: `tests/behavioral/test_pop_schema.py`]</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -3267,14 +3267,14 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-003; SC: SC-NFR-003; DEC: -. Evidence: tests/test_version_identity.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-001; SC: SC-POP-001; DEC: -. Evidence: tests/behavioral/test_pop_schema.py; migration. Риск регрессии: средний: enum migration + отчёты.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-227</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3284,21 +3284,21 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>ERD + data dictionary + migration plan (AG): инвентарь сущностей §15, retailer_id NOT NULL + двухуровневый RLS</t>
+          <t>Валидация proof_event_v1: playback_result/failure_reason, clock-drift quarantine, no internal IDs/PII</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>as-built ERD из моделей; каждая группа §15 присутствует или имеет migration task; tenant-таблицы с retailer_id+FK+RLS [artifact: `tests/behavioral/test_adr018_multitenancy_rls.py`]; behavioral RLS proof под ролью приложения NOBYPASSRLS [behavioral: `tests/behavioral/test_adr018_multitenancy_rls.py`]</t>
+          <t>недопустимый playback_result/внутренний ID/сдвиг часов → 422 или quarantine; SHA/signature проверены [behavioral: `tests/test_contract_pop.py`]</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3323,14 +3323,14 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/erd/data-dictionary-as-built.md (62 таблицы, 38 RLS) и кандидат docs/architecture/erd/migration-plan-v2.6.md (§13 → present/missing → задачи); PII/retention колонки - RM-TECH-253/RM-OPS-005. Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-004; SC: SC-POP-004; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_pop_schema.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-230</t>
+          <t>RM-TECH-228</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3340,21 +3340,21 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Channel Adapter contract (design-only до второго канала): versioned task, receipt, proof/ack, error, health, mock mode</t>
+          <t>Окно совместимости device/API/manifest: heartbeat объявляет версии, сервер выбирает представление</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>contract spec + JSON Schema без реализации adapter/mock (ADR-019) [artifact: `docs/architecture contract`]</t>
+          <t>совместимая версия выбрана по объявленным capabilities; breaking change без staged rollout отклонён contract-тестом [behavioral: `tests/test_version_identity.py`]</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3379,14 +3379,14 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-006; SC: SC-ORCH-005; DEC: -. Evidence: docs/architecture contract; schema. Риск регрессии: низкий: только документ.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-003; SC: SC-NFR-003; DEC: -. Evidence: tests/test_version_identity.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-231</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3401,16 +3401,16 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>channel-capability-matrix.yaml (AG) для первого канала KSO: channel/surface/rendition/proof/SLA/vendor constraints</t>
+          <t>ERD + data dictionary + migration plan (AG): инвентарь сущностей §15, retailer_id NOT NULL + двухуровневый RLS</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-230</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -3422,14 +3422,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>матрица покрывает KSO channel/surface/rendition/proof/SLA/vendor constraints; каждая строка ссылается на REQ-CHAN-*/REQ-MAN-*/REQ-POP-* [artifact: `docs/product/channel-capability-matrix.yaml`]; артефакт принят владельцем как часть handoff-пакета AG [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>as-built ERD из моделей; каждая группа §15 присутствует или имеет migration task; tenant-таблицы с retailer_id+FK+RLS [artifact: `tests/behavioral/test_adr018_multitenancy_rls.py`]; behavioral RLS proof под ролью приложения NOBYPASSRLS [behavioral: `tests/behavioral/test_adr018_multitenancy_rls.py`]</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3439,14 +3435,14 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-012 (предложение 2026-08-31): AG требует channel-capability-matrix до старта разработки, а RM-TECH-261 держит матрицу за решением OD-021 (второй канал). Первый канал KSO описывается без OD-021; RM-TECH-261 расширяет матрицу вторым каналом. REQ: REQ-CHAN-001, REQ-CHAN-002, REQ-CHAN-003; SC: SC-CHAN-002; DEC: DEC-001 (расширение). Evidence: артефакт; ACCEPT владельца. Риск регрессии: нет (документ). Утверждена OD-042 (2026-08-31). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/channel-capability-matrix.yaml (KSO + declared каналы §7); приёмка - внутри задачи после Gate-S.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/erd/data-dictionary-as-built.md (62 таблицы, 38 RLS) и кандидат docs/architecture/erd/migration-plan-v2.6.md (§13 → present/missing → задачи); PII/retention колонки - RM-TECH-253/RM-OPS-005. Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-253</t>
+          <t>RM-TECH-230</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3461,16 +3457,16 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Data protection: data classes, lawful purpose, минимизация PII, residency; retention по OD-009</t>
+          <t>Channel Adapter contract (design-only до второго канала): versioned task, receipt, proof/ack, error, health, mock mode</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
@@ -3485,7 +3481,7 @@
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>реестр data classes для всех сущностей; новая PII-сущность без класса — красный design-gate [artifact: `docs/architecture data classes`]</t>
+          <t>contract spec + JSON Schema без реализации adapter/mock (ADR-019) [artifact: `docs/architecture contract`]</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -3495,14 +3491,14 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: docs/architecture data classes. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено CORE → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-006; SC: SC-ORCH-005; DEC: -. Evidence: docs/architecture contract; schema. Риск регрессии: низкий: только документ.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-288</t>
+          <t>RM-TECH-231</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3512,21 +3508,21 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>nfr-slo.yaml + load-profiles.yaml (AG): method, percentile, error budget, generator, CI evidence</t>
+          <t>channel-capability-matrix.yaml (AG) для первого канала KSO: channel/surface/rendition/proof/SLA/vendor constraints</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-230</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -3538,10 +3534,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>каждый SLO имеет window/denominator/exclusions; load generator и прогон в CI/стенде [artifact: `nfr-slo.yaml`]</t>
+          <t>матрица покрывает KSO channel/surface/rendition/proof/SLA/vendor constraints; каждая строка ссылается на REQ-CHAN-*/REQ-MAN-*/REQ-POP-* [artifact: `docs/product/channel-capability-matrix.yaml`]; артефакт принят владельцем как часть handoff-пакета AG [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -3551,14 +3551,14 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки):ы docs/product/nfr-slo.yaml и docs/product/load-profiles.yaml (7 профилей); load generator отсутствует (new). Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>RM-GOV-012 (предложение 2026-08-31): AG требует channel-capability-matrix до старта разработки, а RM-TECH-261 держит матрицу за решением OD-021 (второй канал). Первый канал KSO описывается без OD-021; RM-TECH-261 расширяет матрицу вторым каналом. REQ: REQ-CHAN-001, REQ-CHAN-002, REQ-CHAN-003; SC: SC-CHAN-002; DEC: DEC-001 (расширение). Evidence: артефакт; ACCEPT владельца. Риск регрессии: нет (документ). Утверждена OD-042 (2026-08-31). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/channel-capability-matrix.yaml (KSO + declared каналы §7); приёмка - внутри задачи после Gate-S.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-011</t>
+          <t>RM-TECH-253</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3568,21 +3568,21 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>role-scope-matrix.yaml + portal-route-matrix.yaml + journeys/ (AG) из seed/pg_policies/registry</t>
+          <t>Data protection: data classes, lawful purpose, минимизация PII, residency; retention по OD-009</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004, RM-STAB-006</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>матрицы генерируются и сверяются guard; deny-cases покрыты behavioral [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+          <t>реестр data classes для всех сущностей; новая PII-сущность без класса — красный design-gate [artifact: `docs/architecture data classes`]</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3607,19 +3607,19 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено U → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/product/role-scope-matrix.yaml (5 seeded ролей × 30 permissions, Q2 target 7 ролей, 38 RLS-таблиц, deny-cases), docs/product/portal-route-matrix.yaml (admin 16 + advertiser 9 маршрутов), docs/product/journeys/journeys.yaml (79 journeys, нормативный формат); generated-сверка guard - после старта задачи; задача planned до Gate-S (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: docs/architecture data classes. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено CORE → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-001</t>
+          <t>RM-TECH-288</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3629,16 +3629,16 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Записать managed-first scope</t>
+          <t>nfr-slo.yaml + load-profiles.yaml (AG): method, percentile, error budget, generator, CI evidence</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>roadmap явно исключает `self.campaign_create` из ближайшего control-plane pilot [artifact: `docs/product/roadmap.yaml (pilot scope)`]</t>
+          <t>каждый SLO имеет window/denominator/exclusions; load generator и прогон в CI/стенде [artifact: `nfr-slo.yaml`]</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3663,38 +3663,38 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): ссылки OD-005/DEC-011, REQ-SCOPE-001</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки):ы docs/product/nfr-slo.yaml и docs/product/load-profiles.yaml (7 профилей); load generator отсутствует (new). Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201</t>
+          <t>RM-UX-011</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Таксономия причин недопоказа</t>
+          <t>role-scope-matrix.yaml + portal-route-matrix.yaml + journeys/ (AG) из seed/pg_policies/registry</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-STAB-004, RM-STAB-006</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>8 категорий ТЗ, source/report/history contract и owner-approved artifact [artifact: `docs/product/underdelivery-reason-taxonomy.yaml`]</t>
+          <t>матрицы генерируются и сверяются guard; deny-cases покрыты behavioral [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3719,14 +3719,14 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено U → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/product/role-scope-matrix.yaml (5 seeded ролей × 30 permissions, Q2 target 7 ролей, 38 RLS-таблиц, deny-cases), docs/product/portal-route-matrix.yaml (admin 16 + advertiser 9 маршрутов), docs/product/journeys/journeys.yaml (79 journeys, нормативный формат); generated-сверка guard - после старта задачи; задача planned до Gate-S (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202</t>
+          <t>RM-BIZ-001</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3736,21 +3736,21 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Вытеснение и объяснимые приоритеты</t>
+          <t>Записать managed-first scope</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>versioned rules [behavioral: `tests/behavioral/test_campaign_preemption.py`]</t>
+          <t>roadmap явно исключает `self.campaign_create` из ближайшего control-plane pilot [artifact: `docs/product/roadmap.yaml (pilot scope)`]</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3775,14 +3775,14 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-007 и порядок приоритета §12; исключение §3.1 (OD-018) — единственная точка изменения engine → RM-TECH-285 зависит от неё</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): ссылки OD-005/DEC-011, REQ-SCOPE-001</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-203</t>
+          <t>RM-TECH-201</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3792,21 +3792,21 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Overbooking policy</t>
+          <t>Таксономия причин недопоказа</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>default deny [behavioral: `tests/behavioral/test_inventory_overbooking_policy.py`]</t>
+          <t>8 категорий ТЗ, source/report/history contract и owner-approved artifact [artifact: `docs/product/underdelivery-reason-taxonomy.yaml`]</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-204</t>
+          <t>RM-TECH-202</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3853,16 +3853,16 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Creative QA без неутверждённого HTML5</t>
+          <t>Вытеснение и объяснимые приоритеты</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-201</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>metadata/antivirus/executable deny и immutable QA result [behavioral: `tests/behavioral/test_creative_qa.py`]</t>
+          <t>versioned rules [behavioral: `tests/behavioral/test_campaign_preemption.py`]</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3887,14 +3887,14 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-007 и порядок приоритета §12; исключение §3.1 (OD-018) — единственная точка изменения engine → RM-TECH-285 зависит от неё</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-206</t>
+          <t>RM-TECH-203</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3909,16 +3909,16 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>License renewal/grant boundary</t>
+          <t>Overbooking policy</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-202</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>атомарная семантика §1.6 [behavioral: `tests/behavioral/test_license_renewal_boundary.py`]</t>
+          <t>default deny [behavioral: `tests/behavioral/test_inventory_overbooking_policy.py`]</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3950,7 +3950,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>RM-TECH-204</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3965,16 +3965,16 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Универсальная иерархия носителей: migration + seed network/branch/cluster/store/store_group/channel/device/surface</t>
+          <t>Creative QA без неутверждённого HTML5</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -3986,14 +3986,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>все уровни существуют с FK и RLS; seed заполняет иерархию; чужой scope не видит [behavioral: `tests/behavioral/test_scope_rls.py`]</t>
+          <t>metadata/antivirus/executable deny и immutable QA result [behavioral: `tests/behavioral/test_creative_qa.py`]</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -4003,14 +3999,14 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-001; SC: SC-DATA-001; DEC: -. Evidence: migration; tests/behavioral/test_scope_rls.py. Риск регрессии: высокий: схема ядра.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-241</t>
+          <t>RM-TECH-206</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4025,16 +4021,16 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Target resolution boundary: broad target → display_surface_id, запрет physical_device_id как target</t>
+          <t>License renewal/grant boundary</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -4049,7 +4045,7 @@
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>планирование разрешает target до surface; physical_device_id в target отклоняется [behavioral: `tests/test_s089_inventory_simulation.py`]</t>
+          <t>атомарная семантика §1.6 [behavioral: `tests/behavioral/test_license_renewal_boundary.py`]</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -4059,14 +4055,14 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-003; SC: SC-ARCH-002; DEC: -. Evidence: tests/test_s089_inventory_simulation.py. Риск регрессии: средний.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-242</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4081,16 +4077,16 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Outbox для любой OLTP-записи с domain event; revocation/refresh manifest при pause/archive/expiry</t>
+          <t>Универсальная иерархия носителей: migration + seed network/branch/cluster/store/store_group/channel/device/surface</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -4102,10 +4098,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>каждая доменная мутация создаёт outbox event в той же транзакции; pause/archive порождают revocation [behavioral: `tests/behavioral/test_outbox.py`]</t>
+          <t>все уровни существуют с FK и RLS; seed заполняет иерархию; чужой scope не видит [behavioral: `tests/behavioral/test_scope_rls.py`]</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4115,14 +4115,14 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-003; SC: SC-ORCH-002; DEC: -. Evidence: tests/behavioral/test_outbox.py. Риск регрессии: средний: транзакционные границы всех сервисов.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-001; SC: SC-DATA-001; DEC: -. Evidence: migration; tests/behavioral/test_scope_rls.py. Риск регрессии: высокий: схема ядра.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-243</t>
+          <t>RM-TECH-241</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4137,16 +4137,16 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Outbox relay: lease/publishing, Nats-Msg-Id, 7 попыток → dead_letter, partition order, DLQ policy, no PII</t>
+          <t>Target resolution boundary: broad target → display_surface_id, запрет physical_device_id как target</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-242</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>7 отказов брокера → dead_letter с operator action; ack → published; replay идемпотентен [behavioral: `tests/behavioral/test_outbox_relay.py`]; NATS recovery integration зелёный [command: `tests/behavioral/test_outbox_relay.py`]</t>
+          <t>планирование разрешает target до surface; physical_device_id в target отклоняется [behavioral: `tests/test_s089_inventory_simulation.py`]</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-004; SC: SC-ORCH-003; DEC: DEC-004. Evidence: tests/behavioral/test_outbox_relay.py; tests/integration/test_nats_recovery.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-003; SC: SC-ARCH-002; DEC: -. Evidence: tests/test_s089_inventory_simulation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-244</t>
+          <t>RM-TECH-242</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4193,16 +4193,16 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Adapter task lifecycle через persisted queue (event-driven массовая публикация)</t>
+          <t>Outbox для любой OLTP-записи с domain event; revocation/refresh manifest при pause/archive/expiry</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-243</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>активация на 1000 устройств не ждёт устройств; задачи агрегируют статусы [behavioral: `tests/behavioral/test_delivery_foundation.py`]</t>
+          <t>каждая доменная мутация создаёт outbox event в той же транзакции; pause/archive порождают revocation [behavioral: `tests/behavioral/test_outbox.py`]</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -4227,14 +4227,14 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-002; SC: SC-ORCH-006; DEC: DEC-004. Evidence: tests/behavioral/test_delivery_foundation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-003; SC: SC-ORCH-002; DEC: -. Evidence: tests/behavioral/test_outbox.py. Риск регрессии: средний: транзакционные границы всех сервисов.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-TECH-243</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4249,16 +4249,16 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Campaign lifecycle по ADR-015/OD-036: scheduled, resume, revise, archive; единый guard и audit</t>
+          <t>Outbox relay: lease/publishing, Nats-Msg-Id, 7 попыток → dead_letter, partition order, DLQ policy, no PII</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-TECH-242</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -4270,14 +4270,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>_CAMPAIGN_TRANSITIONS = ADR-015; каждый переход через guard с audit; возврат в draft создаёт revision [behavioral: `tests/behavioral/test_campaign_domain.py`]; campaign.* smokes зелёные после изменения [ui_smoke: `tests/ui-smoke/test_rm_tech_245.py`]</t>
+          <t>7 отказов брокера → dead_letter с operator action; ack → published; replay идемпотентен [behavioral: `tests/behavioral/test_outbox_relay.py`]; NATS recovery integration зелёный [command: `tests/behavioral/test_outbox_relay.py`]</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -4287,14 +4283,14 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-010; SC: -; DEC: DEC-025. Evidence: tests/behavioral/test_campaign_domain.py; tests/ui-smoke/test_uismoke__campaign__*.py. Риск регрессии: высокий: меняет runtime enum кампании и UI.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-004; SC: SC-ORCH-003; DEC: DEC-004. Evidence: tests/behavioral/test_outbox_relay.py; tests/integration/test_nats_recovery.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-246</t>
+          <t>RM-TECH-244</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4309,16 +4305,16 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Commerce order: отмена по OD-020 (draft→cancelled, confirmed — reversal), payment projection отдельно</t>
+          <t>Adapter task lifecycle через persisted queue (event-driven массовая публикация)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-TECH-243</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -4333,7 +4329,7 @@
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>_ORDER_TRANSITIONS: draft→cancelled разрешён, confirmed→cancelled запрещён, reversal с audit [behavioral: `tests/test_commerce_a2.py`]</t>
+          <t>активация на 1000 устройств не ждёт устройств; задачи агрегируют статусы [behavioral: `tests/behavioral/test_delivery_foundation.py`]</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -4343,14 +4339,14 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-014; SC: -; DEC: DEC-017, DEC-026. Evidence: tests/test_commerce_a2.py; tests/behavioral/test_commerce_rls.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-002; SC: SC-ORCH-006; DEC: DEC-004. Evidence: tests/behavioral/test_delivery_foundation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-247</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4365,16 +4361,16 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Approval policy: required roles/scope/порядок/timeout per campaign/placement/creative</t>
+          <t>Campaign lifecycle по ADR-015/OD-036: scheduled, resume, revise, archive; единый guard и audit</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -4386,10 +4382,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>политика версионирована; submit/approve соблюдают порядок и timeout; negative для чужого scope [behavioral: `tests/behavioral/test_campaign_approval.py`]</t>
+          <t>_CAMPAIGN_TRANSITIONS = ADR-015; каждый переход через guard с audit; возврат в draft создаёт revision [behavioral: `tests/behavioral/test_campaign_domain.py`]; campaign.* smokes зелёные после изменения [ui_smoke: `tests/ui-smoke/test_rm_tech_245.py`]</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-003; SC: -; DEC: -. Evidence: tests/behavioral/test_campaign_approval.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-010; SC: -; DEC: DEC-025. Evidence: tests/behavioral/test_campaign_domain.py; tests/ui-smoke/test_uismoke__campaign__*.py. Риск регрессии: высокий: меняет runtime enum кампании и UI.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-248</t>
+          <t>RM-TECH-246</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4421,16 +4421,16 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Flight/placement windows: versioned start_at/end_at UTC, проверка при simulation/manifest/runtime</t>
+          <t>Commerce order: отмена по OD-020 (draft→cancelled, confirmed — reversal), payment projection отдельно</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>показ вне окна запрещён на трёх уровнях; DST/праздники/closed stores — версионированные правила [behavioral: `tests/test_s063_pop_timezone.py`]</t>
+          <t>_ORDER_TRANSITIONS: draft→cancelled разрешён, confirmed→cancelled запрещён, reversal с audit [behavioral: `tests/test_commerce_a2.py`]</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -4455,14 +4455,14 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-005, REQ-NFR-002; SC: SC-NFR-002; DEC: -. Evidence: tests/test_s063_pop_timezone.py; новый behavioral. Риск регрессии: высокий: расписание доставки.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-014; SC: -; DEC: DEC-017, DEC-026. Evidence: tests/test_commerce_a2.py; tests/behavioral/test_commerce_rls.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-249</t>
+          <t>RM-TECH-247</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4477,16 +4477,16 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Manifest eligibility: approved status + валидный flight/contract + resolved target + readiness</t>
+          <t>Approval policy: required roles/scope/порядок/timeout per campaign/placement/creative</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-248</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>неэлигибельная кампания не попадает в manifest; причина объяснима [behavioral: `tests/behavioral/test_delivery_generation.py`]</t>
+          <t>политика версионирована; submit/approve соблюдают порядок и timeout; negative для чужого scope [behavioral: `tests/behavioral/test_campaign_approval.py`]</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -4511,14 +4511,14 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-006; SC: -; DEC: -. Evidence: tests/behavioral/test_delivery_generation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-003; SC: -; DEC: -. Evidence: tests/behavioral/test_campaign_approval.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-250</t>
+          <t>RM-TECH-248</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4533,16 +4533,16 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Creative/rendition state machine и immutable media history (uploaded→scanning→qa_failed/approved→superseded→retained)</t>
+          <t>Flight/placement windows: versioned start_at/end_at UTC, проверка при simulation/manifest/runtime</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-204</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -4554,14 +4554,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>каждая версия хранит uploader/SHA-256/QA-решение/связь; закрытый отчёт воспроизводим после logical delete [behavioral: `tests/behavioral/test_creative_assets.py`]</t>
+          <t>показ вне окна запрещён на трёх уровнях; DST/праздники/closed stores — версионированные правила [behavioral: `tests/test_s063_pop_timezone.py`]</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -4571,14 +4567,14 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CONT-002; SC: SC-DATA-002; DEC: -. Evidence: tests/behavioral/test_creative_assets.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-005, REQ-NFR-002; SC: SC-NFR-002; DEC: -. Evidence: tests/test_s063_pop_timezone.py; новый behavioral. Риск регрессии: высокий: расписание доставки.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-251</t>
+          <t>RM-TECH-249</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4593,16 +4589,16 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Data ownership/lineage: immutable versioning и diff campaign/placement/playlist, словарь владельцев</t>
+          <t>Manifest eligibility: approved status + валидный flight/contract + resolved target + readiness</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-248</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -4617,7 +4613,7 @@
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>сохранение создаёт версию с diff и actor; предыдущая неизменяема [behavioral: `tests/behavioral/test_rm_tech_251.py`]</t>
+          <t>неэлигибельная кампания не попадает в manifest; причина объяснима [behavioral: `tests/behavioral/test_delivery_generation.py`]</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -4627,14 +4623,14 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-001; SC: SC-DATA-004; DEC: DEC-007. Evidence: новый behavioral. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-006; SC: -; DEC: -. Evidence: tests/behavioral/test_delivery_generation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-252</t>
+          <t>RM-TECH-250</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4649,16 +4645,16 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Identity: AD/LDAP или SSO для internal staff, MFA до production (OD-008)</t>
+          <t>Creative/rendition state machine и immutable media history (uploaded→scanning→qa_failed/approved→superseded→retained)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-TECH-204</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -4672,12 +4668,12 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>protected_boundary</t>
+          <t>migration_application</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>логин через IdP; production-профиль без MFA отклоняет; TLS-профиль зафиксирован [behavioral: `tests/test_phase3_auth_api.py`]</t>
+          <t>каждая версия хранит uploader/SHA-256/QA-решение/связь; закрытый отчёт воспроизводим после logical delete [behavioral: `tests/behavioral/test_creative_assets.py`]</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -4687,14 +4683,14 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-001; SC: SC-SEC-008; DEC: -. Evidence: tests/test_phase3_auth_api.py; tests/behavioral/test_auth_dual_e2e.py. Риск регрессии: высокий: вход всех пользователей.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CONT-002; SC: SC-DATA-002; DEC: -. Evidence: tests/behavioral/test_creative_assets.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-254</t>
+          <t>RM-TECH-251</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4709,16 +4705,16 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Emergency state machine: requested→authorized→dispatching→applied→resuming→closed, MFA+reason, приоритетный канал</t>
+          <t>Data ownership/lineage: immutable versioning и diff campaign/placement/playlist, словарь владельцев</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -4733,7 +4729,7 @@
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>emergency с причиной; per-target result; audit actor/reason/affected; resume возвращает штатный manifest [behavioral: `tests/test_phase3_emergency_api.py`]; emergency.* smokes зелёные [ui_smoke: `tests/ui-smoke/test_uismoke__emergency__activate.py`]</t>
+          <t>сохранение создаёт версию с diff и actor; предыдущая неизменяема [behavioral: `tests/behavioral/test_rm_tech_251.py`]</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -4743,14 +4739,14 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-007; SC: SC-OPS-003; DEC: -. Evidence: tests/test_phase3_emergency_api.py; tests/ui-smoke/test_uismoke__emergency__activate.py. Риск регрессии: высокий: аварийный контур.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-001; SC: SC-DATA-004; DEC: DEC-007. Evidence: новый behavioral. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-255</t>
+          <t>RM-TECH-252</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4765,16 +4761,16 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Device health/commands: пороги статусов по профилю, per-device view, команды с подтверждением</t>
+          <t>Identity: AD/LDAP или SSO для internal staff, MFA до production (OD-008)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -4786,10 +4782,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>protected_boundary</t>
+        </is>
+      </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>online→degraded→offline по порогам; команда доставлена и подтверждена [behavioral: `tests/behavioral/test_rm_tech_255.py`]; device.health_view smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__device__health_view.py`]</t>
+          <t>логин через IdP; production-профиль без MFA отклоняет; TLS-профиль зафиксирован [behavioral: `tests/test_phase3_auth_api.py`]</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -4799,19 +4799,19 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-001; SC: SC-OPS-006; DEC: -. Evidence: tests/ui-smoke/test_uismoke__device__health_view.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-001; SC: SC-SEC-008; DEC: -. Evidence: tests/test_phase3_auth_api.py; tests/behavioral/test_auth_dual_e2e.py. Риск регрессии: высокий: вход всех пользователей.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-002</t>
+          <t>RM-TECH-254</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4821,16 +4821,16 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>`self.campaign_create` в будущей ветке</t>
+          <t>Emergency state machine: requested→authorized→dispatching→applied→resuming→closed, MFA+reason, приоритетный канал</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-001</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -4839,17 +4839,13 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>mini-design, journey, backend/UI/RLS, intended-role smoke, walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__campaign_create.py`]</t>
+          <t>emergency с причиной; per-target result; audit actor/reason/affected; resume возвращает штатный manifest [behavioral: `tests/test_phase3_emergency_api.py`]; emergency.* smokes зелёные [ui_smoke: `tests/ui-smoke/test_uismoke__emergency__activate.py`]</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4859,19 +4855,19 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2). RM-GOV-009 (OD-037): blocked до OD-013 — полный self-service вне pilot scope (REQ-V26-003, OD-005)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-007; SC: SC-OPS-003; DEC: -. Evidence: tests/test_phase3_emergency_api.py; tests/ui-smoke/test_uismoke__emergency__activate.py. Риск регрессии: высокий: аварийный контур.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001</t>
+          <t>RM-TECH-255</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4881,16 +4877,16 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Accessibility оставшихся форм + route matrix (A3)</t>
+          <t>Device health/commands: пороги статусов по профилю, per-device view, команды с подтверждением</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -4905,7 +4901,7 @@
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>labels/ARIA/axe/targeted vitest [artifact: `docs/product/ux-route-matrix.yaml`]</t>
+          <t>online→degraded→offline по порогам; команда доставлена и подтверждена [behavioral: `tests/behavioral/test_rm_tech_255.py`]; device.health_view smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__device__health_view.py`]</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4915,14 +4911,14 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-001; SC: SC-OPS-006; DEC: -. Evidence: tests/ui-smoke/test_uismoke__device__health_view.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-002</t>
+          <t>RM-BIZ-002</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4937,12 +4933,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Поиск/сортировка/усечение таблиц (A2)</t>
+          <t>`self.campaign_create` в будущей ветке</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001</t>
+          <t>RM-BIZ-001</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
@@ -4955,13 +4951,17 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>server semantics для pagination [ui_smoke: `tests/ui-smoke/test_uismoke__campaign__create.py`]</t>
+          <t>mini-design, journey, backend/UI/RLS, intended-role smoke, walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__campaign_create.py`]</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4971,14 +4971,14 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2). RM-GOV-009 (OD-037): blocked до OD-013 — полный self-service вне pilot scope (REQ-V26-003, OD-005)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-003</t>
+          <t>RM-UX-001</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4993,16 +4993,16 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Responsive-проверка (A4)</t>
+          <t>Accessibility оставшихся форм + route matrix (A3)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-002</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>все routes из `ux-route-matrix.yaml` проверены на 390px без overflow/crop [artifact: `docs/product/ux-responsive-report.yaml`]</t>
+          <t>labels/ARIA/axe/targeted vitest [artifact: `docs/product/ux-route-matrix.yaml`]</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -5034,7 +5034,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-004</t>
+          <t>RM-UX-002</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -5049,16 +5049,16 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Согласованность состояний и терминов (A6)</t>
+          <t>Поиск/сортировка/усечение таблиц (A2)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-003</t>
+          <t>RM-UX-001</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>route matrix покрывает empty/loading/error/403/success и locale-key check [artifact: `docs/product/ux-route-matrix.yaml (states coverage)`]</t>
+          <t>server semantics для pagination [ui_smoke: `tests/ui-smoke/test_uismoke__campaign__create.py`]</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-005</t>
+          <t>RM-UX-003</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5105,16 +5105,16 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Adoption доказанных primitives малыми slices (A1b)</t>
+          <t>Responsive-проверка (A4)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-004</t>
+          <t>RM-UX-002</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>каждый slice имеет отдельный diff/test/review [ci_job: `frontend`]</t>
+          <t>все routes из `ux-route-matrix.yaml` проверены на 390px без overflow/crop [artifact: `docs/product/ux-responsive-report.yaml`]</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-006</t>
+          <t>RM-UX-004</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -5161,16 +5161,16 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Advertiser-web UX audit/fixes (A5)</t>
+          <t>Согласованность состояний и терминов (A6)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-005</t>
+          <t>RM-UX-003</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>versioned `docs/product/advertiser-route-matrix.yaml` с точным списком 15 routes [artifact: `docs/product/advertiser-route-matrix.yaml`]</t>
+          <t>route matrix покрывает empty/loading/error/403/success и locale-key check [artifact: `docs/product/ux-route-matrix.yaml (states coverage)`]</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -5202,7 +5202,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-007</t>
+          <t>RM-UX-005</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5212,21 +5212,21 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Human operator walkthrough (A7)</t>
+          <t>Adoption доказанных primitives малыми slices (A1b)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001, RM-UX-002, RM-UX-003, RM-UX-004, RM-UX-005, RM-UX-006</t>
+          <t>RM-UX-004</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>человек проходит exact stand bundle [human: `PROJECT_STATE.md строка `operator walkthrough` (AGENTS.md правило 8); сценарии docs/product/operator-walkthrough-dev.md`]</t>
+          <t>каждый slice имеет отдельный diff/test/review [ci_job: `frontend`]</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -5251,14 +5251,14 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) ПРИОСТАНОВЛЕНО владельцем 2026-08-31 (OD-041) до выравнивания ТЗ/roadmap/gates и утверждения единого плана реализации; не закрывать, done не ставить.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-008</t>
+          <t>RM-UX-006</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -5273,16 +5273,16 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Campaign readiness matrix по каналам (rendition/inventory/conflicts/forecast/PoP mode/SLA) с действием на blocked</t>
+          <t>Advertiser-web UX audit/fixes (A5)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-249, RM-UX-004</t>
+          <t>RM-UX-005</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>экран согласования показывает матрицу; каждый blocked/warning ведёт к действию [ui_smoke: `tests/ui-smoke/test_rm_ux_008.py`]</t>
+          <t>versioned `docs/product/advertiser-route-matrix.yaml` с точным списком 15 routes [artifact: `docs/product/advertiser-route-matrix.yaml`]</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -5307,14 +5307,14 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-004; SC: SC-UX-002; DEC: -. Evidence: новый ui-smoke; vitest. Риск регрессии: средний.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-009</t>
+          <t>RM-UX-007</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5324,21 +5324,21 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Договор рекламодателя: immutable file versions, server-side SHA-256, legal status (юр. решение)</t>
+          <t>Human operator walkthrough (A7)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-250</t>
+          <t>RM-UX-001, RM-UX-002, RM-UX-003, RM-UX-004, RM-UX-005, RM-UX-006</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>повторная загрузка создаёт новую версию, SHA проверен сервером; старая версия неизменяема [behavioral: `tests/test_advertiser_contracts.py`]; advertiser.contract_crud smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py`]</t>
+          <t>человек проходит exact stand bundle [human: `PROJECT_STATE.md строка `operator walkthrough` (AGENTS.md правило 8); сценарии docs/product/operator-walkthrough-dev.md`]</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -5363,38 +5363,38 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-017; SC: -; DEC: -. Evidence: tests/test_advertiser_contracts.py; tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py. Риск регрессии: низкий.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) ПРИОСТАНОВЛЕНО владельцем 2026-08-31 (OD-041) до выравнивания ТЗ/roadmap/gates и утверждения единого плана реализации; не закрывать, done не ставить.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207A</t>
+          <t>RM-UX-008</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>KSO environment + player/playlist design</t>
+          <t>Campaign readiness matrix по каналам (rendition/inventory/conflicts/forecast/PoP mode/SLA) с действием на blocked</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-249, RM-UX-004</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -5406,14 +5406,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>versioned environment audit, import/contract mini-design и test plan [artifact: `docs/architecture/kso-environment-audit.md`]</t>
+          <t>экран согласования показывает матрицу; каждый blocked/warning ведёт к действию [ui_smoke: `tests/ui-smoke/test_rm_ux_008.py`]</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -5423,19 +5419,19 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-STAND-003 feasibility gate явно в acceptance; ADR-019/OD-022</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-004; SC: SC-UX-002; DEC: -. Evidence: новый ui-smoke; vitest. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-UX-009</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5445,16 +5441,16 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>KSO player/playlist/PoP chain</t>
+          <t>Договор рекламодателя: immutable file versions, server-side SHA-256, legal status (юр. решение)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207A</t>
+          <t>RM-TECH-250</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
@@ -5466,14 +5462,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+      <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>contract tests и playback→manifest→PoP behavioral proof [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; Playlist entity и state machine §6 ТЗ (draft → validating → valid/invalid → approved → published → superseded/rolled_back); published immutable [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; manifest target lifecycle (generated → signed → queued → delivered → applied/failed/expired) и canonical POST /api/v1/pop/batch [behavioral: `tests/behavioral/test_kso_playback_chain.py`]</t>
+          <t>повторная загрузка создаёт новую версию, SHA проверен сервером; старая версия неизменяема [behavioral: `tests/test_advertiser_contracts.py`]; advertiser.contract_crud smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py`]</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -5483,14 +5475,14 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-017; SC: -; DEC: -. Evidence: tests/test_advertiser_contracts.py; tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-208</t>
+          <t>RM-TECH-207A</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5500,21 +5492,21 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Signed licensing Layer 2</t>
+          <t>KSO environment + player/playlist design</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-206, RM-TECH-207B, RM-STAB-010</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -5528,12 +5520,12 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>protected_boundary</t>
+          <t>scope_decision</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Ed25519 offline verify, kid/rotation/revocation, UI, tamper/rollback [behavioral: `tests/behavioral/test_signed_license_layer2.py`]</t>
+          <t>versioned environment audit, import/contract mini-design и test plan [artifact: `docs/architecture/kso-environment-audit.md`]</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -5543,14 +5535,14 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-STAND-003 feasibility gate явно в acceptance; ADR-019/OD-022</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-260</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5565,16 +5557,16 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Runtime cache lifecycle: лимит по профилю, детерминированная очистка, last-known-good</t>
+          <t>KSO player/playlist/PoP chain</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-207A</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -5593,7 +5585,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>кэш на лимите: очистка по правилу; last-known-good сохранён; просроченная реклама не показывается [behavioral: `tests/behavioral/test_rm_tech_260.py`]</t>
+          <t>contract tests и playback→manifest→PoP behavioral proof [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; Playlist entity и state machine §6 ТЗ (draft → validating → valid/invalid → approved → published → superseded/rolled_back); published immutable [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; manifest target lifecycle (generated → signed → queued → delivered → applied/failed/expired) и canonical POST /api/v1/pop/batch [behavioral: `tests/behavioral/test_kso_playback_chain.py`]</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -5603,14 +5595,14 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-008; SC: SC-EDGE-002; DEC: -. Evidence: runtime simulator tests. Риск регрессии: средний: плеер.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-261</t>
+          <t>RM-TECH-208</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5620,17 +5612,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Второй канал: решение OD-021 + channel-capability-matrix.yaml (AG); extraction design по ADR-019</t>
+          <t>Signed licensing Layer 2</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B, RM-TECH-230</t>
+          <t>RM-TECH-206, RM-TECH-207B, RM-STAB-010</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
@@ -5643,17 +5635,17 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>scope_decision</t>
+          <t>protected_boundary</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>владелец назвал канал и владельца (OD-021); матрица возможностей утверждена [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; extraction design: KSO-вертикаль как первый adapter без поломки контрактов [artifact: `docs/audit/RM-TECH-261-artifact.md (создаётся задачей)`]</t>
+          <t>Ed25519 offline verify, kid/rotation/revocation, UI, tamper/rollback [behavioral: `tests/behavioral/test_signed_license_layer2.py`]</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -5663,14 +5655,14 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CHAN-001, REQ-ORCH-005; SC: SC-CHAN-002, SC-ORCH-004; DEC: DEC-001, DEC-002. Evidence: OD-021; design doc. Риск регрессии: высокий: рефакторинг KSO-вертикали. blocked до OD-021; Orchestrator/Adapter Layer/mock не создаются раньше (ADR-019/OD-022).</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-262</t>
+          <t>RM-TECH-260</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5685,16 +5677,16 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Dynamic creative binding/rendition safety (V26-008) на одном канале</t>
+          <t>Runtime cache lifecycle: лимит по профилю, детерминированная очистка, last-known-good</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280, RM-TECH-261</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
@@ -5706,10 +5698,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>master-confirmed price/promo подставляется при manifest generation; SLA-тест dynamic manifest [behavioral: `tests/behavioral/test_rm_tech_262.py`]</t>
+          <t>кэш на лимите: очистка по правилу; last-known-good сохранён; просроченная реклама не показывается [behavioral: `tests/behavioral/test_rm_tech_260.py`]</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -5719,14 +5715,14 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-008; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. ложная ESL-посылка снимается prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-008; SC: SC-EDGE-002; DEC: -. Evidence: runtime simulator tests. Риск регрессии: средний: плеер.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-263</t>
+          <t>RM-TECH-261</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5736,21 +5732,21 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Field mobile operations: scoped mobile web для сотрудника магазина (устройства, фото, инциденты)</t>
+          <t>Второй канал: решение OD-021 + channel-capability-matrix.yaml (AG); extraction design по ADR-019</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-210, RM-TECH-255</t>
+          <t>RM-TECH-207B, RM-TECH-230</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
@@ -5759,13 +5755,17 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>journey field_ops.device_confirm под ролью магазина с RLS; negative чужой магазин [ui_smoke: `tests/ui-smoke/test_rm_tech_263.py`]</t>
+          <t>владелец назвал канал и владельца (OD-021); матрица возможностей утверждена [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; extraction design: KSO-вертикаль как первый adapter без поломки контрактов [artifact: `docs/audit/RM-TECH-261-artifact.md (создаётся задачей)`]</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -5775,14 +5775,14 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-009; SC: -; DEC: -. Evidence: new ui-smoke. Риск регрессии: средний. prerequisite RM-TECH-210 (RLS device) - planned по зависимости; feature field_ops.device_confirm blocked до задачи (RM-GOV-012 выравнивание: blocked = решение владельца/внешний факт, а не зависимость).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CHAN-001, REQ-ORCH-005; SC: SC-CHAN-002, SC-ORCH-004; DEC: DEC-001, DEC-002. Evidence: OD-021; design doc. Риск регрессии: высокий: рефакторинг KSO-вертикали. blocked до OD-021; Orchestrator/Adapter Layer/mock не создаются раньше (ADR-019/OD-022).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-264</t>
+          <t>RM-TECH-262</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>ESL/price-checker: интеграция только через approved price/SKU master (INT-002)</t>
+          <t>Dynamic creative binding/rendition safety (V26-008) на одном канале</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-280, RM-TECH-261</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
@@ -5821,7 +5821,7 @@
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>price-related данные приходят из master или проходят reconciliation; расхождение блокирует показ [behavioral: `tests/behavioral/test_rm_tech_264.py`]</t>
+          <t>master-confirmed price/promo подставляется при manifest generation; SLA-тест dynamic manifest [behavioral: `tests/behavioral/test_rm_tech_262.py`]</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -5831,14 +5831,14 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. OD-023 approved 2026-08-31 - planned после RM-TECH-280.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-008; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. ложная ESL-посылка снимается prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-263</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5848,21 +5848,21 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: master-data adapter цен/SKU (контракт, owner OD-023, reconciliation)</t>
+          <t>Field mobile operations: scoped mobile web для сотрудника магазина (устройства, фото, инциденты)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-210, RM-TECH-255</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
@@ -5874,14 +5874,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>владелец master-данных назначен (OD-023 approved); contract + reconciliation design утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; adapter в mock/test mode проходит contract tests [behavioral: `tests/behavioral/test_rm_tech_280.py`]</t>
+          <t>journey field_ops.device_confirm под ролью магазина с RLS; negative чужой магазин [ui_smoke: `tests/ui-smoke/test_rm_tech_263.py`]</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -5891,19 +5887,19 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: OD-023; contract tests. Риск регрессии: средний. отсутствующий prerequisite по AQ.1 №5; OD-023 approved 2026-08-31 (роль Product Data Owner) - planned; owner gate: контракт/scope adapter.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-009; SC: -; DEC: -. Evidence: new ui-smoke. Риск регрессии: средний. prerequisite RM-TECH-210 (RLS device) - planned по зависимости; feature field_ops.device_confirm blocked до задачи (RM-GOV-012 выравнивание: blocked = решение владельца/внешний факт, а не зависимость).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-003</t>
+          <t>RM-TECH-264</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5913,16 +5909,16 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>`self.report_view` plan/fact</t>
+          <t>ESL/price-checker: интеграция только через approved price/SKU master (INT-002)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201, RM-TECH-207B</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -5937,7 +5933,7 @@
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>реальные PoP/причины/RLS, journey/smoke/walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__report_view.py`]</t>
+          <t>price-related данные приходят из master или проходят reconciliation; расхождение блокирует показ [behavioral: `tests/behavioral/test_rm_tech_264.py`]</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -5947,34 +5943,34 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-011; зависит от RM-TECH-207B (реальные PoP) — без изменений</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. OD-023 approved 2026-08-31 - planned после RM-TECH-280.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-209</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>ClickHouse capacity trigger</t>
+          <t>Prerequisite: master-data adapter цен/SKU (контракт, owner OD-023, reconciliation)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
@@ -5990,10 +5986,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>измеряемый PoP rate/retention threshold и owner migration gate [artifact: `docs/product/clickhouse-capacity-trigger.yaml`]</t>
+          <t>владелец master-данных назначен (OD-023 approved); contract + reconciliation design утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; adapter в mock/test mode проходит contract tests [behavioral: `tests/behavioral/test_rm_tech_280.py`]</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -6003,14 +6003,14 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: OD-023; contract tests. Риск регрессии: средний. отсутствующий prerequisite по AQ.1 №5; OD-023 approved 2026-08-31 (роль Product Data Owner) - planned; owner gate: контракт/scope adapter.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-256</t>
+          <t>RM-BIZ-003</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -6020,21 +6020,21 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Business outcome KPI: baseline/target/metric definition для целей §1.2 (OD-024 exit criteria)</t>
+          <t>`self.report_view` plan/fact</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-201, RM-TECH-207B</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
@@ -6046,14 +6046,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>каждая бизнес-цель имеет baseline/target/формулу/владельца, утверждено владельцем [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>реальные PoP/причины/RLS, journey/smoke/walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__report_view.py`]</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -6063,14 +6059,14 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-013; SC: -; DEC: DEC-010. Evidence: artifact kpi register. Риск регрессии: низкий.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-011; зависит от RM-TECH-207B (реальные PoP) — без изменений</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-281</t>
+          <t>RM-TECH-209</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -6080,21 +6076,21 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: sales-reference ingestion (агрегаты store/SKU/day) + методология baseline/test-control</t>
+          <t>ClickHouse capacity trigger</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -6109,7 +6105,7 @@
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>пакетная загрузка агрегатов без PII; versioned baseline; методика утверждена владельцем [behavioral: `tests/behavioral/test_rm_tech_281.py`]</t>
+          <t>измеряемый PoP rate/retention threshold и owner migration gate [artifact: `docs/product/clickhouse-capacity-trigger.yaml`]</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -6119,14 +6115,14 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-001; SC: -; DEC: -. Evidence: new behavioral; methodology doc. Риск регрессии: средний. prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-282</t>
+          <t>RM-TECH-256</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -6136,21 +6132,21 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Attribution &amp; sales lift: test/control, versioned baseline, pilot lift report</t>
+          <t>Business outcome KPI: baseline/target/metric definition для целей §1.2 (OD-024 exit criteria)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-281, RM-TECH-229</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -6159,13 +6155,17 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr"/>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>pilot lift report по test/control с explainable методикой; RLS scope [behavioral: `tests/behavioral/test_rm_tech_282.py`]</t>
+          <t>каждая бизнес-цель имеет baseline/target/формулу/владельца, утверждено владельцем [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -6175,14 +6175,14 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-002; SC: -; DEC: DEC-005, DEC-027. Evidence: new behavioral; report. Риск регрессии: средний. blocked OD-014 (DEC-027); OD-023 approved 2026-08-31.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-013; SC: -; DEC: DEC-010. Evidence: artifact kpi register. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-283</t>
+          <t>RM-TECH-281</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -6192,17 +6192,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: audience source/privacy contract (анонимные store-атрибуты, 152-ФЗ, OD-032)</t>
+          <t>Prerequisite: sales-reference ingestion (агрегаты store/SKU/day) + методология baseline/test-control</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280, RM-TECH-253</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
@@ -6215,17 +6215,13 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>privacy/legal решение (OD-032) и контракт источника утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>пакетная загрузка агрегатов без PII; versioned baseline; методика утверждена владельцем [behavioral: `tests/behavioral/test_rm_tech_281.py`]</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -6235,14 +6231,14 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-005; SC: -; DEC: DEC-005, DEC-019. Evidence: OD-032; contract. Риск регрессии: низкий. blocked OD-032 (DEC-019); OD-023 approved 2026-08-31.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-001; SC: -; DEC: -. Evidence: new behavioral; methodology doc. Риск регрессии: средний. prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-284</t>
+          <t>RM-TECH-282</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -6257,16 +6253,16 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>A/B attribution и winner metric (minimum sample, owner approval результата)</t>
+          <t>Attribution &amp; sales lift: test/control, versioned baseline, pilot lift report</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-282</t>
+          <t>RM-TECH-281, RM-TECH-229</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -6281,7 +6277,7 @@
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>A/B фиксирует группы/период/метрику; winner только при minimum sample и ручном утверждении [behavioral: `tests/behavioral/test_rm_tech_284.py`]</t>
+          <t>pilot lift report по test/control с explainable методикой; RLS scope [behavioral: `tests/behavioral/test_rm_tech_282.py`]</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -6291,14 +6287,14 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-012, REQ-V26-010; SC: -; DEC: DEC-027. Evidence: new behavioral. Риск регрессии: средний. blocked OD-014 (DEC-027) - методика winner metric не утверждена.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-002; SC: -; DEC: DEC-005, DEC-027. Evidence: new behavioral; report. Риск регрессии: средний. blocked OD-014 (DEC-027); OD-023 approved 2026-08-31.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-285</t>
+          <t>RM-TECH-283</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -6308,17 +6304,17 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Competitive separation: competitive_category, интервал/исключение в playlist/manifest (исключение §3.1 по OD-018)</t>
+          <t>Prerequisite: audience source/privacy contract (анонимные store-атрибуты, 152-ФЗ, OD-032)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202, RM-TECH-280</t>
+          <t>RM-TECH-280, RM-TECH-253</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
@@ -6331,13 +6327,17 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>separation block/override test; изменение priority engine ограничено §3.1 [behavioral: `tests/behavioral/test_rm_tech_285.py`]</t>
+          <t>privacy/legal решение (OD-032) и контракт источника утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -6347,14 +6347,14 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-004; SC: -; DEC: DEC-005, DEC-022. Evidence: new behavioral. Риск регрессии: высокий: priority engine. OD-023 approved 2026-08-31, DEC-022 = OD-018 approved - planned после RM-TECH-280.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-005; SC: -; DEC: DEC-005, DEC-019. Evidence: OD-032; contract. Риск регрессии: низкий. blocked OD-032 (DEC-019); OD-023 approved 2026-08-31.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-286</t>
+          <t>RM-TECH-284</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -6369,16 +6369,16 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Financial-system exchange: versioned/idempotent export + payment-status contract (после DEC-017)</t>
+          <t>A/B attribution и winner metric (minimum sample, owner approval результата)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-246</t>
+          <t>RM-TECH-282</t>
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>idempotent export round-trip; повтор не создаёт дубликатов; scope финансового контура зафиксирован [behavioral: `tests/behavioral/test_rm_tech_286.py`]</t>
+          <t>A/B фиксирует группы/период/метрику; winner только при minimum sample и ручном утверждении [behavioral: `tests/behavioral/test_rm_tech_284.py`]</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -6403,14 +6403,14 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-006, REQ-BIZ-009; SC: -; DEC: DEC-017. Evidence: new behavioral. Риск регрессии: средний. blocked OD-030.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-012, REQ-V26-010; SC: -; DEC: DEC-027. Evidence: new behavioral. Риск регрессии: средний. blocked OD-014 (DEC-027) - методика winner metric не утверждена.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-287</t>
+          <t>RM-TECH-285</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -6425,16 +6425,16 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>BI/export/SIEM/vendor API: scoped keys, rate-limit, immutable audit, circuit breaker (после DEC-013)</t>
+          <t>Competitive separation: competitive_category, интервал/исключение в playlist/manifest (исключение §3.1 по OD-018)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-013</t>
+          <t>RM-TECH-202, RM-TECH-280</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
@@ -6443,13 +6443,13 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>401/403/429 negative; vendor connector с отдельными credentials и failure mode [behavioral: `tests/test_s065_rate_limit.py`]</t>
+          <t>separation block/override test; изменение priority engine ограничено §3.1 [behavioral: `tests/behavioral/test_rm_tech_285.py`]</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -6459,14 +6459,14 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-003; SC: SC-SEC-002; DEC: DEC-013. Evidence: tests/test_s065_rate_limit.py; new behavioral. Риск регрессии: средний. blocked OD-026.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-004; SC: -; DEC: DEC-005, DEC-022. Evidence: new behavioral. Риск регрессии: высокий: priority engine. OD-023 approved 2026-08-31, DEC-022 = OD-018 approved - planned после RM-TECH-280.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-289</t>
+          <t>RM-TECH-286</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -6476,21 +6476,21 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Extension points designed-not-implemented: ADR для programmatic (V26-007) и external measurement (V26-011)</t>
+          <t>Financial-system exchange: versioned/idempotent export + payment-status contract (после DEC-017)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-246</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
@@ -6499,13 +6499,13 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>ADR принят с пометкой designed-not-implemented; код не пишется до OD-021/OD-031 [artifact: `docs/audit/RM-TECH-289-artifact.md (создаётся задачей)`]</t>
+          <t>idempotent export round-trip; повтор не создаёт дубликатов; scope финансового контура зафиксирован [behavioral: `tests/behavioral/test_rm_tech_286.py`]</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -6515,14 +6515,14 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-007, REQ-V26-011; SC: SC-ARCH-006; DEC: DEC-001, DEC-018. Evidence: ADR. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-006, REQ-BIZ-009; SC: -; DEC: DEC-017. Evidence: new behavioral. Риск регрессии: средний. blocked OD-030.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-010</t>
+          <t>RM-TECH-287</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -6537,16 +6537,16 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Service-quality reporting: доля active devices/logical carriers, plan/fact по каналу (analytics.compare)</t>
+          <t>BI/export/SIEM/vendor API: scoped keys, rate-limit, immutable audit, circuit breaker (после DEC-013)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-003</t>
+          <t>RM-STAB-013</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -6555,13 +6555,13 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>отчёт по каналу с долями и причинами; RLS scope advertiser [ui_smoke: `tests/ui-smoke/test_rm_ux_010.py`]</t>
+          <t>401/403/429 negative; vendor connector с отдельными credentials и failure mode [behavioral: `tests/test_s065_rate_limit.py`]</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -6571,38 +6571,38 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-004; SC: -; DEC: -. Evidence: новый ui-smoke; tests/behavioral/test_pop_reporting_scope.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-003; SC: SC-SEC-002; DEC: DEC-013. Evidence: tests/test_s065_rate_limit.py; new behavioral. Риск регрессии: средний. blocked OD-026.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-001</t>
+          <t>RM-TECH-289</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>external</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Production readiness</t>
+          <t>Extension points designed-not-implemented: ADR для programmatic (V26-007) и external measurement (V26-011)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-003</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -6614,14 +6614,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+      <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>не запускается автоматически после pilot [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой; OD-025/OD-028)`]</t>
+          <t>ADR принят с пометкой designed-not-implemented; код не пишется до OD-021/OD-031 [artifact: `docs/audit/RM-TECH-289-artifact.md (создаётся задачей)`]</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -6631,19 +6627,19 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): зависит от OD-025 (RTO/RPO) и OD-028 (топология); REQ-OPS-005/006; HA baseline выделен в RM-OPS-003</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-007, REQ-V26-011; SC: SC-ARCH-006; DEC: DEC-001, DEC-018. Evidence: ADR. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-002</t>
+          <t>RM-UX-010</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6653,12 +6649,12 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Network segmentation: firewall rules по environment + negative reachability tests из device-сегмента</t>
+          <t>Service-quality reporting: доля active devices/logical carriers, plan/fact по каналу (analytics.compare)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-BIZ-003</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
@@ -6677,7 +6673,7 @@
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>Admin API/PostgreSQL/MinIO/Redis недостижимы из device-сегмента; Gateway только HTTPS/mTLS [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+          <t>отчёт по каналу с долями и причинами; RLS scope advertiser [ui_smoke: `tests/ui-smoke/test_rm_ux_010.py`]</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -6687,14 +6683,14 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-008; SC: SC-SEC-006; DEC: -. Evidence: reachability test log. Риск регрессии: средний: сеть пилота.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-004; SC: -; DEC: -. Evidence: новый ui-smoke; tests/behavioral/test_pop_reporting_scope.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-003</t>
+          <t>RM-OPS-001</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -6704,21 +6700,21 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>external-plan</t>
+          <t>external</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Production HA baseline: ≥2 backend, масштабируемый Gateway, standby PostgreSQL, MinIO replication, quarterly restore drill</t>
+          <t>Production readiness</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-001</t>
+          <t>RM-PILOT-003</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -6727,7 +6723,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -6737,7 +6733,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>production config gate зелёный; restore drill выполнен и записан [command: `tests/test_production_config_gate.py`]; топология утверждена (OD-028), RTO/RPO (OD-025) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>не запускается автоматически после pilot [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой; OD-025/OD-028)`]</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -6747,14 +6743,14 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-006, REQ-ARCH-004; SC: SC-OPS-001, SC-OPS-005; DEC: DEC-012, DEC-015. Evidence: tests/test_production_config_gate.py; drill record. Риск регрессии: высокий. blocked OD-025/OD-028.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): зависит от OD-025 (RTO/RPO) и OD-028 (топология); REQ-OPS-005/006; HA baseline выделен в RM-OPS-003</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-004</t>
+          <t>RM-OPS-002</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -6769,7 +6765,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Rollout entity/state machine и feature flags: planned→lab→canary→staged→paused→completed/rolled_back</t>
+          <t>Network segmentation: firewall rules по environment + negative reachability tests из device-сегмента</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6787,13 +6783,13 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>rollback возвращает предыдущую версию; flag отключает функцию; ответственность по OD-010 [behavioral: `tests/integration/test_stand_rollback_drill.py`]</t>
+          <t>Admin API/PostgreSQL/MinIO/Redis недостижимы из device-сегмента; Gateway только HTTPS/mTLS [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6803,14 +6799,14 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-002; SC: SC-OPS-007; DEC: DEC-008. Evidence: tests/integration/test_stand_rollback_drill.py. Риск регрессии: средний. blocked OD-010.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-008; SC: SC-SEC-006; DEC: -. Evidence: reachability test log. Риск регрессии: средний: сеть пилота.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-001</t>
+          <t>RM-OPS-003</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -6820,21 +6816,21 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>external-plan</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Managed control-plane pilot scope</t>
+          <t>Production HA baseline: ≥2 backend, масштабируемый Gateway, standby PostgreSQL, MinIO replication, quarterly restore drill</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Gate-S, Gate-U, RM-ENV-001</t>
+          <t>RM-OPS-001</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
@@ -6843,13 +6839,17 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
+          <t>production config gate зелёный; restore drill выполнен и записан [command: `tests/test_production_config_gate.py`]; топология утверждена (OD-028), RTO/RPO (OD-025) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -6859,38 +6859,38 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): deps += OD-024 (exit criteria ступеней), REQ-ARCH-004</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-006, REQ-ARCH-004; SC: SC-OPS-001, SC-OPS-005; DEC: DEC-012, DEC-015. Evidence: tests/test_production_config_gate.py; drill record. Риск регрессии: высокий. blocked OD-025/OD-028.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>RM-OPS-004</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Rollout entity/state machine и feature flags: planned→lab→canary→staged→paused→completed/rolled_back</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
           <t>RM-PILOT-002</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>POPS</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>external-plan</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>Deployment plan/preflight</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>RM-PILOT-001</t>
-        </is>
-      </c>
       <c r="F113" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
@@ -6899,13 +6899,13 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
+          <t>rollback возвращает предыдущую версию; flag отключает функцию; ответственность по OD-010 [behavioral: `tests/integration/test_stand_rollback_drill.py`]</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -6915,14 +6915,14 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-002; SC: SC-OPS-007; DEC: DEC-008. Evidence: tests/integration/test_stand_rollback_drill.py. Риск регрессии: средний. blocked OD-010.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002A</t>
+          <t>RM-PILOT-001</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -6932,21 +6932,21 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Pilot-compose поднимается под ENVIRONMENT=pilot без ручных шагов; verify честный</t>
+          <t>Managed control-plane pilot scope</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gate-S, Gate-U, RM-ENV-001</t>
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
@@ -6955,81 +6955,193 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>pilot-compose из образов коммита под ENVIRONMENT=pilot - db-migrate сам создаёт retail_media_app (NOBYPASSRLS), все сервисы healthy в пределах таймаута, readiness со строгой проверкой роли, identity из образа, device-токен control-api принят device-gateway, конфиг orchestrator-worker грузится; таймаут или любой отказ роняют проверку [command: `CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env &lt;version&gt; &lt;sha&gt;`]; каждый backend-сервис получает из pilot-compose все переменные, которых требует валидатор prod; пустой JWT_AUDIENCE - отказ при старте [command: `python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py`]</t>
+          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/36571330932; verified · command · CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env ci-pilot-smoke &lt;sha&gt;; verified · command · python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>done - PR #12 смержен в develop @ af6810c, push-run develop 36571330932 success 42/42 (решение владельца 2026-09-29). Решение владельца 2026-09-29 (этап RF-05, область RM-PILOT-002, Protected Boundary Docker/deployment с условиями). Находки ревью main@8ad0228: P0-1..P0-5, P1-16, P2-I9, P2-I11, T12 (+ FU5 healthcheck frontend). REQ: REQ-ARCH-004; SC: -; DEC: -. Не покрывает: TLS/reverse proxy (001D), ack/DLQ воркера при ошибке (RF-04), публикацию релиза и verify-pilot-images на GHCR (внешнее действие владельца). Риск регрессии: средний - обязательный JWT_AUDIENCE вне dev; pilot-хосты без него не стартуют.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): deps += OD-024 (exit criteria ступеней), REQ-ARCH-004</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>RM-PILOT-002</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>external-plan</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Deployment plan/preflight</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-001</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-002A</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Pilot-compose поднимается под ENVIRONMENT=pilot без ручных шагов; verify честный</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>pilot-compose из образов коммита под ENVIRONMENT=pilot - db-migrate сам создаёт retail_media_app (NOBYPASSRLS), все сервисы healthy в пределах таймаута, readiness со строгой проверкой роли, identity из образа, device-токен control-api принят device-gateway, конфиг orchestrator-worker грузится; таймаут или любой отказ роняют проверку [command: `CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env &lt;version&gt; &lt;sha&gt;`]; каждый backend-сервис получает из pilot-compose все переменные, которых требует валидатор prod; пустой JWT_AUDIENCE - отказ при старте [command: `python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py`]</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/36571330932; verified · command · CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env ci-pilot-smoke &lt;sha&gt;; verified · command · python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>done - PR #12 смержен в develop @ af6810c, push-run develop 36571330932 success 42/42 (решение владельца 2026-09-29). Решение владельца 2026-09-29 (этап RF-05, область RM-PILOT-002, Protected Boundary Docker/deployment с условиями). Находки ревью main@8ad0228: P0-1..P0-5, P1-16, P2-I9, P2-I11, T12 (+ FU5 healthcheck frontend). REQ: REQ-ARCH-004; SC: -; DEC: -. Не покрывает: TLS/reverse proxy (001D), ack/DLQ воркера при ошибке (RF-04), публикацию релиза и verify-pilot-images на GHCR (внешнее действие владельца). Риск регрессии: средний - обязательный JWT_AUDIENCE вне dev; pilot-хосты без него не стартуют.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
           <t>RM-PILOT-003</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>POPS</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Controlled pilot deploy</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>RM-PILOT-002</t>
         </is>
       </c>
-      <c r="F115" s="2" t="n">
+      <c r="F117" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr">
         <is>
           <t>deployment</t>
         </is>
       </c>
-      <c r="J115" s="2" t="inlineStr">
+      <c r="J117" s="2" t="inlineStr">
         <is>
           <t>SHA/lock/schema/health, stand-safe journeys, rollback readiness [owner: `docs/audit/&lt;дата&gt;-pilot-deploy-&lt;sha&gt;.md + ACCEPT владельца с датой (deployment gate)`]</t>
         </is>
       </c>
-      <c r="K115" s="2" t="inlineStr">
+      <c r="K117" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L115" s="2" t="inlineStr">
+      <c r="L117" s="2" t="inlineStr">
         <is>
           <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L117"/>
+  <dimension ref="A1:L127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1586,11 +1586,11 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-003, RM-STAB-006</t>
+          <t>RM-STAB-003, RM-STAB-006, RM-STAB-025</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) OD-044 (2026-08-31): реализовать по mini-design RM-STAB-003 - 4 bundles аддитивно, alias operator, scope_type=retailer в resolve_scope_context/require_scoped_permission; D3 - retailer scope по умолчанию внутренним non-admin (seed); D2 - analyst read-only retailer-scoped; security_admin не трогать (D1 → RM-STAB-015). 2026-08-31 старт (OD-043: RM-STAB-003/006 done; план владельца после CI 33408891221).</t>
+          <t>2026-10-07 (OD-047) - возвращена в planned решением владельца: веток, PR и правок по задаче нет, в коде scope_type=retailer не реализован, приёмочный тест отсутствует. P0-8 исполняется отдельной задачей раньше неё. полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) OD-044 (2026-08-31): реализовать по mini-design RM-STAB-003 - 4 bundles аддитивно, alias operator, scope_type=retailer в resolve_scope_context/require_scoped_permission; D3 - retailer scope по умолчанию внутренним non-admin (seed); D2 - analyst read-only retailer-scoped; security_admin не трогать (D1 → RM-STAB-015). 2026-08-31 старт (OD-043: RM-STAB-003/006 done; план владельца после CI 33408891221).</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-009; SC: SC-SEC-007; DEC: -. Evidence: tests/test_phase3_user_management.py; tests/test_s019_role_safety.py. Риск регрессии: средний: миграция permission-кодов затрагивает seed ролей (RM-STAB-004). OD-044 D1 (2026-08-31): сузить security_admin до модели Q2 (снять campaigns.manage/approve, creatives.moderate, inventory.manage, users.manage) отдельной миграцией с negative-тестами.</t>
+          <t>Намерение владельца 2026-10-07 (в объём задачи) - security_admin может деактивировать любую учётку, кроме system_admin и break-glass; реактивация, сброс пароля и роли - по строгому правилу подмножества прав (RM-STAB-022); оповещение владельца учётки при сбросе пароля; правило «админские роли назначает только is_admin». RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-009; SC: SC-SEC-007; DEC: -. Evidence: tests/test_phase3_user_management.py; tests/test_s019_role_safety.py. Риск регрессии: средний: миграция permission-кодов затрагивает seed ролей (RM-STAB-004). OD-044 D1 (2026-08-31): сузить security_admin до модели Q2 (снять campaigns.manage/approve, creatives.moderate, inventory.manage, users.manage) отдельной миграцией с negative-тестами.</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2626,12 +2626,12 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · behavioral · tests/behavioral/test_rm_stab_022_role_escalation.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/37585486496</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Решение владельца 2026-10-05, этап RF-12 (находки P0-6, P1-11.a, T2 ревью main @ 8ad0228; сверка RF-00). REQ: -; SC: -; DEC: -. Mini-design одобрен владельцем 2026-10-05 с дополнениями (журнал RF-12). Не покрывает: привязку прав к конкретной организации рекламодателя (P0-8, T3), T7, фронтенд (P1-11.b), RM-STAB-004, RM-STAB-015. Риск регрессии: средний - пользователи только со scoped-ролями теряют доступ к маршрутам require_permission (перечень - журнал RF-12, раздел Мини-дизайн, М5).</t>
+          <t>done - PR #17 смержен в develop @ 88a4e9e, push-run develop 37585486496 success 42/42 (решение владельца 2026-10-07). Этап RF-12 расширен решениями владельца 2026-10-05 - запрет сброса пароля, реактивации и деактивации учётки с правами выше актора. Решение владельца 2026-10-05, этап RF-12 (находки P0-6, P1-11.a, T2 ревью main @ 8ad0228; сверка RF-00). REQ: -; SC: -; DEC: -. Mini-design одобрен владельцем 2026-10-05 с дополнениями (журнал RF-12). Не покрывает: привязку прав к конкретной организации рекламодателя (P0-8, T3), T7, фронтенд (P1-11.b), RM-STAB-004, RM-STAB-015. Риск регрессии: средний - пользователи только со scoped-ролями теряют доступ к маршрутам require_permission (перечень - журнал RF-12, раздел Мини-дизайн, М5).</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-210</t>
+          <t>RM-STAB-024</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2709,16 +2709,16 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>RLS-контекст на device-маршрутах онбординга</t>
+          <t>Настройки AD: отдельные права чтения и изменения только у system_admin; вне dev подключение к AD только по TLS с проверкой сертификата (PUT и POST /test)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-002</t>
+          <t>RM-STAB-022</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -2727,58 +2727,54 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; bootstrap-RLS миграции 037: без RLS-контекста роль приложения видит 0 onboarding codes (fail-closed); со своим app.rmp_device_code — только свою строку; с чужим кодом — 0 [behavioral: `tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap`]</t>
+          <t>под retail_media_app (NOBYPASSRLS): GET/PUT /auth/ad-settings и POST /auth/ad-settings/test доступны только держателю отдельных прав (в сиде - system_admin), security_admin получает 403; вне dev PUT и POST /test отклоняют подключение без TLS или без проверки сертификата; пароль привязки не возвращается в ответе никому [behavioral: `tests/behavioral/test_rm_stab_024_ad_settings.py`]; уже сохранённые небезопасные настройки после исправления не ломают вход через AD молча - поведение явное и видно администратору (способ определяется мини-дизайном этапа) [behavioral: `tests/behavioral/test_rm_stab_024_ad_settings.py`]</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py; verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap; verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33408891221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика. 2026-08-31 (стадия S, OD-043: зависимость RM-STAB-002 done): реализовано локально - set_rls_context на /identity/device-codes, bootstrap-контекст кода/fingerprint на /device/onboard, миграция 037 (rehearsal down/up), allowlist элевации снят; targeted 97 passed под ролью приложения; design-gate docs/architecture/rm-tech-210-device-onboarding-rls-bootstrap-design-gate.md (на тот момент - до CI-evidence и owner gate). verification 2026-08-31: CI 33408891221 success (условием done тогда оставался owner gate device_contract). 2026-08-31: приёмка №2 уточнена владельцем — три утверждения bootstrap-RLS (без контекста 0; свой app.rmp_device_code — только свой; чужой — 0); ref → TestRMTech210BootstrapRLS. done 2026-08-31: owner gate device_contract granted - OD-045 (fail-closed контракт принят владельцем).</t>
+          <t>Решения владельца 2026-10-07 - «задача про PUT /auth/ad-settings, стадия S, первая в очереди»; «права + запрет небезопасного транспорта. Запрет действует и на PUT, и на POST /auth/ad-settings/test»; «security_admin настройки AD не читает. Пароль привязки не возвращается в ответе никому, включая system_admin»; «вход через AD не должен молча сломаться»; миграция 039 разрешена - «только добавление строк, downgrade удаляет только добавленное, существующие строки не меняются». Детали формулировки и приёмки - «вне dev», «отдельные права», «в сиде - system_admin» - предложены агентом (вариант, показанный владельцу в чате 2026-10-07) и подтверждаются мини-дизайном RF-13; дословно владелец решил только процитированное выше. Этап RF-13. REQ: -; SC: -; DEC: -. Не покрывает: список разрешённых хостов AD (RM-STAB-026), создание AD-учёток и роли из групп AD (RM-TECH-252), загрузку настроек из БД при старте.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-005</t>
+          <t>RM-STAB-025</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>retention-policy.yaml + legal decision register (AG): сроки, 152-ФЗ, deletion/archive, review date</t>
+          <t>Права scoped-роли действуют только в её scope (P0-8)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-253</t>
+          <t>RM-STAB-022</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -2787,17 +2783,13 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>юридическое утверждение retention/152-ФЗ (OD-009) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>под retail_media_app (NOBYPASSRLS): роль с scope организации A плюс членство в организации B не даёт прав этой роли в B на маршрутах require_scoped_permission [behavioral: `tests/behavioral/test_rm_stab_025_scoped_permissions.py`]</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2807,38 +2799,38 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено POPS → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). 2026-08-31: кандидат docs/product/retention-policy.yaml подготовлен (working defaults REQ-DATA-001, legal register) - не действует до OD-009; задача остаётся blocked.</t>
+          <t>Решение владельца 2026-10-07 («P0-8 отдельной задачей»; OD-047). Находки P0-8, T3 ревью main @ 8ad0228. Исполняется отдельным этапом, раньше RM-STAB-004. Способ (модель прав) определяется мини-дизайном этапа. REQ: -; SC: -; DEC: -.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-210</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>SLO objectives и измерение</t>
+          <t>RLS-контекст на device-маршрутах онбординга</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-STAB-002</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
@@ -2847,30 +2839,34 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>каждое число ТЗ имеет formula/window/owner/metric либо `not measurable` [artifact: `docs/product/slo-objectives.yaml`]</t>
+          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; bootstrap-RLS миграции 037: без RLS-контекста роль приложения видит 0 onboarding codes (fail-closed); со своим app.rmp_device_code — только свою строку; с чужим кодом — 0 [behavioral: `tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap`]</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py; verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap; verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33408891221</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288 RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/slo-objectives.yaml - 11 объектов, каждое число §8 с formula/window/owner/status; пороги OD-011/OD-025 open. Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика. 2026-08-31 (стадия S, OD-043: зависимость RM-STAB-002 done): реализовано локально - set_rls_context на /identity/device-codes, bootstrap-контекст кода/fingerprint на /device/onboard, миграция 037 (rehearsal down/up), allowlist элевации снят; targeted 97 passed под ролью приложения; design-gate docs/architecture/rm-tech-210-device-onboarding-rls-bootstrap-design-gate.md (на тот момент - до CI-evidence и owner gate). verification 2026-08-31: CI 33408891221 success (условием done тогда оставался owner gate device_contract). 2026-08-31: приёмка №2 уточнена владельцем — три утверждения bootstrap-RLS (без контекста 0; свой app.rmp_device_code — только свой; чужой — 0); ref → TestRMTech210BootstrapRLS. done 2026-08-31: owner gate device_contract granted - OD-045 (fail-closed контракт принят владельцем).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-OPS-005</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2880,21 +2876,21 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>OpenAPI + event/manifest JSON Schema (AG): as-built генерация + target из §26/AB, contract tests</t>
+          <t>retention-policy.yaml + legal decision register (AG): сроки, 152-ФЗ, deletion/archive, review date</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-253</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -2906,10 +2902,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>OpenAPI/event schemas версионированы, examples и deprecation policy; contract tests зелёные [command: `python3 scripts/ci/roadmap-governance-guard.py`]; одна canonical opaque идентификация на версию API; alias {id} с deprecation date [behavioral: `tests/behavioral/test_rm_tech_220.py`]</t>
+          <t>юридическое утверждение retention/152-ФЗ (OD-009) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2919,14 +2919,14 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/api/openapi-as-built-v1.json (113 paths/128 ops/149 схем), target docs/architecture/api/openapi-target-v2.6.md, envelope docs/architecture/events/event-envelope-v1.schema.json; contract tests и версионирование - после старта задачи; задача planned до Gate-S (OD-043).</t>
+          <t>2026-10-07 (OD-009) - разблокирована решением владельца по объёму и сроку: сроки хранения и минимизация ПДн - до пилота; OD-009 делится на четыре задачи - эта (сроки хранения), RM-OPS-007 (VPN), RM-OPS-008 (SIEM) и минимизация ПДн (задача ещё не заведена - ожидает подтверждения владельцем приёмки). Юридическое утверждение retention/152-ФЗ НЕ дано: приёмка задачи этим не закрыта. Записи ниже - до 2026-10-07 (исторические): RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено POPS → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). 2026-08-31: кандидат docs/product/retention-policy.yaml подготовлен (working defaults REQ-DATA-001, legal register) - не действует до OD-009; задача остаётся blocked.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-221</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2936,21 +2936,21 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Разделение User/Device/analytics/emergency API; device client не достигает admin</t>
+          <t>SLO objectives и измерение</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>device JWT → admin endpoint = 403 на всех admin-роутах [behavioral: `tests/test_phase3_protected_identity.py`]</t>
+          <t>каждое число ТЗ имеет formula/window/owner/metric либо `not measurable` [artifact: `docs/product/slo-objectives.yaml`]</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2975,14 +2975,14 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-002; SC: SC-API-002; DEC: -. Evidence: tests/test_phase3_protected_identity.py; новый negative. Риск регрессии: низкий.</t>
+          <t>OD-011 решён владельцем 2026-10-07 - до пилота только замер базовой линии, нагрузочные профили - на ступени 500. Замер выделен в RM-TECH-291 (решение владельца 2026-10-08). Записи ниже - до 2026-10-07 (исторические): полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288 RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/slo-objectives.yaml - 11 объектов, каждое число §8 с formula/window/owner/status; пороги OD-011/OD-025 open. Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-222</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2997,16 +2997,16 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Канонический POST /api/v1/pop/batch, legacy /device/pop/batch как alias с deprecation</t>
+          <t>OpenAPI + event/manifest JSON Schema (AG): as-built генерация + target из §26/AB, contract tests</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>ответы канонического и legacy идентичны; deprecation header; batch&gt;500 → 422; чужой device_id отклонён [behavioral: `tests/test_contract_pop.py`]</t>
+          <t>OpenAPI/event schemas версионированы, examples и deprecation policy; contract tests зелёные [command: `python3 scripts/ci/roadmap-governance-guard.py`]; одна canonical opaque идентификация на версию API; alias {id} с deprecation date [behavioral: `tests/behavioral/test_rm_tech_220.py`]</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3031,14 +3031,14 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-003, REQ-POP-003; SC: SC-API-003, SC-POP-003; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_edge002fu_real_endpoint.py. Риск регрессии: средний: runtime/плеер использует legacy path.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/api/openapi-as-built-v1.json (113 paths/128 ops/149 схем), target docs/architecture/api/openapi-target-v2.6.md, envelope docs/architecture/events/event-envelope-v1.schema.json; contract tests и версионирование - после старта задачи; задача planned до Gate-S (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-223</t>
+          <t>RM-TECH-221</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Manifest field contract и ACK-состояния runtime (opaque media_ref, no MinIO keys)</t>
+          <t>Разделение User/Device/analytics/emergency API; device client не достигает admin</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3074,14 +3074,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>все обязательные поля §25 REQ-MAN-004 в schema; внутренний object key не раскрыт; 6 ACK states принимаются [behavioral: `tests/test_contract_manifest.py`]</t>
+          <t>device JWT → admin endpoint = 403 на всех admin-роутах [behavioral: `tests/test_phase3_protected_identity.py`]</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3091,14 +3087,14 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-MAN-004; SC: SC-MAN-001; DEC: -. Evidence: tests/test_contract_manifest.py; tests/behavioral/test_edge002_manifest_delivery.py. Риск регрессии: высокий: меняет device-facing контракт — owner gate device_contract.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-002; SC: SC-API-002; DEC: -. Evidence: tests/test_phase3_protected_identity.py; новый negative. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-222</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3113,7 +3109,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat contract POST /api/v1/device/heartbeat: дедуп, scope, clock drift, freshness thresholds</t>
+          <t>Канонический POST /api/v1/pop/batch, legacy /device/pop/batch как alias с deprecation</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3134,14 +3130,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+      <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>валидный/повтор/чужой scope/просроченный heartbeat дают ожидаемые результаты; legacy alias с той же семантикой [behavioral: `tests/behavioral/test_edge004_heartbeat.py`]</t>
+          <t>ответы канонического и legacy идентичны; deprecation header; batch&gt;500 → 422; чужой device_id отклонён [behavioral: `tests/test_contract_pop.py`]</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3151,14 +3143,14 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-009; SC: SC-OPS-002; DEC: -. Evidence: tests/behavioral/test_edge004_heartbeat.py. Риск регрессии: высокий: device-facing.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-003, REQ-POP-003; SC: SC-API-003, SC-POP-003; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_edge002fu_real_endpoint.py. Риск регрессии: средний: runtime/плеер использует legacy path.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-223</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3173,16 +3165,16 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>PoP duplicate semantics по OD-019: 200 + per-event duplicate/409, amendment ADR-017</t>
+          <t>Manifest field contract и ACK-состояния runtime (opaque media_ref, no MinIO keys)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-222</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -3194,10 +3186,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>ADR-017 amendment принят; behavioral: повтор batch → per-event duplicate, summary не удвоен, порядок хронологический [behavioral: `tests/behavioral/test_edge003_pop_ingestion.py`]</t>
+          <t>все обязательные поля §25 REQ-MAN-004 в schema; внутренний object key не раскрыт; 6 ACK states принимаются [behavioral: `tests/test_contract_manifest.py`]</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3207,14 +3203,14 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-002; SC: SC-POP-002; DEC: DEC-024. Evidence: tests/behavioral/test_edge003_pop_ingestion.py; ADR-017 amendment. Риск регрессии: низкий: закрепляет текущее поведение.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-MAN-004; SC: SC-MAN-001; DEC: -. Evidence: tests/test_contract_manifest.py; tests/behavioral/test_edge002_manifest_delivery.py. Риск регрессии: высокий: меняет device-facing контракт — owner gate device_contract.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-226</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3229,16 +3225,16 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Proof model: pop_mode error/not_applied — schema/runtime migration из compatibility projection</t>
+          <t>Heartbeat contract POST /api/v1/device/heartbeat: дедуп, scope, clock drift, freshness thresholds</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -3252,12 +3248,12 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>migration_application</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>ProofMode содержит 9 значений; отчёт не смешивает playback/apply/delivery/error [behavioral: `tests/behavioral/test_pop_schema.py`]</t>
+          <t>валидный/повтор/чужой scope/просроченный heartbeat дают ожидаемые результаты; legacy alias с той же семантикой [behavioral: `tests/behavioral/test_edge004_heartbeat.py`]</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -3267,14 +3263,14 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-001; SC: SC-POP-001; DEC: -. Evidence: tests/behavioral/test_pop_schema.py; migration. Риск регрессии: средний: enum migration + отчёты.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-009; SC: SC-OPS-002; DEC: -. Evidence: tests/behavioral/test_edge004_heartbeat.py. Риск регрессии: высокий: device-facing.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-227</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3289,16 +3285,16 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Валидация proof_event_v1: playback_result/failure_reason, clock-drift quarantine, no internal IDs/PII</t>
+          <t>PoP duplicate semantics по OD-019: 200 + per-event duplicate/409, amendment ADR-017</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-222</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -3313,7 +3309,7 @@
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>недопустимый playback_result/внутренний ID/сдвиг часов → 422 или quarantine; SHA/signature проверены [behavioral: `tests/test_contract_pop.py`]</t>
+          <t>ADR-017 amendment принят; behavioral: повтор batch → per-event duplicate, summary не удвоен, порядок хронологический [behavioral: `tests/behavioral/test_edge003_pop_ingestion.py`]</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3323,14 +3319,14 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-004; SC: SC-POP-004; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_pop_schema.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-002; SC: SC-POP-002; DEC: DEC-024. Evidence: tests/behavioral/test_edge003_pop_ingestion.py; ADR-017 amendment. Риск регрессии: низкий: закрепляет текущее поведение.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-228</t>
+          <t>RM-TECH-226</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3345,16 +3341,16 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Окно совместимости device/API/manifest: heartbeat объявляет версии, сервер выбирает представление</t>
+          <t>Proof model: pop_mode error/not_applied — schema/runtime migration из compatibility projection</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -3366,10 +3362,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>совместимая версия выбрана по объявленным capabilities; breaking change без staged rollout отклонён contract-тестом [behavioral: `tests/test_version_identity.py`]</t>
+          <t>ProofMode содержит 9 значений; отчёт не смешивает playback/apply/delivery/error [behavioral: `tests/behavioral/test_pop_schema.py`]</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3379,14 +3379,14 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-003; SC: SC-NFR-003; DEC: -. Evidence: tests/test_version_identity.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-001; SC: SC-POP-001; DEC: -. Evidence: tests/behavioral/test_pop_schema.py; migration. Риск регрессии: средний: enum migration + отчёты.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-227</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3396,21 +3396,21 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>ERD + data dictionary + migration plan (AG): инвентарь сущностей §15, retailer_id NOT NULL + двухуровневый RLS</t>
+          <t>Валидация proof_event_v1: playback_result/failure_reason, clock-drift quarantine, no internal IDs/PII</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>as-built ERD из моделей; каждая группа §15 присутствует или имеет migration task; tenant-таблицы с retailer_id+FK+RLS [artifact: `tests/behavioral/test_adr018_multitenancy_rls.py`]; behavioral RLS proof под ролью приложения NOBYPASSRLS [behavioral: `tests/behavioral/test_adr018_multitenancy_rls.py`]</t>
+          <t>недопустимый playback_result/внутренний ID/сдвиг часов → 422 или quarantine; SHA/signature проверены [behavioral: `tests/test_contract_pop.py`]</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3435,14 +3435,14 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/erd/data-dictionary-as-built.md (62 таблицы, 38 RLS) и кандидат docs/architecture/erd/migration-plan-v2.6.md (§13 → present/missing → задачи); PII/retention колонки - RM-TECH-253/RM-OPS-005. Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-004; SC: SC-POP-004; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_pop_schema.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-230</t>
+          <t>RM-TECH-228</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3452,21 +3452,21 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Channel Adapter contract (design-only до второго канала): versioned task, receipt, proof/ack, error, health, mock mode</t>
+          <t>Окно совместимости device/API/manifest: heartbeat объявляет версии, сервер выбирает представление</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>contract spec + JSON Schema без реализации adapter/mock (ADR-019) [artifact: `docs/architecture contract`]</t>
+          <t>совместимая версия выбрана по объявленным capabilities; breaking change без staged rollout отклонён contract-тестом [behavioral: `tests/test_version_identity.py`]</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -3491,14 +3491,14 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-006; SC: SC-ORCH-005; DEC: -. Evidence: docs/architecture contract; schema. Риск регрессии: низкий: только документ.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-003; SC: SC-NFR-003; DEC: -. Evidence: tests/test_version_identity.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-231</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3513,16 +3513,16 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>channel-capability-matrix.yaml (AG) для первого канала KSO: channel/surface/rendition/proof/SLA/vendor constraints</t>
+          <t>ERD + data dictionary + migration plan (AG): инвентарь сущностей §15, retailer_id NOT NULL + двухуровневый RLS</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-230</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -3534,14 +3534,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>матрица покрывает KSO channel/surface/rendition/proof/SLA/vendor constraints; каждая строка ссылается на REQ-CHAN-*/REQ-MAN-*/REQ-POP-* [artifact: `docs/product/channel-capability-matrix.yaml`]; артефакт принят владельцем как часть handoff-пакета AG [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>as-built ERD из моделей; каждая группа §15 присутствует или имеет migration task; tenant-таблицы с retailer_id+FK+RLS [artifact: `tests/behavioral/test_adr018_multitenancy_rls.py`]; behavioral RLS proof под ролью приложения NOBYPASSRLS [behavioral: `tests/behavioral/test_adr018_multitenancy_rls.py`]</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -3551,14 +3547,14 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-012 (предложение 2026-08-31): AG требует channel-capability-matrix до старта разработки, а RM-TECH-261 держит матрицу за решением OD-021 (второй канал). Первый канал KSO описывается без OD-021; RM-TECH-261 расширяет матрицу вторым каналом. REQ: REQ-CHAN-001, REQ-CHAN-002, REQ-CHAN-003; SC: SC-CHAN-002; DEC: DEC-001 (расширение). Evidence: артефакт; ACCEPT владельца. Риск регрессии: нет (документ). Утверждена OD-042 (2026-08-31). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/channel-capability-matrix.yaml (KSO + declared каналы §7); приёмка - внутри задачи после Gate-S.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/erd/data-dictionary-as-built.md (62 таблицы, 38 RLS) и кандидат docs/architecture/erd/migration-plan-v2.6.md (§13 → present/missing → задачи); PII/retention колонки - RM-TECH-253/RM-OPS-005. Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-253</t>
+          <t>RM-TECH-230</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3573,16 +3569,16 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Data protection: data classes, lawful purpose, минимизация PII, residency; retention по OD-009</t>
+          <t>Channel Adapter contract (design-only до второго канала): versioned task, receipt, proof/ack, error, health, mock mode</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -3597,7 +3593,7 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>реестр data classes для всех сущностей; новая PII-сущность без класса — красный design-gate [artifact: `docs/architecture data classes`]</t>
+          <t>contract spec + JSON Schema без реализации adapter/mock (ADR-019) [artifact: `docs/architecture contract`]</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3607,14 +3603,14 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: docs/architecture data classes. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено CORE → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-006; SC: SC-ORCH-005; DEC: -. Evidence: docs/architecture contract; schema. Риск регрессии: низкий: только документ.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-288</t>
+          <t>RM-TECH-231</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3624,21 +3620,21 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>nfr-slo.yaml + load-profiles.yaml (AG): method, percentile, error budget, generator, CI evidence</t>
+          <t>channel-capability-matrix.yaml (AG) для первого канала KSO: channel/surface/rendition/proof/SLA/vendor constraints</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-230</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -3650,10 +3646,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>каждый SLO имеет window/denominator/exclusions; load generator и прогон в CI/стенде [artifact: `nfr-slo.yaml`]</t>
+          <t>матрица покрывает KSO channel/surface/rendition/proof/SLA/vendor constraints; каждая строка ссылается на REQ-CHAN-*/REQ-MAN-*/REQ-POP-* [artifact: `docs/product/channel-capability-matrix.yaml`]; артефакт принят владельцем как часть handoff-пакета AG [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3663,14 +3663,14 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки):ы docs/product/nfr-slo.yaml и docs/product/load-profiles.yaml (7 профилей); load generator отсутствует (new). Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>RM-GOV-012 (предложение 2026-08-31): AG требует channel-capability-matrix до старта разработки, а RM-TECH-261 держит матрицу за решением OD-021 (второй канал). Первый канал KSO описывается без OD-021; RM-TECH-261 расширяет матрицу вторым каналом. REQ: REQ-CHAN-001, REQ-CHAN-002, REQ-CHAN-003; SC: SC-CHAN-002; DEC: DEC-001 (расширение). Evidence: артефакт; ACCEPT владельца. Риск регрессии: нет (документ). Утверждена OD-042 (2026-08-31). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/channel-capability-matrix.yaml (KSO + declared каналы §7); приёмка - внутри задачи после Gate-S.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-011</t>
+          <t>RM-TECH-253</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3680,21 +3680,21 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>role-scope-matrix.yaml + portal-route-matrix.yaml + journeys/ (AG) из seed/pg_policies/registry</t>
+          <t>Data protection: data classes, lawful purpose, минимизация PII, residency; retention по OD-009</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004, RM-STAB-006</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>матрицы генерируются и сверяются guard; deny-cases покрыты behavioral [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+          <t>реестр data classes для всех сущностей; новая PII-сущность без класса — красный design-gate [artifact: `docs/architecture data classes`]</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3719,19 +3719,19 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено U → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/product/role-scope-matrix.yaml (5 seeded ролей × 30 permissions, Q2 target 7 ролей, 38 RLS-таблиц, deny-cases), docs/product/portal-route-matrix.yaml (admin 16 + advertiser 9 маршрутов), docs/product/journeys/journeys.yaml (79 journeys, нормативный формат); generated-сверка guard - после старта задачи; задача planned до Gate-S (OD-043).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: docs/architecture data classes. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено CORE → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-001</t>
+          <t>RM-TECH-288</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3741,16 +3741,16 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Записать managed-first scope</t>
+          <t>nfr-slo.yaml + load-profiles.yaml (AG): method, percentile, error budget, generator, CI evidence</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>roadmap явно исключает `self.campaign_create` из ближайшего control-plane pilot [artifact: `docs/product/roadmap.yaml (pilot scope)`]</t>
+          <t>каждый SLO имеет window/denominator/exclusions; load generator и прогон в CI/стенде [artifact: `nfr-slo.yaml`]</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3775,38 +3775,38 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): ссылки OD-005/DEC-011, REQ-SCOPE-001</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки):ы docs/product/nfr-slo.yaml и docs/product/load-profiles.yaml (7 профилей); load generator отсутствует (new). Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201</t>
+          <t>RM-UX-011</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Таксономия причин недопоказа</t>
+          <t>role-scope-matrix.yaml + portal-route-matrix.yaml + journeys/ (AG) из seed/pg_policies/registry</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-STAB-004, RM-STAB-006</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>8 категорий ТЗ, source/report/history contract и owner-approved artifact [artifact: `docs/product/underdelivery-reason-taxonomy.yaml`]</t>
+          <t>матрицы генерируются и сверяются guard; deny-cases покрыты behavioral [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3831,14 +3831,14 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено U → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/product/role-scope-matrix.yaml (5 seeded ролей × 30 permissions, Q2 target 7 ролей, 38 RLS-таблиц, deny-cases), docs/product/portal-route-matrix.yaml (admin 16 + advertiser 9 маршрутов), docs/product/journeys/journeys.yaml (79 journeys, нормативный формат); generated-сверка guard - после старта задачи; задача planned до Gate-S (OD-043).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202</t>
+          <t>RM-BIZ-001</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3848,21 +3848,21 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Вытеснение и объяснимые приоритеты</t>
+          <t>Записать managed-first scope</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>versioned rules [behavioral: `tests/behavioral/test_campaign_preemption.py`]</t>
+          <t>roadmap явно исключает `self.campaign_create` из ближайшего control-plane pilot [artifact: `docs/product/roadmap.yaml (pilot scope)`]</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3887,14 +3887,14 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-007 и порядок приоритета §12; исключение §3.1 (OD-018) — единственная точка изменения engine → RM-TECH-285 зависит от неё</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): ссылки OD-005/DEC-011, REQ-SCOPE-001</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-203</t>
+          <t>RM-STAB-026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3909,16 +3909,16 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Overbooking policy</t>
+          <t>Настройки AD: сервер AD задаётся только из списка разрешённых хостов</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202</t>
+          <t>RM-STAB-024</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>default deny [behavioral: `tests/behavioral/test_inventory_overbooking_policy.py`]</t>
+          <t>адрес сервера AD вне списка разрешённых хостов отклоняется при сохранении настроек и при проверке подключения [behavioral: `tests/behavioral/test_rm_stab_026_ad_allowed_hosts.py`]</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3943,14 +3943,14 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>Решение владельца 2026-10-07 («Список разрешённых хостов — отдельным этапом, в долг»). Срок не назначен. Способ задания списка определяется мини-дизайном этапа. REQ: -; SC: -; DEC: -. Перенесена из стадии S по ответу владельца 2026-10-08 («перенеси»): в условие Gate-S не входит. Целевая стадия CORE выбрана агентом - ожидает подтверждения владельца.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-204</t>
+          <t>RM-TECH-201</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Creative QA без неутверждённого HTML5</t>
+          <t>Таксономия причин недопоказа</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>metadata/antivirus/executable deny и immutable QA result [behavioral: `tests/behavioral/test_creative_qa.py`]</t>
+          <t>8 категорий ТЗ, source/report/history contract и owner-approved artifact [artifact: `docs/product/underdelivery-reason-taxonomy.yaml`]</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-206</t>
+          <t>RM-TECH-202</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4021,16 +4021,16 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>License renewal/grant boundary</t>
+          <t>Вытеснение и объяснимые приоритеты</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-201</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>атомарная семантика §1.6 [behavioral: `tests/behavioral/test_license_renewal_boundary.py`]</t>
+          <t>versioned rules [behavioral: `tests/behavioral/test_campaign_preemption.py`]</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -4055,14 +4055,14 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-007 и порядок приоритета §12; исключение §3.1 (OD-018) — единственная точка изменения engine → RM-TECH-285 зависит от неё</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>RM-TECH-203</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Универсальная иерархия носителей: migration + seed network/branch/cluster/store/store_group/channel/device/surface</t>
+          <t>Overbooking policy</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-202</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
@@ -4098,14 +4098,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>все уровни существуют с FK и RLS; seed заполняет иерархию; чужой scope не видит [behavioral: `tests/behavioral/test_scope_rls.py`]</t>
+          <t>default deny [behavioral: `tests/behavioral/test_inventory_overbooking_policy.py`]</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4115,14 +4111,14 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-001; SC: SC-DATA-001; DEC: -. Evidence: migration; tests/behavioral/test_scope_rls.py. Риск регрессии: высокий: схема ядра.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-241</t>
+          <t>RM-TECH-204</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4137,16 +4133,16 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Target resolution boundary: broad target → display_surface_id, запрет physical_device_id как target</t>
+          <t>Creative QA без неутверждённого HTML5</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -4161,7 +4157,7 @@
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>планирование разрешает target до surface; physical_device_id в target отклоняется [behavioral: `tests/test_s089_inventory_simulation.py`]</t>
+          <t>metadata/antivirus/executable deny и immutable QA result [behavioral: `tests/behavioral/test_creative_qa.py`]</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -4171,14 +4167,14 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-003; SC: SC-ARCH-002; DEC: -. Evidence: tests/test_s089_inventory_simulation.py. Риск регрессии: средний.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-242</t>
+          <t>RM-TECH-206</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4193,16 +4189,16 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Outbox для любой OLTP-записи с domain event; revocation/refresh manifest при pause/archive/expiry</t>
+          <t>License renewal/grant boundary</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
@@ -4217,7 +4213,7 @@
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>каждая доменная мутация создаёт outbox event в той же транзакции; pause/archive порождают revocation [behavioral: `tests/behavioral/test_outbox.py`]</t>
+          <t>атомарная семантика §1.6 [behavioral: `tests/behavioral/test_license_renewal_boundary.py`]</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -4227,14 +4223,14 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-003; SC: SC-ORCH-002; DEC: -. Evidence: tests/behavioral/test_outbox.py. Риск регрессии: средний: транзакционные границы всех сервисов.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-243</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4249,16 +4245,16 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Outbox relay: lease/publishing, Nats-Msg-Id, 7 попыток → dead_letter, partition order, DLQ policy, no PII</t>
+          <t>Универсальная иерархия носителей: migration + seed network/branch/cluster/store/store_group/channel/device/surface</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-242</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -4270,10 +4266,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>7 отказов брокера → dead_letter с operator action; ack → published; replay идемпотентен [behavioral: `tests/behavioral/test_outbox_relay.py`]; NATS recovery integration зелёный [command: `tests/behavioral/test_outbox_relay.py`]</t>
+          <t>все уровни существуют с FK и RLS; seed заполняет иерархию; чужой scope не видит [behavioral: `tests/behavioral/test_scope_rls.py`]</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -4283,14 +4283,14 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-004; SC: SC-ORCH-003; DEC: DEC-004. Evidence: tests/behavioral/test_outbox_relay.py; tests/integration/test_nats_recovery.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-001; SC: SC-DATA-001; DEC: -. Evidence: migration; tests/behavioral/test_scope_rls.py. Риск регрессии: высокий: схема ядра.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-244</t>
+          <t>RM-TECH-241</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4305,16 +4305,16 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Adapter task lifecycle через persisted queue (event-driven массовая публикация)</t>
+          <t>Target resolution boundary: broad target → display_surface_id, запрет physical_device_id как target</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-243</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>активация на 1000 устройств не ждёт устройств; задачи агрегируют статусы [behavioral: `tests/behavioral/test_delivery_foundation.py`]</t>
+          <t>планирование разрешает target до surface; physical_device_id в target отклоняется [behavioral: `tests/test_s089_inventory_simulation.py`]</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -4339,14 +4339,14 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-002; SC: SC-ORCH-006; DEC: DEC-004. Evidence: tests/behavioral/test_delivery_foundation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-003; SC: SC-ARCH-002; DEC: -. Evidence: tests/test_s089_inventory_simulation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-TECH-242</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4361,16 +4361,16 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Campaign lifecycle по ADR-015/OD-036: scheduled, resume, revise, archive; единый guard и audit</t>
+          <t>Outbox для любой OLTP-записи с domain event; revocation/refresh manifest при pause/archive/expiry</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -4382,14 +4382,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>_CAMPAIGN_TRANSITIONS = ADR-015; каждый переход через guard с audit; возврат в draft создаёт revision [behavioral: `tests/behavioral/test_campaign_domain.py`]; campaign.* smokes зелёные после изменения [ui_smoke: `tests/ui-smoke/test_rm_tech_245.py`]</t>
+          <t>каждая доменная мутация создаёт outbox event в той же транзакции; pause/archive порождают revocation [behavioral: `tests/behavioral/test_outbox.py`]</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -4399,14 +4395,14 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-010; SC: -; DEC: DEC-025. Evidence: tests/behavioral/test_campaign_domain.py; tests/ui-smoke/test_uismoke__campaign__*.py. Риск регрессии: высокий: меняет runtime enum кампании и UI.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-003; SC: SC-ORCH-002; DEC: -. Evidence: tests/behavioral/test_outbox.py. Риск регрессии: средний: транзакционные границы всех сервисов.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-246</t>
+          <t>RM-TECH-243</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4421,16 +4417,16 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Commerce order: отмена по OD-020 (draft→cancelled, confirmed — reversal), payment projection отдельно</t>
+          <t>Outbox relay: lease/publishing, Nats-Msg-Id, 7 попыток → dead_letter, partition order, DLQ policy, no PII</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-TECH-242</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -4445,7 +4441,7 @@
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>_ORDER_TRANSITIONS: draft→cancelled разрешён, confirmed→cancelled запрещён, reversal с audit [behavioral: `tests/test_commerce_a2.py`]</t>
+          <t>7 отказов брокера → dead_letter с operator action; ack → published; replay идемпотентен [behavioral: `tests/behavioral/test_outbox_relay.py`]; NATS recovery integration зелёный [command: `tests/behavioral/test_outbox_relay.py`]</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -4455,14 +4451,14 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-014; SC: -; DEC: DEC-017, DEC-026. Evidence: tests/test_commerce_a2.py; tests/behavioral/test_commerce_rls.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-004; SC: SC-ORCH-003; DEC: DEC-004. Evidence: tests/behavioral/test_outbox_relay.py; tests/integration/test_nats_recovery.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-247</t>
+          <t>RM-TECH-244</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4477,16 +4473,16 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Approval policy: required roles/scope/порядок/timeout per campaign/placement/creative</t>
+          <t>Adapter task lifecycle через persisted queue (event-driven массовая публикация)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-TECH-243</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -4501,7 +4497,7 @@
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>политика версионирована; submit/approve соблюдают порядок и timeout; negative для чужого scope [behavioral: `tests/behavioral/test_campaign_approval.py`]</t>
+          <t>активация на 1000 устройств не ждёт устройств; задачи агрегируют статусы [behavioral: `tests/behavioral/test_delivery_foundation.py`]</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -4511,14 +4507,14 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-003; SC: -; DEC: -. Evidence: tests/behavioral/test_campaign_approval.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-002; SC: SC-ORCH-006; DEC: DEC-004. Evidence: tests/behavioral/test_delivery_foundation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-248</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4533,12 +4529,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Flight/placement windows: versioned start_at/end_at UTC, проверка при simulation/manifest/runtime</t>
+          <t>Campaign lifecycle по ADR-015/OD-036: scheduled, resume, revise, archive; единый guard и audit</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
@@ -4554,10 +4550,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>показ вне окна запрещён на трёх уровнях; DST/праздники/closed stores — версионированные правила [behavioral: `tests/test_s063_pop_timezone.py`]</t>
+          <t>_CAMPAIGN_TRANSITIONS = ADR-015; каждый переход через guard с audit; возврат в draft создаёт revision [behavioral: `tests/behavioral/test_campaign_domain.py`]; campaign.* smokes зелёные после изменения [ui_smoke: `tests/ui-smoke/test_rm_tech_245.py`]</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -4567,14 +4567,14 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-005, REQ-NFR-002; SC: SC-NFR-002; DEC: -. Evidence: tests/test_s063_pop_timezone.py; новый behavioral. Риск регрессии: высокий: расписание доставки.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-010; SC: -; DEC: DEC-025. Evidence: tests/behavioral/test_campaign_domain.py; tests/ui-smoke/test_uismoke__campaign__*.py. Риск регрессии: высокий: меняет runtime enum кампании и UI.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-249</t>
+          <t>RM-TECH-246</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4589,16 +4589,16 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Manifest eligibility: approved status + валидный flight/contract + resolved target + readiness</t>
+          <t>Commerce order: отмена по OD-020 (draft→cancelled, confirmed — reversal), payment projection отдельно</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-248</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>неэлигибельная кампания не попадает в manifest; причина объяснима [behavioral: `tests/behavioral/test_delivery_generation.py`]</t>
+          <t>_ORDER_TRANSITIONS: draft→cancelled разрешён, confirmed→cancelled запрещён, reversal с audit [behavioral: `tests/test_commerce_a2.py`]</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -4623,14 +4623,14 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-006; SC: -; DEC: -. Evidence: tests/behavioral/test_delivery_generation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-014; SC: -; DEC: DEC-017, DEC-026. Evidence: tests/test_commerce_a2.py; tests/behavioral/test_commerce_rls.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-250</t>
+          <t>RM-TECH-247</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4645,16 +4645,16 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Creative/rendition state machine и immutable media history (uploaded→scanning→qa_failed/approved→superseded→retained)</t>
+          <t>Approval policy: required roles/scope/порядок/timeout per campaign/placement/creative</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-204</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -4666,14 +4666,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>каждая версия хранит uploader/SHA-256/QA-решение/связь; закрытый отчёт воспроизводим после logical delete [behavioral: `tests/behavioral/test_creative_assets.py`]</t>
+          <t>политика версионирована; submit/approve соблюдают порядок и timeout; negative для чужого scope [behavioral: `tests/behavioral/test_campaign_approval.py`]</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -4683,14 +4679,14 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CONT-002; SC: SC-DATA-002; DEC: -. Evidence: tests/behavioral/test_creative_assets.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-003; SC: -; DEC: -. Evidence: tests/behavioral/test_campaign_approval.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-251</t>
+          <t>RM-TECH-248</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4705,16 +4701,16 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Data ownership/lineage: immutable versioning и diff campaign/placement/playlist, словарь владельцев</t>
+          <t>Flight/placement windows: versioned start_at/end_at UTC, проверка при simulation/manifest/runtime</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -4729,7 +4725,7 @@
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>сохранение создаёт версию с diff и actor; предыдущая неизменяема [behavioral: `tests/behavioral/test_rm_tech_251.py`]</t>
+          <t>показ вне окна запрещён на трёх уровнях; DST/праздники/closed stores — версионированные правила [behavioral: `tests/test_s063_pop_timezone.py`]</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -4739,14 +4735,14 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-001; SC: SC-DATA-004; DEC: DEC-007. Evidence: новый behavioral. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-005, REQ-NFR-002; SC: SC-NFR-002; DEC: -. Evidence: tests/test_s063_pop_timezone.py; новый behavioral. Риск регрессии: высокий: расписание доставки.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-252</t>
+          <t>RM-TECH-249</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4761,16 +4757,16 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Identity: AD/LDAP или SSO для internal staff, MFA до production (OD-008)</t>
+          <t>Manifest eligibility: approved status + валидный flight/contract + resolved target + readiness</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-TECH-248</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -4782,14 +4778,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>protected_boundary</t>
-        </is>
-      </c>
+      <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>логин через IdP; production-профиль без MFA отклоняет; TLS-профиль зафиксирован [behavioral: `tests/test_phase3_auth_api.py`]</t>
+          <t>неэлигибельная кампания не попадает в manifest; причина объяснима [behavioral: `tests/behavioral/test_delivery_generation.py`]</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -4799,14 +4791,14 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-001; SC: SC-SEC-008; DEC: -. Evidence: tests/test_phase3_auth_api.py; tests/behavioral/test_auth_dual_e2e.py. Риск регрессии: высокий: вход всех пользователей.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-006; SC: -; DEC: -. Evidence: tests/behavioral/test_delivery_generation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-254</t>
+          <t>RM-TECH-250</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4821,16 +4813,16 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Emergency state machine: requested→authorized→dispatching→applied→resuming→closed, MFA+reason, приоритетный канал</t>
+          <t>Creative/rendition state machine и immutable media history (uploaded→scanning→qa_failed/approved→superseded→retained)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-TECH-204</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -4842,10 +4834,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>emergency с причиной; per-target result; audit actor/reason/affected; resume возвращает штатный manifest [behavioral: `tests/test_phase3_emergency_api.py`]; emergency.* smokes зелёные [ui_smoke: `tests/ui-smoke/test_uismoke__emergency__activate.py`]</t>
+          <t>каждая версия хранит uploader/SHA-256/QA-решение/связь; закрытый отчёт воспроизводим после logical delete [behavioral: `tests/behavioral/test_creative_assets.py`]</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4855,14 +4851,14 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-007; SC: SC-OPS-003; DEC: -. Evidence: tests/test_phase3_emergency_api.py; tests/ui-smoke/test_uismoke__emergency__activate.py. Риск регрессии: высокий: аварийный контур.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CONT-002; SC: SC-DATA-002; DEC: -. Evidence: tests/behavioral/test_creative_assets.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-255</t>
+          <t>RM-TECH-251</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4877,12 +4873,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Device health/commands: пороги статусов по профилю, per-device view, команды с подтверждением</t>
+          <t>Data ownership/lineage: immutable versioning и diff campaign/placement/playlist, словарь владельцев</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
@@ -4901,7 +4897,7 @@
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>online→degraded→offline по порогам; команда доставлена и подтверждена [behavioral: `tests/behavioral/test_rm_tech_255.py`]; device.health_view smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__device__health_view.py`]</t>
+          <t>сохранение создаёт версию с diff и actor; предыдущая неизменяема [behavioral: `tests/behavioral/test_rm_tech_251.py`]</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4911,19 +4907,19 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-001; SC: SC-OPS-006; DEC: -. Evidence: tests/ui-smoke/test_uismoke__device__health_view.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-001; SC: SC-DATA-004; DEC: DEC-007. Evidence: новый behavioral. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-002</t>
+          <t>RM-TECH-252</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4933,16 +4929,16 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>`self.campaign_create` в будущей ветке</t>
+          <t>Identity: AD/LDAP или SSO для internal staff, MFA до production (OD-008)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-001</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
@@ -4951,17 +4947,17 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>scope_decision</t>
+          <t>protected_boundary</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>mini-design, journey, backend/UI/RLS, intended-role smoke, walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__campaign_create.py`]</t>
+          <t>логин через IdP; production-профиль без MFA отклоняет; TLS-профиль зафиксирован [behavioral: `tests/test_phase3_auth_api.py`]</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4971,19 +4967,19 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2). RM-GOV-009 (OD-037): blocked до OD-013 — полный self-service вне pilot scope (REQ-V26-003, OD-005)</t>
+          <t>OD-008 решён владельцем 2026-10-07 - MFA в пилоте не делается; MFA для system_admin и security_admin обязателен до первого внешнего пользователя, но не позже production (условие строже прежнего «до production»). Записи ниже - до 2026-10-07 (исторические): RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-001; SC: SC-SEC-008; DEC: -. Evidence: tests/test_phase3_auth_api.py; tests/behavioral/test_auth_dual_e2e.py. Риск регрессии: высокий: вход всех пользователей.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001</t>
+          <t>RM-TECH-254</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4993,16 +4989,16 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Accessibility оставшихся форм + route matrix (A3)</t>
+          <t>Emergency state machine: requested→authorized→dispatching→applied→resuming→closed, MFA+reason, приоритетный канал</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -5017,7 +5013,7 @@
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>labels/ARIA/axe/targeted vitest [artifact: `docs/product/ux-route-matrix.yaml`]</t>
+          <t>emergency с причиной; per-target result; audit actor/reason/affected; resume возвращает штатный manifest [behavioral: `tests/test_phase3_emergency_api.py`]; emergency.* smokes зелёные [ui_smoke: `tests/ui-smoke/test_uismoke__emergency__activate.py`]</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -5027,19 +5023,19 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-007; SC: SC-OPS-003; DEC: -. Evidence: tests/test_phase3_emergency_api.py; tests/ui-smoke/test_uismoke__emergency__activate.py. Риск регрессии: высокий: аварийный контур.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-002</t>
+          <t>RM-TECH-255</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5049,16 +5045,16 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Поиск/сортировка/усечение таблиц (A2)</t>
+          <t>Device health/commands: пороги статусов по профилю, per-device view, команды с подтверждением</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
@@ -5073,7 +5069,7 @@
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>server semantics для pagination [ui_smoke: `tests/ui-smoke/test_uismoke__campaign__create.py`]</t>
+          <t>online→degraded→offline по порогам; команда доставлена и подтверждена [behavioral: `tests/behavioral/test_rm_tech_255.py`]; device.health_view smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__device__health_view.py`]</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -5083,19 +5079,19 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-001; SC: SC-OPS-006; DEC: -. Evidence: tests/ui-smoke/test_uismoke__device__health_view.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-003</t>
+          <t>RM-TECH-290</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5105,16 +5101,16 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Responsive-проверка (A4)</t>
+          <t>Часовые пояса в пилоте: расписание показов исполняется по местному времени магазина</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-002</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -5129,7 +5125,7 @@
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>все routes из `ux-route-matrix.yaml` проверены на 390px без overflow/crop [artifact: `docs/product/ux-responsive-report.yaml`]</t>
+          <t>показы по расписанию и окна PoP считаются в часовом поясе магазина; праздничный календарь не входит [behavioral: `tests/behavioral/test_rm_tech_290_timezones.py`]</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -5139,14 +5135,14 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>Решения владельца 2026-10-07 и 2026-10-08 («OD-012 — часовые пояса да, праздничный календарь нет»; «завести две новые задачи: часовые пояса в пилоте (OD-012) и замер базовой линии производительности до пилота (OD-011)»). REQ: -; SC: -; DEC: -. Пункт «окна PoP в часовом поясе магазина» оставлен по ответу владельца 2026-10-08 («оставить» / «да» - при обоих прочтениях нумерации вопросов результат один).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-004</t>
+          <t>RM-BIZ-002</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -5161,16 +5157,16 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Согласованность состояний и терминов (A6)</t>
+          <t>`self.campaign_create` в будущей ветке</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-003</t>
+          <t>RM-BIZ-001</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -5179,13 +5175,17 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>route matrix покрывает empty/loading/error/403/success и locale-key check [artifact: `docs/product/ux-route-matrix.yaml (states coverage)`]</t>
+          <t>mini-design, journey, backend/UI/RLS, intended-role smoke, walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__campaign_create.py`]</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -5195,14 +5195,14 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>OD-013 решён владельцем 2026-10-07 - self-service не включается в первый пилот. Остаётся blocked решением владельца 2026-10-08; перевод в deferred и правка трассировки - ближайший документальный этап. Записи ниже - до 2026-10-07 (исторические): полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2). RM-GOV-009 (OD-037): blocked до OD-013 — полный self-service вне pilot scope (REQ-V26-003, OD-005)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-005</t>
+          <t>RM-UX-001</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5217,16 +5217,16 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Adoption доказанных primitives малыми slices (A1b)</t>
+          <t>Accessibility оставшихся форм + route matrix (A3)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-004</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>каждый slice имеет отдельный diff/test/review [ci_job: `frontend`]</t>
+          <t>labels/ARIA/axe/targeted vitest [artifact: `docs/product/ux-route-matrix.yaml`]</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -5258,7 +5258,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-006</t>
+          <t>RM-UX-002</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -5273,16 +5273,16 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Advertiser-web UX audit/fixes (A5)</t>
+          <t>Поиск/сортировка/усечение таблиц (A2)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-005</t>
+          <t>RM-UX-001</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>versioned `docs/product/advertiser-route-matrix.yaml` с точным списком 15 routes [artifact: `docs/product/advertiser-route-matrix.yaml`]</t>
+          <t>server semantics для pagination [ui_smoke: `tests/ui-smoke/test_uismoke__campaign__create.py`]</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-007</t>
+          <t>RM-UX-003</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5324,21 +5324,21 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Human operator walkthrough (A7)</t>
+          <t>Responsive-проверка (A4)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001, RM-UX-002, RM-UX-003, RM-UX-004, RM-UX-005, RM-UX-006</t>
+          <t>RM-UX-002</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>человек проходит exact stand bundle [human: `PROJECT_STATE.md строка `operator walkthrough` (AGENTS.md правило 8); сценарии docs/product/operator-walkthrough-dev.md`]</t>
+          <t>все routes из `ux-route-matrix.yaml` проверены на 390px без overflow/crop [artifact: `docs/product/ux-responsive-report.yaml`]</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -5363,14 +5363,14 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) ПРИОСТАНОВЛЕНО владельцем 2026-08-31 (OD-041) до выравнивания ТЗ/roadmap/gates и утверждения единого плана реализации; не закрывать, done не ставить.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-008</t>
+          <t>RM-UX-004</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -5385,16 +5385,16 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Campaign readiness matrix по каналам (rendition/inventory/conflicts/forecast/PoP mode/SLA) с действием на blocked</t>
+          <t>Согласованность состояний и терминов (A6)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-249, RM-UX-004</t>
+          <t>RM-UX-003</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>экран согласования показывает матрицу; каждый blocked/warning ведёт к действию [ui_smoke: `tests/ui-smoke/test_rm_ux_008.py`]</t>
+          <t>route matrix покрывает empty/loading/error/403/success и locale-key check [artifact: `docs/product/ux-route-matrix.yaml (states coverage)`]</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -5419,14 +5419,14 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-004; SC: SC-UX-002; DEC: -. Evidence: новый ui-smoke; vitest. Риск регрессии: средний.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-009</t>
+          <t>RM-UX-005</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5441,16 +5441,16 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Договор рекламодателя: immutable file versions, server-side SHA-256, legal status (юр. решение)</t>
+          <t>Adoption доказанных primitives малыми slices (A1b)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-250</t>
+          <t>RM-UX-004</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>повторная загрузка создаёт новую версию, SHA проверен сервером; старая версия неизменяема [behavioral: `tests/test_advertiser_contracts.py`]; advertiser.contract_crud smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py`]</t>
+          <t>каждый slice имеет отдельный diff/test/review [ci_job: `frontend`]</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -5475,38 +5475,38 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-017; SC: -; DEC: -. Evidence: tests/test_advertiser_contracts.py; tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py. Риск регрессии: низкий.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207A</t>
+          <t>RM-UX-006</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>KSO environment + player/playlist design</t>
+          <t>Advertiser-web UX audit/fixes (A5)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-UX-005</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -5518,14 +5518,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>versioned environment audit, import/contract mini-design и test plan [artifact: `docs/architecture/kso-environment-audit.md`]</t>
+          <t>versioned `docs/product/advertiser-route-matrix.yaml` с точным списком 15 routes [artifact: `docs/product/advertiser-route-matrix.yaml`]</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -5535,38 +5531,38 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-STAND-003 feasibility gate явно в acceptance; ADR-019/OD-022</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-UX-007</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>KSO player/playlist/PoP chain</t>
+          <t>Human operator walkthrough (A7)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207A</t>
+          <t>RM-UX-001, RM-UX-002, RM-UX-003, RM-UX-004, RM-UX-005, RM-UX-006</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -5578,14 +5574,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+      <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>contract tests и playback→manifest→PoP behavioral proof [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; Playlist entity и state machine §6 ТЗ (draft → validating → valid/invalid → approved → published → superseded/rolled_back); published immutable [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; manifest target lifecycle (generated → signed → queued → delivered → applied/failed/expired) и canonical POST /api/v1/pop/batch [behavioral: `tests/behavioral/test_kso_playback_chain.py`]</t>
+          <t>человек проходит exact stand bundle [human: `PROJECT_STATE.md строка `operator walkthrough` (AGENTS.md правило 8); сценарии docs/product/operator-walkthrough-dev.md`]</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -5595,19 +5587,19 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) ПРИОСТАНОВЛЕНО владельцем 2026-08-31 (OD-041) до выравнивания ТЗ/roadmap/gates и утверждения единого плана реализации; не закрывать, done не ставить.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-208</t>
+          <t>RM-UX-008</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5617,16 +5609,16 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Signed licensing Layer 2</t>
+          <t>Campaign readiness matrix по каналам (rendition/inventory/conflicts/forecast/PoP mode/SLA) с действием на blocked</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-206, RM-TECH-207B, RM-STAB-010</t>
+          <t>RM-TECH-249, RM-UX-004</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -5638,14 +5630,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>protected_boundary</t>
-        </is>
-      </c>
+      <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Ed25519 offline verify, kid/rotation/revocation, UI, tamper/rollback [behavioral: `tests/behavioral/test_signed_license_layer2.py`]</t>
+          <t>экран согласования показывает матрицу; каждый blocked/warning ведёт к действию [ui_smoke: `tests/ui-smoke/test_rm_ux_008.py`]</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -5655,19 +5643,19 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-004; SC: SC-UX-002; DEC: -. Evidence: новый ui-smoke; vitest. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-260</t>
+          <t>RM-UX-009</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5677,12 +5665,12 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Runtime cache lifecycle: лимит по профилю, детерминированная очистка, last-known-good</t>
+          <t>Договор рекламодателя: immutable file versions, server-side SHA-256, legal status (юр. решение)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-250</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
@@ -5698,14 +5686,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+      <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>кэш на лимите: очистка по правилу; last-known-good сохранён; просроченная реклама не показывается [behavioral: `tests/behavioral/test_rm_tech_260.py`]</t>
+          <t>повторная загрузка создаёт новую версию, SHA проверен сервером; старая версия неизменяема [behavioral: `tests/test_advertiser_contracts.py`]; advertiser.contract_crud smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py`]</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -5715,14 +5699,14 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-008; SC: SC-EDGE-002; DEC: -. Evidence: runtime simulator tests. Риск регрессии: средний: плеер.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-017; SC: -; DEC: -. Evidence: tests/test_advertiser_contracts.py; tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-261</t>
+          <t>RM-TECH-207A</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5737,16 +5721,16 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Второй канал: решение OD-021 + channel-capability-matrix.yaml (AG); extraction design по ADR-019</t>
+          <t>KSO environment + player/playlist design</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B, RM-TECH-230</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
@@ -5755,7 +5739,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -5765,7 +5749,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>владелец назвал канал и владельца (OD-021); матрица возможностей утверждена [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; extraction design: KSO-вертикаль как первый adapter без поломки контрактов [artifact: `docs/audit/RM-TECH-261-artifact.md (создаётся задачей)`]</t>
+          <t>versioned environment audit, import/contract mini-design и test plan [artifact: `docs/architecture/kso-environment-audit.md`]</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -5775,14 +5759,14 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CHAN-001, REQ-ORCH-005; SC: SC-CHAN-002, SC-ORCH-004; DEC: DEC-001, DEC-002. Evidence: OD-021; design doc. Риск регрессии: высокий: рефакторинг KSO-вертикали. blocked до OD-021; Orchestrator/Adapter Layer/mock не создаются раньше (ADR-019/OD-022).</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-STAND-003 feasibility gate явно в acceptance; ADR-019/OD-022</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-262</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5797,16 +5781,16 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Dynamic creative binding/rendition safety (V26-008) на одном канале</t>
+          <t>KSO player/playlist/PoP chain</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280, RM-TECH-261</t>
+          <t>RM-TECH-207A</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
@@ -5818,10 +5802,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>master-confirmed price/promo подставляется при manifest generation; SLA-тест dynamic manifest [behavioral: `tests/behavioral/test_rm_tech_262.py`]</t>
+          <t>contract tests и playback→manifest→PoP behavioral proof [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; Playlist entity и state machine §6 ТЗ (draft → validating → valid/invalid → approved → published → superseded/rolled_back); published immutable [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; manifest target lifecycle (generated → signed → queued → delivered → applied/failed/expired) и canonical POST /api/v1/pop/batch [behavioral: `tests/behavioral/test_kso_playback_chain.py`]</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -5831,14 +5819,14 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-008; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. ложная ESL-посылка снимается prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-263</t>
+          <t>RM-TECH-208</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5853,16 +5841,16 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Field mobile operations: scoped mobile web для сотрудника магазина (устройства, фото, инциденты)</t>
+          <t>Signed licensing Layer 2</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-210, RM-TECH-255</t>
+          <t>RM-TECH-206, RM-TECH-207B, RM-STAB-010</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
@@ -5874,10 +5862,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>protected_boundary</t>
+        </is>
+      </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>journey field_ops.device_confirm под ролью магазина с RLS; negative чужой магазин [ui_smoke: `tests/ui-smoke/test_rm_tech_263.py`]</t>
+          <t>Ed25519 offline verify, kid/rotation/revocation, UI, tamper/rollback [behavioral: `tests/behavioral/test_signed_license_layer2.py`]</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -5887,14 +5879,14 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-009; SC: -; DEC: -. Evidence: new ui-smoke. Риск регрессии: средний. prerequisite RM-TECH-210 (RLS device) - planned по зависимости; feature field_ops.device_confirm blocked до задачи (RM-GOV-012 выравнивание: blocked = решение владельца/внешний факт, а не зависимость).</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-264</t>
+          <t>RM-TECH-260</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5909,16 +5901,16 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>ESL/price-checker: интеграция только через approved price/SKU master (INT-002)</t>
+          <t>Runtime cache lifecycle: лимит по профилю, детерминированная очистка, last-known-good</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -5930,10 +5922,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>price-related данные приходят из master или проходят reconciliation; расхождение блокирует показ [behavioral: `tests/behavioral/test_rm_tech_264.py`]</t>
+          <t>кэш на лимите: очистка по правилу; last-known-good сохранён; просроченная реклама не показывается [behavioral: `tests/behavioral/test_rm_tech_260.py`]</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -5943,14 +5939,14 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. OD-023 approved 2026-08-31 - planned после RM-TECH-280.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-008; SC: SC-EDGE-002; DEC: -. Evidence: runtime simulator tests. Риск регрессии: средний: плеер.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-261</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5965,12 +5961,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: master-data adapter цен/SKU (контракт, owner OD-023, reconciliation)</t>
+          <t>Второй канал: решение OD-021 + channel-capability-matrix.yaml (AG); extraction design по ADR-019</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-207B, RM-TECH-230</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
@@ -5983,7 +5979,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -5993,7 +5989,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>владелец master-данных назначен (OD-023 approved); contract + reconciliation design утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; adapter в mock/test mode проходит contract tests [behavioral: `tests/behavioral/test_rm_tech_280.py`]</t>
+          <t>владелец назвал канал и владельца (OD-021); матрица возможностей утверждена [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; extraction design: KSO-вертикаль как первый adapter без поломки контрактов [artifact: `docs/audit/RM-TECH-261-artifact.md (создаётся задачей)`]</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -6003,19 +5999,19 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: OD-023; contract tests. Риск регрессии: средний. отсутствующий prerequisite по AQ.1 №5; OD-023 approved 2026-08-31 (роль Product Data Owner) - planned; owner gate: контракт/scope adapter.</t>
+          <t>OD-021 решён владельцем 2026-10-07 - только КСО, второй канал после пилота. Остаётся blocked решением владельца 2026-10-08; перевод в deferred и правка трассировки - ближайший документальный этап. Записи ниже - до 2026-10-07 (исторические): RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CHAN-001, REQ-ORCH-005; SC: SC-CHAN-002, SC-ORCH-004; DEC: DEC-001, DEC-002. Evidence: OD-021; design doc. Риск регрессии: высокий: рефакторинг KSO-вертикали. blocked до OD-021; Orchestrator/Adapter Layer/mock не создаются раньше (ADR-019/OD-022).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-003</t>
+          <t>RM-TECH-262</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -6025,16 +6021,16 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>`self.report_view` plan/fact</t>
+          <t>Dynamic creative binding/rendition safety (V26-008) на одном канале</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201, RM-TECH-207B</t>
+          <t>RM-TECH-280, RM-TECH-261</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
@@ -6049,7 +6045,7 @@
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>реальные PoP/причины/RLS, journey/smoke/walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__report_view.py`]</t>
+          <t>master-confirmed price/promo подставляется при manifest generation; SLA-тест dynamic manifest [behavioral: `tests/behavioral/test_rm_tech_262.py`]</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -6059,38 +6055,38 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-011; зависит от RM-TECH-207B (реальные PoP) — без изменений</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-008; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. ложная ESL-посылка снимается prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-209</t>
+          <t>RM-TECH-263</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>ClickHouse capacity trigger</t>
+          <t>Field mobile operations: scoped mobile web для сотрудника магазина (устройства, фото, инциденты)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-210, RM-TECH-255</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -6105,7 +6101,7 @@
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>измеряемый PoP rate/retention threshold и owner migration gate [artifact: `docs/product/clickhouse-capacity-trigger.yaml`]</t>
+          <t>journey field_ops.device_confirm под ролью магазина с RLS; negative чужой магазин [ui_smoke: `tests/ui-smoke/test_rm_tech_263.py`]</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -6115,38 +6111,38 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-009; SC: -; DEC: -. Evidence: new ui-smoke. Риск регрессии: средний. prerequisite RM-TECH-210 (RLS device) - planned по зависимости; feature field_ops.device_confirm blocked до задачи (RM-GOV-012 выравнивание: blocked = решение владельца/внешний факт, а не зависимость).</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-256</t>
+          <t>RM-TECH-264</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Business outcome KPI: baseline/target/metric definition для целей §1.2 (OD-024 exit criteria)</t>
+          <t>ESL/price-checker: интеграция только через approved price/SKU master (INT-002)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -6158,14 +6154,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>каждая бизнес-цель имеет baseline/target/формулу/владельца, утверждено владельцем [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>price-related данные приходят из master или проходят reconciliation; расхождение блокирует показ [behavioral: `tests/behavioral/test_rm_tech_264.py`]</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -6175,38 +6167,38 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-013; SC: -; DEC: DEC-010. Evidence: artifact kpi register. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. OD-023 approved 2026-08-31 - planned после RM-TECH-280.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-281</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: sales-reference ingestion (агрегаты store/SKU/day) + методология baseline/test-control</t>
+          <t>Prerequisite: master-data adapter цен/SKU (контракт, owner OD-023, reconciliation)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
@@ -6218,10 +6210,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>пакетная загрузка агрегатов без PII; versioned baseline; методика утверждена владельцем [behavioral: `tests/behavioral/test_rm_tech_281.py`]</t>
+          <t>владелец master-данных назначен (OD-023 approved); contract + reconciliation design утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; adapter в mock/test mode проходит contract tests [behavioral: `tests/behavioral/test_rm_tech_280.py`]</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -6231,14 +6227,14 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-001; SC: -; DEC: -. Evidence: new behavioral; methodology doc. Риск регрессии: средний. prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: OD-023; contract tests. Риск регрессии: средний. отсутствующий prerequisite по AQ.1 №5; OD-023 approved 2026-08-31 (роль Product Data Owner) - planned; owner gate: контракт/scope adapter.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-282</t>
+          <t>RM-BIZ-003</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -6253,16 +6249,16 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Attribution &amp; sales lift: test/control, versioned baseline, pilot lift report</t>
+          <t>`self.report_view` plan/fact</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-281, RM-TECH-229</t>
+          <t>RM-TECH-201, RM-TECH-207B</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -6271,13 +6267,13 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>pilot lift report по test/control с explainable методикой; RLS scope [behavioral: `tests/behavioral/test_rm_tech_282.py`]</t>
+          <t>реальные PoP/причины/RLS, journey/smoke/walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__report_view.py`]</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -6287,14 +6283,14 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-002; SC: -; DEC: DEC-005, DEC-027. Evidence: new behavioral; report. Риск регрессии: средний. blocked OD-014 (DEC-027); OD-023 approved 2026-08-31.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-011; зависит от RM-TECH-207B (реальные PoP) — без изменений</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-283</t>
+          <t>RM-TECH-209</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -6304,21 +6300,21 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: audience source/privacy contract (анонимные store-атрибуты, 152-ФЗ, OD-032)</t>
+          <t>ClickHouse capacity trigger</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280, RM-TECH-253</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -6327,17 +6323,13 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>privacy/legal решение (OD-032) и контракт источника утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>измеряемый PoP rate/retention threshold и owner migration gate [artifact: `docs/product/clickhouse-capacity-trigger.yaml`]</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -6347,14 +6339,14 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-005; SC: -; DEC: DEC-005, DEC-019. Evidence: OD-032; contract. Риск регрессии: низкий. blocked OD-032 (DEC-019); OD-023 approved 2026-08-31.</t>
+          <t>OD-011 решён владельцем 2026-10-07 - оценка триггера ClickHouse по нагрузочным профилям ступени 500. Записи ниже - до 2026-10-07 (исторические): полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-284</t>
+          <t>RM-TECH-256</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -6364,21 +6356,21 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>A/B attribution и winner metric (minimum sample, owner approval результата)</t>
+          <t>Business outcome KPI: baseline/target/metric definition для целей §1.2 (OD-024 exit criteria)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-282</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -6387,13 +6379,17 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr"/>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>A/B фиксирует группы/период/метрику; winner только при minimum sample и ручном утверждении [behavioral: `tests/behavioral/test_rm_tech_284.py`]</t>
+          <t>каждая бизнес-цель имеет baseline/target/формулу/владельца, утверждено владельцем [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -6403,14 +6399,14 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-012, REQ-V26-010; SC: -; DEC: DEC-027. Evidence: new behavioral. Риск регрессии: средний. blocked OD-014 (DEC-027) - методика winner metric не утверждена.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-013; SC: -; DEC: DEC-010. Evidence: artifact kpi register. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-285</t>
+          <t>RM-TECH-281</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -6425,12 +6421,12 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Competitive separation: competitive_category, интервал/исключение в playlist/manifest (исключение §3.1 по OD-018)</t>
+          <t>Prerequisite: sales-reference ingestion (агрегаты store/SKU/day) + методология baseline/test-control</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202, RM-TECH-280</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
@@ -6449,7 +6445,7 @@
       <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>separation block/override test; изменение priority engine ограничено §3.1 [behavioral: `tests/behavioral/test_rm_tech_285.py`]</t>
+          <t>пакетная загрузка агрегатов без PII; versioned baseline; методика утверждена владельцем [behavioral: `tests/behavioral/test_rm_tech_281.py`]</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -6459,14 +6455,14 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-004; SC: -; DEC: DEC-005, DEC-022. Evidence: new behavioral. Риск регрессии: высокий: priority engine. OD-023 approved 2026-08-31, DEC-022 = OD-018 approved - planned после RM-TECH-280.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-001; SC: -; DEC: -. Evidence: new behavioral; methodology doc. Риск регрессии: средний. prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-286</t>
+          <t>RM-TECH-282</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -6481,16 +6477,16 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Financial-system exchange: versioned/idempotent export + payment-status contract (после DEC-017)</t>
+          <t>Attribution &amp; sales lift: test/control, versioned baseline, pilot lift report</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-246</t>
+          <t>RM-TECH-281, RM-TECH-229</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
@@ -6505,7 +6501,7 @@
       <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>idempotent export round-trip; повтор не создаёт дубликатов; scope финансового контура зафиксирован [behavioral: `tests/behavioral/test_rm_tech_286.py`]</t>
+          <t>pilot lift report по test/control с explainable методикой; RLS scope [behavioral: `tests/behavioral/test_rm_tech_282.py`]</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -6515,14 +6511,14 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-006, REQ-BIZ-009; SC: -; DEC: DEC-017. Evidence: new behavioral. Риск регрессии: средний. blocked OD-030.</t>
+          <t>OD-014 решён владельцем 2026-10-07 - отложено, пересмотр после ступени 100. Остаётся blocked решением владельца 2026-10-08; перевод в deferred и правка трассировки - ближайший документальный этап. Записи ниже - до 2026-10-07 (исторические): RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-002; SC: -; DEC: DEC-005, DEC-027. Evidence: new behavioral; report. Риск регрессии: средний. blocked OD-014 (DEC-027); OD-023 approved 2026-08-31.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-287</t>
+          <t>RM-TECH-283</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -6532,21 +6528,21 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>BI/export/SIEM/vendor API: scoped keys, rate-limit, immutable audit, circuit breaker (после DEC-013)</t>
+          <t>Prerequisite: audience source/privacy contract (анонимные store-атрибуты, 152-ФЗ, OD-032)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-013</t>
+          <t>RM-TECH-280, RM-TECH-253</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -6558,10 +6554,14 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>401/403/429 negative; vendor connector с отдельными credentials и failure mode [behavioral: `tests/test_s065_rate_limit.py`]</t>
+          <t>privacy/legal решение (OD-032) и контракт источника утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -6571,14 +6571,14 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-003; SC: SC-SEC-002; DEC: DEC-013. Evidence: tests/test_s065_rate_limit.py; new behavioral. Риск регрессии: средний. blocked OD-026.</t>
+          <t>OD-032 решён владельцем 2026-10-07 - вне первой очереди, пересмотр после пилота. Остаётся blocked решением владельца 2026-10-08; перевод в deferred и правка трассировки - ближайший документальный этап. Записи ниже - до 2026-10-07 (исторические): RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-005; SC: -; DEC: DEC-005, DEC-019. Evidence: OD-032; contract. Риск регрессии: низкий. blocked OD-032 (DEC-019); OD-023 approved 2026-08-31.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-289</t>
+          <t>RM-TECH-284</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -6588,21 +6588,21 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Extension points designed-not-implemented: ADR для programmatic (V26-007) и external measurement (V26-011)</t>
+          <t>A/B attribution и winner metric (minimum sample, owner approval результата)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-282</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -6611,13 +6611,13 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>ADR принят с пометкой designed-not-implemented; код не пишется до OD-021/OD-031 [artifact: `docs/audit/RM-TECH-289-artifact.md (создаётся задачей)`]</t>
+          <t>A/B фиксирует группы/период/метрику; winner только при minimum sample и ручном утверждении [behavioral: `tests/behavioral/test_rm_tech_284.py`]</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -6627,14 +6627,14 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-007, REQ-V26-011; SC: SC-ARCH-006; DEC: DEC-001, DEC-018. Evidence: ADR. Риск регрессии: низкий.</t>
+          <t>OD-014 решён владельцем 2026-10-07 - отложено, пересмотр после ступени 100. Остаётся blocked решением владельца 2026-10-08; перевод в deferred и правка трассировки - ближайший документальный этап. Записи ниже - до 2026-10-07 (исторические): RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-012, REQ-V26-010; SC: -; DEC: DEC-027. Evidence: new behavioral. Риск регрессии: средний. blocked OD-014 (DEC-027) - методика winner metric не утверждена.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-010</t>
+          <t>RM-TECH-285</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Service-quality reporting: доля active devices/logical carriers, plan/fact по каналу (analytics.compare)</t>
+          <t>Competitive separation: competitive_category, интервал/исключение в playlist/manifest (исключение §3.1 по OD-018)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-003</t>
+          <t>RM-TECH-202, RM-TECH-280</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
@@ -6673,7 +6673,7 @@
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>отчёт по каналу с долями и причинами; RLS scope advertiser [ui_smoke: `tests/ui-smoke/test_rm_ux_010.py`]</t>
+          <t>separation block/override test; изменение priority engine ограничено §3.1 [behavioral: `tests/behavioral/test_rm_tech_285.py`]</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -6683,38 +6683,38 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-004; SC: -; DEC: -. Evidence: новый ui-smoke; tests/behavioral/test_pop_reporting_scope.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-004; SC: -; DEC: DEC-005, DEC-022. Evidence: new behavioral. Риск регрессии: высокий: priority engine. OD-023 approved 2026-08-31, DEC-022 = OD-018 approved - planned после RM-TECH-280.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-001</t>
+          <t>RM-TECH-286</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>external</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Production readiness</t>
+          <t>Financial-system exchange: versioned/idempotent export + payment-status contract (после DEC-017)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-003</t>
+          <t>RM-TECH-246</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -6723,17 +6723,13 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>не запускается автоматически после pilot [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой; OD-025/OD-028)`]</t>
+          <t>idempotent export round-trip; повтор не создаёт дубликатов; scope финансового контура зафиксирован [behavioral: `tests/behavioral/test_rm_tech_286.py`]</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -6743,19 +6739,19 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): зависит от OD-025 (RTO/RPO) и OD-028 (топология); REQ-OPS-005/006; HA baseline выделен в RM-OPS-003</t>
+          <t>OD-030 решён владельцем 2026-10-07 - вне первой очереди, пересмотр после пилота. Остаётся blocked решением владельца 2026-10-08; перевод в deferred и правка трассировки - ближайший документальный этап. Записи ниже - до 2026-10-07 (исторические): RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-006, REQ-BIZ-009; SC: -; DEC: DEC-017. Evidence: new behavioral. Риск регрессии: средний. blocked OD-030.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-002</t>
+          <t>RM-TECH-287</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6765,16 +6761,16 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Network segmentation: firewall rules по environment + negative reachability tests из device-сегмента</t>
+          <t>BI/export/SIEM/vendor API: scoped keys, rate-limit, immutable audit, circuit breaker (после DEC-013)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-STAB-013</t>
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
@@ -6783,13 +6779,13 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>Admin API/PostgreSQL/MinIO/Redis недостижимы из device-сегмента; Gateway только HTTPS/mTLS [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+          <t>401/403/429 negative; vendor connector с отдельными credentials и failure mode [behavioral: `tests/test_s065_rate_limit.py`]</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6799,38 +6795,38 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-008; SC: SC-SEC-006; DEC: -. Evidence: reachability test log. Риск регрессии: средний: сеть пилота.</t>
+          <t>OD-026 решён владельцем 2026-10-07 - вне первой очереди, пересмотр после пилота. Остаётся blocked решением владельца 2026-10-08; перевод в deferred и правка трассировки - ближайший документальный этап. Записи ниже - до 2026-10-07 (исторические): RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-003; SC: SC-SEC-002; DEC: DEC-013. Evidence: tests/test_s065_rate_limit.py; new behavioral. Риск регрессии: средний. blocked OD-026.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-003</t>
+          <t>RM-TECH-289</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>external-plan</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Production HA baseline: ≥2 backend, масштабируемый Gateway, standby PostgreSQL, MinIO replication, quarterly restore drill</t>
+          <t>Extension points designed-not-implemented: ADR для programmatic (V26-007) и external measurement (V26-011)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-001</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
@@ -6839,17 +6835,13 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>production config gate зелёный; restore drill выполнен и записан [command: `tests/test_production_config_gate.py`]; топология утверждена (OD-028), RTO/RPO (OD-025) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>ADR принят с пометкой designed-not-implemented; код не пишется до OD-021/OD-031 [artifact: `docs/audit/RM-TECH-289-artifact.md (создаётся задачей)`]</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -6859,19 +6851,19 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-006, REQ-ARCH-004; SC: SC-OPS-001, SC-OPS-005; DEC: DEC-012, DEC-015. Evidence: tests/test_production_config_gate.py; drill record. Риск регрессии: высокий. blocked OD-025/OD-028.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-007, REQ-V26-011; SC: SC-ARCH-006; DEC: DEC-001, DEC-018. Evidence: ADR. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-004</t>
+          <t>RM-UX-010</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6881,12 +6873,12 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Rollout entity/state machine и feature flags: planned→lab→canary→staged→paused→completed/rolled_back</t>
+          <t>Service-quality reporting: доля active devices/logical carriers, plan/fact по каналу (analytics.compare)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-BIZ-003</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
@@ -6899,13 +6891,13 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>rollback возвращает предыдущую версию; flag отключает функцию; ответственность по OD-010 [behavioral: `tests/integration/test_stand_rollback_drill.py`]</t>
+          <t>отчёт по каналу с долями и причинами; RLS scope advertiser [ui_smoke: `tests/ui-smoke/test_rm_ux_010.py`]</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -6915,14 +6907,14 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-002; SC: SC-OPS-007; DEC: DEC-008. Evidence: tests/integration/test_stand_rollback_drill.py. Риск регрессии: средний. blocked OD-010.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-004; SC: -; DEC: -. Evidence: новый ui-smoke; tests/behavioral/test_pop_reporting_scope.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-001</t>
+          <t>RM-OPS-001</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -6932,21 +6924,21 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>external</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Managed control-plane pilot scope</t>
+          <t>Production readiness</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Gate-S, Gate-U, RM-ENV-001</t>
+          <t>RM-PILOT-003</t>
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
@@ -6958,10 +6950,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
+          <t>не запускается автоматически после pilot [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой; OD-025/OD-028)`]</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -6971,38 +6967,38 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): deps += OD-024 (exit criteria ступеней), REQ-ARCH-004</t>
+          <t>OD-009, OD-010, OD-025, OD-028 решены владельцем 2026-10-07 по срокам - VPN и SIEM до первого внешнего пользователя, но не позже production; feature flags, RTO/RPO и топология - до production. Содержание НЕ утверждено и вынесено в открытые OD-048 (значения RTO/RPO) и OD-049 (топология production), срок обоих - до production (решение владельца 2026-10-08): приёмка не закрыта. Записи ниже - до 2026-10-07 (исторические): полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): зависит от OD-025 (RTO/RPO) и OD-028 (топология); REQ-OPS-005/006; HA baseline выделен в RM-OPS-003</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>RM-OPS-002</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Network segmentation: firewall rules по environment + negative reachability tests из device-сегмента</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
           <t>RM-PILOT-002</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>POPS</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>external-plan</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Deployment plan/preflight</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>RM-PILOT-001</t>
-        </is>
-      </c>
       <c r="F115" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
@@ -7017,7 +7013,7 @@
       <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
+          <t>Admin API/PostgreSQL/MinIO/Redis недостижимы из device-сегмента; Gateway только HTTPS/mTLS [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -7027,14 +7023,14 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-008; SC: SC-SEC-006; DEC: -. Evidence: reachability test log. Риск регрессии: средний: сеть пилота.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002A</t>
+          <t>RM-OPS-003</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -7044,53 +7040,57 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>external-plan</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Pilot-compose поднимается под ENVIRONMENT=pilot без ручных шагов; verify честный</t>
+          <t>Production HA baseline: ≥2 backend, масштабируемый Gateway, standby PostgreSQL, MinIO replication, quarterly restore drill</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
+          <t>RM-OPS-001</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>production config gate зелёный; restore drill выполнен и записан [command: `tests/test_production_config_gate.py`]; топология утверждена (OD-028), RTO/RPO (OD-025) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>pilot-compose из образов коммита под ENVIRONMENT=pilot - db-migrate сам создаёт retail_media_app (NOBYPASSRLS), все сервисы healthy в пределах таймаута, readiness со строгой проверкой роли, identity из образа, device-токен control-api принят device-gateway, конфиг orchestrator-worker грузится; таймаут или любой отказ роняют проверку [command: `CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env &lt;version&gt; &lt;sha&gt;`]; каждый backend-сервис получает из pilot-compose все переменные, которых требует валидатор prod; пустой JWT_AUDIENCE - отказ при старте [command: `python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py`]</t>
-        </is>
-      </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/36571330932; verified · command · CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env ci-pilot-smoke &lt;sha&gt;; verified · command · python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py</t>
-        </is>
-      </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>done - PR #12 смержен в develop @ af6810c, push-run develop 36571330932 success 42/42 (решение владельца 2026-09-29). Решение владельца 2026-09-29 (этап RF-05, область RM-PILOT-002, Protected Boundary Docker/deployment с условиями). Находки ревью main@8ad0228: P0-1..P0-5, P1-16, P2-I9, P2-I11, T12 (+ FU5 healthcheck frontend). REQ: REQ-ARCH-004; SC: -; DEC: -. Не покрывает: TLS/reverse proxy (001D), ack/DLQ воркера при ошибке (RF-04), публикацию релиза и verify-pilot-images на GHCR (внешнее действие владельца). Риск регрессии: средний - обязательный JWT_AUDIENCE вне dev; pilot-хосты без него не стартуют.</t>
+          <t>OD-025 и OD-028 решены владельцем 2026-10-07 только по сроку - RTO/RPO до production (владелец DR - владелец продукта), топология - по итогам пилота. Содержание НЕ утверждено и вынесено в открытые OD-048 (значения RTO/RPO) и OD-049 (топология production), срок обоих - до production (решение владельца 2026-10-08): задача blocked ими, приёмка не закрыта. Записи ниже - до 2026-10-07 (исторические): RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-006, REQ-ARCH-004; SC: SC-OPS-001, SC-OPS-005; DEC: DEC-012, DEC-015. Evidence: tests/test_production_config_gate.py; drill record. Риск регрессии: высокий. blocked OD-025/OD-028.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-003</t>
+          <t>RM-OPS-004</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>external</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Controlled pilot deploy</t>
+          <t>Rollout entity/state machine и feature flags: planned→lab→canary→staged→paused→completed/rolled_back</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -7123,27 +7123,595 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>flag отключает функцию; rollout проходит состояния planned→lab→canary→staged→paused→completed/rolled_back; ответственность по OD-010 [behavioral: `tests/behavioral/test_rm_ops_004_rollout_flags.py`]</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>Решение владельца 2026-10-08 - задача разделена: откат релиза до пилота выделен в RM-OPS-009 (вместе с функцией release.rollback); здесь остаются rollout entity/state machine и feature flags - до production (OD-010, 2026-10-07). Приёмка сужена до флагов и состояний rollout. Остаётся blocked решением владельца 2026-10-08; перевод в deferred и правка трассировки - ближайший документальный этап. Записи ниже - до 2026-10-07 (исторические): RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-002; SC: SC-OPS-007; DEC: DEC-008. Evidence: tests/integration/test_stand_rollback_drill.py. Риск регрессии: средний. blocked OD-010.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>RM-OPS-007</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Доступ администратора только через VPN</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>admin-портал и административный API недоступны вне VPN; срок - до первого внешнего пользователя, но не позже production [artifact: `docs/audit/&lt;дата&gt;-admin-vpn-access.md`]</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>Решение владельца 2026-10-07 по OD-009 («разбить на четыре задачи … Доступ админа через VPN и SIEM-экспорт — до первого внешнего пользователя, но не позже production»). Способ определяется мини-дизайном этапа. REQ: -; SC: -; DEC: DEC-007.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>RM-OPS-008</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>SIEM-экспорт событий аудита</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>RM-STAB-014</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>события аудита экспортируются в SIEM; срок - до первого внешнего пользователя, но не позже production [artifact: `docs/audit/&lt;дата&gt;-siem-export.md`]</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>Решение владельца 2026-10-07 по OD-009 (SIEM/Wazuh-экспорт; «до первого внешнего пользователя, но не позже production»). Формат и приёмник определяются мини-дизайном этапа. REQ: -; SC: -; DEC: DEC-007.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>RM-OPS-009</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Откат релиза до пилота: возврат на предыдущий bundle с сохранением данных</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-002</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>откат возвращает предыдущую версию; данные сохранены [command: `python -m pytest tests/integration/test_rm_ops_009_release_rollback.py (новый тест; обязателен в CI либо записанный прогон на стенде с артефактом)`]</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>Решения владельца - 2026-10-07 «OD-010 — откат до пилота, feature flags до production»; 2026-10-08 «разделить RM-OPS-004: „откат“ — до пилота, „feature flags“ — до production». Выделена из RM-OPS-004 вместе с функцией release.rollback. Объём отката (сервисы, схема, данные) определяется в этапе. REQ: REQ-OPS-002; SC: SC-OPS-007; DEC: DEC-008.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-001</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Managed control-plane pilot scope</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Gate-S, Gate-U, RM-ENV-001</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>OD-024 решён владельцем 2026-10-07 - критерии перехода между ступенями утверждены (пороги - в OD-024). Записи ниже - до 2026-10-07 (исторические): полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): deps += OD-024 (exit criteria ступеней), REQ-ARCH-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-002</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>external-plan</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Deployment plan/preflight</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-001</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>OD-010 решён владельцем 2026-10-07 - откат до пилота, feature flags до production. Откат выделен в отдельную задачу RM-OPS-009 (решение владельца 2026-10-08). Записи ниже - до 2026-10-07 (исторические): полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-002A</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Pilot-compose поднимается под ENVIRONMENT=pilot без ручных шагов; verify честный</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>pilot-compose из образов коммита под ENVIRONMENT=pilot - db-migrate сам создаёт retail_media_app (NOBYPASSRLS), все сервисы healthy в пределах таймаута, readiness со строгой проверкой роли, identity из образа, device-токен control-api принят device-gateway, конфиг orchestrator-worker грузится; таймаут или любой отказ роняют проверку [command: `CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env &lt;version&gt; &lt;sha&gt;`]; каждый backend-сервис получает из pilot-compose все переменные, которых требует валидатор prod; пустой JWT_AUDIENCE - отказ при старте [command: `python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py`]</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/36571330932; verified · command · CI job pilot-compose-smoke: bash scripts/ci/verify-pilot-run.sh --images-from-env ci-pilot-smoke &lt;sha&gt;; verified · command · python -m pytest tests/test_rf05_pilot_boot.py tests/test_production_config_gate.py</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>done - PR #12 смержен в develop @ af6810c, push-run develop 36571330932 success 42/42 (решение владельца 2026-09-29). Решение владельца 2026-09-29 (этап RF-05, область RM-PILOT-002, Protected Boundary Docker/deployment с условиями). Находки ревью main@8ad0228: P0-1..P0-5, P1-16, P2-I9, P2-I11, T12 (+ FU5 healthcheck frontend). REQ: REQ-ARCH-004; SC: -; DEC: -. Не покрывает: TLS/reverse proxy (001D), ack/DLQ воркера при ошибке (RF-04), публикацию релиза и verify-pilot-images на GHCR (внешнее действие владельца). Риск регрессии: средний - обязательный JWT_AUDIENCE вне dev; pilot-хосты без него не стартуют.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-002B</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Конфигурация pilot-контура: проверка JWT_AUDIENCE, restart воркера в phase1, том NATS в DR-runbook</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-002A</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>protected_boundary</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>validate-pilot-env.py и local_stand.py отклоняют окружение без корректного JWT_AUDIENCE [command: `python -m pytest tests/test_rf05_pilot_boot.py`]; воркер в phase1-compose перезапускается после отказа старта; DR-runbook содержит шаг про том NATS [artifact: `docs/runbook/backup-restore-dr.md`]</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>Решение владельца 2026-10-07 («JWT_AUDIENCE и долг RF-11 — одним небольшим этапом про конфигурацию pilot-контура»). Долг RF-05 (JWT_AUDIENCE) и RF-11 (phase1 restart, DR runbook, verified_by при ручном доказательстве). Protected Boundary: Docker/compose и скрипты деплоя - разрешение по файлам в карточке этапа. REQ: -; SC: -; DEC: -. Пункт долга RF-11 «verified_by при ручном доказательстве» в приёмку не включён - это формат записи приёмки RM-STAB-021, решается в этапе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-003</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Controlled pilot deploy</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-002, RM-OPS-009, RM-TECH-291, RM-TECH-290, RM-OPS-005</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
         <is>
           <t>deployment</t>
         </is>
       </c>
-      <c r="J117" s="2" t="inlineStr">
+      <c r="J125" s="2" t="inlineStr">
         <is>
           <t>SHA/lock/schema/health, stand-safe journeys, rollback readiness [owner: `docs/audit/&lt;дата&gt;-pilot-deploy-&lt;sha&gt;.md + ACCEPT владельца с датой (deployment gate)`]</t>
         </is>
       </c>
-      <c r="K117" s="2" t="inlineStr">
+      <c r="K125" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L117" s="2" t="inlineStr">
-        <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>До пилота выполняются откат релиза (RM-OPS-009), замер базовой линии производительности (RM-TECH-291), часовые пояса (RM-TECH-290) и сроки хранения (RM-OPS-005) - добавлены в зависимости агентом как следствие решений владельца 2026-10-07/08 («до пилота», «в пилоте»); названы владельцу в отчёте этапа RF-GOV-1. Записи ниже - до 2026-10-07 (исторические): полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) Минимизация ПДн (задача ещё не заведена - ожидает подтверждения владельца) добавится после её заведения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>RM-STAB-027</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>MinIO в pilot- и phase1-compose работает не под root</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>protected_boundary</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>в pilot- и phase1-compose у сервиса MinIO нет user 0; стек поднимается, бакеты доступны [command: `CI job pilot-compose-smoke`]</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>Решение владельца 2026-10-07 («user: "0" для MinIO в phase1 — подтверждаю; перевод на non-root отдельной задачей»); В цитате владельца - phase1; pilot включён по долгу RF-CI (2026-09-28) - оставлены оба контура по ответу владельца 2026-10-08 («оба» / «оставить» - при обоих прочтениях нумерации вопросов результат один). Protected Boundary: Docker/compose - разрешение по файлам в карточке этапа. Срок не назначен. REQ: -; SC: -; DEC: -. Перенесена из стадии S по ответу владельца 2026-10-08 («перенеси»): в условие Gate-S не входит. Целевая стадия POPS выбрана агентом - ожидает подтверждения владельца.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-291</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Замер базовой линии производительности до пилота</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Gate-S</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>базовые показатели производительности измерены на стенде и записаны; пороги и нагрузочные профили не устанавливаются (ступень 500, OD-011) [artifact: `docs/audit/&lt;дата&gt;-performance-baseline.md`]</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>Решения владельца 2026-10-07 и 2026-10-08 («OD-011 — нагрузочные профили отложить до ступени 500; до пилота — замер базовой линии»; «завести две новые задачи …»). Состав показателей определяется в этапе. REQ: -; SC: -; DEC: DEC-009.</t>
         </is>
       </c>
     </row>
@@ -11911,12 +12479,12 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-004</t>
+          <t>RM-OPS-009</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>функция реализована задачей RM-OPS-004 и имеет зелёный smoke/behavioral proof</t>
+          <t>функция реализована задачей RM-OPS-009 и имеет зелёный smoke/behavioral proof</t>
         </is>
       </c>
     </row>
